--- a/benchmarks/results/plots/results-Fig1.xlsx
+++ b/benchmarks/results/plots/results-Fig1.xlsx
@@ -480,10 +480,10 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>57041993720.71903</v>
+        <v>57.04199372071903</v>
       </c>
       <c r="J2">
-        <v>57041993720.71903</v>
+        <v>57.04199372071903</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -512,10 +512,10 @@
         <v>41769539528.3253</v>
       </c>
       <c r="I3">
-        <v>57041993668.24519</v>
+        <v>4.568153710662557</v>
       </c>
       <c r="J3">
-        <v>15272454192.39373</v>
+        <v>15.27245419239373</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -544,10 +544,10 @@
         <v>46242761531.82452</v>
       </c>
       <c r="I4">
-        <v>57041993667.58222</v>
+        <v>3.905185663747737</v>
       </c>
       <c r="J4">
-        <v>10799232188.89452</v>
+        <v>10.79923218889452</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -576,10 +576,10 @@
         <v>56189117913.37925</v>
       </c>
       <c r="I5">
-        <v>57041993664.52991</v>
+        <v>0.8528758073397853</v>
       </c>
       <c r="J5">
-        <v>852875807.3397827</v>
+        <v>0.8528758073397827</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -608,10 +608,10 @@
         <v>44356041784.4061</v>
       </c>
       <c r="I6">
-        <v>57041993668.08908</v>
+        <v>4.412045690450931</v>
       </c>
       <c r="J6">
-        <v>12685951936.31293</v>
+        <v>12.68595193631293</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -640,10 +640,10 @@
         <v>30679257017.14791</v>
       </c>
       <c r="I7">
-        <v>57041993670.51965</v>
+        <v>6.842614467927547</v>
       </c>
       <c r="J7">
-        <v>26362736703.57112</v>
+        <v>26.36273670357112</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -672,10 +672,10 @@
         <v>49742988368.73362</v>
       </c>
       <c r="I8">
-        <v>57041993666.76957</v>
+        <v>3.092532086116982</v>
       </c>
       <c r="J8">
-        <v>7299005351.985413</v>
+        <v>7.299005351985413</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -704,10 +704,10 @@
         <v>51715464527.26919</v>
       </c>
       <c r="I9">
-        <v>57041993665.79048</v>
+        <v>2.113445999692836</v>
       </c>
       <c r="J9">
-        <v>5326529193.449844</v>
+        <v>5.326529193449844</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -736,10 +736,10 @@
         <v>32247048443.66209</v>
       </c>
       <c r="I10">
-        <v>57041993670.08095</v>
+        <v>6.403908831381607</v>
       </c>
       <c r="J10">
-        <v>24794945277.05694</v>
+        <v>24.79494527705694</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -768,10 +768,10 @@
         <v>44572615202.19429</v>
       </c>
       <c r="I11">
-        <v>57041993668.12152</v>
+        <v>4.444480220495734</v>
       </c>
       <c r="J11">
-        <v>12469378518.52474</v>
+        <v>12.46937851852474</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -800,10 +800,10 @@
         <v>45168642402.08564</v>
       </c>
       <c r="I12">
-        <v>57041993667.94418</v>
+        <v>4.267145241410745</v>
       </c>
       <c r="J12">
-        <v>11873351318.63339</v>
+        <v>11.87335131863339</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -832,10 +832,10 @@
         <v>39936030607.30549</v>
       </c>
       <c r="I13">
-        <v>57041993668.32006</v>
+        <v>4.643024179052986</v>
       </c>
       <c r="J13">
-        <v>17105963113.41354</v>
+        <v>17.10596311341354</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -864,10 +864,10 @@
         <v>39273447630.39705</v>
       </c>
       <c r="I14">
-        <v>57041993668.33996</v>
+        <v>4.662923330513188</v>
       </c>
       <c r="J14">
-        <v>17768546090.32198</v>
+        <v>17.76854609032198</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -896,10 +896,10 @@
         <v>47163097316.6035</v>
       </c>
       <c r="I15">
-        <v>57041993667.5649</v>
+        <v>3.887855542098848</v>
       </c>
       <c r="J15">
-        <v>9878896404.115532</v>
+        <v>9.878896404115531</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -928,10 +928,10 @@
         <v>17898880377.03814</v>
       </c>
       <c r="I16">
-        <v>57041993670.84615</v>
+        <v>7.169110141580262</v>
       </c>
       <c r="J16">
-        <v>39143113343.68089</v>
+        <v>39.14311334368089</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -960,10 +960,10 @@
         <v>26463110805.79538</v>
       </c>
       <c r="I17">
-        <v>57041993670.51398</v>
+        <v>6.836941656739725</v>
       </c>
       <c r="J17">
-        <v>30578882914.92365</v>
+        <v>30.57888291492365</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -992,10 +992,10 @@
         <v>36874487459.67752</v>
       </c>
       <c r="I18">
-        <v>57041993669.06585</v>
+        <v>5.388809029966907</v>
       </c>
       <c r="J18">
-        <v>20167506261.04151</v>
+        <v>20.16750626104151</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1024,10 +1024,10 @@
         <v>30887304962.56219</v>
       </c>
       <c r="I19">
-        <v>57041993670.13342</v>
+        <v>6.456378163572268</v>
       </c>
       <c r="J19">
-        <v>26154688758.15684</v>
+        <v>26.15468875815684</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1056,10 +1056,10 @@
         <v>42755703409.40675</v>
       </c>
       <c r="I20">
-        <v>57041993668.22463</v>
+        <v>4.547595038171082</v>
       </c>
       <c r="J20">
-        <v>14286290311.31228</v>
+        <v>14.28629031131228</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1088,10 +1088,10 @@
         <v>49490997255.18467</v>
       </c>
       <c r="I21">
-        <v>57041993666.85777</v>
+        <v>3.180737325288874</v>
       </c>
       <c r="J21">
-        <v>7550996465.534363</v>
+        <v>7.550996465534363</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1120,10 +1120,10 @@
         <v>44809966644.00132</v>
       </c>
       <c r="I22">
-        <v>57041993668.12625</v>
+        <v>4.449209702534425</v>
       </c>
       <c r="J22">
-        <v>12232027076.71771</v>
+        <v>12.23202707671771</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1152,10 +1152,10 @@
         <v>48753039842.15779</v>
       </c>
       <c r="I23">
-        <v>57041993666.76673</v>
+        <v>3.089696176074682</v>
       </c>
       <c r="J23">
-        <v>8288953878.561241</v>
+        <v>8.288953878561241</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1184,10 +1184,10 @@
         <v>50290697075.671</v>
       </c>
       <c r="I24">
-        <v>57041993666.61101</v>
+        <v>2.933966708292438</v>
       </c>
       <c r="J24">
-        <v>6751296645.048035</v>
+        <v>6.751296645048035</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1216,10 +1216,10 @@
         <v>29652835706.6311</v>
       </c>
       <c r="I25">
-        <v>57041993670.49325</v>
+        <v>6.816208238368091</v>
       </c>
       <c r="J25">
-        <v>27389158014.08793</v>
+        <v>27.38915801408793</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1248,10 +1248,10 @@
         <v>29511422214.18769</v>
       </c>
       <c r="I26">
-        <v>57041993670.08137</v>
+        <v>6.404325527263481</v>
       </c>
       <c r="J26">
-        <v>27530571506.53134</v>
+        <v>27.53057150653134</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1280,10 +1280,10 @@
         <v>51354102372.14358</v>
       </c>
       <c r="I27">
-        <v>57041993666.2044</v>
+        <v>2.527358734914436</v>
       </c>
       <c r="J27">
-        <v>5687891348.575455</v>
+        <v>5.687891348575454</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1312,10 +1312,10 @@
         <v>35478689597.73202</v>
       </c>
       <c r="I28">
-        <v>57041993669.11265</v>
+        <v>5.435611693972852</v>
       </c>
       <c r="J28">
-        <v>21563304122.98701</v>
+        <v>21.56330412298701</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1344,10 +1344,10 @@
         <v>48368985998.09631</v>
       </c>
       <c r="I29">
-        <v>57041993666.79166</v>
+        <v>3.114625138595635</v>
       </c>
       <c r="J29">
-        <v>8673007722.622719</v>
+        <v>8.673007722622719</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1376,10 +1376,10 @@
         <v>33300215138.64154</v>
       </c>
       <c r="I30">
-        <v>57041993670.0241</v>
+        <v>6.347062689632473</v>
       </c>
       <c r="J30">
-        <v>23741778582.07749</v>
+        <v>23.74177858207749</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -1408,10 +1408,10 @@
         <v>40775095558.39653</v>
       </c>
       <c r="I31">
-        <v>57041993668.60639</v>
+        <v>4.929354751595532</v>
       </c>
       <c r="J31">
-        <v>16266898162.3225</v>
+        <v>16.2668981623225</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1440,10 +1440,10 @@
         <v>25938560948.99037</v>
       </c>
       <c r="I32">
-        <v>57041993670.50697</v>
+        <v>6.829931616540257</v>
       </c>
       <c r="J32">
-        <v>31103432771.72866</v>
+        <v>31.10343277172866</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -1472,10 +1472,10 @@
         <v>23110203716.36913</v>
       </c>
       <c r="I33">
-        <v>57041993670.28445</v>
+        <v>6.607410090255122</v>
       </c>
       <c r="J33">
-        <v>33931790004.3499</v>
+        <v>33.93179000434991</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -1504,10 +1504,10 @@
         <v>42239861443.92123</v>
       </c>
       <c r="I34">
-        <v>57041993668.35927</v>
+        <v>4.682226853202913</v>
       </c>
       <c r="J34">
-        <v>14802132276.79781</v>
+        <v>14.80213227679781</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -1536,10 +1536,10 @@
         <v>47512689311.54627</v>
       </c>
       <c r="I35">
-        <v>57041993667.52747</v>
+        <v>3.850435246668596</v>
       </c>
       <c r="J35">
-        <v>9529304409.17276</v>
+        <v>9.529304409172759</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -1568,10 +1568,10 @@
         <v>28108705957.48798</v>
       </c>
       <c r="I36">
-        <v>57041993670.29247</v>
+        <v>6.615430249406543</v>
       </c>
       <c r="J36">
-        <v>28933287763.23105</v>
+        <v>28.93328776323105</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -1600,10 +1600,10 @@
         <v>33437329737.95723</v>
       </c>
       <c r="I37">
-        <v>57041993670.05785</v>
+        <v>6.380810994503527</v>
       </c>
       <c r="J37">
-        <v>23604663982.7618</v>
+        <v>23.6046639827618</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -1632,10 +1632,10 @@
         <v>-3.309322252153853e+23</v>
       </c>
       <c r="I38">
-        <v>57041993691.39246</v>
+        <v>27.71542015271903</v>
       </c>
       <c r="J38">
-        <v>3.309322252154423e+23</v>
+        <v>330932225215442.3</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -1664,10 +1664,10 @@
         <v>31447593293.69208</v>
       </c>
       <c r="I39">
-        <v>57041993670.11783</v>
+        <v>6.440789624389431</v>
       </c>
       <c r="J39">
-        <v>25594400427.02695</v>
+        <v>25.59440042702695</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -1696,10 +1696,10 @@
         <v>24515555613.91069</v>
       </c>
       <c r="I40">
-        <v>57041993670.19711</v>
+        <v>6.520068291272267</v>
       </c>
       <c r="J40">
-        <v>32526438106.80834</v>
+        <v>32.52643810680834</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -1728,10 +1728,10 @@
         <v>37778226555.59573</v>
       </c>
       <c r="I41">
-        <v>57041993669.10413</v>
+        <v>5.427085116354277</v>
       </c>
       <c r="J41">
-        <v>19263767165.1233</v>
+        <v>19.2637671651233</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -1760,10 +1760,10 @@
         <v>39596869278.30653</v>
       </c>
       <c r="I42">
-        <v>57041993668.32513</v>
+        <v>4.648085106170583</v>
       </c>
       <c r="J42">
-        <v>17445124442.4125</v>
+        <v>17.4451244424125</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -1792,10 +1792,10 @@
         <v>30337479356.45204</v>
       </c>
       <c r="I43">
-        <v>57041993670.15224</v>
+        <v>6.475200261552722</v>
       </c>
       <c r="J43">
-        <v>26704514364.26699</v>
+        <v>26.70451436426699</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -1824,10 +1824,10 @@
         <v>31948831930.81232</v>
       </c>
       <c r="I44">
-        <v>57041993670.11191</v>
+        <v>6.434869918429733</v>
       </c>
       <c r="J44">
-        <v>25093161789.90671</v>
+        <v>25.09316178990671</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -1856,10 +1856,10 @@
         <v>27262726773.40766</v>
       </c>
       <c r="I45">
-        <v>57041993670.25546</v>
+        <v>6.578427452470727</v>
       </c>
       <c r="J45">
-        <v>29779266947.31137</v>
+        <v>29.77926694731137</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -1888,10 +1888,10 @@
         <v>26909928481.04249</v>
       </c>
       <c r="I46">
-        <v>57041993670.27154</v>
+        <v>6.594501882890071</v>
       </c>
       <c r="J46">
-        <v>30132065239.67654</v>
+        <v>30.13206523967654</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -1920,10 +1920,10 @@
         <v>38171182173.89679</v>
       </c>
       <c r="I47">
-        <v>57041993669.10225</v>
+        <v>5.425213190661012</v>
       </c>
       <c r="J47">
-        <v>18870811546.82224</v>
+        <v>18.87081154682224</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -1952,10 +1952,10 @@
         <v>39824031266.53966</v>
       </c>
       <c r="I48">
-        <v>57041993668.73229</v>
+        <v>5.055253991587975</v>
       </c>
       <c r="J48">
-        <v>17217962454.17937</v>
+        <v>17.21796245417937</v>
       </c>
     </row>
     <row r="49" spans="1:10">
@@ -1984,10 +1984,10 @@
         <v>55418303818.50417</v>
       </c>
       <c r="I49">
-        <v>57041993664.5776</v>
+        <v>0.9005612263117513</v>
       </c>
       <c r="J49">
-        <v>1623689902.214859</v>
+        <v>1.623689902214859</v>
       </c>
     </row>
     <row r="50" spans="1:10">
@@ -2016,10 +2016,10 @@
         <v>28040916901.26657</v>
       </c>
       <c r="I50">
-        <v>57041993670.21365</v>
+        <v>6.536607822594803</v>
       </c>
       <c r="J50">
-        <v>29001076819.45246</v>
+        <v>29.00107681945246</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -2048,10 +2048,10 @@
         <v>44486500783.63541</v>
       </c>
       <c r="I51">
-        <v>57041993668.52937</v>
+        <v>4.852331877844207</v>
       </c>
       <c r="J51">
-        <v>12555492937.08363</v>
+        <v>12.55549293708363</v>
       </c>
     </row>
     <row r="52" spans="1:10">
@@ -2080,10 +2080,10 @@
         <v>22843093787.7366</v>
       </c>
       <c r="I52">
-        <v>57041993670.57738</v>
+        <v>6.900337080231942</v>
       </c>
       <c r="J52">
-        <v>34198899932.98243</v>
+        <v>34.19889993298244</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -2112,10 +2112,10 @@
         <v>46929742223.68663</v>
       </c>
       <c r="I53">
-        <v>57041993667.59311</v>
+        <v>3.916068634760101</v>
       </c>
       <c r="J53">
-        <v>10112251497.0324</v>
+        <v>10.1122514970324</v>
       </c>
     </row>
     <row r="54" spans="1:10">
@@ -2144,10 +2144,10 @@
         <v>36390771347.82562</v>
       </c>
       <c r="I54">
-        <v>57041993669.08472</v>
+        <v>5.407681398460532</v>
       </c>
       <c r="J54">
-        <v>20651222372.89341</v>
+        <v>20.65122237289341</v>
       </c>
     </row>
     <row r="55" spans="1:10">
@@ -2176,10 +2176,10 @@
         <v>52583787807.80419</v>
       </c>
       <c r="I55">
-        <v>57041993665.07169</v>
+        <v>1.394656117036007</v>
       </c>
       <c r="J55">
-        <v>4458205912.914841</v>
+        <v>4.458205912914841</v>
       </c>
     </row>
     <row r="56" spans="1:10">
@@ -2208,10 +2208,10 @@
         <v>21853746383.63091</v>
       </c>
       <c r="I56">
-        <v>57041993670.96381</v>
+        <v>7.286773264914814</v>
       </c>
       <c r="J56">
-        <v>35188247337.08812</v>
+        <v>35.18824733708812</v>
       </c>
     </row>
     <row r="57" spans="1:10">
@@ -2240,10 +2240,10 @@
         <v>43773382131.25483</v>
       </c>
       <c r="I57">
-        <v>57041993668.17825</v>
+        <v>4.501215454321752</v>
       </c>
       <c r="J57">
-        <v>13268611589.4642</v>
+        <v>13.2686115894642</v>
       </c>
     </row>
     <row r="58" spans="1:10">
@@ -2272,10 +2272,10 @@
         <v>36313297318.30293</v>
       </c>
       <c r="I58">
-        <v>57041993669.57962</v>
+        <v>5.902583006638714</v>
       </c>
       <c r="J58">
-        <v>20728696402.4161</v>
+        <v>20.7286964024161</v>
       </c>
     </row>
     <row r="59" spans="1:10">
@@ -2304,10 +2304,10 @@
         <v>19013587086.557</v>
       </c>
       <c r="I59">
-        <v>57041993670.66309</v>
+        <v>6.986052180165096</v>
       </c>
       <c r="J59">
-        <v>38028406634.16203</v>
+        <v>38.02840663416203</v>
       </c>
     </row>
     <row r="60" spans="1:10">
@@ -2336,10 +2336,10 @@
         <v>31248737388.13833</v>
       </c>
       <c r="I60">
-        <v>57041993670.12431</v>
+        <v>6.447267202738331</v>
       </c>
       <c r="J60">
-        <v>25793256332.5807</v>
+        <v>25.7932563325807</v>
       </c>
     </row>
     <row r="61" spans="1:10">
@@ -2368,10 +2368,10 @@
         <v>16642852675.34803</v>
       </c>
       <c r="I61">
-        <v>57041993670.99894</v>
+        <v>7.321904494607857</v>
       </c>
       <c r="J61">
-        <v>40399141045.371</v>
+        <v>40.399141045371</v>
       </c>
     </row>
     <row r="62" spans="1:10">
@@ -2400,10 +2400,10 @@
         <v>46493649235.37974</v>
       </c>
       <c r="I62">
-        <v>57041993667.65542</v>
+        <v>3.978379158548798</v>
       </c>
       <c r="J62">
-        <v>10548344485.33929</v>
+        <v>10.54834448533929</v>
       </c>
     </row>
     <row r="63" spans="1:10">
@@ -2432,10 +2432,10 @@
         <v>23448076380.87272</v>
       </c>
       <c r="I63">
-        <v>57041993670.47684</v>
+        <v>6.799805793440534</v>
       </c>
       <c r="J63">
-        <v>33593917339.84631</v>
+        <v>33.59391733984631</v>
       </c>
     </row>
     <row r="64" spans="1:10">
@@ -2464,10 +2464,10 @@
         <v>37600621511.99935</v>
       </c>
       <c r="I64">
-        <v>57041993669.47808</v>
+        <v>5.801040421203417</v>
       </c>
       <c r="J64">
-        <v>19441372208.71968</v>
+        <v>19.44137220871968</v>
       </c>
     </row>
     <row r="65" spans="1:10">
@@ -2496,10 +2496,10 @@
         <v>28565979684.98584</v>
       </c>
       <c r="I65">
-        <v>57041993670.25552</v>
+        <v>6.578483106315701</v>
       </c>
       <c r="J65">
-        <v>28476014035.73319</v>
+        <v>28.47601403573319</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -2528,10 +2528,10 @@
         <v>32375058129.71281</v>
       </c>
       <c r="I66">
-        <v>57041993670.03165</v>
+        <v>6.354615624425797</v>
       </c>
       <c r="J66">
-        <v>24666935591.00622</v>
+        <v>24.66693559100622</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -2560,10 +2560,10 @@
         <v>52020661092.52408</v>
       </c>
       <c r="I67">
-        <v>57041993665.71092</v>
+        <v>2.033883688972281</v>
       </c>
       <c r="J67">
-        <v>5021332628.194954</v>
+        <v>5.021332628194954</v>
       </c>
     </row>
     <row r="68" spans="1:10">
@@ -2592,10 +2592,10 @@
         <v>33575363571.7458</v>
       </c>
       <c r="I68">
-        <v>57041993670.17685</v>
+        <v>6.499813095283571</v>
       </c>
       <c r="J68">
-        <v>23466630148.97323</v>
+        <v>23.46663014897323</v>
       </c>
     </row>
     <row r="69" spans="1:10">
@@ -2624,10 +2624,10 @@
         <v>25583801417.68838</v>
       </c>
       <c r="I69">
-        <v>57041993670.42046</v>
+        <v>6.743426373633447</v>
       </c>
       <c r="J69">
-        <v>31458192303.03065</v>
+        <v>31.45819230303065</v>
       </c>
     </row>
     <row r="70" spans="1:10">
@@ -2656,10 +2656,10 @@
         <v>41346042924.12611</v>
       </c>
       <c r="I70">
-        <v>57041993668.29492</v>
+        <v>4.617880123861767</v>
       </c>
       <c r="J70">
-        <v>15695950796.59293</v>
+        <v>15.69595079659293</v>
       </c>
     </row>
     <row r="71" spans="1:10">
@@ -2688,10 +2688,10 @@
         <v>53481526883.11742</v>
       </c>
       <c r="I71">
-        <v>57041993664.84875</v>
+        <v>1.171711604017517</v>
       </c>
       <c r="J71">
-        <v>3560466837.601616</v>
+        <v>3.560466837601616</v>
       </c>
     </row>
     <row r="72" spans="1:10">
@@ -2720,10 +2720,10 @@
         <v>35593499396.0629</v>
       </c>
       <c r="I72">
-        <v>57041993669.73459</v>
+        <v>6.057552420999293</v>
       </c>
       <c r="J72">
-        <v>21448494324.65614</v>
+        <v>21.44849432465614</v>
       </c>
     </row>
     <row r="73" spans="1:10">
@@ -2752,10 +2752,10 @@
         <v>15150081851.91754</v>
       </c>
       <c r="I73">
-        <v>57041993670.9446</v>
+        <v>7.267557894961158</v>
       </c>
       <c r="J73">
-        <v>41891911868.80149</v>
+        <v>41.89191186880149</v>
       </c>
     </row>
     <row r="74" spans="1:10">
@@ -2784,10 +2784,10 @@
         <v>24030918915.60656</v>
       </c>
       <c r="I74">
-        <v>57041993670.2345</v>
+        <v>6.557465365286092</v>
       </c>
       <c r="J74">
-        <v>33011074805.11247</v>
+        <v>33.01107480511247</v>
       </c>
     </row>
     <row r="75" spans="1:10">
@@ -2816,10 +2816,10 @@
         <v>22283963000.99296</v>
       </c>
       <c r="I75">
-        <v>57041993670.49406</v>
+        <v>6.817014678541057</v>
       </c>
       <c r="J75">
-        <v>34758030719.72607</v>
+        <v>34.75803071972607</v>
       </c>
     </row>
     <row r="76" spans="1:10">
@@ -2848,10 +2848,10 @@
         <v>45593076613.99068</v>
       </c>
       <c r="I76">
-        <v>57041993667.91828</v>
+        <v>4.241243829924365</v>
       </c>
       <c r="J76">
-        <v>11448917106.72836</v>
+        <v>11.44891710672836</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -2880,10 +2880,10 @@
         <v>45734434311.10162</v>
       </c>
       <c r="I77">
-        <v>57041993667.87714</v>
+        <v>4.200103518624537</v>
       </c>
       <c r="J77">
-        <v>11307559409.61741</v>
+        <v>11.30755940961741</v>
       </c>
     </row>
     <row r="78" spans="1:10">
@@ -2912,10 +2912,10 @@
         <v>21429917127.08603</v>
       </c>
       <c r="I78">
-        <v>57041993671.09686</v>
+        <v>7.419822575775868</v>
       </c>
       <c r="J78">
-        <v>35612076593.633</v>
+        <v>35.61207659363301</v>
       </c>
     </row>
     <row r="79" spans="1:10">
@@ -2944,10 +2944,10 @@
         <v>54120370649.9624</v>
       </c>
       <c r="I79">
-        <v>57041993664.61118</v>
+        <v>0.9341433321801773</v>
       </c>
       <c r="J79">
-        <v>2921623070.75663</v>
+        <v>2.92162307075663</v>
       </c>
     </row>
     <row r="80" spans="1:10">
@@ -2976,10 +2976,10 @@
         <v>49278262313.9927</v>
       </c>
       <c r="I80">
-        <v>57041993667.31445</v>
+        <v>3.637412338168893</v>
       </c>
       <c r="J80">
-        <v>7763731406.726334</v>
+        <v>7.763731406726333</v>
       </c>
     </row>
     <row r="81" spans="1:10">
@@ -3008,10 +3008,10 @@
         <v>44235393277.19426</v>
       </c>
       <c r="I81">
-        <v>57041993668.19276</v>
+        <v>4.515716768785197</v>
       </c>
       <c r="J81">
-        <v>12806600443.52477</v>
+        <v>12.80660044352477</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -3040,10 +3040,10 @@
         <v>36329818746.78777</v>
       </c>
       <c r="I82">
-        <v>57041993669.20381</v>
+        <v>5.526772908917387</v>
       </c>
       <c r="J82">
-        <v>20712174973.93126</v>
+        <v>20.71217497393126</v>
       </c>
     </row>
     <row r="83" spans="1:10">
@@ -3072,10 +3072,10 @@
         <v>27914221716.56769</v>
       </c>
       <c r="I83">
-        <v>57041993670.51765</v>
+        <v>6.840613267913447</v>
       </c>
       <c r="J83">
-        <v>29127772004.15134</v>
+        <v>29.12777200415134</v>
       </c>
     </row>
     <row r="84" spans="1:10">
@@ -3104,10 +3104,10 @@
         <v>33679069251.2508</v>
       </c>
       <c r="I84">
-        <v>57041993670.172</v>
+        <v>6.494959693657357</v>
       </c>
       <c r="J84">
-        <v>23362924469.46823</v>
+        <v>23.36292446946823</v>
       </c>
     </row>
     <row r="85" spans="1:10">
@@ -3136,10 +3136,10 @@
         <v>25458712796.18905</v>
       </c>
       <c r="I85">
-        <v>57041993670.32266</v>
+        <v>6.645622385542701</v>
       </c>
       <c r="J85">
-        <v>31583280924.52998</v>
+        <v>31.58328092452998</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -3168,10 +3168,10 @@
         <v>52907930036.52733</v>
       </c>
       <c r="I86">
-        <v>57041993665.08862</v>
+        <v>1.411577972809141</v>
       </c>
       <c r="J86">
-        <v>4134063684.191704</v>
+        <v>4.134063684191704</v>
       </c>
     </row>
     <row r="87" spans="1:10">
@@ -3200,10 +3200,10 @@
         <v>47744771123.593</v>
       </c>
       <c r="I87">
-        <v>57041993667.55954</v>
+        <v>3.882502214434787</v>
       </c>
       <c r="J87">
-        <v>9297222597.12603</v>
+        <v>9.29722259712603</v>
       </c>
     </row>
     <row r="88" spans="1:10">
@@ -3232,10 +3232,10 @@
         <v>54836011744.77605</v>
       </c>
       <c r="I88">
-        <v>57041993664.61221</v>
+        <v>0.9351753499856414</v>
       </c>
       <c r="J88">
-        <v>2205981975.942986</v>
+        <v>2.205981975942986</v>
       </c>
     </row>
     <row r="89" spans="1:10">
@@ -3264,10 +3264,10 @@
         <v>40320690532.70197</v>
       </c>
       <c r="I89">
-        <v>57041993668.67844</v>
+        <v>5.001400390035407</v>
       </c>
       <c r="J89">
-        <v>16721303188.01706</v>
+        <v>16.72130318801706</v>
       </c>
     </row>
     <row r="90" spans="1:10">
@@ -3296,10 +3296,10 @@
         <v>42951857818.11324</v>
       </c>
       <c r="I90">
-        <v>57041993668.65997</v>
+        <v>4.982937087349946</v>
       </c>
       <c r="J90">
-        <v>14090135902.60579</v>
+        <v>14.09013590260579</v>
       </c>
     </row>
     <row r="91" spans="1:10">
@@ -3328,10 +3328,10 @@
         <v>50286350883.36978</v>
       </c>
       <c r="I91">
-        <v>57041993667.10529</v>
+        <v>3.428253213065872</v>
       </c>
       <c r="J91">
-        <v>6755642837.349251</v>
+        <v>6.755642837349251</v>
       </c>
     </row>
     <row r="92" spans="1:10">
@@ -3360,10 +3360,10 @@
         <v>51144907510.52708</v>
       </c>
       <c r="I92">
-        <v>57041993665.81461</v>
+        <v>2.137571408134697</v>
       </c>
       <c r="J92">
-        <v>5897086210.191956</v>
+        <v>5.897086210191955</v>
       </c>
     </row>
     <row r="93" spans="1:10">
@@ -3392,10 +3392,10 @@
         <v>45373207807.0712</v>
       </c>
       <c r="I93">
-        <v>57041993668.007</v>
+        <v>4.329956144602058</v>
       </c>
       <c r="J93">
-        <v>11668785913.64783</v>
+        <v>11.66878591364783</v>
       </c>
     </row>
     <row r="94" spans="1:10">
@@ -3424,10 +3424,10 @@
         <v>46706241807.85506</v>
       </c>
       <c r="I94">
-        <v>57041993667.59233</v>
+        <v>3.915289890118927</v>
       </c>
       <c r="J94">
-        <v>10335751912.86398</v>
+        <v>10.33575191286397</v>
       </c>
     </row>
     <row r="95" spans="1:10">
@@ -3456,10 +3456,10 @@
         <v>49988206341.31714</v>
       </c>
       <c r="I95">
-        <v>57041993666.78467</v>
+        <v>3.107627328661941</v>
       </c>
       <c r="J95">
-        <v>7053787379.401894</v>
+        <v>7.053787379401894</v>
       </c>
     </row>
     <row r="96" spans="1:10">
@@ -3488,10 +3488,10 @@
         <v>24645845297.91649</v>
       </c>
       <c r="I96">
-        <v>57041993670.25304</v>
+        <v>6.575996844372845</v>
       </c>
       <c r="J96">
-        <v>32396148422.80254</v>
+        <v>32.39614842280255</v>
       </c>
     </row>
     <row r="97" spans="1:10">
@@ -3520,10 +3520,10 @@
         <v>53869513225.86115</v>
       </c>
       <c r="I97">
-        <v>57041993664.72227</v>
+        <v>1.045228877908954</v>
       </c>
       <c r="J97">
-        <v>3172480494.85788</v>
+        <v>3.17248049485788</v>
       </c>
     </row>
     <row r="98" spans="1:10">
@@ -3552,10 +3552,10 @@
         <v>49271363169.08135</v>
       </c>
       <c r="I98">
-        <v>57041993666.87971</v>
+        <v>3.202668909473253</v>
       </c>
       <c r="J98">
-        <v>7770630551.63768</v>
+        <v>7.77063055163768</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -3584,10 +3584,10 @@
         <v>34193087012.12502</v>
       </c>
       <c r="I99">
-        <v>57041993670.04907</v>
+        <v>6.372030423043718</v>
       </c>
       <c r="J99">
-        <v>22848906708.59401</v>
+        <v>22.84890670859401</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -3616,10 +3616,10 @@
         <v>47720610317.88171</v>
       </c>
       <c r="I100">
-        <v>57041993667.89133</v>
+        <v>4.214293705248707</v>
       </c>
       <c r="J100">
-        <v>9321383402.837326</v>
+        <v>9.321383402837325</v>
       </c>
     </row>
     <row r="101" spans="1:10">
@@ -3648,10 +3648,10 @@
         <v>38560442406.92709</v>
       </c>
       <c r="I101">
-        <v>57041993669.08487</v>
+        <v>5.407830857248108</v>
       </c>
       <c r="J101">
-        <v>18481551313.79194</v>
+        <v>18.48155131379194</v>
       </c>
     </row>
     <row r="102" spans="1:10">
@@ -3680,10 +3680,10 @@
         <v>24829105894.70695</v>
       </c>
       <c r="I102">
-        <v>57041993670.44408</v>
+        <v>6.767045341898097</v>
       </c>
       <c r="J102">
-        <v>32212887826.01208</v>
+        <v>32.21288782601208</v>
       </c>
     </row>
     <row r="103" spans="1:10">
@@ -3712,10 +3712,10 @@
         <v>42902527471.60964</v>
       </c>
       <c r="I103">
-        <v>57041993668.73978</v>
+        <v>5.062742147101062</v>
       </c>
       <c r="J103">
-        <v>14139466249.10939</v>
+        <v>14.13946624910939</v>
       </c>
     </row>
     <row r="104" spans="1:10">
@@ -3744,10 +3744,10 @@
         <v>48552085186.75314</v>
       </c>
       <c r="I104">
-        <v>57041993666.77498</v>
+        <v>3.097938242836157</v>
       </c>
       <c r="J104">
-        <v>8489908533.965889</v>
+        <v>8.489908533965888</v>
       </c>
     </row>
     <row r="105" spans="1:10">
@@ -3776,10 +3776,10 @@
         <v>45728436137.24068</v>
       </c>
       <c r="I105">
-        <v>57041993668.01563</v>
+        <v>4.338596402255604</v>
       </c>
       <c r="J105">
-        <v>11313557583.47836</v>
+        <v>11.31355758347835</v>
       </c>
     </row>
     <row r="106" spans="1:10">
@@ -3808,10 +3808,10 @@
         <v>30352073877.14516</v>
       </c>
       <c r="I106">
-        <v>57041993670.49324</v>
+        <v>6.816203320439065</v>
       </c>
       <c r="J106">
-        <v>26689919843.57387</v>
+        <v>26.68991984357387</v>
       </c>
     </row>
     <row r="107" spans="1:10">
@@ -3840,10 +3840,10 @@
         <v>51474195452.10434</v>
       </c>
       <c r="I107">
-        <v>57041993665.80364</v>
+        <v>2.126603954823942</v>
       </c>
       <c r="J107">
-        <v>5567798268.614693</v>
+        <v>5.567798268614693</v>
       </c>
     </row>
     <row r="108" spans="1:10">
@@ -3872,10 +3872,10 @@
         <v>15834783466.76808</v>
       </c>
       <c r="I108">
-        <v>57041993671.07464</v>
+        <v>7.397600966039157</v>
       </c>
       <c r="J108">
-        <v>41207210253.95095</v>
+        <v>41.20721025395095</v>
       </c>
     </row>
     <row r="109" spans="1:10">
@@ -3904,10 +3904,10 @@
         <v>21362505775.50931</v>
       </c>
       <c r="I109">
-        <v>57041993670.60676</v>
+        <v>6.929722746881296</v>
       </c>
       <c r="J109">
-        <v>35679487945.20972</v>
+        <v>35.67948794520971</v>
       </c>
     </row>
     <row r="110" spans="1:10">
@@ -3936,10 +3936,10 @@
         <v>18117997022.21794</v>
       </c>
       <c r="I110">
-        <v>57041993686.3044</v>
+        <v>22.62735942184372</v>
       </c>
       <c r="J110">
-        <v>38923996698.50109</v>
+        <v>38.92399669850109</v>
       </c>
     </row>
     <row r="111" spans="1:10">
@@ -3968,10 +3968,10 @@
         <v>19229131395.56729</v>
       </c>
       <c r="I111">
-        <v>57041993686.3044</v>
+        <v>22.62735952141033</v>
       </c>
       <c r="J111">
-        <v>37812862325.15174</v>
+        <v>37.81286232515174</v>
       </c>
     </row>
     <row r="112" spans="1:10">
@@ -4000,10 +4000,10 @@
         <v>22562534515.61537</v>
       </c>
       <c r="I112">
-        <v>57041993686.3044</v>
+        <v>22.62735982011016</v>
       </c>
       <c r="J112">
-        <v>34479459205.10366</v>
+        <v>34.47945920510366</v>
       </c>
     </row>
     <row r="113" spans="1:10">
@@ -4032,10 +4032,10 @@
         <v>-1512043573.620744</v>
       </c>
       <c r="I113">
-        <v>57041993686.3044</v>
+        <v>22.62735932227712</v>
       </c>
       <c r="J113">
-        <v>58554037294.33978</v>
+        <v>58.55403729433978</v>
       </c>
     </row>
     <row r="114" spans="1:10">
@@ -4064,10 +4064,10 @@
         <v>-771287324.7211709</v>
       </c>
       <c r="I114">
-        <v>57041993686.3044</v>
+        <v>22.62735972054355</v>
       </c>
       <c r="J114">
-        <v>57813281045.4402</v>
+        <v>57.8132810454402</v>
       </c>
     </row>
     <row r="115" spans="1:10">
@@ -4096,10 +4096,10 @@
         <v>14784593902.16986</v>
       </c>
       <c r="I115">
-        <v>57041993686.3044</v>
+        <v>22.62736011880997</v>
       </c>
       <c r="J115">
-        <v>42257399818.54917</v>
+        <v>42.25739981854917</v>
       </c>
     </row>
     <row r="116" spans="1:10">
@@ -4128,10 +4128,10 @@
         <v>7377031413.174132</v>
       </c>
       <c r="I116">
-        <v>57041993686.3044</v>
+        <v>22.62736011880998</v>
       </c>
       <c r="J116">
-        <v>49664962307.5449</v>
+        <v>49.6649623075449</v>
       </c>
     </row>
     <row r="117" spans="1:10">
@@ -4160,10 +4160,10 @@
         <v>34329915805.71241</v>
       </c>
       <c r="I117">
-        <v>57041993681.39623</v>
+        <v>17.71919546470478</v>
       </c>
       <c r="J117">
-        <v>22712077915.00662</v>
+        <v>22.71207791500662</v>
       </c>
     </row>
     <row r="118" spans="1:10">
@@ -4192,10 +4192,10 @@
         <v>16266106399.969</v>
       </c>
       <c r="I118">
-        <v>57041993686.3044</v>
+        <v>22.62735991967678</v>
       </c>
       <c r="J118">
-        <v>40775887320.75003</v>
+        <v>40.77588732075003</v>
       </c>
     </row>
     <row r="119" spans="1:10">
@@ -4224,10 +4224,10 @@
         <v>41562476765.6128</v>
       </c>
       <c r="I119">
-        <v>57041993671.14935</v>
+        <v>7.472303264689621</v>
       </c>
       <c r="J119">
-        <v>15479516955.10623</v>
+        <v>15.47951695510623</v>
       </c>
     </row>
     <row r="120" spans="1:10">
@@ -4256,10 +4256,10 @@
         <v>31942015252.20591</v>
       </c>
       <c r="I120">
-        <v>57041993681.39623</v>
+        <v>17.71919505620676</v>
       </c>
       <c r="J120">
-        <v>25099978468.51312</v>
+        <v>25.09997846851312</v>
       </c>
     </row>
     <row r="121" spans="1:10">
@@ -4288,10 +4288,10 @@
         <v>1450981421.977548</v>
       </c>
       <c r="I121">
-        <v>57041993686.3044</v>
+        <v>22.62735991967678</v>
       </c>
       <c r="J121">
-        <v>55591012298.74149</v>
+        <v>55.59101229874148</v>
       </c>
     </row>
     <row r="122" spans="1:10">
@@ -4320,10 +4320,10 @@
         <v>49566689333.08701</v>
       </c>
       <c r="I122">
-        <v>57041993667.62621</v>
+        <v>3.949171017886641</v>
       </c>
       <c r="J122">
-        <v>7475304387.632019</v>
+        <v>7.475304387632019</v>
       </c>
     </row>
     <row r="123" spans="1:10">
@@ -4352,10 +4352,10 @@
         <v>42640360646.38022</v>
       </c>
       <c r="I123">
-        <v>57041993670.76597</v>
+        <v>7.088928898338423</v>
       </c>
       <c r="J123">
-        <v>14401633074.33881</v>
+        <v>14.40163307433881</v>
       </c>
     </row>
     <row r="124" spans="1:10">
@@ -4384,10 +4384,10 @@
         <v>30205360304.20119</v>
       </c>
       <c r="I124">
-        <v>57041993681.39623</v>
+        <v>17.71919528963421</v>
       </c>
       <c r="J124">
-        <v>26836633416.51784</v>
+        <v>26.83663341651784</v>
       </c>
     </row>
     <row r="125" spans="1:10">
@@ -4416,10 +4416,10 @@
         <v>47215931857.43513</v>
       </c>
       <c r="I125">
-        <v>57041993667.62621</v>
+        <v>3.949172913708267</v>
       </c>
       <c r="J125">
-        <v>9826061863.283905</v>
+        <v>9.826061863283906</v>
       </c>
     </row>
     <row r="126" spans="1:10">
@@ -4448,10 +4448,10 @@
         <v>43018334262.76189</v>
       </c>
       <c r="I126">
-        <v>57041993671.14934</v>
+        <v>7.472302090580378</v>
       </c>
       <c r="J126">
-        <v>14023659457.95715</v>
+        <v>14.02365945795715</v>
       </c>
     </row>
     <row r="127" spans="1:10">
@@ -4480,10 +4480,10 @@
         <v>40106619268.46371</v>
       </c>
       <c r="I127">
-        <v>57041993671.14935</v>
+        <v>7.472304438798865</v>
       </c>
       <c r="J127">
-        <v>16935374452.25533</v>
+        <v>16.93537445225532</v>
       </c>
     </row>
     <row r="128" spans="1:10">
@@ -4512,10 +4512,10 @@
         <v>-400909200.2713702</v>
       </c>
       <c r="I128">
-        <v>57041993686.3044</v>
+        <v>22.62735942184371</v>
       </c>
       <c r="J128">
-        <v>57442902920.9904</v>
+        <v>57.4429029209904</v>
       </c>
     </row>
     <row r="129" spans="1:10">
@@ -4544,10 +4544,10 @@
         <v>28468705356.19645</v>
       </c>
       <c r="I129">
-        <v>57041993681.39623</v>
+        <v>17.71919552306166</v>
       </c>
       <c r="J129">
-        <v>28573288364.52258</v>
+        <v>28.57328836452258</v>
       </c>
     </row>
     <row r="130" spans="1:10">
@@ -4576,10 +4576,10 @@
         <v>31073687778.20354</v>
       </c>
       <c r="I130">
-        <v>57041993681.39623</v>
+        <v>17.71919575648911</v>
       </c>
       <c r="J130">
-        <v>25968305942.51549</v>
+        <v>25.96830594251549</v>
       </c>
     </row>
     <row r="131" spans="1:10">
@@ -4608,10 +4608,10 @@
         <v>11451190782.12178</v>
       </c>
       <c r="I131">
-        <v>57041993686.3044</v>
+        <v>22.62735982011016</v>
       </c>
       <c r="J131">
-        <v>45590802938.59725</v>
+        <v>45.59080293859725</v>
       </c>
     </row>
     <row r="132" spans="1:10">
@@ -4640,10 +4640,10 @@
         <v>6636275164.274556</v>
       </c>
       <c r="I132">
-        <v>57041993686.3044</v>
+        <v>22.62735972054355</v>
       </c>
       <c r="J132">
-        <v>50405718556.44447</v>
+        <v>50.40571855644448</v>
       </c>
     </row>
     <row r="133" spans="1:10">
@@ -4672,10 +4672,10 @@
         <v>30856605909.70296</v>
       </c>
       <c r="I133">
-        <v>57041993681.39623</v>
+        <v>17.71919593155968</v>
       </c>
       <c r="J133">
-        <v>26185387811.01607</v>
+        <v>26.18538781101607</v>
       </c>
     </row>
     <row r="134" spans="1:10">
@@ -4704,10 +4704,10 @@
         <v>-2252799822.520317</v>
       </c>
       <c r="I134">
-        <v>57041993686.3044</v>
+        <v>22.62735991967678</v>
       </c>
       <c r="J134">
-        <v>59294793543.23935</v>
+        <v>59.29479354323935</v>
       </c>
     </row>
     <row r="135" spans="1:10">
@@ -4736,10 +4736,10 @@
         <v>27600377882.19409</v>
       </c>
       <c r="I135">
-        <v>57041993681.39623</v>
+        <v>17.71919505620676</v>
       </c>
       <c r="J135">
-        <v>29441615838.52494</v>
+        <v>29.44161583852494</v>
       </c>
     </row>
     <row r="136" spans="1:10">
@@ -4768,10 +4768,10 @@
         <v>17747618897.76814</v>
       </c>
       <c r="I136">
-        <v>57041993686.3044</v>
+        <v>22.62735972054355</v>
       </c>
       <c r="J136">
-        <v>39294374822.9509</v>
+        <v>39.2943748229509</v>
       </c>
     </row>
     <row r="137" spans="1:10">
@@ -4800,10 +4800,10 @@
         <v>21821778266.71579</v>
       </c>
       <c r="I137">
-        <v>57041993686.3044</v>
+        <v>22.62735942184372</v>
       </c>
       <c r="J137">
-        <v>35220215454.00324</v>
+        <v>35.22021545400325</v>
       </c>
     </row>
     <row r="138" spans="1:10">
@@ -4832,10 +4832,10 @@
         <v>33027424594.70887</v>
       </c>
       <c r="I138">
-        <v>57041993681.39623</v>
+        <v>17.71919534799106</v>
       </c>
       <c r="J138">
-        <v>24014569126.01016</v>
+        <v>24.01456912601016</v>
       </c>
     </row>
     <row r="139" spans="1:10">
@@ -4864,10 +4864,10 @@
         <v>28034541619.19528</v>
       </c>
       <c r="I139">
-        <v>57041993681.39623</v>
+        <v>17.71919587320282</v>
       </c>
       <c r="J139">
-        <v>29007452101.52375</v>
+        <v>29.00745210152375</v>
       </c>
     </row>
     <row r="140" spans="1:10">
@@ -4896,10 +4896,10 @@
         <v>4784384542.025629</v>
       </c>
       <c r="I140">
-        <v>57041993686.3044</v>
+        <v>22.6273592227105</v>
       </c>
       <c r="J140">
-        <v>52257609178.69341</v>
+        <v>52.25760917869341</v>
       </c>
     </row>
     <row r="141" spans="1:10">
@@ -4928,10 +4928,10 @@
         <v>15895728275.51921</v>
       </c>
       <c r="I141">
-        <v>57041993686.3044</v>
+        <v>22.62735922271052</v>
       </c>
       <c r="J141">
-        <v>41146265445.19982</v>
+        <v>41.14626544519982</v>
       </c>
     </row>
     <row r="142" spans="1:10">
@@ -4960,10 +4960,10 @@
         <v>22932912640.06516</v>
       </c>
       <c r="I142">
-        <v>57041993686.3044</v>
+        <v>22.62735952141033</v>
       </c>
       <c r="J142">
-        <v>34109081080.65387</v>
+        <v>34.10908108065387</v>
       </c>
     </row>
     <row r="143" spans="1:10">
@@ -4992,10 +4992,10 @@
         <v>39378690519.88916</v>
       </c>
       <c r="I143">
-        <v>57041993671.14934</v>
+        <v>7.472301112156025</v>
       </c>
       <c r="J143">
-        <v>17663303200.82987</v>
+        <v>17.66330320082987</v>
       </c>
     </row>
     <row r="144" spans="1:10">
@@ -5024,10 +5024,10 @@
         <v>12191947031.02135</v>
       </c>
       <c r="I144">
-        <v>57041993686.3044</v>
+        <v>22.6273592227105</v>
       </c>
       <c r="J144">
-        <v>44850046689.69768</v>
+        <v>44.85004668969768</v>
       </c>
     </row>
     <row r="145" spans="1:10">
@@ -5056,10 +5056,10 @@
         <v>29337032830.19881</v>
       </c>
       <c r="I145">
-        <v>57041993681.39623</v>
+        <v>17.71919598991656</v>
       </c>
       <c r="J145">
-        <v>27704960890.52022</v>
+        <v>27.70496089052022</v>
       </c>
     </row>
     <row r="146" spans="1:10">
@@ -5088,10 +5088,10 @@
         <v>34112833937.21183</v>
       </c>
       <c r="I146">
-        <v>57041993681.39623</v>
+        <v>17.71919563977537</v>
       </c>
       <c r="J146">
-        <v>22929159783.5072</v>
+        <v>22.9291597835072</v>
       </c>
     </row>
     <row r="147" spans="1:10">
@@ -5120,10 +5120,10 @@
         <v>30639524041.20237</v>
       </c>
       <c r="I147">
-        <v>57041993681.39623</v>
+        <v>17.71919493949302</v>
       </c>
       <c r="J147">
-        <v>26402469679.51666</v>
+        <v>26.40246967951666</v>
       </c>
     </row>
     <row r="148" spans="1:10">
@@ -5152,10 +5152,10 @@
         <v>4414006417.575833</v>
       </c>
       <c r="I148">
-        <v>57041993686.3044</v>
+        <v>22.62735952141034</v>
       </c>
       <c r="J148">
-        <v>52627987303.1432</v>
+        <v>52.62798730314319</v>
       </c>
     </row>
     <row r="149" spans="1:10">
@@ -5184,10 +5184,10 @@
         <v>710225173.0779781</v>
       </c>
       <c r="I149">
-        <v>57041993686.3044</v>
+        <v>22.62735952141033</v>
       </c>
       <c r="J149">
-        <v>56331768547.64105</v>
+        <v>56.33176854764105</v>
       </c>
     </row>
     <row r="150" spans="1:10">
@@ -5216,10 +5216,10 @@
         <v>9228922035.423067</v>
       </c>
       <c r="I150">
-        <v>57041993686.3044</v>
+        <v>22.62735962097695</v>
       </c>
       <c r="J150">
-        <v>47813071685.29597</v>
+        <v>47.81307168529597</v>
       </c>
     </row>
     <row r="151" spans="1:10">
@@ -5248,10 +5248,10 @@
         <v>7747409537.623919</v>
       </c>
       <c r="I151">
-        <v>57041993686.3044</v>
+        <v>22.62735982011016</v>
       </c>
       <c r="J151">
-        <v>49294584183.09512</v>
+        <v>49.29458418309512</v>
       </c>
     </row>
     <row r="152" spans="1:10">
@@ -5280,10 +5280,10 @@
         <v>32159097120.70652</v>
       </c>
       <c r="I152">
-        <v>57041993681.39623</v>
+        <v>17.71919604827342</v>
       </c>
       <c r="J152">
-        <v>24882896600.01251</v>
+        <v>24.88289660001251</v>
       </c>
     </row>
     <row r="153" spans="1:10">
@@ -5312,10 +5312,10 @@
         <v>8117787662.073703</v>
       </c>
       <c r="I153">
-        <v>57041993686.3044</v>
+        <v>22.62735952141033</v>
       </c>
       <c r="J153">
-        <v>48924206058.64533</v>
+        <v>48.92420605864533</v>
       </c>
     </row>
     <row r="154" spans="1:10">
@@ -5344,10 +5344,10 @@
         <v>21081022017.81622</v>
       </c>
       <c r="I154">
-        <v>57041993686.3044</v>
+        <v>22.62736001924336</v>
       </c>
       <c r="J154">
-        <v>35960971702.90282</v>
+        <v>35.96097170290282</v>
       </c>
     </row>
     <row r="155" spans="1:10">
@@ -5376,10 +5376,10 @@
         <v>4043628293.126057</v>
       </c>
       <c r="I155">
-        <v>57041993686.3044</v>
+        <v>22.62735982011016</v>
       </c>
       <c r="J155">
-        <v>52998365427.59297</v>
+        <v>52.99836542759297</v>
       </c>
     </row>
     <row r="156" spans="1:10">
@@ -5408,10 +5408,10 @@
         <v>48391310595.26105</v>
       </c>
       <c r="I156">
-        <v>57041993667.62621</v>
+        <v>3.949171965797476</v>
       </c>
       <c r="J156">
-        <v>8650683125.457985</v>
+        <v>8.650683125457984</v>
       </c>
     </row>
     <row r="157" spans="1:10">
@@ -5440,10 +5440,10 @@
         <v>27166214145.19291</v>
       </c>
       <c r="I157">
-        <v>57041993681.39623</v>
+        <v>17.71919540634792</v>
       </c>
       <c r="J157">
-        <v>29875779575.52612</v>
+        <v>29.87577957552612</v>
       </c>
     </row>
     <row r="158" spans="1:10">
@@ -5472,10 +5472,10 @@
         <v>33678670200.21063</v>
       </c>
       <c r="I158">
-        <v>57041993681.39623</v>
+        <v>17.71919598991656</v>
       </c>
       <c r="J158">
-        <v>23363323520.5084</v>
+        <v>23.36332352050841</v>
       </c>
     </row>
     <row r="159" spans="1:10">
@@ -5504,10 +5504,10 @@
         <v>42290405514.18736</v>
       </c>
       <c r="I159">
-        <v>57041993671.14934</v>
+        <v>7.472302677634985</v>
       </c>
       <c r="J159">
-        <v>14751588206.53167</v>
+        <v>14.75158820653167</v>
       </c>
     </row>
     <row r="160" spans="1:10">
@@ -5536,10 +5536,10 @@
         <v>1821359546.427339</v>
       </c>
       <c r="I160">
-        <v>57041993686.3044</v>
+        <v>22.62735962097695</v>
       </c>
       <c r="J160">
-        <v>55220634174.29169</v>
+        <v>55.2206341742917</v>
       </c>
     </row>
     <row r="161" spans="1:10">
@@ -5568,10 +5568,10 @@
         <v>42234099218.32574</v>
       </c>
       <c r="I161">
-        <v>57041993670.76597</v>
+        <v>7.088929225977132</v>
       </c>
       <c r="J161">
-        <v>14807894502.3933</v>
+        <v>14.8078945023933</v>
       </c>
     </row>
     <row r="162" spans="1:10">
@@ -5600,10 +5600,10 @@
         <v>14043837653.27028</v>
       </c>
       <c r="I162">
-        <v>57041993686.3044</v>
+        <v>22.62735972054355</v>
       </c>
       <c r="J162">
-        <v>42998156067.44875</v>
+        <v>42.99815606744875</v>
       </c>
     </row>
     <row r="163" spans="1:10">
@@ -5632,10 +5632,10 @@
         <v>12932703279.92093</v>
       </c>
       <c r="I163">
-        <v>57041993686.3044</v>
+        <v>22.62735962097695</v>
       </c>
       <c r="J163">
-        <v>44109290440.7981</v>
+        <v>44.10929044079811</v>
       </c>
     </row>
     <row r="164" spans="1:10">
@@ -5664,10 +5664,10 @@
         <v>29771196567.2</v>
       </c>
       <c r="I164">
-        <v>57041993681.39623</v>
+        <v>17.71919563977537</v>
       </c>
       <c r="J164">
-        <v>27270797153.51903</v>
+        <v>27.27079715351903</v>
       </c>
     </row>
     <row r="165" spans="1:10">
@@ -5696,10 +5696,10 @@
         <v>1080603297.527763</v>
       </c>
       <c r="I165">
-        <v>57041993686.3044</v>
+        <v>22.62735922271052</v>
       </c>
       <c r="J165">
-        <v>55961390423.19127</v>
+        <v>55.96139042319127</v>
       </c>
     </row>
     <row r="166" spans="1:10">
@@ -5728,10 +5728,10 @@
         <v>5154762666.475415</v>
       </c>
       <c r="I166">
-        <v>57041993686.3044</v>
+        <v>22.62735991967678</v>
       </c>
       <c r="J166">
-        <v>51887231054.24361</v>
+        <v>51.88723105424361</v>
       </c>
     </row>
     <row r="167" spans="1:10">
@@ -5760,10 +5760,10 @@
         <v>40834548017.03828</v>
       </c>
       <c r="I167">
-        <v>57041993671.14935</v>
+        <v>7.472303851744222</v>
       </c>
       <c r="J167">
-        <v>16207445703.68076</v>
+        <v>16.20744570368075</v>
       </c>
     </row>
     <row r="168" spans="1:10">
@@ -5792,10 +5792,10 @@
         <v>19599509520.01707</v>
       </c>
       <c r="I168">
-        <v>57041993686.3044</v>
+        <v>22.62735922271052</v>
       </c>
       <c r="J168">
-        <v>37442484200.70197</v>
+        <v>37.44248420070196</v>
       </c>
     </row>
     <row r="169" spans="1:10">
@@ -5824,10 +5824,10 @@
         <v>2562115795.326912</v>
       </c>
       <c r="I169">
-        <v>57041993686.3044</v>
+        <v>22.62736001924336</v>
       </c>
       <c r="J169">
-        <v>54479877925.39212</v>
+        <v>54.47987792539212</v>
       </c>
     </row>
     <row r="170" spans="1:10">
@@ -5856,10 +5856,10 @@
         <v>47515497783.03429</v>
       </c>
       <c r="I170">
-        <v>57041993670.76597</v>
+        <v>7.088929335190066</v>
       </c>
       <c r="J170">
-        <v>9526495937.684746</v>
+        <v>9.526495937684746</v>
       </c>
     </row>
     <row r="171" spans="1:10">
@@ -5888,10 +5888,10 @@
         <v>8858543910.973274</v>
       </c>
       <c r="I171">
-        <v>57041993686.3044</v>
+        <v>22.62735991967678</v>
       </c>
       <c r="J171">
-        <v>48183449809.74576</v>
+        <v>48.18344980974576</v>
       </c>
     </row>
     <row r="172" spans="1:10">
@@ -5920,10 +5920,10 @@
         <v>11821568906.57156</v>
       </c>
       <c r="I172">
-        <v>57041993686.3044</v>
+        <v>22.62735952141033</v>
       </c>
       <c r="J172">
-        <v>45220424814.14748</v>
+        <v>45.22042481414748</v>
       </c>
     </row>
     <row r="173" spans="1:10">
@@ -5952,10 +5952,10 @@
         <v>15154972026.61964</v>
       </c>
       <c r="I173">
-        <v>57041993686.3044</v>
+        <v>22.62735982011016</v>
       </c>
       <c r="J173">
-        <v>41887021694.0994</v>
+        <v>41.8870216940994</v>
       </c>
     </row>
     <row r="174" spans="1:10">
@@ -5984,10 +5984,10 @@
         <v>9969678284.322634</v>
       </c>
       <c r="I174">
-        <v>57041993686.3044</v>
+        <v>22.62736001924336</v>
       </c>
       <c r="J174">
-        <v>47072315436.3964</v>
+        <v>47.0723154363964</v>
       </c>
     </row>
     <row r="175" spans="1:10">
@@ -6016,10 +6016,10 @@
         <v>31290769646.70414</v>
       </c>
       <c r="I175">
-        <v>57041993681.39623</v>
+        <v>17.71919558141852</v>
       </c>
       <c r="J175">
-        <v>25751224074.01489</v>
+        <v>25.75122407401489</v>
       </c>
     </row>
     <row r="176" spans="1:10">
@@ -6048,10 +6048,10 @@
         <v>32593260857.7077</v>
       </c>
       <c r="I176">
-        <v>57041993681.39623</v>
+        <v>17.71919569813223</v>
       </c>
       <c r="J176">
-        <v>24448732863.01133</v>
+        <v>24.44873286301133</v>
       </c>
     </row>
     <row r="177" spans="1:10">
@@ -6080,10 +6080,10 @@
         <v>31507851515.20473</v>
       </c>
       <c r="I177">
-        <v>57041993681.39623</v>
+        <v>17.71919540634794</v>
       </c>
       <c r="J177">
-        <v>25534142205.5143</v>
+        <v>25.5341422055143</v>
       </c>
     </row>
     <row r="178" spans="1:10">
@@ -6112,10 +6112,10 @@
         <v>17377240773.31836</v>
       </c>
       <c r="I178">
-        <v>57041993686.3044</v>
+        <v>22.62736001924338</v>
       </c>
       <c r="J178">
-        <v>39664752947.40067</v>
+        <v>39.66475294740067</v>
       </c>
     </row>
     <row r="179" spans="1:10">
@@ -6144,10 +6144,10 @@
         <v>54584316921.48884</v>
       </c>
       <c r="I179">
-        <v>57041993666.13471</v>
+        <v>2.457676799230207</v>
       </c>
       <c r="J179">
-        <v>2457676799.230194</v>
+        <v>2.457676799230194</v>
       </c>
     </row>
     <row r="180" spans="1:10">
@@ -6176,10 +6176,10 @@
         <v>28902869093.19764</v>
       </c>
       <c r="I180">
-        <v>57041993681.39623</v>
+        <v>17.71919517292047</v>
       </c>
       <c r="J180">
-        <v>28139124627.52139</v>
+        <v>28.13912462752139</v>
       </c>
     </row>
     <row r="181" spans="1:10">
@@ -6208,10 +6208,10 @@
         <v>-1141665449.170949</v>
       </c>
       <c r="I181">
-        <v>57041993686.3044</v>
+        <v>22.62736001924336</v>
       </c>
       <c r="J181">
-        <v>58183659169.88998</v>
+        <v>58.18365916988999</v>
       </c>
     </row>
     <row r="182" spans="1:10">
@@ -6240,10 +6240,10 @@
         <v>44474191759.91097</v>
       </c>
       <c r="I182">
-        <v>57041993671.14934</v>
+        <v>7.472300916471141</v>
       </c>
       <c r="J182">
-        <v>12567801960.80806</v>
+        <v>12.56780196080806</v>
       </c>
     </row>
     <row r="183" spans="1:10">
@@ -6272,10 +6272,10 @@
         <v>20340265768.91665</v>
       </c>
       <c r="I183">
-        <v>57041993686.3044</v>
+        <v>22.62735962097695</v>
       </c>
       <c r="J183">
-        <v>36701727951.80238</v>
+        <v>36.70172795180238</v>
       </c>
     </row>
     <row r="184" spans="1:10">
@@ -6304,10 +6304,10 @@
         <v>10340056408.77242</v>
       </c>
       <c r="I184">
-        <v>57041993686.3044</v>
+        <v>22.62735972054355</v>
       </c>
       <c r="J184">
-        <v>46701937311.94661</v>
+        <v>46.70193731194661</v>
       </c>
     </row>
     <row r="185" spans="1:10">
@@ -6336,10 +6336,10 @@
         <v>13303081404.37071</v>
       </c>
       <c r="I185">
-        <v>57041993686.3044</v>
+        <v>22.62735932227712</v>
       </c>
       <c r="J185">
-        <v>43738912316.34832</v>
+        <v>43.73891231634832</v>
       </c>
     </row>
     <row r="186" spans="1:10">
@@ -6368,10 +6368,10 @@
         <v>339847048.6281841</v>
       </c>
       <c r="I186">
-        <v>57041993686.3044</v>
+        <v>22.62735982011017</v>
       </c>
       <c r="J186">
-        <v>56702146672.09085</v>
+        <v>56.70214667209085</v>
       </c>
     </row>
     <row r="187" spans="1:10">
@@ -6400,10 +6400,10 @@
         <v>11080812657.672</v>
       </c>
       <c r="I187">
-        <v>57041993686.3044</v>
+        <v>22.62736011880997</v>
       </c>
       <c r="J187">
-        <v>45961181063.04703</v>
+        <v>45.96118106304703</v>
       </c>
     </row>
     <row r="188" spans="1:10">
@@ -6432,10 +6432,10 @@
         <v>3673250168.676273</v>
       </c>
       <c r="I188">
-        <v>57041993686.3044</v>
+        <v>22.62736011880997</v>
       </c>
       <c r="J188">
-        <v>53368743552.04276</v>
+        <v>53.36874355204277</v>
       </c>
     </row>
     <row r="189" spans="1:10">
@@ -6464,10 +6464,10 @@
         <v>13673459528.8205</v>
       </c>
       <c r="I189">
-        <v>57041993686.3044</v>
+        <v>22.62736001924336</v>
       </c>
       <c r="J189">
-        <v>43368534191.89853</v>
+        <v>43.36853419189853</v>
       </c>
     </row>
     <row r="190" spans="1:10">
@@ -6496,10 +6496,10 @@
         <v>37922833022.74009</v>
       </c>
       <c r="I190">
-        <v>57041993671.14934</v>
+        <v>7.472302286265254</v>
       </c>
       <c r="J190">
-        <v>19119160697.97894</v>
+        <v>19.11916069797894</v>
       </c>
     </row>
     <row r="191" spans="1:10">
@@ -6528,10 +6528,10 @@
         <v>2191737670.87712</v>
       </c>
       <c r="I191">
-        <v>57041993686.3044</v>
+        <v>22.62735932227712</v>
       </c>
       <c r="J191">
-        <v>54850256049.84191</v>
+        <v>54.85025604984191</v>
       </c>
     </row>
     <row r="192" spans="1:10">
@@ -6560,10 +6560,10 @@
         <v>3302872044.226478</v>
       </c>
       <c r="I192">
-        <v>57041993686.3044</v>
+        <v>22.62735942184372</v>
       </c>
       <c r="J192">
-        <v>53739121676.49255</v>
+        <v>53.73912167649255</v>
       </c>
     </row>
     <row r="193" spans="1:10">
@@ -6592,10 +6592,10 @@
         <v>50742068070.91293</v>
       </c>
       <c r="I193">
-        <v>57041993667.62621</v>
+        <v>3.949170069975857</v>
       </c>
       <c r="J193">
-        <v>6299925649.806099</v>
+        <v>6.299925649806099</v>
       </c>
     </row>
     <row r="194" spans="1:10">
@@ -6624,10 +6624,10 @@
         <v>8488165786.523487</v>
       </c>
       <c r="I194">
-        <v>57041993686.3044</v>
+        <v>22.62735922271052</v>
       </c>
       <c r="J194">
-        <v>48553827934.19554</v>
+        <v>48.55382793419554</v>
       </c>
     </row>
     <row r="195" spans="1:10">
@@ -6656,10 +6656,10 @@
         <v>15525350151.06943</v>
       </c>
       <c r="I195">
-        <v>57041993686.3044</v>
+        <v>22.62735952141033</v>
       </c>
       <c r="J195">
-        <v>41516643569.6496</v>
+        <v>41.5166435696496</v>
       </c>
     </row>
     <row r="196" spans="1:10">
@@ -6688,10 +6688,10 @@
         <v>-30531075.82159597</v>
       </c>
       <c r="I196">
-        <v>57041993686.3044</v>
+        <v>22.62736011880998</v>
       </c>
       <c r="J196">
-        <v>57072524796.54063</v>
+        <v>57.07252479654063</v>
       </c>
     </row>
     <row r="197" spans="1:10">
@@ -6720,10 +6720,10 @@
         <v>51917446808.73883</v>
       </c>
       <c r="I197">
-        <v>57041993667.62621</v>
+        <v>3.949169122065072</v>
       </c>
       <c r="J197">
-        <v>5124546911.980202</v>
+        <v>5.124546911980202</v>
       </c>
     </row>
     <row r="198" spans="1:10">
@@ -6752,10 +6752,10 @@
         <v>23303290764.51495</v>
       </c>
       <c r="I198">
-        <v>57041993686.3044</v>
+        <v>22.6273592227105</v>
       </c>
       <c r="J198">
-        <v>33738702956.20408</v>
+        <v>33.73870295620408</v>
       </c>
     </row>
     <row r="199" spans="1:10">
@@ -6784,10 +6784,10 @@
         <v>9599300159.872854</v>
       </c>
       <c r="I199">
-        <v>57041993686.3044</v>
+        <v>22.6273593222771</v>
       </c>
       <c r="J199">
-        <v>47442693560.84618</v>
+        <v>47.44269356084617</v>
       </c>
     </row>
     <row r="200" spans="1:10">
@@ -6816,10 +6816,10 @@
         <v>14414215777.72007</v>
       </c>
       <c r="I200">
-        <v>57041993686.3044</v>
+        <v>22.62735942184372</v>
       </c>
       <c r="J200">
-        <v>42627777942.99896</v>
+        <v>42.62777794299896</v>
       </c>
     </row>
     <row r="201" spans="1:10">
@@ -6848,10 +6848,10 @@
         <v>18858753271.11751</v>
       </c>
       <c r="I201">
-        <v>57041993686.3044</v>
+        <v>22.62735982011016</v>
       </c>
       <c r="J201">
-        <v>38183240449.60152</v>
+        <v>38.18324044960152</v>
       </c>
     </row>
     <row r="202" spans="1:10">
@@ -6880,10 +6880,10 @@
         <v>18488375146.66772</v>
       </c>
       <c r="I202">
-        <v>57041993686.3044</v>
+        <v>22.62736011880998</v>
       </c>
       <c r="J202">
-        <v>38553618574.05132</v>
+        <v>38.55361857405131</v>
       </c>
     </row>
     <row r="203" spans="1:10">
@@ -6912,10 +6912,10 @@
         <v>22192156391.16558</v>
       </c>
       <c r="I203">
-        <v>57041993686.3044</v>
+        <v>22.62736011880998</v>
       </c>
       <c r="J203">
-        <v>34849837329.55345</v>
+        <v>34.84983732955345</v>
       </c>
     </row>
     <row r="204" spans="1:10">
@@ -6944,10 +6944,10 @@
         <v>33461588331.71004</v>
       </c>
       <c r="I204">
-        <v>57041993681.39623</v>
+        <v>17.7191949978499</v>
       </c>
       <c r="J204">
-        <v>23580405389.00899</v>
+        <v>23.58040538900899</v>
       </c>
     </row>
     <row r="205" spans="1:10">
@@ -6976,10 +6976,10 @@
         <v>17006862648.86858</v>
       </c>
       <c r="I205">
-        <v>57041993686.3044</v>
+        <v>22.6273593222771</v>
       </c>
       <c r="J205">
-        <v>40035131071.85045</v>
+        <v>40.03513107185045</v>
       </c>
     </row>
     <row r="206" spans="1:10">
@@ -7008,10 +7008,10 @@
         <v>34546997674.21301</v>
       </c>
       <c r="I206">
-        <v>57041993681.39623</v>
+        <v>17.71919528963419</v>
       </c>
       <c r="J206">
-        <v>22494996046.50602</v>
+        <v>22.49499604650602</v>
       </c>
     </row>
     <row r="207" spans="1:10">
@@ -7040,10 +7040,10 @@
         <v>31724933383.70532</v>
       </c>
       <c r="I207">
-        <v>57041993681.39623</v>
+        <v>17.71919523127735</v>
       </c>
       <c r="J207">
-        <v>25317060337.01371</v>
+        <v>25.31706033701371</v>
       </c>
     </row>
     <row r="208" spans="1:10">
@@ -7072,10 +7072,10 @@
         <v>5895518915.374986</v>
       </c>
       <c r="I208">
-        <v>57041993686.3044</v>
+        <v>22.62735932227712</v>
       </c>
       <c r="J208">
-        <v>51146474805.34405</v>
+        <v>51.14647480534405</v>
       </c>
     </row>
     <row r="209" spans="1:10">
@@ -7104,10 +7104,10 @@
         <v>43746263011.33643</v>
       </c>
       <c r="I209">
-        <v>57041993671.14934</v>
+        <v>7.472301503525756</v>
       </c>
       <c r="J209">
-        <v>13295730709.3826</v>
+        <v>13.2957307093826</v>
       </c>
     </row>
     <row r="210" spans="1:10">
@@ -7136,10 +7136,10 @@
         <v>20710643893.36644</v>
       </c>
       <c r="I210">
-        <v>57041993686.3044</v>
+        <v>22.62735932227712</v>
       </c>
       <c r="J210">
-        <v>36331349827.35259</v>
+        <v>36.33134982735259</v>
       </c>
     </row>
     <row r="211" spans="1:10">
@@ -7168,10 +7168,10 @@
         <v>32810342726.20828</v>
       </c>
       <c r="I211">
-        <v>57041993681.39623</v>
+        <v>17.71919552306166</v>
       </c>
       <c r="J211">
-        <v>24231650994.51075</v>
+        <v>24.23165099451075</v>
       </c>
     </row>
     <row r="212" spans="1:10">
@@ -7200,10 +7200,10 @@
         <v>38037577721.57646</v>
       </c>
       <c r="I212">
-        <v>57041993676.62077</v>
+        <v>12.94373601790706</v>
       </c>
       <c r="J212">
-        <v>19004415999.14257</v>
+        <v>19.00441599914257</v>
       </c>
     </row>
     <row r="213" spans="1:10">
@@ -7232,10 +7232,10 @@
         <v>33244506463.20947</v>
       </c>
       <c r="I213">
-        <v>57041993681.39623</v>
+        <v>17.71919517292046</v>
       </c>
       <c r="J213">
-        <v>23797487257.50956</v>
+        <v>23.79748725750956</v>
       </c>
     </row>
     <row r="214" spans="1:10">
@@ -7264,10 +7264,10 @@
         <v>16636484524.41879</v>
       </c>
       <c r="I214">
-        <v>57041993686.3044</v>
+        <v>22.62735962097695</v>
       </c>
       <c r="J214">
-        <v>40405509196.30024</v>
+        <v>40.40550919630024</v>
       </c>
     </row>
     <row r="215" spans="1:10">
@@ -7296,10 +7296,10 @@
         <v>5525140790.925199</v>
       </c>
       <c r="I215">
-        <v>57041993686.3044</v>
+        <v>22.62735962097695</v>
       </c>
       <c r="J215">
-        <v>51516852929.79383</v>
+        <v>51.51685292979383</v>
       </c>
     </row>
     <row r="216" spans="1:10">
@@ -7328,10 +7328,10 @@
         <v>38650761771.31464</v>
       </c>
       <c r="I216">
-        <v>57041993671.14934</v>
+        <v>7.472301699210625</v>
       </c>
       <c r="J216">
-        <v>18391231949.4044</v>
+        <v>18.3912319494044</v>
       </c>
     </row>
     <row r="217" spans="1:10">
@@ -7360,10 +7360,10 @@
         <v>21451400142.26601</v>
       </c>
       <c r="I217">
-        <v>57041993686.3044</v>
+        <v>22.62735972054355</v>
       </c>
       <c r="J217">
-        <v>35590593578.45302</v>
+        <v>35.59059357845302</v>
       </c>
     </row>
     <row r="218" spans="1:10">
@@ -7392,10 +7392,10 @@
         <v>19969887644.46686</v>
       </c>
       <c r="I218">
-        <v>57041993686.3044</v>
+        <v>22.62735991967678</v>
       </c>
       <c r="J218">
-        <v>37072106076.25217</v>
+        <v>37.07210607625217</v>
       </c>
     </row>
     <row r="219" spans="1:10">
@@ -7424,10 +7424,10 @@
         <v>10710434533.22221</v>
       </c>
       <c r="I219">
-        <v>57041993686.3044</v>
+        <v>22.62735942184372</v>
       </c>
       <c r="J219">
-        <v>46331559187.49683</v>
+        <v>46.33155918749683</v>
       </c>
     </row>
     <row r="220" spans="1:10">
@@ -7456,10 +7456,10 @@
         <v>43046622074.43474</v>
       </c>
       <c r="I220">
-        <v>57041993670.76597</v>
+        <v>7.088928570699686</v>
       </c>
       <c r="J220">
-        <v>13995371646.28429</v>
+        <v>13.99537164628429</v>
       </c>
     </row>
     <row r="221" spans="1:10">
@@ -7488,10 +7488,10 @@
         <v>2932493919.7767</v>
       </c>
       <c r="I221">
-        <v>57041993686.3044</v>
+        <v>22.62735972054355</v>
       </c>
       <c r="J221">
-        <v>54109499800.94233</v>
+        <v>54.10949980094233</v>
       </c>
     </row>
     <row r="222" spans="1:10">
@@ -7520,10 +7520,10 @@
         <v>-1882421698.070527</v>
       </c>
       <c r="I222">
-        <v>57041993686.3044</v>
+        <v>22.62735962097695</v>
       </c>
       <c r="J222">
-        <v>58924415418.78956</v>
+        <v>58.92441541878956</v>
       </c>
     </row>
     <row r="223" spans="1:10">
@@ -7552,10 +7552,10 @@
         <v>6265897039.824774</v>
       </c>
       <c r="I223">
-        <v>57041993686.3044</v>
+        <v>22.62736001924336</v>
       </c>
       <c r="J223">
-        <v>50776096680.89426</v>
+        <v>50.77609668089426</v>
       </c>
     </row>
     <row r="224" spans="1:10">
@@ -7584,10 +7584,10 @@
         <v>12562325155.47114</v>
       </c>
       <c r="I224">
-        <v>57041993686.3044</v>
+        <v>22.62735991967678</v>
       </c>
       <c r="J224">
-        <v>44479668565.24789</v>
+        <v>44.47966856524789</v>
       </c>
     </row>
     <row r="225" spans="1:10">
@@ -7616,10 +7616,10 @@
         <v>32376178989.2071</v>
       </c>
       <c r="I225">
-        <v>57041993681.39623</v>
+        <v>17.71919587320282</v>
       </c>
       <c r="J225">
-        <v>24665814731.51193</v>
+        <v>24.66581473151193</v>
       </c>
     </row>
     <row r="226" spans="1:10">
@@ -7648,10 +7648,10 @@
         <v>38326181541.29015</v>
       </c>
       <c r="I226">
-        <v>57041993676.62077</v>
+        <v>12.94373578515594</v>
       </c>
       <c r="J226">
-        <v>18715812179.42888</v>
+        <v>18.71581217942888</v>
       </c>
     </row>
     <row r="227" spans="1:10">
@@ -7680,10 +7680,10 @@
         <v>7006653288.724345</v>
       </c>
       <c r="I227">
-        <v>57041993686.3044</v>
+        <v>22.62735942184372</v>
       </c>
       <c r="J227">
-        <v>50035340431.99469</v>
+        <v>50.03534043199469</v>
       </c>
     </row>
     <row r="228" spans="1:10">
@@ -7712,10 +7712,10 @@
         <v>26732050408.19173</v>
       </c>
       <c r="I228">
-        <v>57041993681.39623</v>
+        <v>17.71919575648911</v>
       </c>
       <c r="J228">
-        <v>30309943312.5273</v>
+        <v>30.3099433125273</v>
       </c>
     </row>
     <row r="229" spans="1:10">
@@ -7744,10 +7744,10 @@
         <v>33895752068.71122</v>
       </c>
       <c r="I229">
-        <v>57041993681.39623</v>
+        <v>17.71919581484597</v>
       </c>
       <c r="J229">
-        <v>23146241652.00781</v>
+        <v>23.14624165200781</v>
       </c>
     </row>
     <row r="230" spans="1:10">
@@ -7776,10 +7776,10 @@
         <v>22495291914.99209</v>
       </c>
       <c r="I230">
-        <v>57041993682.47943</v>
+        <v>18.80239266196423</v>
       </c>
       <c r="J230">
-        <v>34546701805.72694</v>
+        <v>34.54670180572695</v>
       </c>
     </row>
     <row r="231" spans="1:10">
@@ -7808,10 +7808,10 @@
         <v>23568767551.54756</v>
       </c>
       <c r="I231">
-        <v>57041993682.47943</v>
+        <v>18.8023927581563</v>
       </c>
       <c r="J231">
-        <v>33473226169.17147</v>
+        <v>33.47322616917147</v>
       </c>
     </row>
     <row r="232" spans="1:10">
@@ -7840,10 +7840,10 @@
         <v>29804402365.21104</v>
       </c>
       <c r="I232">
-        <v>57041993678.05471</v>
+        <v>14.37767456734859</v>
       </c>
       <c r="J232">
-        <v>27237591355.50799</v>
+        <v>27.23759135550799</v>
       </c>
     </row>
     <row r="233" spans="1:10">
@@ -7872,10 +7872,10 @@
         <v>826408309.5641029</v>
       </c>
       <c r="I233">
-        <v>57041993686.90788</v>
+        <v>23.23084594725715</v>
       </c>
       <c r="J233">
-        <v>56215585411.15493</v>
+        <v>56.21558541115493</v>
       </c>
     </row>
     <row r="234" spans="1:10">
@@ -7904,10 +7904,10 @@
         <v>1506506032.354017</v>
       </c>
       <c r="I234">
-        <v>57041993686.90788</v>
+        <v>23.23084631291062</v>
       </c>
       <c r="J234">
-        <v>55535487688.36501</v>
+        <v>55.53548768836502</v>
       </c>
     </row>
     <row r="235" spans="1:10">
@@ -7936,10 +7936,10 @@
         <v>19274865005.32568</v>
       </c>
       <c r="I235">
-        <v>57041993682.47943</v>
+        <v>18.80239333530879</v>
       </c>
       <c r="J235">
-        <v>37767128715.39336</v>
+        <v>37.76712871539335</v>
       </c>
     </row>
     <row r="236" spans="1:10">
@@ -7968,10 +7968,10 @@
         <v>8987580983.043152</v>
       </c>
       <c r="I236">
-        <v>57041993686.90788</v>
+        <v>23.23084667856409</v>
       </c>
       <c r="J236">
-        <v>48054412737.67588</v>
+        <v>48.05441273767588</v>
       </c>
     </row>
     <row r="237" spans="1:10">
@@ -8000,10 +8000,10 @@
         <v>40654351445.21875</v>
       </c>
       <c r="I237">
-        <v>57041993674.66484</v>
+        <v>10.98779857065323</v>
       </c>
       <c r="J237">
-        <v>16387642275.50028</v>
+        <v>16.38764227550028</v>
       </c>
     </row>
     <row r="238" spans="1:10">
@@ -8032,10 +8032,10 @@
         <v>20706165854.0663</v>
       </c>
       <c r="I238">
-        <v>57041993682.47943</v>
+        <v>18.80239314292462</v>
       </c>
       <c r="J238">
-        <v>36335827866.65273</v>
+        <v>36.33582786665274</v>
       </c>
     </row>
     <row r="239" spans="1:10">
@@ -8064,10 +8064,10 @@
         <v>43471661500.6281</v>
       </c>
       <c r="I239">
-        <v>57041993674.66484</v>
+        <v>10.98779882310696</v>
       </c>
       <c r="J239">
-        <v>13570332220.09093</v>
+        <v>13.57033222009093</v>
       </c>
     </row>
     <row r="240" spans="1:10">
@@ -8096,10 +8096,10 @@
         <v>38071817227.76017</v>
       </c>
       <c r="I240">
-        <v>57041993674.66483</v>
+        <v>10.98779812885921</v>
       </c>
       <c r="J240">
-        <v>18970176492.95886</v>
+        <v>18.97017649295886</v>
       </c>
     </row>
     <row r="241" spans="1:10">
@@ -8128,10 +8128,10 @@
         <v>3546799200.72378</v>
       </c>
       <c r="I241">
-        <v>57041993686.90788</v>
+        <v>23.23084649573737</v>
       </c>
       <c r="J241">
-        <v>53495194519.99525</v>
+        <v>53.49519451999525</v>
       </c>
     </row>
     <row r="242" spans="1:10">
@@ -8160,10 +8160,10 @@
         <v>46426374345.03645</v>
       </c>
       <c r="I242">
-        <v>57041993673.18262</v>
+        <v>9.505585509584478</v>
       </c>
       <c r="J242">
-        <v>10615619375.68258</v>
+        <v>10.61561937568258</v>
       </c>
     </row>
     <row r="243" spans="1:10">
@@ -8192,10 +8192,10 @@
         <v>41828230634.97266</v>
       </c>
       <c r="I243">
-        <v>57041993674.66484</v>
+        <v>10.98779888622037</v>
       </c>
       <c r="J243">
-        <v>15213763085.74638</v>
+        <v>15.21376308574638</v>
       </c>
     </row>
     <row r="244" spans="1:10">
@@ -8224,10 +8224,10 @@
         <v>36193610524.15395</v>
       </c>
       <c r="I244">
-        <v>57041993674.66484</v>
+        <v>10.98779838131293</v>
       </c>
       <c r="J244">
-        <v>20848383196.56508</v>
+        <v>20.84838319656508</v>
       </c>
     </row>
     <row r="245" spans="1:10">
@@ -8256,10 +8256,10 @@
         <v>44880316528.33279</v>
       </c>
       <c r="I245">
-        <v>57041993674.66484</v>
+        <v>10.98779894933381</v>
       </c>
       <c r="J245">
-        <v>12161677192.38625</v>
+        <v>12.16167719238625</v>
       </c>
     </row>
     <row r="246" spans="1:10">
@@ -8288,10 +8288,10 @@
         <v>43941213176.52967</v>
       </c>
       <c r="I246">
-        <v>57041993674.66484</v>
+        <v>10.98779844442635</v>
       </c>
       <c r="J246">
-        <v>13100780544.18936</v>
+        <v>13.10078054418936</v>
       </c>
     </row>
     <row r="247" spans="1:10">
@@ -8320,10 +8320,10 @@
         <v>43002109824.72654</v>
       </c>
       <c r="I247">
-        <v>57041993674.66484</v>
+        <v>10.98779920178753</v>
       </c>
       <c r="J247">
-        <v>14039883895.99249</v>
+        <v>14.03988389599249</v>
       </c>
     </row>
     <row r="248" spans="1:10">
@@ -8352,10 +8352,10 @@
         <v>1846554893.748986</v>
       </c>
       <c r="I248">
-        <v>57041993686.90788</v>
+        <v>23.23084603867051</v>
       </c>
       <c r="J248">
-        <v>55195438826.97005</v>
+        <v>55.19543882697005</v>
       </c>
     </row>
     <row r="249" spans="1:10">
@@ -8384,10 +8384,10 @@
         <v>46740664513.85955</v>
       </c>
       <c r="I249">
-        <v>57041993673.18262</v>
+        <v>9.505584614371791</v>
       </c>
       <c r="J249">
-        <v>10301329206.85948</v>
+        <v>10.30132920685948</v>
       </c>
     </row>
     <row r="250" spans="1:10">
@@ -8416,10 +8416,10 @@
         <v>32617509304.41427</v>
       </c>
       <c r="I250">
-        <v>57041993678.05471</v>
+        <v>14.37767445931554</v>
       </c>
       <c r="J250">
-        <v>24424484416.30476</v>
+        <v>24.42448441630476</v>
       </c>
     </row>
     <row r="251" spans="1:10">
@@ -8448,10 +8448,10 @@
         <v>37132713875.95704</v>
       </c>
       <c r="I251">
-        <v>57041993674.66484</v>
+        <v>10.98779888622038</v>
       </c>
       <c r="J251">
-        <v>19909279844.76199</v>
+        <v>19.90927984476199</v>
       </c>
     </row>
     <row r="252" spans="1:10">
@@ -8480,10 +8480,10 @@
         <v>16054438095.65927</v>
       </c>
       <c r="I252">
-        <v>57041993682.47943</v>
+        <v>18.80239304673255</v>
       </c>
       <c r="J252">
-        <v>40987555625.05976</v>
+        <v>40.98755562505976</v>
       </c>
     </row>
     <row r="253" spans="1:10">
@@ -8512,10 +8512,10 @@
         <v>8307483260.253226</v>
       </c>
       <c r="I253">
-        <v>57041993686.90788</v>
+        <v>23.23084631291062</v>
       </c>
       <c r="J253">
-        <v>48734510460.46581</v>
+        <v>48.73451046046581</v>
       </c>
     </row>
     <row r="254" spans="1:10">
@@ -8544,10 +8544,10 @@
         <v>36897938038.00629</v>
       </c>
       <c r="I254">
-        <v>57041993674.66484</v>
+        <v>10.98779907556064</v>
       </c>
       <c r="J254">
-        <v>20144055682.71275</v>
+        <v>20.14405568271275</v>
       </c>
     </row>
     <row r="255" spans="1:10">
@@ -8576,10 +8576,10 @@
         <v>146310586.7741867</v>
       </c>
       <c r="I255">
-        <v>57041993686.90788</v>
+        <v>23.23084649573735</v>
       </c>
       <c r="J255">
-        <v>56895683133.94485</v>
+        <v>56.89568313394485</v>
       </c>
     </row>
     <row r="256" spans="1:10">
@@ -8608,10 +8608,10 @@
         <v>31813764464.64191</v>
       </c>
       <c r="I256">
-        <v>57041993678.05471</v>
+        <v>14.3776740271834</v>
       </c>
       <c r="J256">
-        <v>25228229256.07712</v>
+        <v>25.22822925607712</v>
       </c>
     </row>
     <row r="257" spans="1:10">
@@ -8640,10 +8640,10 @@
         <v>22137466702.80694</v>
       </c>
       <c r="I257">
-        <v>57041993682.47943</v>
+        <v>18.80239295054045</v>
       </c>
       <c r="J257">
-        <v>34904527017.91209</v>
+        <v>34.90452701791209</v>
       </c>
     </row>
     <row r="258" spans="1:10">
@@ -8672,10 +8672,10 @@
         <v>26073544036.84365</v>
       </c>
       <c r="I258">
-        <v>57041993682.47943</v>
+        <v>18.80239266196423</v>
       </c>
       <c r="J258">
-        <v>30968449683.87538</v>
+        <v>30.96844968387538</v>
       </c>
     </row>
     <row r="259" spans="1:10">
@@ -8704,10 +8704,10 @@
         <v>39245696417.51408</v>
       </c>
       <c r="I259">
-        <v>57041993674.66484</v>
+        <v>10.98779844442635</v>
       </c>
       <c r="J259">
-        <v>17796297303.20496</v>
+        <v>17.79629730320496</v>
       </c>
     </row>
     <row r="260" spans="1:10">
@@ -8736,10 +8736,10 @@
         <v>32215636884.5281</v>
       </c>
       <c r="I260">
-        <v>57041993678.05471</v>
+        <v>14.37767478341466</v>
       </c>
       <c r="J260">
-        <v>24826356836.19093</v>
+        <v>24.82635683619093</v>
       </c>
     </row>
     <row r="261" spans="1:10">
@@ -8768,10 +8768,10 @@
         <v>6607238953.278423</v>
       </c>
       <c r="I261">
-        <v>57041993686.90788</v>
+        <v>23.23084585584378</v>
       </c>
       <c r="J261">
-        <v>50434754767.44061</v>
+        <v>50.43475476744062</v>
       </c>
     </row>
     <row r="262" spans="1:10">
@@ -8800,10 +8800,10 @@
         <v>20348340641.88115</v>
       </c>
       <c r="I262">
-        <v>57041993682.47943</v>
+        <v>18.80239246958006</v>
       </c>
       <c r="J262">
-        <v>36693653078.83788</v>
+        <v>36.69365307883788</v>
       </c>
     </row>
     <row r="263" spans="1:10">
@@ -8832,10 +8832,10 @@
         <v>30206274785.09723</v>
       </c>
       <c r="I263">
-        <v>57041993678.05471</v>
+        <v>14.37767424324945</v>
       </c>
       <c r="J263">
-        <v>26835718935.6218</v>
+        <v>26.8357189356218</v>
       </c>
     </row>
     <row r="264" spans="1:10">
@@ -8864,10 +8864,10 @@
         <v>42767333986.77576</v>
       </c>
       <c r="I264">
-        <v>57041993674.66483</v>
+        <v>10.98779812885921</v>
       </c>
       <c r="J264">
-        <v>14274659733.94328</v>
+        <v>14.27465973394328</v>
       </c>
     </row>
     <row r="265" spans="1:10">
@@ -8896,10 +8896,10 @@
         <v>16770088520.02958</v>
       </c>
       <c r="I265">
-        <v>57041993682.47943</v>
+        <v>18.80239246958006</v>
       </c>
       <c r="J265">
-        <v>40271905200.68945</v>
+        <v>40.27190520068945</v>
       </c>
     </row>
     <row r="266" spans="1:10">
@@ -8928,10 +8928,10 @@
         <v>33421254144.18663</v>
       </c>
       <c r="I266">
-        <v>57041993678.05471</v>
+        <v>14.3776748914477</v>
       </c>
       <c r="J266">
-        <v>23620739576.5324</v>
+        <v>23.6207395765324</v>
       </c>
     </row>
     <row r="267" spans="1:10">
@@ -8960,10 +8960,10 @@
         <v>40419575607.26797</v>
       </c>
       <c r="I267">
-        <v>57041993674.66484</v>
+        <v>10.98779875999352</v>
       </c>
       <c r="J267">
-        <v>16622418113.45107</v>
+        <v>16.62241811345107</v>
       </c>
     </row>
     <row r="268" spans="1:10">
@@ -8992,10 +8992,10 @@
         <v>36663162200.0555</v>
       </c>
       <c r="I268">
-        <v>57041993674.66483</v>
+        <v>10.98779800263233</v>
       </c>
       <c r="J268">
-        <v>20378831520.66354</v>
+        <v>20.37883152066354</v>
       </c>
     </row>
     <row r="269" spans="1:10">
@@ -9024,10 +9024,10 @@
         <v>6267190091.883459</v>
       </c>
       <c r="I269">
-        <v>57041993686.90788</v>
+        <v>23.2308461300839</v>
       </c>
       <c r="J269">
-        <v>50774803628.83557</v>
+        <v>50.77480362883557</v>
       </c>
     </row>
     <row r="270" spans="1:10">
@@ -9056,10 +9056,10 @@
         <v>2866701477.933868</v>
       </c>
       <c r="I270">
-        <v>57041993686.90788</v>
+        <v>23.23084613008388</v>
       </c>
       <c r="J270">
-        <v>54175292242.78516</v>
+        <v>54.17529224278516</v>
       </c>
     </row>
     <row r="271" spans="1:10">
@@ -9088,10 +9088,10 @@
         <v>13907486822.54833</v>
       </c>
       <c r="I271">
-        <v>57041993682.47943</v>
+        <v>18.8023928543484</v>
       </c>
       <c r="J271">
-        <v>43134506898.1707</v>
+        <v>43.1345068981707</v>
       </c>
     </row>
     <row r="272" spans="1:10">
@@ -9120,10 +9120,10 @@
         <v>12476185973.80771</v>
       </c>
       <c r="I272">
-        <v>57041993682.47943</v>
+        <v>18.80239304673255</v>
       </c>
       <c r="J272">
-        <v>44565807746.91132</v>
+        <v>44.56580774691133</v>
       </c>
     </row>
     <row r="273" spans="1:10">
@@ -9152,10 +9152,10 @@
         <v>38306593065.71097</v>
       </c>
       <c r="I273">
-        <v>57041993674.66484</v>
+        <v>10.98779920178752</v>
       </c>
       <c r="J273">
-        <v>18735400655.00806</v>
+        <v>18.73540065500806</v>
       </c>
     </row>
     <row r="274" spans="1:10">
@@ -9184,10 +9184,10 @@
         <v>12834011185.99287</v>
       </c>
       <c r="I274">
-        <v>57041993682.47943</v>
+        <v>18.8023927581563</v>
       </c>
       <c r="J274">
-        <v>44207982534.72617</v>
+        <v>44.20798253472616</v>
       </c>
     </row>
     <row r="275" spans="1:10">
@@ -9216,10 +9216,10 @@
         <v>25357893612.47334</v>
       </c>
       <c r="I275">
-        <v>57041993682.47943</v>
+        <v>18.80239323911672</v>
       </c>
       <c r="J275">
-        <v>31684100108.24569</v>
+        <v>31.68410010824569</v>
       </c>
     </row>
     <row r="276" spans="1:10">
@@ -9248,10 +9248,10 @@
         <v>5927141230.488508</v>
       </c>
       <c r="I276">
-        <v>57041993686.90788</v>
+        <v>23.23084640432398</v>
       </c>
       <c r="J276">
-        <v>51114852490.23052</v>
+        <v>51.11485249023053</v>
       </c>
     </row>
     <row r="277" spans="1:10">
@@ -9280,10 +9280,10 @@
         <v>46056362757.93286</v>
       </c>
       <c r="I277">
-        <v>57041993673.18262</v>
+        <v>9.505585807988702</v>
       </c>
       <c r="J277">
-        <v>10985630962.78617</v>
+        <v>10.98563096278617</v>
       </c>
     </row>
     <row r="278" spans="1:10">
@@ -9312,10 +9312,10 @@
         <v>31411892044.75574</v>
       </c>
       <c r="I278">
-        <v>57041993678.05471</v>
+        <v>14.37767435128251</v>
       </c>
       <c r="J278">
-        <v>25630101675.96329</v>
+        <v>25.63010167596329</v>
       </c>
     </row>
     <row r="279" spans="1:10">
@@ -9344,10 +9344,10 @@
         <v>39950023931.36641</v>
       </c>
       <c r="I279">
-        <v>57041993674.66484</v>
+        <v>10.98779913867409</v>
       </c>
       <c r="J279">
-        <v>17091969789.35262</v>
+        <v>17.09196978935262</v>
       </c>
     </row>
     <row r="280" spans="1:10">
@@ -9376,10 +9376,10 @@
         <v>43706437338.5789</v>
       </c>
       <c r="I280">
-        <v>57041993674.66484</v>
+        <v>10.98779863376664</v>
       </c>
       <c r="J280">
-        <v>13335556382.14013</v>
+        <v>13.33555638214013</v>
       </c>
     </row>
     <row r="281" spans="1:10">
@@ -9408,10 +9408,10 @@
         <v>3886848062.118744</v>
       </c>
       <c r="I281">
-        <v>57041993686.90788</v>
+        <v>23.23084622149725</v>
       </c>
       <c r="J281">
-        <v>53155145658.60029</v>
+        <v>53.15514565860029</v>
       </c>
     </row>
     <row r="282" spans="1:10">
@@ -9440,10 +9440,10 @@
         <v>41593454797.02186</v>
       </c>
       <c r="I282">
-        <v>57041993674.66484</v>
+        <v>10.98779907556067</v>
       </c>
       <c r="J282">
-        <v>15448538923.69717</v>
+        <v>15.44853892369717</v>
       </c>
     </row>
     <row r="283" spans="1:10">
@@ -9472,10 +9472,10 @@
         <v>18559214580.95537</v>
       </c>
       <c r="I283">
-        <v>57041993682.47943</v>
+        <v>18.80239295054045</v>
       </c>
       <c r="J283">
-        <v>38482779139.76366</v>
+        <v>38.48277913976366</v>
       </c>
     </row>
     <row r="284" spans="1:10">
@@ -9504,10 +9504,10 @@
         <v>17485738944.3999</v>
       </c>
       <c r="I284">
-        <v>57041993682.47943</v>
+        <v>18.80239285434838</v>
       </c>
       <c r="J284">
-        <v>39556254776.31914</v>
+        <v>39.55625477631914</v>
       </c>
     </row>
     <row r="285" spans="1:10">
@@ -9536,10 +9536,10 @@
         <v>33823126564.07281</v>
       </c>
       <c r="I285">
-        <v>57041993678.05471</v>
+        <v>14.37767456734856</v>
       </c>
       <c r="J285">
-        <v>23218867156.64622</v>
+        <v>23.21886715664622</v>
       </c>
     </row>
     <row r="286" spans="1:10">
@@ -9568,10 +9568,10 @@
         <v>3206750339.328827</v>
       </c>
       <c r="I286">
-        <v>57041993686.90788</v>
+        <v>23.23084585584378</v>
       </c>
       <c r="J286">
-        <v>53835243381.39021</v>
+        <v>53.83524338139021</v>
       </c>
     </row>
     <row r="287" spans="1:10">
@@ -9600,10 +9600,10 @@
         <v>6947287814.673388</v>
       </c>
       <c r="I287">
-        <v>57041993686.90788</v>
+        <v>23.23084649573737</v>
       </c>
       <c r="J287">
-        <v>50094705906.04565</v>
+        <v>50.09470590604565</v>
       </c>
     </row>
     <row r="288" spans="1:10">
@@ -9632,10 +9632,10 @@
         <v>43236885662.67732</v>
       </c>
       <c r="I288">
-        <v>57041993674.66484</v>
+        <v>10.98779901244725</v>
       </c>
       <c r="J288">
-        <v>13805108058.04171</v>
+        <v>13.80510805804171</v>
       </c>
     </row>
     <row r="289" spans="1:10">
@@ -9664,10 +9664,10 @@
         <v>23926592763.73272</v>
       </c>
       <c r="I289">
-        <v>57041993682.47943</v>
+        <v>18.80239246958006</v>
       </c>
       <c r="J289">
-        <v>33115400956.98631</v>
+        <v>33.11540095698631</v>
       </c>
     </row>
     <row r="290" spans="1:10">
@@ -9696,10 +9696,10 @@
         <v>4566945784.908664</v>
       </c>
       <c r="I290">
-        <v>57041993686.90788</v>
+        <v>23.23084658715072</v>
       </c>
       <c r="J290">
-        <v>52475047935.81037</v>
+        <v>52.47504793581037</v>
       </c>
     </row>
     <row r="291" spans="1:10">
@@ -9728,10 +9728,10 @@
         <v>44645540690.38201</v>
       </c>
       <c r="I291">
-        <v>57041993674.66484</v>
+        <v>10.98779913867409</v>
       </c>
       <c r="J291">
-        <v>12396453030.33702</v>
+        <v>12.39645303033702</v>
       </c>
     </row>
     <row r="292" spans="1:10">
@@ -9760,10 +9760,10 @@
         <v>13549661610.36318</v>
       </c>
       <c r="I292">
-        <v>57041993682.47943</v>
+        <v>18.80239314292462</v>
       </c>
       <c r="J292">
-        <v>43492332110.35585</v>
+        <v>43.49233211035585</v>
       </c>
     </row>
     <row r="293" spans="1:10">
@@ -9792,10 +9792,10 @@
         <v>16412263307.84443</v>
       </c>
       <c r="I293">
-        <v>57041993682.47943</v>
+        <v>18.8023927581563</v>
       </c>
       <c r="J293">
-        <v>40629730412.8746</v>
+        <v>40.6297304128746</v>
       </c>
     </row>
     <row r="294" spans="1:10">
@@ -9824,10 +9824,10 @@
         <v>19632690217.51083</v>
       </c>
       <c r="I294">
-        <v>57041993682.47943</v>
+        <v>18.80239304673255</v>
       </c>
       <c r="J294">
-        <v>37409303503.20821</v>
+        <v>37.40930350320821</v>
       </c>
     </row>
     <row r="295" spans="1:10">
@@ -9856,10 +9856,10 @@
         <v>14623137246.91864</v>
       </c>
       <c r="I295">
-        <v>57041993682.47943</v>
+        <v>18.80239323911672</v>
       </c>
       <c r="J295">
-        <v>42418856473.80039</v>
+        <v>42.41885647380039</v>
       </c>
     </row>
     <row r="296" spans="1:10">
@@ -9888,10 +9888,10 @@
         <v>37367489713.90783</v>
       </c>
       <c r="I296">
-        <v>57041993674.66484</v>
+        <v>10.98779869688008</v>
       </c>
       <c r="J296">
-        <v>19674504006.8112</v>
+        <v>19.6745040068112</v>
       </c>
     </row>
     <row r="297" spans="1:10">
@@ -9920,10 +9920,10 @@
         <v>38776144741.61252</v>
       </c>
       <c r="I297">
-        <v>57041993674.66484</v>
+        <v>10.98779882310694</v>
       </c>
       <c r="J297">
-        <v>18265848979.10651</v>
+        <v>18.26584897910652</v>
       </c>
     </row>
     <row r="298" spans="1:10">
@@ -9952,10 +9952,10 @@
         <v>37602265551.8586</v>
       </c>
       <c r="I298">
-        <v>57041993674.66484</v>
+        <v>10.98779850753981</v>
       </c>
       <c r="J298">
-        <v>19439728168.86044</v>
+        <v>19.43972816886043</v>
       </c>
     </row>
     <row r="299" spans="1:10">
@@ -9984,10 +9984,10 @@
         <v>21779641490.62178</v>
       </c>
       <c r="I299">
-        <v>57041993682.47943</v>
+        <v>18.80239323911672</v>
       </c>
       <c r="J299">
-        <v>35262352230.09725</v>
+        <v>35.26235223009725</v>
       </c>
     </row>
     <row r="300" spans="1:10">
@@ -10016,10 +10016,10 @@
         <v>48129067150.88944</v>
       </c>
       <c r="I300">
-        <v>57041993672.58997</v>
+        <v>8.912926569829594</v>
       </c>
       <c r="J300">
-        <v>8912926569.82959</v>
+        <v>8.91292656982959</v>
       </c>
     </row>
     <row r="301" spans="1:10">
@@ -10048,10 +10048,10 @@
         <v>33019381724.30045</v>
       </c>
       <c r="I301">
-        <v>57041993678.05471</v>
+        <v>14.37767413521644</v>
       </c>
       <c r="J301">
-        <v>24022611996.41858</v>
+        <v>24.02261199641858</v>
       </c>
     </row>
     <row r="302" spans="1:10">
@@ -10080,10 +10080,10 @@
         <v>1166457170.959064</v>
       </c>
       <c r="I302">
-        <v>57041993686.90788</v>
+        <v>23.23084658715072</v>
       </c>
       <c r="J302">
-        <v>55875536549.75997</v>
+        <v>55.87553654975997</v>
       </c>
     </row>
     <row r="303" spans="1:10">
@@ -10112,10 +10112,10 @@
         <v>44410764852.43124</v>
       </c>
       <c r="I303">
-        <v>57041993674.66483</v>
+        <v>10.98779806574577</v>
       </c>
       <c r="J303">
-        <v>12631228868.2878</v>
+        <v>12.6312288682878</v>
       </c>
     </row>
     <row r="304" spans="1:10">
@@ -10144,10 +10144,10 @@
         <v>24642243188.10304</v>
       </c>
       <c r="I304">
-        <v>57041993682.47943</v>
+        <v>18.80239285434838</v>
       </c>
       <c r="J304">
-        <v>32399750532.61599</v>
+        <v>32.399750532616</v>
       </c>
     </row>
     <row r="305" spans="1:10">
@@ -10176,10 +10176,10 @@
         <v>14980962459.10381</v>
       </c>
       <c r="I305">
-        <v>57041993682.47943</v>
+        <v>18.80239295054047</v>
       </c>
       <c r="J305">
-        <v>42061031261.61522</v>
+        <v>42.06103126161522</v>
       </c>
     </row>
     <row r="306" spans="1:10">
@@ -10208,10 +10208,10 @@
         <v>17843564156.58506</v>
       </c>
       <c r="I306">
-        <v>57041993682.47943</v>
+        <v>18.80239256577214</v>
       </c>
       <c r="J306">
-        <v>39198429564.13397</v>
+        <v>39.19842956413397</v>
       </c>
     </row>
     <row r="307" spans="1:10">
@@ -10240,10 +10240,10 @@
         <v>2526652616.538904</v>
       </c>
       <c r="I307">
-        <v>57041993686.90788</v>
+        <v>23.230846404324</v>
       </c>
       <c r="J307">
-        <v>54515341104.18013</v>
+        <v>54.51534110418013</v>
       </c>
     </row>
     <row r="308" spans="1:10">
@@ -10272,10 +10272,10 @@
         <v>15696612883.47412</v>
       </c>
       <c r="I308">
-        <v>57041993682.47943</v>
+        <v>18.80239333530879</v>
       </c>
       <c r="J308">
-        <v>41345380837.24491</v>
+        <v>41.34538083724491</v>
       </c>
     </row>
     <row r="309" spans="1:10">
@@ -10304,10 +10304,10 @@
         <v>5587092369.093546</v>
       </c>
       <c r="I309">
-        <v>57041993686.90788</v>
+        <v>23.23084667856409</v>
       </c>
       <c r="J309">
-        <v>51454901351.62549</v>
+        <v>51.45490135162549</v>
       </c>
     </row>
     <row r="310" spans="1:10">
@@ -10336,10 +10336,10 @@
         <v>18201389368.77021</v>
       </c>
       <c r="I310">
-        <v>57041993682.47943</v>
+        <v>18.80239323911672</v>
       </c>
       <c r="J310">
-        <v>38840604351.94882</v>
+        <v>38.84060435194882</v>
       </c>
     </row>
     <row r="311" spans="1:10">
@@ -10368,10 +10368,10 @@
         <v>42297782310.87421</v>
       </c>
       <c r="I311">
-        <v>57041993674.66484</v>
+        <v>10.98779850753977</v>
       </c>
       <c r="J311">
-        <v>14744211409.84483</v>
+        <v>14.74421140984483</v>
       </c>
     </row>
     <row r="312" spans="1:10">
@@ -10400,10 +10400,10 @@
         <v>4226896923.513704</v>
       </c>
       <c r="I312">
-        <v>57041993686.90788</v>
+        <v>23.23084594725715</v>
       </c>
       <c r="J312">
-        <v>52815096797.20533</v>
+        <v>52.81509679720533</v>
       </c>
     </row>
     <row r="313" spans="1:10">
@@ -10432,10 +10432,10 @@
         <v>5247043507.698585</v>
       </c>
       <c r="I313">
-        <v>57041993686.90788</v>
+        <v>23.23084603867053</v>
       </c>
       <c r="J313">
-        <v>51794950213.02045</v>
+        <v>51.79495021302045</v>
       </c>
     </row>
     <row r="314" spans="1:10">
@@ -10464,10 +10464,10 @@
         <v>46796385932.14005</v>
       </c>
       <c r="I314">
-        <v>57041993673.18262</v>
+        <v>9.505585211180247</v>
       </c>
       <c r="J314">
-        <v>10245607788.57898</v>
+        <v>10.24560778857898</v>
       </c>
     </row>
     <row r="315" spans="1:10">
@@ -10496,10 +10496,10 @@
         <v>13191836398.17803</v>
       </c>
       <c r="I315">
-        <v>57041993682.47943</v>
+        <v>18.80239246958006</v>
       </c>
       <c r="J315">
-        <v>43850157322.541</v>
+        <v>43.850157322541</v>
       </c>
     </row>
     <row r="316" spans="1:10">
@@ -10528,10 +10528,10 @@
         <v>19990515429.69599</v>
       </c>
       <c r="I316">
-        <v>57041993682.47943</v>
+        <v>18.80239275815632</v>
       </c>
       <c r="J316">
-        <v>37051478291.02304</v>
+        <v>37.05147829102304</v>
       </c>
     </row>
     <row r="317" spans="1:10">
@@ -10560,10 +10560,10 @@
         <v>2186603755.14395</v>
       </c>
       <c r="I317">
-        <v>57041993686.90788</v>
+        <v>23.23084667856409</v>
       </c>
       <c r="J317">
-        <v>54855389965.57508</v>
+        <v>54.85538996557508</v>
       </c>
     </row>
     <row r="318" spans="1:10">
@@ -10592,10 +10592,10 @@
         <v>47166397519.24362</v>
       </c>
       <c r="I318">
-        <v>57041993673.18262</v>
+        <v>9.505584912776044</v>
       </c>
       <c r="J318">
-        <v>9875596201.47541</v>
+        <v>9.87559620147541</v>
       </c>
     </row>
     <row r="319" spans="1:10">
@@ -10624,10 +10624,10 @@
         <v>30608147204.9834</v>
       </c>
       <c r="I319">
-        <v>57041993678.05471</v>
+        <v>14.37767391915035</v>
       </c>
       <c r="J319">
-        <v>26433846515.73563</v>
+        <v>26.43384651573563</v>
       </c>
     </row>
     <row r="320" spans="1:10">
@@ -10656,10 +10656,10 @@
         <v>14265312034.73349</v>
       </c>
       <c r="I320">
-        <v>57041993682.47943</v>
+        <v>18.80239256577214</v>
       </c>
       <c r="J320">
-        <v>42776681685.98554</v>
+        <v>42.77668168598554</v>
       </c>
     </row>
     <row r="321" spans="1:10">
@@ -10688,10 +10688,10 @@
         <v>18917039793.14053</v>
       </c>
       <c r="I321">
-        <v>57041993682.47943</v>
+        <v>18.80239266196423</v>
       </c>
       <c r="J321">
-        <v>38124953927.57851</v>
+        <v>38.12495392757851</v>
       </c>
     </row>
     <row r="322" spans="1:10">
@@ -10720,10 +10720,10 @@
         <v>23210942339.36241</v>
       </c>
       <c r="I322">
-        <v>57041993682.47943</v>
+        <v>18.80239304673255</v>
       </c>
       <c r="J322">
-        <v>33831051381.35662</v>
+        <v>33.83105138135662</v>
       </c>
     </row>
     <row r="323" spans="1:10">
@@ -10752,10 +10752,10 @@
         <v>22853117127.17725</v>
       </c>
       <c r="I323">
-        <v>57041993682.47943</v>
+        <v>18.80239333530879</v>
       </c>
       <c r="J323">
-        <v>34188876593.54178</v>
+        <v>34.18887659354179</v>
       </c>
     </row>
     <row r="324" spans="1:10">
@@ -10784,10 +10784,10 @@
         <v>29402529945.32487</v>
       </c>
       <c r="I324">
-        <v>57041993678.05471</v>
+        <v>14.3776748914477</v>
       </c>
       <c r="J324">
-        <v>27639463775.39416</v>
+        <v>27.63946377539416</v>
       </c>
     </row>
     <row r="325" spans="1:10">
@@ -10816,10 +10816,10 @@
         <v>39715248093.41564</v>
       </c>
       <c r="I325">
-        <v>57041993674.66483</v>
+        <v>10.98779806574577</v>
       </c>
       <c r="J325">
-        <v>17326745627.30339</v>
+        <v>17.32674562730339</v>
       </c>
     </row>
     <row r="326" spans="1:10">
@@ -10848,10 +10848,10 @@
         <v>21421816278.43662</v>
       </c>
       <c r="I326">
-        <v>57041993682.47943</v>
+        <v>18.80239256577214</v>
       </c>
       <c r="J326">
-        <v>35620177442.28241</v>
+        <v>35.62017744228241</v>
       </c>
     </row>
     <row r="327" spans="1:10">
@@ -10880,10 +10880,10 @@
         <v>40889127283.16953</v>
       </c>
       <c r="I327">
-        <v>57041993674.66484</v>
+        <v>10.98779838131293</v>
       </c>
       <c r="J327">
-        <v>16152866437.5495</v>
+        <v>16.1528664375495</v>
       </c>
     </row>
     <row r="328" spans="1:10">
@@ -10912,10 +10912,10 @@
         <v>37837041389.8094</v>
       </c>
       <c r="I328">
-        <v>57041993674.66484</v>
+        <v>10.98779831819949</v>
       </c>
       <c r="J328">
-        <v>19204952330.90963</v>
+        <v>19.20495233090963</v>
       </c>
     </row>
     <row r="329" spans="1:10">
@@ -10944,10 +10944,10 @@
         <v>7627385537.463311</v>
       </c>
       <c r="I329">
-        <v>57041993686.90788</v>
+        <v>23.23084594725714</v>
       </c>
       <c r="J329">
-        <v>49414608183.25572</v>
+        <v>49.41460818325572</v>
       </c>
     </row>
     <row r="330" spans="1:10">
@@ -10976,10 +10976,10 @@
         <v>44175989014.48045</v>
       </c>
       <c r="I330">
-        <v>57041993674.66483</v>
+        <v>10.98779825508606</v>
       </c>
       <c r="J330">
-        <v>12866004706.23858</v>
+        <v>12.86600470623858</v>
       </c>
     </row>
     <row r="331" spans="1:10">
@@ -11008,10 +11008,10 @@
         <v>25000068400.28819</v>
       </c>
       <c r="I331">
-        <v>57041993682.47943</v>
+        <v>18.80239256577214</v>
       </c>
       <c r="J331">
-        <v>32041925320.43084</v>
+        <v>32.04192532043084</v>
       </c>
     </row>
     <row r="332" spans="1:10">
@@ -11040,10 +11040,10 @@
         <v>39010920579.56329</v>
       </c>
       <c r="I332">
-        <v>57041993674.66484</v>
+        <v>10.98779863376665</v>
       </c>
       <c r="J332">
-        <v>18031073141.15574</v>
+        <v>18.03107314115574</v>
       </c>
     </row>
     <row r="333" spans="1:10">
@@ -11072,10 +11072,10 @@
         <v>41123903121.12032</v>
       </c>
       <c r="I333">
-        <v>57041993674.66483</v>
+        <v>10.98779819197264</v>
       </c>
       <c r="J333">
-        <v>15918090599.59871</v>
+        <v>15.91809059959871</v>
       </c>
     </row>
     <row r="334" spans="1:10">
@@ -11104,10 +11104,10 @@
         <v>39480472255.46486</v>
       </c>
       <c r="I334">
-        <v>57041993674.66483</v>
+        <v>10.98779825508606</v>
       </c>
       <c r="J334">
-        <v>17561521465.25417</v>
+        <v>17.56152146525417</v>
       </c>
     </row>
     <row r="335" spans="1:10">
@@ -11136,10 +11136,10 @@
         <v>21063991066.25146</v>
       </c>
       <c r="I335">
-        <v>57041993682.47943</v>
+        <v>18.80239285434838</v>
       </c>
       <c r="J335">
-        <v>35978002654.46758</v>
+        <v>35.97800265446757</v>
       </c>
     </row>
     <row r="336" spans="1:10">
@@ -11168,10 +11168,10 @@
         <v>7287336676.068351</v>
       </c>
       <c r="I336">
-        <v>57041993686.90788</v>
+        <v>23.23084622149725</v>
       </c>
       <c r="J336">
-        <v>49754657044.65068</v>
+        <v>49.75465704465068</v>
       </c>
     </row>
     <row r="337" spans="1:10">
@@ -11200,10 +11200,10 @@
         <v>42532558148.82499</v>
       </c>
       <c r="I337">
-        <v>57041993674.66484</v>
+        <v>10.9877983181995</v>
       </c>
       <c r="J337">
-        <v>14509435571.89404</v>
+        <v>14.50943557189404</v>
       </c>
     </row>
     <row r="338" spans="1:10">
@@ -11232,10 +11232,10 @@
         <v>25715718824.6585</v>
       </c>
       <c r="I338">
-        <v>57041993682.47943</v>
+        <v>18.80239295054045</v>
       </c>
       <c r="J338">
-        <v>31326274896.06053</v>
+        <v>31.32627489606053</v>
       </c>
     </row>
     <row r="339" spans="1:10">
@@ -11264,10 +11264,10 @@
         <v>24284417975.91787</v>
       </c>
       <c r="I339">
-        <v>57041993682.47943</v>
+        <v>18.80239314292462</v>
       </c>
       <c r="J339">
-        <v>32757575744.80116</v>
+        <v>32.75757574480117</v>
       </c>
     </row>
     <row r="340" spans="1:10">
@@ -11296,10 +11296,10 @@
         <v>15338787671.28896</v>
       </c>
       <c r="I340">
-        <v>57041993682.47943</v>
+        <v>18.80239266196423</v>
       </c>
       <c r="J340">
-        <v>41703206049.43007</v>
+        <v>41.70320604943007</v>
       </c>
     </row>
     <row r="341" spans="1:10">
@@ -11328,10 +11328,10 @@
         <v>42063006472.92344</v>
       </c>
       <c r="I341">
-        <v>57041993674.66484</v>
+        <v>10.98779869688008</v>
       </c>
       <c r="J341">
-        <v>14978987247.79559</v>
+        <v>14.97898724779559</v>
       </c>
     </row>
     <row r="342" spans="1:10">
@@ -11360,10 +11360,10 @@
         <v>4906994646.303631</v>
       </c>
       <c r="I342">
-        <v>57041993686.90788</v>
+        <v>23.23084631291061</v>
       </c>
       <c r="J342">
-        <v>52134999074.41541</v>
+        <v>52.1349990744154</v>
       </c>
     </row>
     <row r="343" spans="1:10">
@@ -11392,10 +11392,10 @@
         <v>486359448.1691473</v>
       </c>
       <c r="I343">
-        <v>57041993686.90788</v>
+        <v>23.23084622149725</v>
       </c>
       <c r="J343">
-        <v>56555634272.54989</v>
+        <v>56.55563427254989</v>
       </c>
     </row>
     <row r="344" spans="1:10">
@@ -11424,10 +11424,10 @@
         <v>7967434398.858269</v>
       </c>
       <c r="I344">
-        <v>57041993686.90788</v>
+        <v>23.23084658715072</v>
       </c>
       <c r="J344">
-        <v>49074559321.86076</v>
+        <v>49.07455932186076</v>
       </c>
     </row>
     <row r="345" spans="1:10">
@@ -11456,10 +11456,10 @@
         <v>17127913732.21474</v>
       </c>
       <c r="I345">
-        <v>57041993682.47943</v>
+        <v>18.80239314292462</v>
       </c>
       <c r="J345">
-        <v>39914079988.50429</v>
+        <v>39.91407998850429</v>
       </c>
     </row>
     <row r="346" spans="1:10">
@@ -11488,10 +11488,10 @@
         <v>38541368903.66174</v>
       </c>
       <c r="I346">
-        <v>57041993674.66484</v>
+        <v>10.98779901244723</v>
       </c>
       <c r="J346">
-        <v>18500624817.05729</v>
+        <v>18.50062481705729</v>
       </c>
     </row>
     <row r="347" spans="1:10">
@@ -11520,10 +11520,10 @@
         <v>41358678959.0711</v>
       </c>
       <c r="I347">
-        <v>57041993674.66483</v>
+        <v>10.98779800263233</v>
       </c>
       <c r="J347">
-        <v>15683314761.64793</v>
+        <v>15.68331476164793</v>
       </c>
     </row>
     <row r="348" spans="1:10">
@@ -11552,10 +11552,10 @@
         <v>8647532121.648191</v>
       </c>
       <c r="I348">
-        <v>57041993686.90788</v>
+        <v>23.23084603867051</v>
       </c>
       <c r="J348">
-        <v>48394461599.07084</v>
+        <v>48.39446159907084</v>
       </c>
     </row>
     <row r="349" spans="1:10">
@@ -11584,10 +11584,10 @@
         <v>31010019624.86958</v>
       </c>
       <c r="I349">
-        <v>57041993678.05471</v>
+        <v>14.37767467538163</v>
       </c>
       <c r="J349">
-        <v>26031974095.84945</v>
+        <v>26.03197409584945</v>
       </c>
     </row>
     <row r="350" spans="1:10">
@@ -11616,10 +11616,10 @@
         <v>40184799769.31719</v>
       </c>
       <c r="I350">
-        <v>57041993674.66484</v>
+        <v>10.98779894933379</v>
       </c>
       <c r="J350">
-        <v>16857193951.40184</v>
+        <v>16.85719395140184</v>
       </c>
     </row>
     <row r="351" spans="1:10">
@@ -11648,10 +11648,10 @@
         <v>24981933326.57693</v>
       </c>
       <c r="I351">
-        <v>57041993678.05471</v>
+        <v>14.37767413521644</v>
       </c>
       <c r="J351">
-        <v>32060060394.1421</v>
+        <v>32.0600603941421</v>
       </c>
     </row>
     <row r="352" spans="1:10">
@@ -11680,10 +11680,10 @@
         <v>26187550586.23547</v>
       </c>
       <c r="I352">
-        <v>57041993678.05471</v>
+        <v>14.37767424324945</v>
       </c>
       <c r="J352">
-        <v>30854443134.48356</v>
+        <v>30.85444313448356</v>
       </c>
     </row>
     <row r="353" spans="1:10">
@@ -11712,10 +11712,10 @@
         <v>30654437105.30693</v>
       </c>
       <c r="I353">
-        <v>57041993674.66629</v>
+        <v>10.98925431859293</v>
       </c>
       <c r="J353">
-        <v>26387556615.4121</v>
+        <v>26.3875566154121</v>
       </c>
     </row>
     <row r="354" spans="1:10">
@@ -11744,10 +11744,10 @@
         <v>3530555669.178797</v>
       </c>
       <c r="I354">
-        <v>57041993682.47943</v>
+        <v>18.80239256577214</v>
       </c>
       <c r="J354">
-        <v>53511438051.54024</v>
+        <v>53.51143805154024</v>
       </c>
     </row>
     <row r="355" spans="1:10">
@@ -11776,10 +11776,10 @@
         <v>4246206093.549111</v>
       </c>
       <c r="I355">
-        <v>57041993682.47943</v>
+        <v>18.80239295054047</v>
       </c>
       <c r="J355">
-        <v>52795787627.16992</v>
+        <v>52.79578762716992</v>
       </c>
     </row>
     <row r="356" spans="1:10">
@@ -11808,10 +11808,10 @@
         <v>21365081547.60135</v>
       </c>
       <c r="I356">
-        <v>57041993678.05471</v>
+        <v>14.3776748914477</v>
       </c>
       <c r="J356">
-        <v>35676912173.11768</v>
+        <v>35.67691217311769</v>
       </c>
     </row>
     <row r="357" spans="1:10">
@@ -11840,10 +11840,10 @@
         <v>13327633149.87783</v>
       </c>
       <c r="I357">
-        <v>57041993678.05471</v>
+        <v>14.3776748914477</v>
       </c>
       <c r="J357">
-        <v>43714360570.8412</v>
+        <v>43.7143605708412</v>
       </c>
     </row>
     <row r="358" spans="1:10">
@@ -11872,10 +11872,10 @@
         <v>40518975011.42419</v>
       </c>
       <c r="I358">
-        <v>57041993674.66629</v>
+        <v>10.98925412455685</v>
       </c>
       <c r="J358">
-        <v>16523018709.29485</v>
+        <v>16.52301870929485</v>
       </c>
     </row>
     <row r="359" spans="1:10">
@@ -11904,10 +11904,10 @@
         <v>22972571227.14606</v>
       </c>
       <c r="I359">
-        <v>57041993678.05471</v>
+        <v>14.37767467538163</v>
       </c>
       <c r="J359">
-        <v>34069422493.57297</v>
+        <v>34.06942249357297</v>
       </c>
     </row>
     <row r="360" spans="1:10">
@@ -11936,10 +11936,10 @@
         <v>45641164374.07758</v>
       </c>
       <c r="I360">
-        <v>57041993670.169</v>
+        <v>6.491956992568277</v>
       </c>
       <c r="J360">
-        <v>11400829346.64145</v>
+        <v>11.40082934664145</v>
       </c>
     </row>
     <row r="361" spans="1:10">
@@ -11968,10 +11968,10 @@
         <v>37872391670.75858</v>
       </c>
       <c r="I361">
-        <v>57041993674.66629</v>
+        <v>10.98925367180596</v>
       </c>
       <c r="J361">
-        <v>19169602049.96045</v>
+        <v>19.16960204996045</v>
       </c>
     </row>
     <row r="362" spans="1:10">
@@ -12000,10 +12000,10 @@
         <v>6897674431.699013</v>
       </c>
       <c r="I362">
-        <v>57041993678.05471</v>
+        <v>14.37767467538163</v>
       </c>
       <c r="J362">
-        <v>50144319289.02002</v>
+        <v>50.14431928902002</v>
       </c>
     </row>
     <row r="363" spans="1:10">
@@ -12032,10 +12032,10 @@
         <v>49749699482.47138</v>
       </c>
       <c r="I363">
-        <v>57041993668.73146</v>
+        <v>5.054422243882897</v>
       </c>
       <c r="J363">
-        <v>7292294238.24765</v>
+        <v>7.29229423824765</v>
       </c>
     </row>
     <row r="364" spans="1:10">
@@ -12064,10 +12064,10 @@
         <v>42517335519.95004</v>
       </c>
       <c r="I364">
-        <v>57041993670.169</v>
+        <v>6.491957112534081</v>
       </c>
       <c r="J364">
-        <v>14524658200.76899</v>
+        <v>14.52465820076899</v>
       </c>
     </row>
     <row r="365" spans="1:10">
@@ -12096,10 +12096,10 @@
         <v>35947603786.63813</v>
       </c>
       <c r="I365">
-        <v>57041993674.66629</v>
+        <v>10.98925393052077</v>
       </c>
       <c r="J365">
-        <v>21094389934.0809</v>
+        <v>21.0943899340809</v>
       </c>
     </row>
     <row r="366" spans="1:10">
@@ -12128,10 +12128,10 @@
         <v>48257783616.37225</v>
       </c>
       <c r="I366">
-        <v>57041993668.73146</v>
+        <v>5.054423447072182</v>
       </c>
       <c r="J366">
-        <v>8784210104.346779</v>
+        <v>8.784210104346778</v>
       </c>
     </row>
     <row r="367" spans="1:10">
@@ -12160,10 +12160,10 @@
         <v>46533686903.82831</v>
       </c>
       <c r="I367">
-        <v>57041993670.16899</v>
+        <v>6.491956272773272</v>
       </c>
       <c r="J367">
-        <v>10508306816.89072</v>
+        <v>10.50830681689072</v>
       </c>
     </row>
     <row r="368" spans="1:10">
@@ -12192,10 +12192,10 @@
         <v>44748641844.32686</v>
       </c>
       <c r="I368">
-        <v>57041993670.169</v>
+        <v>6.491957712363252</v>
       </c>
       <c r="J368">
-        <v>12293351876.39217</v>
+        <v>12.29335187639217</v>
       </c>
     </row>
     <row r="369" spans="1:10">
@@ -12224,10 +12224,10 @@
         <v>4888312332.268147</v>
       </c>
       <c r="I369">
-        <v>57041993678.05471</v>
+        <v>14.37767413521642</v>
       </c>
       <c r="J369">
-        <v>52153681388.45088</v>
+        <v>52.15368138845088</v>
       </c>
     </row>
     <row r="370" spans="1:10">
@@ -12256,10 +12256,10 @@
         <v>34022815902.5177</v>
       </c>
       <c r="I370">
-        <v>57041993674.66629</v>
+        <v>10.98925418923555</v>
       </c>
       <c r="J370">
-        <v>23019177818.20133</v>
+        <v>23.01917781820133</v>
       </c>
     </row>
     <row r="371" spans="1:10">
@@ -12288,10 +12288,10 @@
         <v>36909997728.69836</v>
       </c>
       <c r="I371">
-        <v>57041993674.66629</v>
+        <v>10.98925444795034</v>
       </c>
       <c r="J371">
-        <v>20131995992.02068</v>
+        <v>20.13199599202068</v>
       </c>
     </row>
     <row r="372" spans="1:10">
@@ -12320,10 +12320,10 @@
         <v>17748229768.62577</v>
       </c>
       <c r="I372">
-        <v>57041993678.05471</v>
+        <v>14.37767456734858</v>
       </c>
       <c r="J372">
-        <v>39293763952.09326</v>
+        <v>39.29376395209326</v>
       </c>
     </row>
     <row r="373" spans="1:10">
@@ -12352,10 +12352,10 @@
         <v>12523888310.10548</v>
       </c>
       <c r="I373">
-        <v>57041993678.05471</v>
+        <v>14.37767445931554</v>
       </c>
       <c r="J373">
-        <v>44518105410.61356</v>
+        <v>44.51810541061356</v>
       </c>
     </row>
     <row r="374" spans="1:10">
@@ -12384,10 +12384,10 @@
         <v>36669399243.18331</v>
       </c>
       <c r="I374">
-        <v>57041993674.66629</v>
+        <v>10.98925464198643</v>
       </c>
       <c r="J374">
-        <v>20372594477.53572</v>
+        <v>20.37259447753572</v>
       </c>
     </row>
     <row r="375" spans="1:10">
@@ -12416,10 +12416,10 @@
         <v>2814905244.808493</v>
       </c>
       <c r="I375">
-        <v>57041993682.47943</v>
+        <v>18.80239314292462</v>
       </c>
       <c r="J375">
-        <v>54227088475.91054</v>
+        <v>54.22708847591053</v>
       </c>
     </row>
     <row r="376" spans="1:10">
@@ -12448,10 +12448,10 @@
         <v>33060421960.45748</v>
       </c>
       <c r="I376">
-        <v>57041993674.66629</v>
+        <v>10.98925367180595</v>
       </c>
       <c r="J376">
-        <v>23981571760.26155</v>
+        <v>23.98157176026155</v>
       </c>
     </row>
     <row r="377" spans="1:10">
@@ -12480,10 +12480,10 @@
         <v>24580060906.69076</v>
       </c>
       <c r="I377">
-        <v>57041993678.05471</v>
+        <v>14.37767445931554</v>
       </c>
       <c r="J377">
-        <v>32461932814.02827</v>
+        <v>32.46193281402827</v>
       </c>
     </row>
     <row r="378" spans="1:10">
@@ -12512,10 +12512,10 @@
         <v>29464394422.4053</v>
       </c>
       <c r="I378">
-        <v>57041993675.33239</v>
+        <v>11.65535048751769</v>
       </c>
       <c r="J378">
-        <v>27577599298.31373</v>
+        <v>27.57759929831373</v>
       </c>
     </row>
     <row r="379" spans="1:10">
@@ -12544,10 +12544,10 @@
         <v>39075384098.33385</v>
       </c>
       <c r="I379">
-        <v>57041993674.66629</v>
+        <v>10.98925399519946</v>
       </c>
       <c r="J379">
-        <v>17966609622.38519</v>
+        <v>17.96660962238519</v>
       </c>
     </row>
     <row r="380" spans="1:10">
@@ -12576,10 +12576,10 @@
         <v>33541618931.48759</v>
       </c>
       <c r="I380">
-        <v>57041993674.66629</v>
+        <v>10.98925457730773</v>
       </c>
       <c r="J380">
-        <v>23500374789.23144</v>
+        <v>23.50037478923144</v>
       </c>
     </row>
     <row r="381" spans="1:10">
@@ -12608,10 +12608,10 @@
         <v>10514526210.67459</v>
       </c>
       <c r="I381">
-        <v>57041993678.05471</v>
+        <v>14.37767391915035</v>
       </c>
       <c r="J381">
-        <v>46527467510.04444</v>
+        <v>46.52746751004444</v>
       </c>
     </row>
     <row r="382" spans="1:10">
@@ -12640,10 +12640,10 @@
         <v>22570698807.25988</v>
       </c>
       <c r="I382">
-        <v>57041993678.05471</v>
+        <v>14.37767391915035</v>
       </c>
       <c r="J382">
-        <v>34471294913.45915</v>
+        <v>34.47129491345915</v>
       </c>
     </row>
     <row r="383" spans="1:10">
@@ -12672,10 +12672,10 @@
         <v>31135634076.33704</v>
       </c>
       <c r="I383">
-        <v>57041993674.66629</v>
+        <v>10.98925393052075</v>
       </c>
       <c r="J383">
-        <v>25906359644.38199</v>
+        <v>25.90635964438199</v>
       </c>
     </row>
     <row r="384" spans="1:10">
@@ -12704,10 +12704,10 @@
         <v>44302380579.45149</v>
       </c>
       <c r="I384">
-        <v>57041993670.16899</v>
+        <v>6.491955672944087</v>
       </c>
       <c r="J384">
-        <v>12739613141.26754</v>
+        <v>12.73961314126754</v>
       </c>
     </row>
     <row r="385" spans="1:10">
@@ -12736,10 +12736,10 @@
         <v>18551974608.39812</v>
       </c>
       <c r="I385">
-        <v>57041993678.05471</v>
+        <v>14.37767391915035</v>
       </c>
       <c r="J385">
-        <v>38490019112.32091</v>
+        <v>38.49001911232091</v>
       </c>
     </row>
     <row r="386" spans="1:10">
@@ -12768,10 +12768,10 @@
         <v>34985209844.57792</v>
       </c>
       <c r="I386">
-        <v>57041993674.66629</v>
+        <v>10.98925470666514</v>
       </c>
       <c r="J386">
-        <v>22056783876.14111</v>
+        <v>22.05678387614111</v>
       </c>
     </row>
     <row r="387" spans="1:10">
@@ -12800,10 +12800,10 @@
         <v>40278376525.90914</v>
       </c>
       <c r="I387">
-        <v>57041993674.66629</v>
+        <v>10.98925431859294</v>
       </c>
       <c r="J387">
-        <v>16763617194.80989</v>
+        <v>16.76361719480989</v>
       </c>
     </row>
     <row r="388" spans="1:10">
@@ -12832,10 +12832,10 @@
         <v>36428800757.66826</v>
       </c>
       <c r="I388">
-        <v>57041993674.66629</v>
+        <v>10.98925354244855</v>
       </c>
       <c r="J388">
-        <v>20613192963.05077</v>
+        <v>20.61319296305077</v>
       </c>
     </row>
     <row r="389" spans="1:10">
@@ -12864,10 +12864,10 @@
         <v>10112653790.78842</v>
       </c>
       <c r="I389">
-        <v>57041993678.05471</v>
+        <v>14.37767424324945</v>
       </c>
       <c r="J389">
-        <v>46929339929.93061</v>
+        <v>46.92933992993061</v>
       </c>
     </row>
     <row r="390" spans="1:10">
@@ -12896,10 +12896,10 @@
         <v>6093929591.926661</v>
       </c>
       <c r="I390">
-        <v>57041993678.05471</v>
+        <v>14.37767424324947</v>
       </c>
       <c r="J390">
-        <v>50948064128.79237</v>
+        <v>50.94806412879237</v>
       </c>
     </row>
     <row r="391" spans="1:10">
@@ -12928,10 +12928,10 @@
         <v>15336995249.30871</v>
       </c>
       <c r="I391">
-        <v>57041993678.05471</v>
+        <v>14.37767435128249</v>
       </c>
       <c r="J391">
-        <v>41704998471.41032</v>
+        <v>41.70499847141033</v>
       </c>
     </row>
     <row r="392" spans="1:10">
@@ -12960,10 +12960,10 @@
         <v>13729505569.76401</v>
       </c>
       <c r="I392">
-        <v>57041993678.05471</v>
+        <v>14.37767456734858</v>
       </c>
       <c r="J392">
-        <v>43312488150.95502</v>
+        <v>43.31248815095503</v>
       </c>
     </row>
     <row r="393" spans="1:10">
@@ -12992,10 +12992,10 @@
         <v>38112990156.27367</v>
       </c>
       <c r="I393">
-        <v>57041993674.66629</v>
+        <v>10.98925477134382</v>
       </c>
       <c r="J393">
-        <v>18929003564.44537</v>
+        <v>18.92900356444537</v>
       </c>
     </row>
     <row r="394" spans="1:10">
@@ -13024,10 +13024,10 @@
         <v>14131377989.65018</v>
       </c>
       <c r="I394">
-        <v>57041993678.05471</v>
+        <v>14.37767424324945</v>
       </c>
       <c r="J394">
-        <v>42910615731.06885</v>
+        <v>42.91061573106884</v>
       </c>
     </row>
     <row r="395" spans="1:10">
@@ -13056,10 +13056,10 @@
         <v>28527791536.37132</v>
       </c>
       <c r="I395">
-        <v>57041993675.33239</v>
+        <v>11.65535124286228</v>
       </c>
       <c r="J395">
-        <v>28514202184.34771</v>
+        <v>28.51420218434771</v>
       </c>
     </row>
     <row r="396" spans="1:10">
@@ -13088,10 +13088,10 @@
         <v>9710781370.902246</v>
       </c>
       <c r="I396">
-        <v>57041993678.05471</v>
+        <v>14.37767456734858</v>
       </c>
       <c r="J396">
-        <v>47331212349.81679</v>
+        <v>47.33121234981679</v>
       </c>
     </row>
     <row r="397" spans="1:10">
@@ -13120,10 +13120,10 @@
         <v>49003741549.42181</v>
       </c>
       <c r="I397">
-        <v>57041993668.73146</v>
+        <v>5.054422845477532</v>
       </c>
       <c r="J397">
-        <v>8038252171.297226</v>
+        <v>8.038252171297225</v>
       </c>
     </row>
     <row r="398" spans="1:10">
@@ -13152,10 +13152,10 @@
         <v>32579224989.42736</v>
       </c>
       <c r="I398">
-        <v>57041993674.66629</v>
+        <v>10.98925405987816</v>
       </c>
       <c r="J398">
-        <v>24462768731.29167</v>
+        <v>24.46276873129167</v>
       </c>
     </row>
     <row r="399" spans="1:10">
@@ -13184,10 +13184,10 @@
         <v>39797179554.87904</v>
       </c>
       <c r="I399">
-        <v>57041993674.66629</v>
+        <v>10.98925470666512</v>
       </c>
       <c r="J399">
-        <v>17244814165.83999</v>
+        <v>17.24481416583999</v>
       </c>
     </row>
     <row r="400" spans="1:10">
@@ -13216,10 +13216,10 @@
         <v>46087425638.95296</v>
       </c>
       <c r="I400">
-        <v>57041993670.169</v>
+        <v>6.491956632670757</v>
       </c>
       <c r="J400">
-        <v>10954568081.76608</v>
+        <v>10.95456808176607</v>
       </c>
     </row>
     <row r="401" spans="1:10">
@@ -13248,10 +13248,10 @@
         <v>7299546851.585191</v>
       </c>
       <c r="I401">
-        <v>57041993678.05471</v>
+        <v>14.37767435128251</v>
       </c>
       <c r="J401">
-        <v>49742446869.13384</v>
+        <v>49.74244686913384</v>
       </c>
     </row>
     <row r="402" spans="1:10">
@@ -13280,10 +13280,10 @@
         <v>42071074255.07466</v>
       </c>
       <c r="I402">
-        <v>57041993670.169</v>
+        <v>6.491957472431594</v>
       </c>
       <c r="J402">
-        <v>14970919465.64437</v>
+        <v>14.97091946564437</v>
       </c>
     </row>
     <row r="403" spans="1:10">
@@ -13312,10 +13312,10 @@
         <v>20561336707.82899</v>
       </c>
       <c r="I403">
-        <v>57041993678.05471</v>
+        <v>14.37767445931554</v>
       </c>
       <c r="J403">
-        <v>36480657012.89005</v>
+        <v>36.48065701289004</v>
       </c>
     </row>
     <row r="404" spans="1:10">
@@ -13344,10 +13344,10 @@
         <v>19355719448.17046</v>
       </c>
       <c r="I404">
-        <v>57041993678.05471</v>
+        <v>14.37767435128251</v>
       </c>
       <c r="J404">
-        <v>37686274272.54857</v>
+        <v>37.68627427254857</v>
       </c>
     </row>
     <row r="405" spans="1:10">
@@ -13376,10 +13376,10 @@
         <v>35466406815.60804</v>
       </c>
       <c r="I405">
-        <v>57041993674.66629</v>
+        <v>10.98925431859293</v>
       </c>
       <c r="J405">
-        <v>21575586905.11099</v>
+        <v>21.57558690511099</v>
       </c>
     </row>
     <row r="406" spans="1:10">
@@ -13408,10 +13408,10 @@
         <v>6495802011.812841</v>
       </c>
       <c r="I406">
-        <v>57041993678.05471</v>
+        <v>14.37767391915035</v>
       </c>
       <c r="J406">
-        <v>50546191708.90619</v>
+        <v>50.54619170890619</v>
       </c>
     </row>
     <row r="407" spans="1:10">
@@ -13440,10 +13440,10 @@
         <v>10916398630.56078</v>
       </c>
       <c r="I407">
-        <v>57041993678.05471</v>
+        <v>14.37767467538163</v>
       </c>
       <c r="J407">
-        <v>46125595090.15825</v>
+        <v>46.12559509015825</v>
       </c>
     </row>
     <row r="408" spans="1:10">
@@ -13472,10 +13472,10 @@
         <v>45194903109.20222</v>
       </c>
       <c r="I408">
-        <v>57041993670.169</v>
+        <v>6.491957352465768</v>
       </c>
       <c r="J408">
-        <v>11847090611.51682</v>
+        <v>11.84709061151682</v>
       </c>
     </row>
     <row r="409" spans="1:10">
@@ -13504,10 +13504,10 @@
         <v>26589423006.12164</v>
       </c>
       <c r="I409">
-        <v>57041993678.05471</v>
+        <v>14.37767391915035</v>
       </c>
       <c r="J409">
-        <v>30452570714.59739</v>
+        <v>30.45257071459739</v>
       </c>
     </row>
     <row r="410" spans="1:10">
@@ -13536,10 +13536,10 @@
         <v>8103291691.357538</v>
       </c>
       <c r="I410">
-        <v>57041993678.05471</v>
+        <v>14.37767478341466</v>
       </c>
       <c r="J410">
-        <v>48938702029.3615</v>
+        <v>48.93870202936149</v>
       </c>
     </row>
     <row r="411" spans="1:10">
@@ -13568,10 +13568,10 @@
         <v>47872470698.45441</v>
       </c>
       <c r="I411">
-        <v>57041993670.169</v>
+        <v>6.491957592397448</v>
       </c>
       <c r="J411">
-        <v>9169523022.264626</v>
+        <v>9.169523022264626</v>
       </c>
     </row>
     <row r="412" spans="1:10">
@@ -13600,10 +13600,10 @@
         <v>14935122829.42253</v>
       </c>
       <c r="I412">
-        <v>57041993678.05471</v>
+        <v>14.37767467538163</v>
       </c>
       <c r="J412">
-        <v>42106870891.2965</v>
+        <v>42.1068708912965</v>
       </c>
     </row>
     <row r="413" spans="1:10">
@@ -13632,10 +13632,10 @@
         <v>18150102188.51194</v>
       </c>
       <c r="I413">
-        <v>57041993678.05471</v>
+        <v>14.37767424324947</v>
       </c>
       <c r="J413">
-        <v>38891891532.20709</v>
+        <v>38.89189153220709</v>
       </c>
     </row>
     <row r="414" spans="1:10">
@@ -13664,10 +13664,10 @@
         <v>21766953967.48752</v>
       </c>
       <c r="I414">
-        <v>57041993678.05471</v>
+        <v>14.37767456734858</v>
       </c>
       <c r="J414">
-        <v>35275039753.23151</v>
+        <v>35.27503975323151</v>
       </c>
     </row>
     <row r="415" spans="1:10">
@@ -13696,10 +13696,10 @@
         <v>16140740089.08107</v>
       </c>
       <c r="I415">
-        <v>57041993678.05471</v>
+        <v>14.37767478341465</v>
       </c>
       <c r="J415">
-        <v>40901253631.63796</v>
+        <v>40.90125363163796</v>
       </c>
     </row>
     <row r="416" spans="1:10">
@@ -13728,10 +13728,10 @@
         <v>37150596214.21342</v>
       </c>
       <c r="I416">
-        <v>57041993674.66629</v>
+        <v>10.98925425391425</v>
       </c>
       <c r="J416">
-        <v>19891397506.50562</v>
+        <v>19.89139750650562</v>
       </c>
     </row>
     <row r="417" spans="1:10">
@@ -13760,10 +13760,10 @@
         <v>38594187127.30375</v>
       </c>
       <c r="I417">
-        <v>57041993674.66629</v>
+        <v>10.98925438327166</v>
       </c>
       <c r="J417">
-        <v>18447806593.41528</v>
+        <v>18.44780659341528</v>
       </c>
     </row>
     <row r="418" spans="1:10">
@@ -13792,10 +13792,10 @@
         <v>37391194699.72849</v>
       </c>
       <c r="I418">
-        <v>57041993674.66629</v>
+        <v>10.98925405987814</v>
       </c>
       <c r="J418">
-        <v>19650799020.99054</v>
+        <v>19.65079902099054</v>
       </c>
     </row>
     <row r="419" spans="1:10">
@@ -13824,10 +13824,10 @@
         <v>24178188486.80458</v>
       </c>
       <c r="I419">
-        <v>57041993678.05471</v>
+        <v>14.37767478341466</v>
       </c>
       <c r="J419">
-        <v>32863805233.91445</v>
+        <v>32.86380523391446</v>
       </c>
     </row>
     <row r="420" spans="1:10">
@@ -13856,10 +13856,10 @@
         <v>54099131424.65374</v>
       </c>
       <c r="I420">
-        <v>57041993666.6199</v>
+        <v>2.942862296065293</v>
       </c>
       <c r="J420">
-        <v>2942862296.065292</v>
+        <v>2.942862296065292</v>
       </c>
     </row>
     <row r="421" spans="1:10">
@@ -13888,10 +13888,10 @@
         <v>34504012873.5478</v>
       </c>
       <c r="I421">
-        <v>57041993674.66629</v>
+        <v>10.98925380116336</v>
       </c>
       <c r="J421">
-        <v>22537980847.17123</v>
+        <v>22.53798084717123</v>
       </c>
     </row>
     <row r="422" spans="1:10">
@@ -13920,10 +13920,10 @@
         <v>3888380881.363958</v>
       </c>
       <c r="I422">
-        <v>57041993682.47943</v>
+        <v>18.80239323911672</v>
       </c>
       <c r="J422">
-        <v>53153612839.35507</v>
+        <v>53.15361283935507</v>
       </c>
     </row>
     <row r="423" spans="1:10">
@@ -13952,10 +13952,10 @@
         <v>47426209433.57904</v>
       </c>
       <c r="I423">
-        <v>57041993670.16899</v>
+        <v>6.491955552978261</v>
       </c>
       <c r="J423">
-        <v>9615784287.139992</v>
+        <v>9.615784287139991</v>
       </c>
     </row>
     <row r="424" spans="1:10">
@@ -13984,10 +13984,10 @@
         <v>27393167845.89398</v>
       </c>
       <c r="I424">
-        <v>57041993678.05471</v>
+        <v>14.37767435128251</v>
       </c>
       <c r="J424">
-        <v>29648825874.82505</v>
+        <v>29.64882587482505</v>
       </c>
     </row>
     <row r="425" spans="1:10">
@@ -14016,10 +14016,10 @@
         <v>16542612508.96723</v>
       </c>
       <c r="I425">
-        <v>57041993678.05471</v>
+        <v>14.37767445931554</v>
       </c>
       <c r="J425">
-        <v>40499381211.7518</v>
+        <v>40.4993812117518</v>
       </c>
     </row>
     <row r="426" spans="1:10">
@@ -14048,10 +14048,10 @@
         <v>19757591868.05665</v>
       </c>
       <c r="I426">
-        <v>57041993678.05471</v>
+        <v>14.37767402718338</v>
       </c>
       <c r="J426">
-        <v>37284401852.66238</v>
+        <v>37.28440185266238</v>
       </c>
     </row>
     <row r="427" spans="1:10">
@@ -14080,10 +14080,10 @@
         <v>5692057172.040493</v>
       </c>
       <c r="I427">
-        <v>57041993678.05471</v>
+        <v>14.37767456734856</v>
       </c>
       <c r="J427">
-        <v>51349936548.67854</v>
+        <v>51.34993654867854</v>
       </c>
     </row>
     <row r="428" spans="1:10">
@@ -14112,10 +14112,10 @@
         <v>17346357348.73959</v>
       </c>
       <c r="I428">
-        <v>57041993678.05471</v>
+        <v>14.3776748914477</v>
       </c>
       <c r="J428">
-        <v>39695636371.97945</v>
+        <v>39.69563637197945</v>
       </c>
     </row>
     <row r="429" spans="1:10">
@@ -14144,10 +14144,10 @@
         <v>9308908951.016069</v>
       </c>
       <c r="I429">
-        <v>57041993678.05471</v>
+        <v>14.3776748914477</v>
       </c>
       <c r="J429">
-        <v>47733084769.70296</v>
+        <v>47.73308476970296</v>
       </c>
     </row>
     <row r="430" spans="1:10">
@@ -14176,10 +14176,10 @@
         <v>20159464287.94282</v>
       </c>
       <c r="I430">
-        <v>57041993678.05471</v>
+        <v>14.37767478341465</v>
       </c>
       <c r="J430">
-        <v>36882529432.77621</v>
+        <v>36.88252943277622</v>
       </c>
     </row>
     <row r="431" spans="1:10">
@@ -14208,10 +14208,10 @@
         <v>43409858049.70074</v>
       </c>
       <c r="I431">
-        <v>57041993670.169</v>
+        <v>6.491956392739112</v>
       </c>
       <c r="J431">
-        <v>13632135671.0183</v>
+        <v>13.6321356710183</v>
       </c>
     </row>
     <row r="432" spans="1:10">
@@ -14240,10 +14240,10 @@
         <v>7701419271.471367</v>
       </c>
       <c r="I432">
-        <v>57041993678.05471</v>
+        <v>14.37767402718338</v>
       </c>
       <c r="J432">
-        <v>49340574449.24767</v>
+        <v>49.34057444924767</v>
       </c>
     </row>
     <row r="433" spans="1:10">
@@ -14272,10 +14272,10 @@
         <v>8907036531.129894</v>
       </c>
       <c r="I433">
-        <v>57041993678.05471</v>
+        <v>14.37767413521642</v>
       </c>
       <c r="J433">
-        <v>48134957189.58914</v>
+        <v>48.13495718958914</v>
       </c>
     </row>
     <row r="434" spans="1:10">
@@ -14304,10 +14304,10 @@
         <v>51142043034.14726</v>
       </c>
       <c r="I434">
-        <v>57041993666.77572</v>
+        <v>3.098680775282482</v>
       </c>
       <c r="J434">
-        <v>5899950686.57177</v>
+        <v>5.89995068657177</v>
       </c>
     </row>
     <row r="435" spans="1:10">
@@ -14336,10 +14336,10 @@
         <v>14533250409.53635</v>
       </c>
       <c r="I435">
-        <v>57041993678.05471</v>
+        <v>14.37767391915035</v>
       </c>
       <c r="J435">
-        <v>42508743311.18268</v>
+        <v>42.50874331118268</v>
       </c>
     </row>
     <row r="436" spans="1:10">
@@ -14368,10 +14368,10 @@
         <v>22168826387.3737</v>
       </c>
       <c r="I436">
-        <v>57041993678.05471</v>
+        <v>14.37767424324947</v>
       </c>
       <c r="J436">
-        <v>34873167333.34534</v>
+        <v>34.87316733334534</v>
       </c>
     </row>
     <row r="437" spans="1:10">
@@ -14400,10 +14400,10 @@
         <v>5290184752.154319</v>
       </c>
       <c r="I437">
-        <v>57041993678.05471</v>
+        <v>14.37767489144768</v>
       </c>
       <c r="J437">
-        <v>51751808968.56471</v>
+        <v>51.75180896856471</v>
       </c>
     </row>
     <row r="438" spans="1:10">
@@ -14432,10 +14432,10 @@
         <v>52542679119.36658</v>
       </c>
       <c r="I438">
-        <v>57041993666.77572</v>
+        <v>3.098679645707804</v>
       </c>
       <c r="J438">
-        <v>4499314601.352455</v>
+        <v>4.499314601352455</v>
       </c>
     </row>
     <row r="439" spans="1:10">
@@ -14464,10 +14464,10 @@
         <v>31616831047.36715</v>
       </c>
       <c r="I439">
-        <v>57041993674.66629</v>
+        <v>10.98925354244855</v>
       </c>
       <c r="J439">
-        <v>25425162673.35188</v>
+        <v>25.42516267335188</v>
       </c>
     </row>
     <row r="440" spans="1:10">
@@ -14496,10 +14496,10 @@
         <v>15738867669.19489</v>
       </c>
       <c r="I440">
-        <v>57041993678.05471</v>
+        <v>14.37767402718338</v>
       </c>
       <c r="J440">
-        <v>41303126051.52414</v>
+        <v>41.30312605152414</v>
       </c>
     </row>
     <row r="441" spans="1:10">
@@ -14528,10 +14528,10 @@
         <v>20963209127.71518</v>
       </c>
       <c r="I441">
-        <v>57041993678.05471</v>
+        <v>14.37767413521642</v>
       </c>
       <c r="J441">
-        <v>36078784593.00385</v>
+        <v>36.07878459300385</v>
       </c>
     </row>
     <row r="442" spans="1:10">
@@ -14560,10 +14560,10 @@
         <v>25785678166.34929</v>
       </c>
       <c r="I442">
-        <v>57041993678.05471</v>
+        <v>14.37767456734858</v>
       </c>
       <c r="J442">
-        <v>31256315554.36974</v>
+        <v>31.25631555436974</v>
       </c>
     </row>
     <row r="443" spans="1:10">
@@ -14592,10 +14592,10 @@
         <v>25383805746.4631</v>
       </c>
       <c r="I443">
-        <v>57041993678.05471</v>
+        <v>14.3776748914477</v>
       </c>
       <c r="J443">
-        <v>31658187974.25593</v>
+        <v>31.65818797425593</v>
       </c>
     </row>
     <row r="444" spans="1:10">
@@ -14624,10 +14624,10 @@
         <v>30173240134.2768</v>
       </c>
       <c r="I444">
-        <v>57041993674.66629</v>
+        <v>10.98925470666514</v>
       </c>
       <c r="J444">
-        <v>26868753586.44223</v>
+        <v>26.86875358644224</v>
       </c>
     </row>
     <row r="445" spans="1:10">
@@ -14656,10 +14656,10 @@
         <v>39556581069.36398</v>
       </c>
       <c r="I445">
-        <v>57041993674.66629</v>
+        <v>10.98925360712725</v>
       </c>
       <c r="J445">
-        <v>17485412651.35505</v>
+        <v>17.48541265135505</v>
       </c>
     </row>
     <row r="446" spans="1:10">
@@ -14688,10 +14688,10 @@
         <v>23776316066.91841</v>
       </c>
       <c r="I446">
-        <v>57041993678.05471</v>
+        <v>14.37767402718338</v>
       </c>
       <c r="J446">
-        <v>33265677653.80062</v>
+        <v>33.26567765380062</v>
       </c>
     </row>
     <row r="447" spans="1:10">
@@ -14720,10 +14720,10 @@
         <v>40759573496.93927</v>
       </c>
       <c r="I447">
-        <v>57041993674.66629</v>
+        <v>10.98925393052073</v>
       </c>
       <c r="J447">
-        <v>16282420223.77976</v>
+        <v>16.28242022377976</v>
       </c>
     </row>
     <row r="448" spans="1:10">
@@ -14752,10 +14752,10 @@
         <v>37631793185.24352</v>
       </c>
       <c r="I448">
-        <v>57041993674.66629</v>
+        <v>10.98925386584207</v>
       </c>
       <c r="J448">
-        <v>19410200535.47551</v>
+        <v>19.41020053547551</v>
       </c>
     </row>
     <row r="449" spans="1:10">
@@ -14784,10 +14784,10 @@
         <v>11720143470.33313</v>
       </c>
       <c r="I449">
-        <v>57041993678.05471</v>
+        <v>14.37767402718338</v>
       </c>
       <c r="J449">
-        <v>45321850250.3859</v>
+        <v>45.3218502503859</v>
       </c>
     </row>
     <row r="450" spans="1:10">
@@ -14816,10 +14816,10 @@
         <v>46979948168.70368</v>
       </c>
       <c r="I450">
-        <v>57041993670.16899</v>
+        <v>6.491955912875767</v>
       </c>
       <c r="J450">
-        <v>10062045552.01535</v>
+        <v>10.06204555201535</v>
       </c>
     </row>
     <row r="451" spans="1:10">
@@ -14848,10 +14848,10 @@
         <v>28059490093.35432</v>
       </c>
       <c r="I451">
-        <v>57041993675.33239</v>
+        <v>11.65535036162694</v>
       </c>
       <c r="J451">
-        <v>28982503627.36471</v>
+        <v>28.98250362736471</v>
       </c>
     </row>
     <row r="452" spans="1:10">
@@ -14880,10 +14880,10 @@
         <v>38834785612.81881</v>
       </c>
       <c r="I452">
-        <v>57041993674.66629</v>
+        <v>10.98925418923555</v>
       </c>
       <c r="J452">
-        <v>18207208107.90022</v>
+        <v>18.20720810790022</v>
       </c>
     </row>
     <row r="453" spans="1:10">
@@ -14912,10 +14912,10 @@
         <v>41178551725.32391</v>
       </c>
       <c r="I453">
-        <v>57041993670.16899</v>
+        <v>6.491955792909941</v>
       </c>
       <c r="J453">
-        <v>15863441995.39512</v>
+        <v>15.86344199539512</v>
       </c>
     </row>
     <row r="454" spans="1:10">
@@ -14944,10 +14944,10 @@
         <v>39315982583.84892</v>
       </c>
       <c r="I454">
-        <v>57041993674.66629</v>
+        <v>10.98925380116336</v>
       </c>
       <c r="J454">
-        <v>17726011136.87011</v>
+        <v>17.72601113687011</v>
       </c>
     </row>
     <row r="455" spans="1:10">
@@ -14976,10 +14976,10 @@
         <v>23374443647.03222</v>
       </c>
       <c r="I455">
-        <v>57041993678.05471</v>
+        <v>14.37767435128251</v>
       </c>
       <c r="J455">
-        <v>33667550073.68681</v>
+        <v>33.66755007368681</v>
       </c>
     </row>
     <row r="456" spans="1:10">
@@ -15008,10 +15008,10 @@
         <v>11318271050.44695</v>
       </c>
       <c r="I456">
-        <v>57041993678.05471</v>
+        <v>14.37767435128249</v>
       </c>
       <c r="J456">
-        <v>45723722670.27208</v>
+        <v>45.72372267027208</v>
       </c>
     </row>
     <row r="457" spans="1:10">
@@ -15040,10 +15040,10 @@
         <v>43856119314.57612</v>
       </c>
       <c r="I457">
-        <v>57041993670.16899</v>
+        <v>6.491956032841607</v>
       </c>
       <c r="J457">
-        <v>13185874406.14291</v>
+        <v>13.18587440614291</v>
       </c>
     </row>
     <row r="458" spans="1:10">
@@ -15072,10 +15072,10 @@
         <v>28996092979.38832</v>
       </c>
       <c r="I458">
-        <v>57041993675.33239</v>
+        <v>11.65535086518997</v>
       </c>
       <c r="J458">
-        <v>28045900741.33071</v>
+        <v>28.04590074133071</v>
       </c>
     </row>
     <row r="459" spans="1:10">
@@ -15104,10 +15104,10 @@
         <v>26991295426.00782</v>
       </c>
       <c r="I459">
-        <v>57041993678.05471</v>
+        <v>14.37767467538159</v>
       </c>
       <c r="J459">
-        <v>30050698294.71121</v>
+        <v>30.05069829471121</v>
       </c>
     </row>
     <row r="460" spans="1:10">
@@ -15136,10 +15136,10 @@
         <v>16944484928.85342</v>
       </c>
       <c r="I460">
-        <v>57041993678.05471</v>
+        <v>14.37767413521642</v>
       </c>
       <c r="J460">
-        <v>40097508791.86562</v>
+        <v>40.09750879186561</v>
       </c>
     </row>
     <row r="461" spans="1:10">
@@ -15168,10 +15168,10 @@
         <v>42963596784.82541</v>
       </c>
       <c r="I461">
-        <v>57041993670.169</v>
+        <v>6.491956752636575</v>
       </c>
       <c r="J461">
-        <v>14078396935.89362</v>
+        <v>14.07839693589362</v>
       </c>
     </row>
     <row r="462" spans="1:10">
@@ -15200,10 +15200,10 @@
         <v>8505164111.243721</v>
       </c>
       <c r="I462">
-        <v>57041993678.05471</v>
+        <v>14.37767445931552</v>
       </c>
       <c r="J462">
-        <v>48536829609.47531</v>
+        <v>48.53682960947531</v>
       </c>
     </row>
     <row r="463" spans="1:10">
@@ -15232,10 +15232,10 @@
         <v>3172730456.993646</v>
       </c>
       <c r="I463">
-        <v>57041993682.47943</v>
+        <v>18.80239285434838</v>
       </c>
       <c r="J463">
-        <v>53869263263.72539</v>
+        <v>53.86926326372539</v>
       </c>
     </row>
     <row r="464" spans="1:10">
@@ -15264,10 +15264,10 @@
         <v>12122015890.21931</v>
       </c>
       <c r="I464">
-        <v>57041993678.05471</v>
+        <v>14.37767478341465</v>
       </c>
       <c r="J464">
-        <v>44919977830.49973</v>
+        <v>44.91997783049973</v>
       </c>
     </row>
     <row r="465" spans="1:10">
@@ -15296,10 +15296,10 @@
         <v>18953847028.28429</v>
       </c>
       <c r="I465">
-        <v>57041993678.05471</v>
+        <v>14.37767467538163</v>
       </c>
       <c r="J465">
-        <v>38088146692.43474</v>
+        <v>38.08814669243474</v>
       </c>
     </row>
     <row r="466" spans="1:10">
@@ -15328,10 +15328,10 @@
         <v>38353588641.7887</v>
       </c>
       <c r="I466">
-        <v>57041993674.66629</v>
+        <v>10.98925457730773</v>
       </c>
       <c r="J466">
-        <v>18688405078.93034</v>
+        <v>18.68840507893034</v>
       </c>
     </row>
     <row r="467" spans="1:10">
@@ -15360,10 +15360,10 @@
         <v>41624812990.19927</v>
       </c>
       <c r="I467">
-        <v>57041993670.16899</v>
+        <v>6.491955433012443</v>
       </c>
       <c r="J467">
-        <v>15417180730.51976</v>
+        <v>15.41718073051976</v>
       </c>
     </row>
     <row r="468" spans="1:10">
@@ -15392,10 +15392,10 @@
         <v>12925760729.99166</v>
       </c>
       <c r="I468">
-        <v>57041993678.05471</v>
+        <v>14.37767413521642</v>
       </c>
       <c r="J468">
-        <v>44116232990.72737</v>
+        <v>44.11623299072737</v>
       </c>
     </row>
     <row r="469" spans="1:10">
@@ -15424,10 +15424,10 @@
         <v>32098028018.39726</v>
       </c>
       <c r="I469">
-        <v>57041993674.66629</v>
+        <v>10.98925444795034</v>
       </c>
       <c r="J469">
-        <v>24943965702.32177</v>
+        <v>24.94396570232177</v>
       </c>
     </row>
     <row r="470" spans="1:10">
@@ -15456,10 +15456,10 @@
         <v>40037778040.3941</v>
       </c>
       <c r="I470">
-        <v>57041993674.66629</v>
+        <v>10.98925451262903</v>
       </c>
       <c r="J470">
-        <v>17004215680.32494</v>
+        <v>17.00421568032494</v>
       </c>
     </row>
     <row r="471" spans="1:10">
@@ -15488,10 +15488,10 @@
         <v>-26292645863.9519</v>
       </c>
       <c r="I471">
-        <v>57041993666.13471</v>
+        <v>2.457676799230185</v>
       </c>
       <c r="J471">
-        <v>83334639584.67093</v>
+        <v>83.33463958467092</v>
       </c>
     </row>
     <row r="472" spans="1:10">
@@ -15520,10 +15520,10 @@
         <v>46496620642.94477</v>
       </c>
       <c r="I472">
-        <v>57041993666.13472</v>
+        <v>2.457683321735978</v>
       </c>
       <c r="J472">
-        <v>10545373077.77426</v>
+        <v>10.54537307777426</v>
       </c>
     </row>
     <row r="473" spans="1:10">
@@ -15552,10 +15552,10 @@
         <v>54584316921.48884</v>
       </c>
       <c r="I473">
-        <v>57041993666.13471</v>
+        <v>2.457676799230207</v>
       </c>
       <c r="J473">
-        <v>2457676799.230194</v>
+        <v>2.457676799230194</v>
       </c>
     </row>
     <row r="474" spans="1:10">
@@ -15584,10 +15584,10 @@
         <v>-66731127256.67229</v>
       </c>
       <c r="I474">
-        <v>57041993666.13473</v>
+        <v>2.457687670073177</v>
       </c>
       <c r="J474">
-        <v>123773120977.3913</v>
+        <v>123.7731209773913</v>
       </c>
     </row>
     <row r="475" spans="1:10">
@@ -15616,10 +15616,10 @@
         <v>14145835528.76845</v>
       </c>
       <c r="I475">
-        <v>57041993666.13473</v>
+        <v>2.457687670073177</v>
       </c>
       <c r="J475">
-        <v>42896158191.95058</v>
+        <v>42.89615819195058</v>
       </c>
     </row>
     <row r="476" spans="1:10">
@@ -15648,10 +15648,10 @@
         <v>34365076225.12864</v>
       </c>
       <c r="I476">
-        <v>57041993666.13474</v>
+        <v>2.457693105494677</v>
       </c>
       <c r="J476">
-        <v>22676917495.59039</v>
+        <v>22.67691749559039</v>
       </c>
     </row>
     <row r="477" spans="1:10">
@@ -15680,10 +15680,10 @@
         <v>26072154351.05789</v>
       </c>
       <c r="I477">
-        <v>57041993691.33755</v>
+        <v>27.66051711750699</v>
       </c>
       <c r="J477">
-        <v>30969839369.66114</v>
+        <v>30.96983936966114</v>
       </c>
     </row>
     <row r="478" spans="1:10">
@@ -15712,10 +15712,10 @@
         <v>29050544377.99662</v>
       </c>
       <c r="I478">
-        <v>57041993691.33755</v>
+        <v>27.66051738439479</v>
       </c>
       <c r="J478">
-        <v>27991449342.72241</v>
+        <v>27.99144934272241</v>
       </c>
     </row>
     <row r="479" spans="1:10">
@@ -15744,10 +15744,10 @@
         <v>29381476603.21204</v>
       </c>
       <c r="I479">
-        <v>57041993691.33755</v>
+        <v>27.66051711750699</v>
       </c>
       <c r="J479">
-        <v>27660517117.50699</v>
+        <v>27.66051711750699</v>
       </c>
     </row>
     <row r="480" spans="1:10">
@@ -15776,10 +15776,10 @@
         <v>24417493224.98081</v>
       </c>
       <c r="I480">
-        <v>57041993691.33755</v>
+        <v>27.66051756231998</v>
       </c>
       <c r="J480">
-        <v>32624500495.73822</v>
+        <v>32.62450049573822</v>
       </c>
     </row>
     <row r="481" spans="1:10">
@@ -15808,10 +15808,10 @@
         <v>27726815477.13496</v>
       </c>
       <c r="I481">
-        <v>57041993691.33755</v>
+        <v>27.66051756231997</v>
       </c>
       <c r="J481">
-        <v>29315178243.58407</v>
+        <v>29.31517824358407</v>
       </c>
     </row>
     <row r="482" spans="1:10">
@@ -15840,10 +15840,10 @@
         <v>28554146040.1735</v>
       </c>
       <c r="I482">
-        <v>57041993691.33755</v>
+        <v>27.66051778472645</v>
       </c>
       <c r="J482">
-        <v>28487847680.54553</v>
+        <v>28.48784768054553</v>
       </c>
     </row>
     <row r="483" spans="1:10">
@@ -15872,10 +15872,10 @@
         <v>37858225820.73282</v>
       </c>
       <c r="I483">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J483">
-        <v>19183767899.98621</v>
+        <v>19.18376789998621</v>
       </c>
     </row>
     <row r="484" spans="1:10">
@@ -15904,10 +15904,10 @@
         <v>42228262356.56921</v>
       </c>
       <c r="I484">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J484">
-        <v>14813731364.14983</v>
+        <v>14.81373136414983</v>
       </c>
     </row>
     <row r="485" spans="1:10">
@@ -15936,10 +15936,10 @@
         <v>13403801226.80173</v>
       </c>
       <c r="I485">
-        <v>57041993675.71091</v>
+        <v>12.03387111916361</v>
       </c>
       <c r="J485">
-        <v>43638192493.9173</v>
+        <v>43.6381924939173</v>
       </c>
     </row>
     <row r="486" spans="1:10">
@@ -15968,10 +15968,10 @@
         <v>54584316921.48884</v>
       </c>
       <c r="I486">
-        <v>57041993666.13471</v>
+        <v>2.457676799230207</v>
       </c>
       <c r="J486">
-        <v>2457676799.230194</v>
+        <v>2.457676799230194</v>
       </c>
     </row>
     <row r="487" spans="1:10">
@@ -16000,10 +16000,10 @@
         <v>40639158161.71964</v>
       </c>
       <c r="I487">
-        <v>57041993672.53163</v>
+        <v>8.854590633463808</v>
       </c>
       <c r="J487">
-        <v>16402835558.99939</v>
+        <v>16.40283555899939</v>
       </c>
     </row>
     <row r="488" spans="1:10">
@@ -16032,10 +16032,10 @@
         <v>26008584677.71512</v>
       </c>
       <c r="I488">
-        <v>57041993673.41224</v>
+        <v>9.735204034815972</v>
       </c>
       <c r="J488">
-        <v>31033409043.00391</v>
+        <v>31.03340904300391</v>
       </c>
     </row>
     <row r="489" spans="1:10">
@@ -16064,10 +16064,10 @@
         <v>45009194697.55598</v>
       </c>
       <c r="I489">
-        <v>57041993672.53163</v>
+        <v>8.854590633463857</v>
       </c>
       <c r="J489">
-        <v>12032799023.16306</v>
+        <v>12.03279902316306</v>
       </c>
     </row>
     <row r="490" spans="1:10">
@@ -16096,10 +16096,10 @@
         <v>47291816627.43009</v>
       </c>
       <c r="I490">
-        <v>57041993668.59084</v>
+        <v>4.913803690310033</v>
       </c>
       <c r="J490">
-        <v>9750177093.28894</v>
+        <v>9.75017709328894</v>
       </c>
     </row>
     <row r="491" spans="1:10">
@@ -16128,10 +16128,10 @@
         <v>40837796186.07581</v>
       </c>
       <c r="I491">
-        <v>57041993672.53163</v>
+        <v>8.854590633463836</v>
       </c>
       <c r="J491">
-        <v>16204197534.64322</v>
+        <v>16.20419753464322</v>
       </c>
     </row>
     <row r="492" spans="1:10">
@@ -16160,10 +16160,10 @@
         <v>41235072234.78822</v>
       </c>
       <c r="I492">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J492">
-        <v>15806921485.93081</v>
+        <v>15.80692148593081</v>
       </c>
     </row>
     <row r="493" spans="1:10">
@@ -16192,10 +16192,10 @@
         <v>35871845577.17081</v>
       </c>
       <c r="I493">
-        <v>57041993672.53163</v>
+        <v>8.854590633463836</v>
       </c>
       <c r="J493">
-        <v>21170148143.54823</v>
+        <v>21.17014814354823</v>
       </c>
     </row>
     <row r="494" spans="1:10">
@@ -16224,10 +16224,10 @@
         <v>35077293479.74602</v>
       </c>
       <c r="I494">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J494">
-        <v>21964700240.97301</v>
+        <v>21.96470024097302</v>
       </c>
     </row>
     <row r="495" spans="1:10">
@@ -16256,10 +16256,10 @@
         <v>43022814453.99401</v>
       </c>
       <c r="I495">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J495">
-        <v>14019179266.72502</v>
+        <v>14.01917926672502</v>
       </c>
     </row>
     <row r="496" spans="1:10">
@@ -16288,10 +16288,10 @@
         <v>13751366344.58115</v>
       </c>
       <c r="I496">
-        <v>57041993675.76154</v>
+        <v>12.08450674642513</v>
       </c>
       <c r="J496">
-        <v>43290627376.13788</v>
+        <v>43.29062737613788</v>
       </c>
     </row>
     <row r="497" spans="1:10">
@@ -16320,10 +16320,10 @@
         <v>22279651383.17656</v>
       </c>
       <c r="I497">
-        <v>57041993674.2422</v>
+        <v>10.56515287912824</v>
       </c>
       <c r="J497">
-        <v>34762342337.54247</v>
+        <v>34.76234233754247</v>
       </c>
     </row>
     <row r="498" spans="1:10">
@@ -16352,10 +16352,10 @@
         <v>26773458021.67564</v>
       </c>
       <c r="I498">
-        <v>57041993673.19294</v>
+        <v>9.515903146829267</v>
       </c>
       <c r="J498">
-        <v>30268535699.04339</v>
+        <v>30.26853569904339</v>
       </c>
     </row>
     <row r="499" spans="1:10">
@@ -16384,10 +16384,10 @@
         <v>39050053966.87001</v>
       </c>
       <c r="I499">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J499">
-        <v>17991939753.84902</v>
+        <v>17.99193975384902</v>
       </c>
     </row>
     <row r="500" spans="1:10">
@@ -16416,10 +16416,10 @@
         <v>44810556673.19979</v>
       </c>
       <c r="I500">
-        <v>57041993672.53163</v>
+        <v>8.854590633463843</v>
       </c>
       <c r="J500">
-        <v>12231437047.51924</v>
+        <v>12.23143704751924</v>
       </c>
     </row>
     <row r="501" spans="1:10">
@@ -16448,10 +16448,10 @@
         <v>41036434210.432</v>
       </c>
       <c r="I501">
-        <v>57041993672.53163</v>
+        <v>8.854590633463843</v>
       </c>
       <c r="J501">
-        <v>16005559510.28703</v>
+        <v>16.00555951028703</v>
       </c>
     </row>
     <row r="502" spans="1:10">
@@ -16480,10 +16480,10 @@
         <v>44214642600.1312</v>
       </c>
       <c r="I502">
-        <v>57041993672.53163</v>
+        <v>8.854590633463843</v>
       </c>
       <c r="J502">
-        <v>12827351120.58783</v>
+        <v>12.82735112058783</v>
       </c>
     </row>
     <row r="503" spans="1:10">
@@ -16512,10 +16512,10 @@
         <v>24874463944.20275</v>
       </c>
       <c r="I503">
-        <v>57041993673.68734</v>
+        <v>10.01030227240341</v>
       </c>
       <c r="J503">
-        <v>32167529776.51628</v>
+        <v>32.16752977651628</v>
       </c>
     </row>
     <row r="504" spans="1:10">
@@ -16544,10 +16544,10 @@
         <v>12713849295.60189</v>
       </c>
       <c r="I504">
-        <v>57041993675.93098</v>
+        <v>12.25394872078479</v>
       </c>
       <c r="J504">
-        <v>44328144425.11714</v>
+        <v>44.32814442511715</v>
       </c>
     </row>
     <row r="505" spans="1:10">
@@ -16576,10 +16576,10 @@
         <v>43817366551.41882</v>
       </c>
       <c r="I505">
-        <v>57041993672.53163</v>
+        <v>8.854590633463815</v>
       </c>
       <c r="J505">
-        <v>13224627169.30021</v>
+        <v>13.22462716930021</v>
       </c>
     </row>
     <row r="506" spans="1:10">
@@ -16608,10 +16608,10 @@
         <v>18313630101.35769</v>
       </c>
       <c r="I506">
-        <v>57041993675.02586</v>
+        <v>11.34882609469995</v>
       </c>
       <c r="J506">
-        <v>38728363619.36134</v>
+        <v>38.72836361936135</v>
       </c>
     </row>
     <row r="507" spans="1:10">
@@ -16640,10 +16640,10 @@
         <v>29515428797.77243</v>
       </c>
       <c r="I507">
-        <v>57041993672.53163</v>
+        <v>8.854590633463836</v>
       </c>
       <c r="J507">
-        <v>27526564922.9466</v>
+        <v>27.5265649229466</v>
       </c>
     </row>
     <row r="508" spans="1:10">
@@ -16672,10 +16672,10 @@
         <v>37063673723.30801</v>
       </c>
       <c r="I508">
-        <v>57041993672.53163</v>
+        <v>8.854590633463836</v>
       </c>
       <c r="J508">
-        <v>19978319997.41103</v>
+        <v>19.97831999741103</v>
       </c>
     </row>
     <row r="509" spans="1:10">
@@ -16704,10 +16704,10 @@
         <v>21913887508.88958</v>
       </c>
       <c r="I509">
-        <v>57041993674.29879</v>
+        <v>10.62175220517315</v>
       </c>
       <c r="J509">
-        <v>35128106211.82945</v>
+        <v>35.12810621182945</v>
       </c>
     </row>
     <row r="510" spans="1:10">
@@ -16736,10 +16736,10 @@
         <v>19026426124.86738</v>
       </c>
       <c r="I510">
-        <v>57041993674.89127</v>
+        <v>11.21423047738262</v>
       </c>
       <c r="J510">
-        <v>38015567595.85165</v>
+        <v>38.01556759585166</v>
       </c>
     </row>
     <row r="511" spans="1:10">
@@ -16768,10 +16768,10 @@
         <v>38255501869.44521</v>
       </c>
       <c r="I511">
-        <v>57041993672.53163</v>
+        <v>8.854590633463836</v>
       </c>
       <c r="J511">
-        <v>18786491851.27382</v>
+        <v>18.78649185127382</v>
       </c>
     </row>
     <row r="512" spans="1:10">
@@ -16800,10 +16800,10 @@
         <v>43420090502.7064</v>
       </c>
       <c r="I512">
-        <v>57041993672.53163</v>
+        <v>8.854590633463836</v>
       </c>
       <c r="J512">
-        <v>13621903218.01263</v>
+        <v>13.62190321801264</v>
       </c>
     </row>
     <row r="513" spans="1:10">
@@ -16832,10 +16832,10 @@
         <v>29912704846.48483</v>
       </c>
       <c r="I513">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J513">
-        <v>27129288874.2342</v>
+        <v>27.1292888742342</v>
       </c>
     </row>
     <row r="514" spans="1:10">
@@ -16864,10 +16864,10 @@
         <v>27546125908.78413</v>
       </c>
       <c r="I514">
-        <v>57041993672.97441</v>
+        <v>9.297370911593283</v>
       </c>
       <c r="J514">
-        <v>29495867811.9349</v>
+        <v>29.4958678119349</v>
       </c>
     </row>
     <row r="515" spans="1:10">
@@ -16896,10 +16896,10 @@
         <v>20102093206.47307</v>
       </c>
       <c r="I515">
-        <v>57041993674.70095</v>
+        <v>11.02391530616065</v>
       </c>
       <c r="J515">
-        <v>36939900514.24596</v>
+        <v>36.93990051424596</v>
       </c>
     </row>
     <row r="516" spans="1:10">
@@ -16928,10 +16928,10 @@
         <v>33885465333.60881</v>
       </c>
       <c r="I516">
-        <v>57041993672.53163</v>
+        <v>8.854590633463843</v>
       </c>
       <c r="J516">
-        <v>23156528387.11022</v>
+        <v>23.15652838711022</v>
       </c>
     </row>
     <row r="517" spans="1:10">
@@ -16960,10 +16960,10 @@
         <v>11369268889.85138</v>
       </c>
       <c r="I517">
-        <v>57041993676.77142</v>
+        <v>13.09438844643299</v>
       </c>
       <c r="J517">
-        <v>45672724830.86765</v>
+        <v>45.67272483086765</v>
       </c>
     </row>
     <row r="518" spans="1:10">
@@ -16992,10 +16992,10 @@
         <v>35474569528.45842</v>
       </c>
       <c r="I518">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J518">
-        <v>21567424192.26061</v>
+        <v>21.56742419226061</v>
       </c>
     </row>
     <row r="519" spans="1:10">
@@ -17024,10 +17024,10 @@
         <v>26389307742.49439</v>
       </c>
       <c r="I519">
-        <v>57041993673.20189</v>
+        <v>9.524852969061222</v>
       </c>
       <c r="J519">
-        <v>30652685978.22464</v>
+        <v>30.65268597822464</v>
       </c>
     </row>
     <row r="520" spans="1:10">
@@ -17056,10 +17056,10 @@
         <v>22646452173.78152</v>
       </c>
       <c r="I520">
-        <v>57041993674.16796</v>
+        <v>10.49092278979538</v>
       </c>
       <c r="J520">
-        <v>34395541546.93752</v>
+        <v>34.39554154693752</v>
       </c>
     </row>
     <row r="521" spans="1:10">
@@ -17088,10 +17088,10 @@
         <v>34282741382.32121</v>
       </c>
       <c r="I521">
-        <v>57041993672.53163</v>
+        <v>8.854590633463843</v>
       </c>
       <c r="J521">
-        <v>22759252338.39782</v>
+        <v>22.75925233839782</v>
       </c>
     </row>
     <row r="522" spans="1:10">
@@ -17120,10 +17120,10 @@
         <v>36269121625.88322</v>
       </c>
       <c r="I522">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J522">
-        <v>20772872094.83582</v>
+        <v>20.77287209483582</v>
       </c>
     </row>
     <row r="523" spans="1:10">
@@ -17152,10 +17152,10 @@
         <v>52041658240.28119</v>
       </c>
       <c r="I523">
-        <v>57041993666.96777</v>
+        <v>3.290725762877685</v>
       </c>
       <c r="J523">
-        <v>5000335480.437843</v>
+        <v>5.000335480437843</v>
       </c>
     </row>
     <row r="524" spans="1:10">
@@ -17184,10 +17184,10 @@
         <v>40241882113.00723</v>
       </c>
       <c r="I524">
-        <v>57041993672.53163</v>
+        <v>8.854590633463815</v>
       </c>
       <c r="J524">
-        <v>16800111607.7118</v>
+        <v>16.8001116077118</v>
       </c>
     </row>
     <row r="525" spans="1:10">
@@ -17216,10 +17216,10 @@
         <v>18669572369.64102</v>
       </c>
       <c r="I525">
-        <v>57041993674.94194</v>
+        <v>11.26490224466644</v>
       </c>
       <c r="J525">
-        <v>38372421351.07801</v>
+        <v>38.37242135107801</v>
       </c>
     </row>
     <row r="526" spans="1:10">
@@ -17248,10 +17248,10 @@
         <v>42824176429.63779</v>
       </c>
       <c r="I526">
-        <v>57041993672.53163</v>
+        <v>8.854590633463857</v>
       </c>
       <c r="J526">
-        <v>14217817291.08125</v>
+        <v>14.21781729108124</v>
       </c>
     </row>
     <row r="527" spans="1:10">
@@ -17280,10 +17280,10 @@
         <v>48407343637.55212</v>
       </c>
       <c r="I527">
-        <v>57041993668.38493</v>
+        <v>4.707890018181864</v>
       </c>
       <c r="J527">
-        <v>8634650083.166916</v>
+        <v>8.634650083166916</v>
       </c>
     </row>
     <row r="528" spans="1:10">
@@ -17312,10 +17312,10 @@
         <v>16897152675.54328</v>
       </c>
       <c r="I528">
-        <v>57041993675.31608</v>
+        <v>11.63903696737914</v>
       </c>
       <c r="J528">
-        <v>40144841045.17575</v>
+        <v>40.14484104517575</v>
       </c>
     </row>
     <row r="529" spans="1:10">
@@ -17344,10 +17344,10 @@
         <v>39844606064.29482</v>
       </c>
       <c r="I529">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J529">
-        <v>17197387656.42421</v>
+        <v>17.19738765642421</v>
       </c>
     </row>
     <row r="530" spans="1:10">
@@ -17376,10 +17376,10 @@
         <v>14794305431.26759</v>
       </c>
       <c r="I530">
-        <v>57041993675.60155</v>
+        <v>11.92450893864516</v>
       </c>
       <c r="J530">
-        <v>42247688289.45145</v>
+        <v>42.24768828945145</v>
       </c>
     </row>
     <row r="531" spans="1:10">
@@ -17408,10 +17408,10 @@
         <v>12040987165.81911</v>
       </c>
       <c r="I531">
-        <v>57041993676.77142</v>
+        <v>13.09438844643299</v>
       </c>
       <c r="J531">
-        <v>45001006554.89992</v>
+        <v>45.00100655489992</v>
       </c>
     </row>
     <row r="532" spans="1:10">
@@ -17440,10 +17440,10 @@
         <v>27158767455.73264</v>
       </c>
       <c r="I532">
-        <v>57041993673.0856</v>
+        <v>9.408566415129258</v>
       </c>
       <c r="J532">
-        <v>29883226264.98639</v>
+        <v>29.88322626498639</v>
       </c>
     </row>
     <row r="533" spans="1:10">
@@ -17472,10 +17472,10 @@
         <v>12376846303.80298</v>
       </c>
       <c r="I533">
-        <v>57041993676.77142</v>
+        <v>13.09438844643299</v>
       </c>
       <c r="J533">
-        <v>44665147416.91605</v>
+        <v>44.66514741691606</v>
       </c>
     </row>
     <row r="534" spans="1:10">
@@ -17504,10 +17504,10 @@
         <v>15143087625.55058</v>
       </c>
       <c r="I534">
-        <v>57041993675.57575</v>
+        <v>11.89871383554947</v>
       </c>
       <c r="J534">
-        <v>41898906095.16846</v>
+        <v>41.89890609516846</v>
       </c>
     </row>
     <row r="535" spans="1:10">
@@ -17536,10 +17536,10 @@
         <v>28721534152.02061</v>
       </c>
       <c r="I535">
-        <v>57041993672.64478</v>
+        <v>8.967736356623597</v>
       </c>
       <c r="J535">
-        <v>28320459568.69842</v>
+        <v>28.32045956869842</v>
       </c>
     </row>
     <row r="536" spans="1:10">
@@ -17568,10 +17568,10 @@
         <v>47846377913.98282</v>
       </c>
       <c r="I536">
-        <v>57041993668.38493</v>
+        <v>4.707890018181871</v>
       </c>
       <c r="J536">
-        <v>9195615806.736214</v>
+        <v>9.195615806736214</v>
       </c>
     </row>
     <row r="537" spans="1:10">
@@ -17600,10 +17600,10 @@
         <v>29118152749.06003</v>
       </c>
       <c r="I537">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J537">
-        <v>27923840971.659</v>
+        <v>27.923840971659</v>
       </c>
     </row>
     <row r="538" spans="1:10">
@@ -17632,10 +17632,10 @@
         <v>37460949772.02042</v>
       </c>
       <c r="I538">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J538">
-        <v>19581043948.69862</v>
+        <v>19.58104394869862</v>
       </c>
     </row>
     <row r="539" spans="1:10">
@@ -17664,10 +17664,10 @@
         <v>49529275084.69071</v>
       </c>
       <c r="I539">
-        <v>57041993668.38493</v>
+        <v>4.707890018181857</v>
       </c>
       <c r="J539">
-        <v>7512718636.02832</v>
+        <v>7.51271863602832</v>
       </c>
     </row>
     <row r="540" spans="1:10">
@@ -17696,10 +17696,10 @@
         <v>11033409751.86751</v>
       </c>
       <c r="I540">
-        <v>57041993676.77142</v>
+        <v>13.094388446433</v>
       </c>
       <c r="J540">
-        <v>46008583968.85152</v>
+        <v>46.00858396885153</v>
       </c>
     </row>
     <row r="541" spans="1:10">
@@ -17728,10 +17728,10 @@
         <v>17958418920.30566</v>
       </c>
       <c r="I541">
-        <v>57041993675.07217</v>
+        <v>11.39512711768887</v>
       </c>
       <c r="J541">
-        <v>39083574800.41338</v>
+        <v>39.08357480041337</v>
       </c>
     </row>
     <row r="542" spans="1:10">
@@ -17760,10 +17760,10 @@
         <v>41830986307.85679</v>
       </c>
       <c r="I542">
-        <v>57041993672.53163</v>
+        <v>8.854590633463857</v>
       </c>
       <c r="J542">
-        <v>15211007412.86224</v>
+        <v>15.21100741286224</v>
       </c>
     </row>
     <row r="543" spans="1:10">
@@ -17792,10 +17792,10 @@
         <v>16545232071.05532</v>
       </c>
       <c r="I543">
-        <v>57041993675.32182</v>
+        <v>11.64477721525024</v>
       </c>
       <c r="J543">
-        <v>40496761649.66371</v>
+        <v>40.49676164966371</v>
       </c>
     </row>
     <row r="544" spans="1:10">
@@ -17824,10 +17824,10 @@
         <v>49447393529.84593</v>
       </c>
       <c r="I544">
-        <v>57041993667.50925</v>
+        <v>3.832213068502433</v>
       </c>
       <c r="J544">
-        <v>7594600190.8731</v>
+        <v>7.5946001908731</v>
       </c>
     </row>
     <row r="545" spans="1:10">
@@ -17856,10 +17856,10 @@
         <v>44413280624.48743</v>
       </c>
       <c r="I545">
-        <v>57041993672.53163</v>
+        <v>8.854590633463815</v>
       </c>
       <c r="J545">
-        <v>12628713096.23161</v>
+        <v>12.62871309623161</v>
       </c>
     </row>
     <row r="546" spans="1:10">
@@ -17888,10 +17888,10 @@
         <v>40440520137.36341</v>
       </c>
       <c r="I546">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J546">
-        <v>16601473583.35562</v>
+        <v>16.60147358335562</v>
       </c>
     </row>
     <row r="547" spans="1:10">
@@ -17920,10 +17920,10 @@
         <v>30309980895.19722</v>
       </c>
       <c r="I547">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J547">
-        <v>26732012825.52181</v>
+        <v>26.73201282552181</v>
       </c>
     </row>
     <row r="548" spans="1:10">
@@ -17952,10 +17952,10 @@
         <v>21185833307.19346</v>
       </c>
       <c r="I548">
-        <v>57041993674.43254</v>
+        <v>10.75549964431578</v>
       </c>
       <c r="J548">
-        <v>35856160413.52557</v>
+        <v>35.85616041352557</v>
       </c>
     </row>
     <row r="549" spans="1:10">
@@ -17984,10 +17984,10 @@
         <v>10697550613.88366</v>
       </c>
       <c r="I549">
-        <v>57041993676.77142</v>
+        <v>13.09438844643299</v>
       </c>
       <c r="J549">
-        <v>46344443106.83537</v>
+        <v>46.34444310683537</v>
       </c>
     </row>
     <row r="550" spans="1:10">
@@ -18016,10 +18016,10 @@
         <v>48968309361.12141</v>
       </c>
       <c r="I550">
-        <v>57041993668.38493</v>
+        <v>4.707890018181864</v>
       </c>
       <c r="J550">
-        <v>8073684359.597626</v>
+        <v>8.073684359597626</v>
       </c>
     </row>
     <row r="551" spans="1:10">
@@ -18048,10 +18048,10 @@
         <v>43618728527.06261</v>
       </c>
       <c r="I551">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J551">
-        <v>13423265193.65643</v>
+        <v>13.42326519365642</v>
       </c>
     </row>
     <row r="552" spans="1:10">
@@ -18080,10 +18080,10 @@
         <v>50265315114.52147</v>
       </c>
       <c r="I552">
-        <v>57041993666.91209</v>
+        <v>3.235046307452464</v>
       </c>
       <c r="J552">
-        <v>6776678606.197563</v>
+        <v>6.776678606197563</v>
       </c>
     </row>
     <row r="553" spans="1:10">
@@ -18112,10 +18112,10 @@
         <v>36666397674.59561</v>
       </c>
       <c r="I553">
-        <v>57041993672.53163</v>
+        <v>8.854590633463836</v>
       </c>
       <c r="J553">
-        <v>20375596046.12342</v>
+        <v>20.37559604612342</v>
       </c>
     </row>
     <row r="554" spans="1:10">
@@ -18144,10 +18144,10 @@
         <v>38652777918.15762</v>
       </c>
       <c r="I554">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J554">
-        <v>18389215802.56141</v>
+        <v>18.38921580256141</v>
       </c>
     </row>
     <row r="555" spans="1:10">
@@ -18176,10 +18176,10 @@
         <v>41433710259.14439</v>
       </c>
       <c r="I555">
-        <v>57041993672.53163</v>
+        <v>8.854590633463843</v>
       </c>
       <c r="J555">
-        <v>15608283461.57465</v>
+        <v>15.60828346157465</v>
       </c>
     </row>
     <row r="556" spans="1:10">
@@ -18208,10 +18208,10 @@
         <v>42625538405.28161</v>
       </c>
       <c r="I556">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J556">
-        <v>14416455315.43742</v>
+        <v>14.41645531543742</v>
       </c>
     </row>
     <row r="557" spans="1:10">
@@ -18240,10 +18240,10 @@
         <v>45444694490.13243</v>
       </c>
       <c r="I557">
-        <v>57041993671.48994</v>
+        <v>7.812895014555096</v>
       </c>
       <c r="J557">
-        <v>11597299230.5866</v>
+        <v>11.5972992305866</v>
       </c>
     </row>
     <row r="558" spans="1:10">
@@ -18272,10 +18272,10 @@
         <v>15492582762.07593</v>
       </c>
       <c r="I558">
-        <v>57041993675.52446</v>
+        <v>11.84742192403976</v>
       </c>
       <c r="J558">
-        <v>41549410958.6431</v>
+        <v>41.54941095864311</v>
       </c>
     </row>
     <row r="559" spans="1:10">
@@ -18304,10 +18304,10 @@
         <v>20461897446.25027</v>
       </c>
       <c r="I559">
-        <v>57041993674.5591</v>
+        <v>10.88205539565097</v>
       </c>
       <c r="J559">
-        <v>36580096274.46877</v>
+        <v>36.58009627446877</v>
       </c>
     </row>
     <row r="560" spans="1:10">
@@ -18336,10 +18336,10 @@
         <v>50090240808.26</v>
       </c>
       <c r="I560">
-        <v>57041993668.38493</v>
+        <v>4.707890018181857</v>
       </c>
       <c r="J560">
-        <v>6951752912.45903</v>
+        <v>6.95175291245903</v>
       </c>
     </row>
     <row r="561" spans="1:10">
@@ -18368,10 +18368,10 @@
         <v>44611918648.84361</v>
       </c>
       <c r="I561">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J561">
-        <v>12430075071.87542</v>
+        <v>12.43007507187542</v>
       </c>
     </row>
     <row r="562" spans="1:10">
@@ -18400,10 +18400,10 @@
         <v>30707256943.90963</v>
       </c>
       <c r="I562">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J562">
-        <v>26334736776.8094</v>
+        <v>26.3347367768094</v>
       </c>
     </row>
     <row r="563" spans="1:10">
@@ -18432,10 +18432,10 @@
         <v>34680017431.03362</v>
       </c>
       <c r="I563">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J563">
-        <v>22361976289.68541</v>
+        <v>22.36197628968541</v>
       </c>
     </row>
     <row r="564" spans="1:10">
@@ -18464,10 +18464,10 @@
         <v>20823369682.39485</v>
       </c>
       <c r="I564">
-        <v>57041993674.49667</v>
+        <v>10.81963367276355</v>
       </c>
       <c r="J564">
-        <v>36218624038.32418</v>
+        <v>36.21862403832418</v>
       </c>
     </row>
     <row r="565" spans="1:10">
@@ -18496,10 +18496,10 @@
         <v>15842495867.90676</v>
       </c>
       <c r="I565">
-        <v>57041993675.37405</v>
+        <v>11.6970046075535</v>
       </c>
       <c r="J565">
-        <v>41199497852.81227</v>
+        <v>41.19949785281227</v>
       </c>
     </row>
     <row r="566" spans="1:10">
@@ -18528,10 +18528,10 @@
         <v>39447330015.58241</v>
       </c>
       <c r="I566">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J566">
-        <v>17594663705.13662</v>
+        <v>17.59466370513662</v>
       </c>
     </row>
     <row r="567" spans="1:10">
@@ -18560,10 +18560,10 @@
         <v>42029624332.21301</v>
       </c>
       <c r="I567">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J567">
-        <v>15012369388.50602</v>
+        <v>15.01236938850602</v>
       </c>
     </row>
     <row r="568" spans="1:10">
@@ -18592,10 +18592,10 @@
         <v>25628859680.38382</v>
       </c>
       <c r="I568">
-        <v>57041993673.51231</v>
+        <v>9.835270426570482</v>
       </c>
       <c r="J568">
-        <v>31413134040.33521</v>
+        <v>31.41313404033521</v>
       </c>
     </row>
     <row r="569" spans="1:10">
@@ -18624,10 +18624,10 @@
         <v>46815996602.72773</v>
       </c>
       <c r="I569">
-        <v>57041993669.54373</v>
+        <v>5.866689457942208</v>
       </c>
       <c r="J569">
-        <v>10225997117.9913</v>
+        <v>10.2259971179913</v>
       </c>
     </row>
     <row r="570" spans="1:10">
@@ -18656,10 +18656,10 @@
         <v>11705128027.83524</v>
       </c>
       <c r="I570">
-        <v>57041993676.77142</v>
+        <v>13.09438844643299</v>
       </c>
       <c r="J570">
-        <v>45336865692.88379</v>
+        <v>45.33686569288379</v>
       </c>
     </row>
     <row r="571" spans="1:10">
@@ -18688,10 +18688,10 @@
         <v>17250346023.88597</v>
       </c>
       <c r="I571">
-        <v>57041993675.21991</v>
+        <v>11.54287247992839</v>
       </c>
       <c r="J571">
-        <v>39791647696.83306</v>
+        <v>39.79164769683306</v>
       </c>
     </row>
     <row r="572" spans="1:10">
@@ -18720,10 +18720,10 @@
         <v>28327410931.55056</v>
       </c>
       <c r="I572">
-        <v>57041993672.7391</v>
+        <v>9.062060965211266</v>
       </c>
       <c r="J572">
-        <v>28714582789.16847</v>
+        <v>28.71458278916847</v>
       </c>
     </row>
     <row r="573" spans="1:10">
@@ -18752,10 +18752,10 @@
         <v>45732035520.01451</v>
       </c>
       <c r="I573">
-        <v>57041993671.06293</v>
+        <v>7.385895901928905</v>
       </c>
       <c r="J573">
-        <v>11309958200.70452</v>
+        <v>11.30995820070452</v>
       </c>
     </row>
     <row r="574" spans="1:10">
@@ -18784,10 +18784,10 @@
         <v>25250851209.35917</v>
       </c>
       <c r="I574">
-        <v>57041993673.60261</v>
+        <v>9.925569075063855</v>
       </c>
       <c r="J574">
-        <v>31791142511.35986</v>
+        <v>31.79114251135986</v>
       </c>
     </row>
     <row r="575" spans="1:10">
@@ -18816,10 +18816,10 @@
         <v>46050600875.90582</v>
       </c>
       <c r="I575">
-        <v>57041993670.63031</v>
+        <v>6.953267749580917</v>
       </c>
       <c r="J575">
-        <v>10991392844.81321</v>
+        <v>10.99139284481321</v>
       </c>
     </row>
     <row r="576" spans="1:10">
@@ -18848,10 +18848,10 @@
         <v>31501809041.33442</v>
       </c>
       <c r="I576">
-        <v>57041993672.53163</v>
+        <v>8.854590633463836</v>
       </c>
       <c r="J576">
-        <v>25540184679.38461</v>
+        <v>25.54018467938461</v>
       </c>
     </row>
     <row r="577" spans="1:10">
@@ -18880,10 +18880,10 @@
         <v>52716980233.74482</v>
       </c>
       <c r="I577">
-        <v>57041993666.84308</v>
+        <v>3.166036989735566</v>
       </c>
       <c r="J577">
-        <v>4325013486.974213</v>
+        <v>4.325013486974212</v>
       </c>
     </row>
     <row r="578" spans="1:10">
@@ -18912,10 +18912,10 @@
         <v>53775547293.63442</v>
       </c>
       <c r="I578">
-        <v>57041993666.13471</v>
+        <v>2.457676799230207</v>
       </c>
       <c r="J578">
-        <v>3266446427.08461</v>
+        <v>3.26644642708461</v>
       </c>
     </row>
     <row r="579" spans="1:10">
@@ -18944,10 +18944,10 @@
         <v>51053716903.47397</v>
       </c>
       <c r="I579">
-        <v>57041993667.06202</v>
+        <v>3.384977380567065</v>
       </c>
       <c r="J579">
-        <v>5988276817.245064</v>
+        <v>5.988276817245064</v>
       </c>
     </row>
     <row r="580" spans="1:10">
@@ -18976,10 +18976,10 @@
         <v>51704740705.68839</v>
       </c>
       <c r="I580">
-        <v>57041993667.00336</v>
+        <v>3.326316648746506</v>
       </c>
       <c r="J580">
-        <v>5337253015.03064</v>
+        <v>5.337253015030639</v>
       </c>
     </row>
     <row r="581" spans="1:10">
@@ -19008,10 +19008,10 @@
         <v>24126247644.29263</v>
       </c>
       <c r="I581">
-        <v>57041993673.85042</v>
+        <v>10.17338022033609</v>
       </c>
       <c r="J581">
-        <v>32915746076.4264</v>
+        <v>32.9157460764264</v>
       </c>
     </row>
     <row r="582" spans="1:10">
@@ -19040,10 +19040,10 @@
         <v>-3.309322252153853e+23</v>
       </c>
       <c r="I582">
-        <v>57041993691.39246</v>
+        <v>27.71542015271903</v>
       </c>
       <c r="J582">
-        <v>3.309322252154423e+23</v>
+        <v>330932225215442.3</v>
       </c>
     </row>
     <row r="583" spans="1:10">
@@ -19072,10 +19072,10 @@
         <v>23383729233.21111</v>
       </c>
       <c r="I583">
-        <v>57041993674.01356</v>
+        <v>10.3365197495931</v>
       </c>
       <c r="J583">
-        <v>33658264487.50792</v>
+        <v>33.65826448750792</v>
       </c>
     </row>
     <row r="584" spans="1:10">
@@ -19104,10 +19104,10 @@
         <v>23754306153.19304</v>
       </c>
       <c r="I584">
-        <v>57041993673.93314</v>
+        <v>10.25610682352522</v>
       </c>
       <c r="J584">
-        <v>33287687567.52599</v>
+        <v>33.28768756752599</v>
       </c>
     </row>
     <row r="585" spans="1:10">
@@ -19136,10 +19136,10 @@
         <v>32693637187.47162</v>
       </c>
       <c r="I585">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J585">
-        <v>24348356533.24741</v>
+        <v>24.34835653324742</v>
       </c>
     </row>
     <row r="586" spans="1:10">
@@ -19168,10 +19168,10 @@
         <v>52390289509.78645</v>
       </c>
       <c r="I586">
-        <v>57041993666.91231</v>
+        <v>3.235269105218975</v>
       </c>
       <c r="J586">
-        <v>4651704210.932579</v>
+        <v>4.651704210932579</v>
       </c>
     </row>
     <row r="587" spans="1:10">
@@ -19200,10 +19200,10 @@
         <v>31899085090.04681</v>
       </c>
       <c r="I587">
-        <v>57041993672.53163</v>
+        <v>8.854590633463836</v>
       </c>
       <c r="J587">
-        <v>25142908630.67222</v>
+        <v>25.14290863067222</v>
       </c>
     </row>
     <row r="588" spans="1:10">
@@ -19232,10 +19232,10 @@
         <v>51228416810.71766</v>
       </c>
       <c r="I588">
-        <v>57041993667.22072</v>
+        <v>3.543683303219716</v>
       </c>
       <c r="J588">
-        <v>5813576910.001373</v>
+        <v>5.813576910001373</v>
       </c>
     </row>
     <row r="589" spans="1:10">
@@ -19264,10 +19264,10 @@
         <v>42426900380.92541</v>
       </c>
       <c r="I589">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J589">
-        <v>14615093339.79362</v>
+        <v>14.61509333979362</v>
       </c>
     </row>
     <row r="590" spans="1:10">
@@ -19296,10 +19296,10 @@
         <v>19384098943.21065</v>
       </c>
       <c r="I590">
-        <v>57041993674.83627</v>
+        <v>11.15923044649637</v>
       </c>
       <c r="J590">
-        <v>37657894777.50838</v>
+        <v>37.65789477750837</v>
       </c>
     </row>
     <row r="591" spans="1:10">
@@ -19328,10 +19328,10 @@
         <v>33488189284.89642</v>
       </c>
       <c r="I591">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J591">
-        <v>23553804435.82261</v>
+        <v>23.55380443582261</v>
       </c>
     </row>
     <row r="592" spans="1:10">
@@ -19360,10 +19360,10 @@
         <v>24499612178.7907</v>
       </c>
       <c r="I592">
-        <v>57041993673.76524</v>
+        <v>10.08819871775975</v>
       </c>
       <c r="J592">
-        <v>32542381541.92833</v>
+        <v>32.54238154192834</v>
       </c>
     </row>
     <row r="593" spans="1:10">
@@ -19392,10 +19392,10 @@
         <v>21549325981.89934</v>
       </c>
       <c r="I593">
-        <v>57041993674.36661</v>
+        <v>10.68956889308888</v>
       </c>
       <c r="J593">
-        <v>35492667738.81969</v>
+        <v>35.49266773881968</v>
       </c>
     </row>
     <row r="594" spans="1:10">
@@ -19424,10 +19424,10 @@
         <v>31104532992.62202</v>
       </c>
       <c r="I594">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J594">
-        <v>25937460728.09701</v>
+        <v>25.93746072809701</v>
       </c>
     </row>
     <row r="595" spans="1:10">
@@ -19456,10 +19456,10 @@
         <v>19742632107.90998</v>
       </c>
       <c r="I595">
-        <v>57041993674.75996</v>
+        <v>11.08292497640486</v>
       </c>
       <c r="J595">
-        <v>37299361612.80905</v>
+        <v>37.29936161280905</v>
       </c>
     </row>
     <row r="596" spans="1:10">
@@ -19488,10 +19488,10 @@
         <v>41632348283.50063</v>
       </c>
       <c r="I596">
-        <v>57041993672.53163</v>
+        <v>8.854590633463815</v>
       </c>
       <c r="J596">
-        <v>15409645437.2184</v>
+        <v>15.4096454372184</v>
       </c>
     </row>
     <row r="597" spans="1:10">
@@ -19520,10 +19520,10 @@
         <v>32296361138.75923</v>
       </c>
       <c r="I597">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J597">
-        <v>24745632581.9598</v>
+        <v>24.7456325819598</v>
       </c>
     </row>
     <row r="598" spans="1:10">
@@ -19552,10 +19552,10 @@
         <v>23014461848.81642</v>
       </c>
       <c r="I598">
-        <v>57041993674.09179</v>
+        <v>10.41475058976059</v>
       </c>
       <c r="J598">
-        <v>34027531871.90261</v>
+        <v>34.02753187190261</v>
       </c>
     </row>
     <row r="599" spans="1:10">
@@ -19584,10 +19584,10 @@
         <v>45207832721.9122</v>
       </c>
       <c r="I599">
-        <v>57041993672.53163</v>
+        <v>8.854590633463836</v>
       </c>
       <c r="J599">
-        <v>11834160998.80683</v>
+        <v>11.83416099880683</v>
       </c>
     </row>
     <row r="600" spans="1:10">
@@ -19616,10 +19616,10 @@
         <v>46408045642.46646</v>
       </c>
       <c r="I600">
-        <v>57041993670.12711</v>
+        <v>6.450066070001995</v>
       </c>
       <c r="J600">
-        <v>10633948078.25257</v>
+        <v>10.63394807825257</v>
       </c>
     </row>
     <row r="601" spans="1:10">
@@ -19648,10 +19648,10 @@
         <v>43221452478.35021</v>
       </c>
       <c r="I601">
-        <v>57041993672.53163</v>
+        <v>8.854590633463822</v>
       </c>
       <c r="J601">
-        <v>13820541242.36882</v>
+        <v>13.82054124236882</v>
       </c>
     </row>
     <row r="602" spans="1:10">
@@ -19680,10 +19680,10 @@
         <v>44016004575.775</v>
       </c>
       <c r="I602">
-        <v>57041993672.53163</v>
+        <v>8.854590633463836</v>
       </c>
       <c r="J602">
-        <v>13025989144.94403</v>
+        <v>13.02598914494403</v>
       </c>
     </row>
     <row r="603" spans="1:10">
@@ -19712,10 +19712,10 @@
         <v>50740004961.39278</v>
       </c>
       <c r="I603">
-        <v>57041993667.10093</v>
+        <v>3.423888737862747</v>
       </c>
       <c r="J603">
-        <v>6301988759.326256</v>
+        <v>6.301988759326256</v>
       </c>
     </row>
     <row r="604" spans="1:10">
@@ -19744,10 +19744,10 @@
         <v>17673101732.48441</v>
       </c>
       <c r="I604">
-        <v>57041993670.95233</v>
+        <v>7.275296301469922</v>
       </c>
       <c r="J604">
-        <v>39368891988.23462</v>
+        <v>39.36889198823462</v>
       </c>
     </row>
     <row r="605" spans="1:10">
@@ -19776,10 +19776,10 @@
         <v>54770925216.62358</v>
       </c>
       <c r="I605">
-        <v>57041993664.64137</v>
+        <v>0.9643299452474778</v>
       </c>
       <c r="J605">
-        <v>2271068504.095451</v>
+        <v>2.271068504095451</v>
       </c>
     </row>
     <row r="606" spans="1:10">
@@ -19808,10 +19808,10 @@
         <v>16908438321.47385</v>
       </c>
       <c r="I606">
-        <v>57041993670.86147</v>
+        <v>7.184428390161301</v>
       </c>
       <c r="J606">
-        <v>40133555399.24518</v>
+        <v>40.13355539924518</v>
       </c>
     </row>
     <row r="607" spans="1:10">
@@ -19840,10 +19840,10 @@
         <v>18257069324.19238</v>
       </c>
       <c r="I607">
-        <v>57041993670.81037</v>
+        <v>7.133333710342065</v>
       </c>
       <c r="J607">
-        <v>38784924396.52666</v>
+        <v>38.78492439652666</v>
       </c>
     </row>
     <row r="608" spans="1:10">
@@ -19872,10 +19872,10 @@
         <v>22402608520.17279</v>
       </c>
       <c r="I608">
-        <v>57041993670.58872</v>
+        <v>6.911681620064655</v>
       </c>
       <c r="J608">
-        <v>34639385200.54624</v>
+        <v>34.63938520054624</v>
       </c>
     </row>
     <row r="609" spans="1:10">
@@ -19904,10 +19904,10 @@
         <v>55669275056.69038</v>
       </c>
       <c r="I609">
-        <v>57041993664.52681</v>
+        <v>0.8497702602566477</v>
       </c>
       <c r="J609">
-        <v>1372718664.028656</v>
+        <v>1.372718664028656</v>
       </c>
     </row>
     <row r="610" spans="1:10">
@@ -19936,10 +19936,10 @@
         <v>55949492588.53622</v>
       </c>
       <c r="I610">
-        <v>57041993664.57512</v>
+        <v>0.898078616089407</v>
       </c>
       <c r="J610">
-        <v>1092501132.182816</v>
+        <v>1.092501132182816</v>
       </c>
     </row>
     <row r="611" spans="1:10">
@@ -19968,10 +19968,10 @@
         <v>55090812931.40745</v>
       </c>
       <c r="I611">
-        <v>57041993664.60178</v>
+        <v>0.9247481837051978</v>
       </c>
       <c r="J611">
-        <v>1951180789.311584</v>
+        <v>1.951180789311584</v>
       </c>
     </row>
     <row r="612" spans="1:10">
@@ -20000,10 +20000,10 @@
         <v>55342430895.42829</v>
       </c>
       <c r="I612">
-        <v>57041993664.70715</v>
+        <v>1.030109227913137</v>
       </c>
       <c r="J612">
-        <v>1699562825.290741</v>
+        <v>1.699562825290741</v>
       </c>
     </row>
     <row r="613" spans="1:10">
@@ -20032,10 +20032,10 @@
         <v>15686931744.51282</v>
       </c>
       <c r="I613">
-        <v>57041993670.91113</v>
+        <v>7.234094803168176</v>
       </c>
       <c r="J613">
-        <v>41355061976.20621</v>
+        <v>41.35506197620622</v>
       </c>
     </row>
     <row r="614" spans="1:10">
@@ -20064,10 +20064,10 @@
         <v>55597376127.4279</v>
       </c>
       <c r="I614">
-        <v>57041993664.55061</v>
+        <v>0.873576052834224</v>
       </c>
       <c r="J614">
-        <v>1444617593.29113</v>
+        <v>1.44461759329113</v>
       </c>
     </row>
     <row r="615" spans="1:10">
@@ -20096,10 +20096,10 @@
         <v>16202089742.69099</v>
       </c>
       <c r="I615">
-        <v>57041993670.71555</v>
+        <v>7.038505240474791</v>
       </c>
       <c r="J615">
-        <v>40839903978.02805</v>
+        <v>40.83990397802805</v>
       </c>
     </row>
     <row r="616" spans="1:10">
@@ -20128,10 +20128,10 @@
         <v>55205891166.84655</v>
       </c>
       <c r="I616">
-        <v>57041993664.60341</v>
+        <v>0.9263687280666844</v>
       </c>
       <c r="J616">
-        <v>1836102553.872482</v>
+        <v>1.836102553872482</v>
       </c>
     </row>
     <row r="617" spans="1:10">
@@ -20160,10 +20160,10 @@
         <v>19292284580.37217</v>
       </c>
       <c r="I617">
-        <v>57041993670.78077</v>
+        <v>7.103730817850717</v>
       </c>
       <c r="J617">
-        <v>37749709140.34686</v>
+        <v>37.74970914034687</v>
       </c>
     </row>
     <row r="618" spans="1:10">
@@ -20192,10 +20192,10 @@
         <v>18192389576.39477</v>
       </c>
       <c r="I618">
-        <v>57041993670.7296</v>
+        <v>7.052563062282132</v>
       </c>
       <c r="J618">
-        <v>38849604144.32426</v>
+        <v>38.84960414432427</v>
       </c>
     </row>
     <row r="619" spans="1:10">
@@ -20224,10 +20224,10 @@
         <v>15011403545.47689</v>
       </c>
       <c r="I619">
-        <v>57041993670.95509</v>
+        <v>7.278045519366813</v>
       </c>
       <c r="J619">
-        <v>42030590175.24214</v>
+        <v>42.03059017524214</v>
       </c>
     </row>
     <row r="620" spans="1:10">
@@ -20256,10 +20256,10 @@
         <v>20416429905.83108</v>
       </c>
       <c r="I620">
-        <v>57041993670.67924</v>
+        <v>7.002206109334423</v>
       </c>
       <c r="J620">
-        <v>36625563814.88795</v>
+        <v>36.62556381488795</v>
       </c>
     </row>
     <row r="621" spans="1:10">
@@ -20288,10 +20288,10 @@
         <v>19683662888.47696</v>
       </c>
       <c r="I621">
-        <v>57041993670.68906</v>
+        <v>7.012026600234577</v>
       </c>
       <c r="J621">
-        <v>37358330832.24207</v>
+        <v>37.35833083224207</v>
       </c>
     </row>
     <row r="622" spans="1:10">
@@ -20320,10 +20320,10 @@
         <v>18715487498.93219</v>
       </c>
       <c r="I622">
-        <v>57041993670.57418</v>
+        <v>6.897144295957645</v>
       </c>
       <c r="J622">
-        <v>38326506221.78684</v>
+        <v>38.32650622178684</v>
       </c>
     </row>
     <row r="623" spans="1:10">
@@ -20352,10 +20352,10 @@
         <v>20204420819.17849</v>
       </c>
       <c r="I623">
-        <v>57041993670.81756</v>
+        <v>7.140519899358424</v>
       </c>
       <c r="J623">
-        <v>36837572901.54054</v>
+        <v>36.83757290154054</v>
       </c>
     </row>
     <row r="624" spans="1:10">
@@ -20384,10 +20384,10 @@
         <v>54962951956.26079</v>
       </c>
       <c r="I624">
-        <v>57041993664.60406</v>
+        <v>0.9270285704814114</v>
       </c>
       <c r="J624">
-        <v>2079041764.458244</v>
+        <v>2.079041764458244</v>
       </c>
     </row>
     <row r="625" spans="1:10">
@@ -20416,10 +20416,10 @@
         <v>21901477646.57484</v>
       </c>
       <c r="I625">
-        <v>57041993670.67191</v>
+        <v>6.994877846757184</v>
       </c>
       <c r="J625">
-        <v>35140516074.1442</v>
+        <v>35.14051607414419</v>
       </c>
     </row>
     <row r="626" spans="1:10">
@@ -20448,10 +20448,10 @@
         <v>51682371061.17366</v>
       </c>
       <c r="I626">
-        <v>57041993667.62621</v>
+        <v>3.949169311647218</v>
       </c>
       <c r="J626">
-        <v>5359622659.545372</v>
+        <v>5.359622659545372</v>
       </c>
     </row>
     <row r="627" spans="1:10">
@@ -20480,10 +20480,10 @@
         <v>48963279954.40454</v>
       </c>
       <c r="I627">
-        <v>57041993671.38638</v>
+        <v>7.709337425197518</v>
       </c>
       <c r="J627">
-        <v>8078713766.314491</v>
+        <v>8.078713766314491</v>
       </c>
     </row>
     <row r="628" spans="1:10">
@@ -20512,10 +20512,10 @@
         <v>51447295313.60847</v>
       </c>
       <c r="I628">
-        <v>57041993667.62621</v>
+        <v>3.949169501229377</v>
       </c>
       <c r="J628">
-        <v>5594698407.110565</v>
+        <v>5.594698407110565</v>
       </c>
     </row>
     <row r="629" spans="1:10">
@@ -20544,10 +20544,10 @@
         <v>-3.703781244497517e+23</v>
       </c>
       <c r="I629">
-        <v>57041993686.15797</v>
+        <v>22.48092876071903</v>
       </c>
       <c r="J629">
-        <v>3.703781244498088e+23</v>
+        <v>370378124449808.8</v>
       </c>
     </row>
     <row r="630" spans="1:10">
@@ -20576,10 +20576,10 @@
         <v>50977143818.4781</v>
       </c>
       <c r="I630">
-        <v>57041993667.62621</v>
+        <v>3.949169880393704</v>
       </c>
       <c r="J630">
-        <v>6064849902.240929</v>
+        <v>6.064849902240929</v>
       </c>
     </row>
     <row r="631" spans="1:10">
@@ -20608,10 +20608,10 @@
         <v>49055624114.15681</v>
       </c>
       <c r="I631">
-        <v>57041993671.38638</v>
+        <v>7.709337350724482</v>
       </c>
       <c r="J631">
-        <v>7986369606.562225</v>
+        <v>7.986369606562225</v>
       </c>
     </row>
     <row r="632" spans="1:10">
@@ -20640,10 +20640,10 @@
         <v>50506992323.34774</v>
       </c>
       <c r="I632">
-        <v>57041993667.62621</v>
+        <v>3.949170259558016</v>
       </c>
       <c r="J632">
-        <v>6535001397.371292</v>
+        <v>6.535001397371292</v>
       </c>
     </row>
     <row r="633" spans="1:10">
@@ -20672,10 +20672,10 @@
         <v>49221068893.08105</v>
       </c>
       <c r="I633">
-        <v>57041993671.39731</v>
+        <v>7.720268882750041</v>
       </c>
       <c r="J633">
-        <v>7820924827.637985</v>
+        <v>7.820924827637985</v>
       </c>
     </row>
     <row r="634" spans="1:10">
@@ -20704,10 +20704,10 @@
         <v>51212219566.04327</v>
       </c>
       <c r="I634">
-        <v>57041993667.62621</v>
+        <v>3.949169690811566</v>
       </c>
       <c r="J634">
-        <v>5829774154.675766</v>
+        <v>5.829774154675766</v>
       </c>
     </row>
     <row r="635" spans="1:10">
@@ -20736,10 +20736,10 @@
         <v>47092395201.82293</v>
       </c>
       <c r="I635">
-        <v>57041993673.18262</v>
+        <v>9.505584972456866</v>
       </c>
       <c r="J635">
-        <v>9949598518.896103</v>
+        <v>9.949598518896103</v>
       </c>
     </row>
     <row r="636" spans="1:10">
@@ -20768,10 +20768,10 @@
         <v>47794872567.71782</v>
       </c>
       <c r="I636">
-        <v>57041993672.58868</v>
+        <v>8.911635340058787</v>
       </c>
       <c r="J636">
-        <v>9247121153.001213</v>
+        <v>9.247121153001213</v>
       </c>
     </row>
     <row r="637" spans="1:10">
@@ -20800,10 +20800,10 @@
         <v>47018392884.40219</v>
       </c>
       <c r="I637">
-        <v>57041993673.18262</v>
+        <v>9.505585032137738</v>
       </c>
       <c r="J637">
-        <v>10023600836.31684</v>
+        <v>10.02360083631684</v>
       </c>
     </row>
     <row r="638" spans="1:10">
@@ -20832,10 +20832,10 @@
         <v>-3.400488613949266e+23</v>
       </c>
       <c r="I638">
-        <v>57041993686.96327</v>
+        <v>23.28623512871904</v>
       </c>
       <c r="J638">
-        <v>3.400488613949837e+23</v>
+        <v>340048861394983.7</v>
       </c>
     </row>
     <row r="639" spans="1:10">
@@ -20864,10 +20864,10 @@
         <v>46870388249.56078</v>
       </c>
       <c r="I639">
-        <v>57041993673.18262</v>
+        <v>9.505585151499382</v>
       </c>
       <c r="J639">
-        <v>10171605471.15825</v>
+        <v>10.17160547115825</v>
       </c>
     </row>
     <row r="640" spans="1:10">
@@ -20896,10 +20896,10 @@
         <v>47878744088.59351</v>
       </c>
       <c r="I640">
-        <v>57041993672.58868</v>
+        <v>8.911635272418692</v>
       </c>
       <c r="J640">
-        <v>9163249632.125519</v>
+        <v>9.163249632125519</v>
       </c>
     </row>
     <row r="641" spans="1:10">
@@ -20928,10 +20928,10 @@
         <v>48044186219.42191</v>
       </c>
       <c r="I641">
-        <v>57041993672.58997</v>
+        <v>8.912926638283722</v>
       </c>
       <c r="J641">
-        <v>8997807501.297119</v>
+        <v>8.997807501297119</v>
       </c>
     </row>
     <row r="642" spans="1:10">
@@ -20960,10 +20960,10 @@
         <v>46944390566.98151</v>
       </c>
       <c r="I642">
-        <v>57041993673.18262</v>
+        <v>9.505585091818531</v>
       </c>
       <c r="J642">
-        <v>10097603153.73753</v>
+        <v>10.09760315373753</v>
       </c>
     </row>
     <row r="643" spans="1:10">
@@ -20992,10 +20992,10 @@
         <v>52262551902.32273</v>
       </c>
       <c r="I643">
-        <v>57041993666.77572</v>
+        <v>3.098679871622721</v>
       </c>
       <c r="J643">
-        <v>4779441818.396301</v>
+        <v>4.779441818396301</v>
       </c>
     </row>
     <row r="644" spans="1:10">
@@ -21024,10 +21024,10 @@
         <v>52822806336.41046</v>
       </c>
       <c r="I644">
-        <v>57041993666.77572</v>
+        <v>3.098679419792852</v>
       </c>
       <c r="J644">
-        <v>4219187384.308571</v>
+        <v>4.219187384308571</v>
       </c>
     </row>
     <row r="645" spans="1:10">
@@ -21056,10 +21056,10 @@
         <v>51982424685.27883</v>
       </c>
       <c r="I645">
-        <v>57041993666.77572</v>
+        <v>3.098680097537702</v>
       </c>
       <c r="J645">
-        <v>5059569035.440201</v>
+        <v>5.059569035440201</v>
       </c>
     </row>
     <row r="646" spans="1:10">
@@ -21088,10 +21088,10 @@
         <v>-3.414360078836756e+23</v>
       </c>
       <c r="I646">
-        <v>57041993686.82906</v>
+        <v>23.15201740071903</v>
       </c>
       <c r="J646">
-        <v>3.414360078837326e+23</v>
+        <v>341436007883732.6</v>
       </c>
     </row>
     <row r="647" spans="1:10">
@@ -21120,10 +21120,10 @@
         <v>51422170251.19113</v>
       </c>
       <c r="I647">
-        <v>57041993666.77572</v>
+        <v>3.098680549367558</v>
       </c>
       <c r="J647">
-        <v>5619823469.527901</v>
+        <v>5.6198234695279</v>
       </c>
     </row>
     <row r="648" spans="1:10">
@@ -21152,10 +21152,10 @@
         <v>53102933553.45429</v>
       </c>
       <c r="I648">
-        <v>57041993666.77572</v>
+        <v>3.098679193877956</v>
       </c>
       <c r="J648">
-        <v>3939060167.26474</v>
+        <v>3.93906016726474</v>
       </c>
     </row>
     <row r="649" spans="1:10">
@@ -21184,10 +21184,10 @@
         <v>50872290119.16448</v>
       </c>
       <c r="I649">
-        <v>57041993667.04687</v>
+        <v>3.369830507324266</v>
       </c>
       <c r="J649">
-        <v>6169703601.55455</v>
+        <v>6.16970360155455</v>
       </c>
     </row>
     <row r="650" spans="1:10">
@@ -21216,10 +21216,10 @@
         <v>53756849083.18857</v>
       </c>
       <c r="I650">
-        <v>57041993666.6199</v>
+        <v>2.942862572106627</v>
       </c>
       <c r="J650">
-        <v>3285144637.530464</v>
+        <v>3.285144637530464</v>
       </c>
     </row>
     <row r="651" spans="1:10">
@@ -21248,10 +21248,10 @@
         <v>51702297468.23497</v>
       </c>
       <c r="I651">
-        <v>57041993666.77572</v>
+        <v>3.098680323452633</v>
       </c>
       <c r="J651">
-        <v>5339696252.484062</v>
+        <v>5.339696252484062</v>
       </c>
     </row>
   </sheetData>

--- a/benchmarks/results/plots/results-Fig1.xlsx
+++ b/benchmarks/results/plots/results-Fig1.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J663"/>
+  <dimension ref="A1:J807"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22754,7 +22754,7 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C657" t="n">
         <v>2900</v>
@@ -22772,13 +22772,13 @@
         <v>6841.96619517</v>
       </c>
       <c r="H657" t="n">
-        <v>3.7048542e+17</v>
+        <v>53195825100</v>
       </c>
       <c r="I657" t="n">
         <v>2.319081540719033</v>
       </c>
       <c r="J657" t="n">
-        <v>-370485362.9580063</v>
+        <v>3.846168620719032</v>
       </c>
     </row>
     <row r="658">
@@ -22788,7 +22788,7 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="C658" t="n">
         <v>2900</v>
@@ -22800,19 +22800,19 @@
         <v>0.1</v>
       </c>
       <c r="F658" t="n">
-        <v>54.72291218</v>
+        <v>52.99551895</v>
       </c>
       <c r="G658" t="n">
-        <v>6841.96619517</v>
+        <v>3226.373552</v>
       </c>
       <c r="H658" t="n">
-        <v>53195825100</v>
+        <v>40993722300</v>
       </c>
       <c r="I658" t="n">
-        <v>2.319081540719033</v>
+        <v>4.046474770719037</v>
       </c>
       <c r="J658" t="n">
-        <v>3.846168620719032</v>
+        <v>16.04827142071903</v>
       </c>
     </row>
     <row r="659">
@@ -22822,7 +22822,7 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="C659" t="n">
         <v>2900</v>
@@ -22834,19 +22834,19 @@
         <v>0.1</v>
       </c>
       <c r="F659" t="n">
-        <v>52.99551895</v>
+        <v>54.73168499</v>
       </c>
       <c r="G659" t="n">
-        <v>3226.373552</v>
+        <v>6954.92949453</v>
       </c>
       <c r="H659" t="n">
-        <v>40993722300</v>
+        <v>54472968400</v>
       </c>
       <c r="I659" t="n">
-        <v>4.046474770719037</v>
+        <v>2.310308730719036</v>
       </c>
       <c r="J659" t="n">
-        <v>16.04827142071903</v>
+        <v>2.569025320719032</v>
       </c>
     </row>
     <row r="660">
@@ -22856,7 +22856,7 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C660" t="n">
         <v>2900</v>
@@ -22868,19 +22868,19 @@
         <v>0.1</v>
       </c>
       <c r="F660" t="n">
-        <v>54.73168499</v>
+        <v>54.73164069</v>
       </c>
       <c r="G660" t="n">
-        <v>6954.92949453</v>
+        <v>6955.28637105</v>
       </c>
       <c r="H660" t="n">
-        <v>54472968400</v>
+        <v>54731640700</v>
       </c>
       <c r="I660" t="n">
-        <v>2.310308730719036</v>
+        <v>2.310353030719035</v>
       </c>
       <c r="J660" t="n">
-        <v>2.569025320719032</v>
+        <v>2.310353020719032</v>
       </c>
     </row>
     <row r="661">
@@ -22890,7 +22890,7 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C661" t="n">
         <v>2900</v>
@@ -22902,19 +22902,19 @@
         <v>0.1</v>
       </c>
       <c r="F661" t="n">
-        <v>54.73164069</v>
+        <v>54.77731789</v>
       </c>
       <c r="G661" t="n">
-        <v>6955.28637105</v>
+        <v>5547.01036454</v>
       </c>
       <c r="H661" t="n">
-        <v>54731640700</v>
+        <v>52713883800</v>
       </c>
       <c r="I661" t="n">
-        <v>2.310353030719035</v>
+        <v>2.264675830719035</v>
       </c>
       <c r="J661" t="n">
-        <v>2.310353020719032</v>
+        <v>4.328109920719032</v>
       </c>
     </row>
     <row r="662">
@@ -22924,7 +22924,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C662" t="n">
         <v>2900</v>
@@ -22936,19 +22936,19 @@
         <v>0.1</v>
       </c>
       <c r="F662" t="n">
-        <v>54.77731789</v>
+        <v>54.73279509</v>
       </c>
       <c r="G662" t="n">
-        <v>5547.01036454</v>
+        <v>6294.76541596</v>
       </c>
       <c r="H662" t="n">
-        <v>52713883800</v>
+        <v>52625362600</v>
       </c>
       <c r="I662" t="n">
-        <v>2.264675830719035</v>
+        <v>2.309198630719031</v>
       </c>
       <c r="J662" t="n">
-        <v>4.328109920719032</v>
+        <v>4.416631120719032</v>
       </c>
     </row>
     <row r="663">
@@ -22958,31 +22958,4927 @@
         </is>
       </c>
       <c r="B663" t="n">
+        <v>900</v>
+      </c>
+      <c r="C663" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D663" t="n">
+        <v>0</v>
+      </c>
+      <c r="E663" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F663" t="n">
+        <v>52.60129063360343</v>
+      </c>
+      <c r="G663" t="n">
+        <v>2961.141314147122</v>
+      </c>
+      <c r="H663" t="n">
+        <v>-46535135487.67496</v>
+      </c>
+      <c r="I663" t="n">
+        <v>4.440703087115601</v>
+      </c>
+      <c r="J663" t="n">
+        <v>103.577129208394</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>150</v>
+      </c>
+      <c r="C664" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D664" t="n">
+        <v>0</v>
+      </c>
+      <c r="E664" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F664" t="n">
+        <v>52.67575902321241</v>
+      </c>
+      <c r="G664" t="n">
+        <v>3027.303953584812</v>
+      </c>
+      <c r="H664" t="n">
+        <v>35783843434.93441</v>
+      </c>
+      <c r="I664" t="n">
+        <v>4.366234697506627</v>
+      </c>
+      <c r="J664" t="n">
+        <v>21.25815028578462</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B665" t="n">
+        <v>175</v>
+      </c>
+      <c r="C665" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D665" t="n">
+        <v>0</v>
+      </c>
+      <c r="E665" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F665" t="n">
+        <v>52.6181580578502</v>
+      </c>
+      <c r="G665" t="n">
+        <v>2971.216374102334</v>
+      </c>
+      <c r="H665" t="n">
+        <v>33276043826.42352</v>
+      </c>
+      <c r="I665" t="n">
+        <v>4.423835662868832</v>
+      </c>
+      <c r="J665" t="n">
+        <v>23.76594989429551</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>200</v>
+      </c>
+      <c r="C666" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D666" t="n">
+        <v>0</v>
+      </c>
+      <c r="E666" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F666" t="n">
+        <v>52.6181580578502</v>
+      </c>
+      <c r="G666" t="n">
+        <v>2971.216374102334</v>
+      </c>
+      <c r="H666" t="n">
+        <v>30512884650.50542</v>
+      </c>
+      <c r="I666" t="n">
+        <v>4.423835662868832</v>
+      </c>
+      <c r="J666" t="n">
+        <v>26.52910907021361</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>125</v>
+      </c>
+      <c r="C667" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D667" t="n">
+        <v>0</v>
+      </c>
+      <c r="E667" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F667" t="n">
+        <v>52.70163806637728</v>
+      </c>
+      <c r="G667" t="n">
+        <v>3089.642037264008</v>
+      </c>
+      <c r="H667" t="n">
+        <v>38335177212.19666</v>
+      </c>
+      <c r="I667" t="n">
+        <v>4.340355654341757</v>
+      </c>
+      <c r="J667" t="n">
+        <v>18.70681650852237</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>500</v>
+      </c>
+      <c r="C668" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D668" t="n">
+        <v>0</v>
+      </c>
+      <c r="E668" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F668" t="n">
+        <v>52.60401571297889</v>
+      </c>
+      <c r="G668" t="n">
+        <v>2962.144652065069</v>
+      </c>
+      <c r="H668" t="n">
+        <v>-2490438175.275136</v>
+      </c>
+      <c r="I668" t="n">
+        <v>4.437978007740142</v>
+      </c>
+      <c r="J668" t="n">
+        <v>59.53243189599417</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>250</v>
+      </c>
+      <c r="C669" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D669" t="n">
+        <v>0</v>
+      </c>
+      <c r="E669" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F669" t="n">
+        <v>52.6181580578502</v>
+      </c>
+      <c r="G669" t="n">
+        <v>2971.216374102334</v>
+      </c>
+      <c r="H669" t="n">
+        <v>24986566298.66922</v>
+      </c>
+      <c r="I669" t="n">
+        <v>4.423835662868832</v>
+      </c>
+      <c r="J669" t="n">
+        <v>32.05542742204981</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>400</v>
+      </c>
+      <c r="C670" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D670" t="n">
+        <v>0</v>
+      </c>
+      <c r="E670" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F670" t="n">
+        <v>52.60699305916311</v>
+      </c>
+      <c r="G670" t="n">
+        <v>2963.296610754168</v>
+      </c>
+      <c r="H670" t="n">
+        <v>8514289250.226069</v>
+      </c>
+      <c r="I670" t="n">
+        <v>4.435000661555925</v>
+      </c>
+      <c r="J670" t="n">
+        <v>48.52770447049296</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>600</v>
+      </c>
+      <c r="C671" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D671" t="n">
+        <v>0</v>
+      </c>
+      <c r="E671" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F671" t="n">
+        <v>52.60098458117997</v>
+      </c>
+      <c r="G671" t="n">
+        <v>2961.114644152961</v>
+      </c>
+      <c r="H671" t="n">
+        <v>-13489370907.59124</v>
+      </c>
+      <c r="I671" t="n">
+        <v>4.441009139539062</v>
+      </c>
+      <c r="J671" t="n">
+        <v>70.53136462831027</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>75</v>
+      </c>
+      <c r="C672" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D672" t="n">
+        <v>0</v>
+      </c>
+      <c r="E672" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F672" t="n">
+        <v>53.0174790798889</v>
+      </c>
+      <c r="G672" t="n">
+        <v>3337.809819928043</v>
+      </c>
+      <c r="H672" t="n">
+        <v>43705232507.95406</v>
+      </c>
+      <c r="I672" t="n">
+        <v>4.024514640830134</v>
+      </c>
+      <c r="J672" t="n">
+        <v>13.33676121276497</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>700</v>
+      </c>
+      <c r="C673" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D673" t="n">
+        <v>0</v>
+      </c>
+      <c r="E673" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F673" t="n">
+        <v>52.60129654074559</v>
+      </c>
+      <c r="G673" t="n">
+        <v>2961.141532068931</v>
+      </c>
+      <c r="H673" t="n">
+        <v>-24504818339.22909</v>
+      </c>
+      <c r="I673" t="n">
+        <v>4.440697179973448</v>
+      </c>
+      <c r="J673" t="n">
+        <v>81.54681205994812</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>800</v>
+      </c>
+      <c r="C674" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D674" t="n">
+        <v>0</v>
+      </c>
+      <c r="E674" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F674" t="n">
+        <v>52.60129232353071</v>
+      </c>
+      <c r="G674" t="n">
+        <v>2961.141214985125</v>
+      </c>
+      <c r="H674" t="n">
+        <v>-35519972388.84377</v>
+      </c>
+      <c r="I674" t="n">
+        <v>4.440701397188327</v>
+      </c>
+      <c r="J674" t="n">
+        <v>92.5619661095628</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>300</v>
+      </c>
+      <c r="C675" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D675" t="n">
+        <v>0</v>
+      </c>
+      <c r="E675" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F675" t="n">
+        <v>52.6181580578502</v>
+      </c>
+      <c r="G675" t="n">
+        <v>2971.216374102334</v>
+      </c>
+      <c r="H675" t="n">
+        <v>19460247946.83303</v>
+      </c>
+      <c r="I675" t="n">
+        <v>4.423835662868832</v>
+      </c>
+      <c r="J675" t="n">
+        <v>37.581745773886</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>2</v>
+      </c>
+      <c r="C676" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D676" t="n">
+        <v>0</v>
+      </c>
+      <c r="E676" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F676" t="n">
+        <v>54.7316849888842</v>
+      </c>
+      <c r="G676" t="n">
+        <v>6954.929494532066</v>
+      </c>
+      <c r="H676" t="n">
+        <v>54214251727.05424</v>
+      </c>
+      <c r="I676" t="n">
+        <v>2.310308731834837</v>
+      </c>
+      <c r="J676" t="n">
+        <v>2.827741993664795</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>50</v>
+      </c>
+      <c r="C677" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D677" t="n">
+        <v>0</v>
+      </c>
+      <c r="E677" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F677" t="n">
+        <v>53.58054813236661</v>
+      </c>
+      <c r="G677" t="n">
+        <v>2602.742443997326</v>
+      </c>
+      <c r="H677" t="n">
+        <v>48739573419.54012</v>
+      </c>
+      <c r="I677" t="n">
+        <v>3.461445588352426</v>
+      </c>
+      <c r="J677" t="n">
+        <v>8.302420301178909</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>900</v>
+      </c>
+      <c r="C678" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D678" t="n">
+        <v>0</v>
+      </c>
+      <c r="E678" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F678" t="n">
+        <v>52.31123593554544</v>
+      </c>
+      <c r="G678" t="n">
+        <v>2122.338405713366</v>
+      </c>
+      <c r="H678" t="n">
+        <v>-18742801086.30988</v>
+      </c>
+      <c r="I678" t="n">
+        <v>4.730757785173594</v>
+      </c>
+      <c r="J678" t="n">
+        <v>75.78479480702892</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>5</v>
+      </c>
+      <c r="C679" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D679" t="n">
+        <v>0</v>
+      </c>
+      <c r="E679" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F679" t="n">
+        <v>54.53354568104061</v>
+      </c>
+      <c r="G679" t="n">
+        <v>3618.471513448639</v>
+      </c>
+      <c r="H679" t="n">
+        <v>53860527529.12601</v>
+      </c>
+      <c r="I679" t="n">
+        <v>2.508448039678427</v>
+      </c>
+      <c r="J679" t="n">
+        <v>3.181466191593025</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>150</v>
+      </c>
+      <c r="C680" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D680" t="n">
+        <v>0</v>
+      </c>
+      <c r="E680" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F680" t="n">
+        <v>52.38712888817246</v>
+      </c>
+      <c r="G680" t="n">
+        <v>2167.761939489933</v>
+      </c>
+      <c r="H680" t="n">
+        <v>40291332675.18083</v>
+      </c>
+      <c r="I680" t="n">
+        <v>4.654864832546572</v>
+      </c>
+      <c r="J680" t="n">
+        <v>16.7506610455382</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>175</v>
+      </c>
+      <c r="C681" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D681" t="n">
+        <v>0</v>
+      </c>
+      <c r="E681" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F681" t="n">
+        <v>52.32892714274179</v>
+      </c>
+      <c r="G681" t="n">
+        <v>2129.235922172545</v>
+      </c>
+      <c r="H681" t="n">
+        <v>38467962727.19631</v>
+      </c>
+      <c r="I681" t="n">
+        <v>4.713066577977244</v>
+      </c>
+      <c r="J681" t="n">
+        <v>18.57403099352272</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>3</v>
+      </c>
+      <c r="C682" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D682" t="n">
+        <v>0</v>
+      </c>
+      <c r="E682" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F682" t="n">
+        <v>54.55243734345973</v>
+      </c>
+      <c r="G682" t="n">
+        <v>3663.333536283681</v>
+      </c>
+      <c r="H682" t="n">
+        <v>54143619981.11106</v>
+      </c>
+      <c r="I682" t="n">
+        <v>2.489556377259305</v>
+      </c>
+      <c r="J682" t="n">
+        <v>2.898373739607971</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>200</v>
+      </c>
+      <c r="C683" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D683" t="n">
+        <v>0</v>
+      </c>
+      <c r="E683" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F683" t="n">
+        <v>52.32892714274179</v>
+      </c>
+      <c r="G683" t="n">
+        <v>2129.235922172545</v>
+      </c>
+      <c r="H683" t="n">
+        <v>36487824953.54696</v>
+      </c>
+      <c r="I683" t="n">
+        <v>4.713066577977244</v>
+      </c>
+      <c r="J683" t="n">
+        <v>20.55416876717207</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>125</v>
+      </c>
+      <c r="C684" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D684" t="n">
+        <v>0</v>
+      </c>
+      <c r="E684" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F684" t="n">
+        <v>52.41465074299772</v>
+      </c>
+      <c r="G684" t="n">
+        <v>2204.587475600501</v>
+      </c>
+      <c r="H684" t="n">
+        <v>42163586287.68681</v>
+      </c>
+      <c r="I684" t="n">
+        <v>4.627342977721312</v>
+      </c>
+      <c r="J684" t="n">
+        <v>14.87840743303222</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>7</v>
+      </c>
+      <c r="C685" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D685" t="n">
+        <v>0</v>
+      </c>
+      <c r="E685" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F685" t="n">
+        <v>54.53354568104062</v>
+      </c>
+      <c r="G685" t="n">
+        <v>3618.471513448639</v>
+      </c>
+      <c r="H685" t="n">
+        <v>53591320268.36017</v>
+      </c>
+      <c r="I685" t="n">
+        <v>2.508448039678413</v>
+      </c>
+      <c r="J685" t="n">
+        <v>3.450673452358864</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>8</v>
+      </c>
+      <c r="C686" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D686" t="n">
+        <v>0</v>
+      </c>
+      <c r="E686" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F686" t="n">
+        <v>54.53354568104061</v>
+      </c>
+      <c r="G686" t="n">
+        <v>3618.471513448639</v>
+      </c>
+      <c r="H686" t="n">
+        <v>53456716637.97723</v>
+      </c>
+      <c r="I686" t="n">
+        <v>2.508448039678427</v>
+      </c>
+      <c r="J686" t="n">
+        <v>3.585277082741806</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>500</v>
+      </c>
+      <c r="C687" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D687" t="n">
+        <v>0</v>
+      </c>
+      <c r="E687" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F687" t="n">
+        <v>52.31397011497024</v>
+      </c>
+      <c r="G687" t="n">
+        <v>2123.122750986699</v>
+      </c>
+      <c r="H687" t="n">
+        <v>12824916661.15186</v>
+      </c>
+      <c r="I687" t="n">
+        <v>4.728023605748795</v>
+      </c>
+      <c r="J687" t="n">
+        <v>44.21707705956717</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>250</v>
+      </c>
+      <c r="C688" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D688" t="n">
+        <v>0</v>
+      </c>
+      <c r="E688" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F688" t="n">
+        <v>52.32892714274181</v>
+      </c>
+      <c r="G688" t="n">
+        <v>2129.235922172545</v>
+      </c>
+      <c r="H688" t="n">
+        <v>32527549406.24827</v>
+      </c>
+      <c r="I688" t="n">
+        <v>4.713066577977223</v>
+      </c>
+      <c r="J688" t="n">
+        <v>24.51444431447077</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>4</v>
+      </c>
+      <c r="C689" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D689" t="n">
+        <v>0</v>
+      </c>
+      <c r="E689" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F689" t="n">
+        <v>54.53354568104062</v>
+      </c>
+      <c r="G689" t="n">
+        <v>3618.471513448639</v>
+      </c>
+      <c r="H689" t="n">
+        <v>53995131159.50893</v>
+      </c>
+      <c r="I689" t="n">
+        <v>2.508448039678413</v>
+      </c>
+      <c r="J689" t="n">
+        <v>3.046862561210106</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>400</v>
+      </c>
+      <c r="C690" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D690" t="n">
+        <v>0</v>
+      </c>
+      <c r="E690" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F690" t="n">
+        <v>52.31757737845928</v>
+      </c>
+      <c r="G690" t="n">
+        <v>2124.116247991497</v>
+      </c>
+      <c r="H690" t="n">
+        <v>20711551765.45002</v>
+      </c>
+      <c r="I690" t="n">
+        <v>4.724416342259751</v>
+      </c>
+      <c r="J690" t="n">
+        <v>36.33044195526901</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>6</v>
+      </c>
+      <c r="C691" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D691" t="n">
+        <v>0</v>
+      </c>
+      <c r="E691" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F691" t="n">
+        <v>54.53354568104065</v>
+      </c>
+      <c r="G691" t="n">
+        <v>3618.471513448639</v>
+      </c>
+      <c r="H691" t="n">
+        <v>53725923898.74312</v>
+      </c>
+      <c r="I691" t="n">
+        <v>2.508448039678385</v>
+      </c>
+      <c r="J691" t="n">
+        <v>3.316069821975914</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>600</v>
+      </c>
+      <c r="C692" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D692" t="n">
+        <v>0</v>
+      </c>
+      <c r="E692" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F692" t="n">
+        <v>52.31092926687172</v>
+      </c>
+      <c r="G692" t="n">
+        <v>2122.313187769276</v>
+      </c>
+      <c r="H692" t="n">
+        <v>4942134102.136762</v>
+      </c>
+      <c r="I692" t="n">
+        <v>4.731064453847317</v>
+      </c>
+      <c r="J692" t="n">
+        <v>52.09985961858226</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>75</v>
+      </c>
+      <c r="C693" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D693" t="n">
+        <v>0</v>
+      </c>
+      <c r="E693" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F693" t="n">
+        <v>52.71098547460794</v>
+      </c>
+      <c r="G693" t="n">
+        <v>2303.599522325301</v>
+      </c>
+      <c r="H693" t="n">
+        <v>46284110394.1856</v>
+      </c>
+      <c r="I693" t="n">
+        <v>4.331008246111097</v>
+      </c>
+      <c r="J693" t="n">
+        <v>10.75788332653343</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>700</v>
+      </c>
+      <c r="C694" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D694" t="n">
+        <v>0</v>
+      </c>
+      <c r="E694" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F694" t="n">
+        <v>52.31124129429706</v>
+      </c>
+      <c r="G694" t="n">
+        <v>2122.338477275909</v>
+      </c>
+      <c r="H694" t="n">
+        <v>-2953011586.141548</v>
+      </c>
+      <c r="I694" t="n">
+        <v>4.730752426421972</v>
+      </c>
+      <c r="J694" t="n">
+        <v>59.99500530686058</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>800</v>
+      </c>
+      <c r="C695" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D695" t="n">
+        <v>0</v>
+      </c>
+      <c r="E695" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F695" t="n">
+        <v>52.3112376141624</v>
+      </c>
+      <c r="G695" t="n">
+        <v>2122.338356398437</v>
+      </c>
+      <c r="H695" t="n">
+        <v>-10847904937.69052</v>
+      </c>
+      <c r="I695" t="n">
+        <v>4.730756106556633</v>
+      </c>
+      <c r="J695" t="n">
+        <v>67.88989865840955</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>100</v>
+      </c>
+      <c r="C696" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D696" t="n">
+        <v>0</v>
+      </c>
+      <c r="E696" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F696" t="n">
+        <v>52.71098547460792</v>
+      </c>
+      <c r="G696" t="n">
+        <v>2303.599522325301</v>
+      </c>
+      <c r="H696" t="n">
+        <v>44141818700.71146</v>
+      </c>
+      <c r="I696" t="n">
+        <v>4.331008246111118</v>
+      </c>
+      <c r="J696" t="n">
+        <v>12.90017502000758</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>1</v>
+      </c>
+      <c r="C697" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D697" t="n">
+        <v>0</v>
+      </c>
+      <c r="E697" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F697" t="n">
+        <v>54.55243734345975</v>
+      </c>
+      <c r="G697" t="n">
+        <v>3663.333536283681</v>
+      </c>
+      <c r="H697" t="n">
+        <v>54416164889.34352</v>
+      </c>
+      <c r="I697" t="n">
+        <v>2.489556377259284</v>
+      </c>
+      <c r="J697" t="n">
+        <v>2.625828831375511</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B698" t="n">
+        <v>0</v>
+      </c>
+      <c r="C698" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D698" t="n">
+        <v>0</v>
+      </c>
+      <c r="E698" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F698" t="n">
+        <v>54.5524325580635</v>
+      </c>
+      <c r="G698" t="n">
+        <v>3663.427016317523</v>
+      </c>
+      <c r="H698" t="n">
+        <v>54552432558.0635</v>
+      </c>
+      <c r="I698" t="n">
+        <v>2.489561162655534</v>
+      </c>
+      <c r="J698" t="n">
+        <v>2.489561162655533</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B699" t="n">
+        <v>300</v>
+      </c>
+      <c r="C699" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D699" t="n">
+        <v>0</v>
+      </c>
+      <c r="E699" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F699" t="n">
+        <v>52.32892714274182</v>
+      </c>
+      <c r="G699" t="n">
+        <v>2129.235922172545</v>
+      </c>
+      <c r="H699" t="n">
+        <v>28567273858.94957</v>
+      </c>
+      <c r="I699" t="n">
+        <v>4.713066577977216</v>
+      </c>
+      <c r="J699" t="n">
+        <v>28.47471986176946</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>10</v>
+      </c>
+      <c r="C700" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D700" t="n">
+        <v>0</v>
+      </c>
+      <c r="E700" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F700" t="n">
+        <v>54.49507329687875</v>
+      </c>
+      <c r="G700" t="n">
+        <v>3120.123147541268</v>
+      </c>
+      <c r="H700" t="n">
+        <v>53334417751.18793</v>
+      </c>
+      <c r="I700" t="n">
+        <v>2.546920423840284</v>
+      </c>
+      <c r="J700" t="n">
+        <v>3.707575969531105</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B701" t="n">
+        <v>2</v>
+      </c>
+      <c r="C701" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D701" t="n">
+        <v>0</v>
+      </c>
+      <c r="E701" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F701" t="n">
+        <v>54.55243734345973</v>
+      </c>
+      <c r="G701" t="n">
+        <v>3663.333536283681</v>
+      </c>
+      <c r="H701" t="n">
+        <v>54279892435.22729</v>
+      </c>
+      <c r="I701" t="n">
+        <v>2.489556377259305</v>
+      </c>
+      <c r="J701" t="n">
+        <v>2.762101285491745</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B702" t="n">
         <v>9</v>
       </c>
-      <c r="C663" t="n">
-        <v>2900</v>
-      </c>
-      <c r="D663" t="n">
-        <v>0</v>
-      </c>
-      <c r="E663" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F663" t="n">
-        <v>54.73279509</v>
-      </c>
-      <c r="G663" t="n">
-        <v>6294.76541596</v>
-      </c>
-      <c r="H663" t="n">
-        <v>52625362600</v>
-      </c>
-      <c r="I663" t="n">
-        <v>2.309198630719031</v>
-      </c>
-      <c r="J663" t="n">
-        <v>4.416631120719032</v>
+      <c r="C702" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D702" t="n">
+        <v>0</v>
+      </c>
+      <c r="E702" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F702" t="n">
+        <v>54.49180050078591</v>
+      </c>
+      <c r="G702" t="n">
+        <v>3420.568830219919</v>
+      </c>
+      <c r="H702" t="n">
+        <v>53346623917.99417</v>
+      </c>
+      <c r="I702" t="n">
+        <v>2.550193219933128</v>
+      </c>
+      <c r="J702" t="n">
+        <v>3.695369802724861</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B703" t="n">
+        <v>50</v>
+      </c>
+      <c r="C703" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D703" t="n">
+        <v>0</v>
+      </c>
+      <c r="E703" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F703" t="n">
+        <v>53.54218304461931</v>
+      </c>
+      <c r="G703" t="n">
+        <v>2619.048218557824</v>
+      </c>
+      <c r="H703" t="n">
+        <v>48670880381.94035</v>
+      </c>
+      <c r="I703" t="n">
+        <v>3.499810676099727</v>
+      </c>
+      <c r="J703" t="n">
+        <v>8.371113338778679</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B704" t="n">
+        <v>900</v>
+      </c>
+      <c r="C704" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D704" t="n">
+        <v>0</v>
+      </c>
+      <c r="E704" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F704" t="n">
+        <v>51.85577605400933</v>
+      </c>
+      <c r="G704" t="n">
+        <v>1987.046037248741</v>
+      </c>
+      <c r="H704" t="n">
+        <v>-14668790581.888</v>
+      </c>
+      <c r="I704" t="n">
+        <v>5.186217666709702</v>
+      </c>
+      <c r="J704" t="n">
+        <v>71.71078430260702</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B705" t="n">
+        <v>5</v>
+      </c>
+      <c r="C705" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D705" t="n">
+        <v>0</v>
+      </c>
+      <c r="E705" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F705" t="n">
+        <v>54.49732010159343</v>
+      </c>
+      <c r="G705" t="n">
+        <v>3659.247248453363</v>
+      </c>
+      <c r="H705" t="n">
+        <v>53816717860.73026</v>
+      </c>
+      <c r="I705" t="n">
+        <v>2.544673619125604</v>
+      </c>
+      <c r="J705" t="n">
+        <v>3.225275859988769</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B706" t="n">
+        <v>150</v>
+      </c>
+      <c r="C706" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D706" t="n">
+        <v>0</v>
+      </c>
+      <c r="E706" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F706" t="n">
+        <v>52.38356063202608</v>
+      </c>
+      <c r="G706" t="n">
+        <v>2218.395861604231</v>
+      </c>
+      <c r="H706" t="n">
+        <v>40005234500.87234</v>
+      </c>
+      <c r="I706" t="n">
+        <v>4.658433088692952</v>
+      </c>
+      <c r="J706" t="n">
+        <v>17.03675921984669</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>175</v>
+      </c>
+      <c r="C707" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D707" t="n">
+        <v>0</v>
+      </c>
+      <c r="E707" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F707" t="n">
+        <v>52.36161374955817</v>
+      </c>
+      <c r="G707" t="n">
+        <v>2202.36230535371</v>
+      </c>
+      <c r="H707" t="n">
+        <v>38024608992.70685</v>
+      </c>
+      <c r="I707" t="n">
+        <v>4.680379971160868</v>
+      </c>
+      <c r="J707" t="n">
+        <v>19.01738472801219</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>3</v>
+      </c>
+      <c r="C708" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D708" t="n">
+        <v>0</v>
+      </c>
+      <c r="E708" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F708" t="n">
+        <v>54.5147866743216</v>
+      </c>
+      <c r="G708" t="n">
+        <v>3679.15077925509</v>
+      </c>
+      <c r="H708" t="n">
+        <v>54104204153.6855</v>
+      </c>
+      <c r="I708" t="n">
+        <v>2.527207046397436</v>
+      </c>
+      <c r="J708" t="n">
+        <v>2.937789567033531</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>200</v>
+      </c>
+      <c r="C709" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D709" t="n">
+        <v>0</v>
+      </c>
+      <c r="E709" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F709" t="n">
+        <v>52.3451635069723</v>
+      </c>
+      <c r="G709" t="n">
+        <v>2191.457804570416</v>
+      </c>
+      <c r="H709" t="n">
+        <v>36041142583.78249</v>
+      </c>
+      <c r="I709" t="n">
+        <v>4.696830213746736</v>
+      </c>
+      <c r="J709" t="n">
+        <v>21.00085113693654</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>125</v>
+      </c>
+      <c r="C710" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D710" t="n">
+        <v>0</v>
+      </c>
+      <c r="E710" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F710" t="n">
+        <v>52.40503847815681</v>
+      </c>
+      <c r="G710" t="n">
+        <v>2236.585691932613</v>
+      </c>
+      <c r="H710" t="n">
+        <v>42005186196.68531</v>
+      </c>
+      <c r="I710" t="n">
+        <v>4.636955242562223</v>
+      </c>
+      <c r="J710" t="n">
+        <v>15.03680752403372</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>7</v>
+      </c>
+      <c r="C711" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D711" t="n">
+        <v>0</v>
+      </c>
+      <c r="E711" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F711" t="n">
+        <v>54.49261664040981</v>
+      </c>
+      <c r="G711" t="n">
+        <v>3649.472533636047</v>
+      </c>
+      <c r="H711" t="n">
+        <v>53542318772.56948</v>
+      </c>
+      <c r="I711" t="n">
+        <v>2.549377080309227</v>
+      </c>
+      <c r="J711" t="n">
+        <v>3.499674948149551</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>8</v>
+      </c>
+      <c r="C712" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D712" t="n">
+        <v>0</v>
+      </c>
+      <c r="E712" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F712" t="n">
+        <v>54.48984787588714</v>
+      </c>
+      <c r="G712" t="n">
+        <v>3644.794158971186</v>
+      </c>
+      <c r="H712" t="n">
+        <v>53405185417.77999</v>
+      </c>
+      <c r="I712" t="n">
+        <v>2.552145844831891</v>
+      </c>
+      <c r="J712" t="n">
+        <v>3.636808302939041</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>500</v>
+      </c>
+      <c r="C713" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D713" t="n">
+        <v>0</v>
+      </c>
+      <c r="E713" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F713" t="n">
+        <v>51.97674410999981</v>
+      </c>
+      <c r="G713" t="n">
+        <v>2032.876562660908</v>
+      </c>
+      <c r="H713" t="n">
+        <v>14166225989.63983</v>
+      </c>
+      <c r="I713" t="n">
+        <v>5.065249610719228</v>
+      </c>
+      <c r="J713" t="n">
+        <v>42.8757677310792</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>250</v>
+      </c>
+      <c r="C714" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D714" t="n">
+        <v>0</v>
+      </c>
+      <c r="E714" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F714" t="n">
+        <v>52.2933652224079</v>
+      </c>
+      <c r="G714" t="n">
+        <v>2155.600867861585</v>
+      </c>
+      <c r="H714" t="n">
+        <v>32246799884.50561</v>
+      </c>
+      <c r="I714" t="n">
+        <v>4.748628498311135</v>
+      </c>
+      <c r="J714" t="n">
+        <v>24.79519383621342</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>4</v>
+      </c>
+      <c r="C715" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D715" t="n">
+        <v>0</v>
+      </c>
+      <c r="E715" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F715" t="n">
+        <v>54.50001811436281</v>
+      </c>
+      <c r="G715" t="n">
+        <v>3662.989539426787</v>
+      </c>
+      <c r="H715" t="n">
+        <v>53954979483.29552</v>
+      </c>
+      <c r="I715" t="n">
+        <v>2.541975606356225</v>
+      </c>
+      <c r="J715" t="n">
+        <v>3.087014237423515</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>400</v>
+      </c>
+      <c r="C716" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D716" t="n">
+        <v>0</v>
+      </c>
+      <c r="E716" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F716" t="n">
+        <v>52.06042612356784</v>
+      </c>
+      <c r="G716" t="n">
+        <v>2066.226336869693</v>
+      </c>
+      <c r="H716" t="n">
+        <v>21315779926.76551</v>
+      </c>
+      <c r="I716" t="n">
+        <v>4.981567597151198</v>
+      </c>
+      <c r="J716" t="n">
+        <v>35.72621379395352</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>6</v>
+      </c>
+      <c r="C717" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D717" t="n">
+        <v>0</v>
+      </c>
+      <c r="E717" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F717" t="n">
+        <v>54.49267579601518</v>
+      </c>
+      <c r="G717" t="n">
+        <v>3649.481307316717</v>
+      </c>
+      <c r="H717" t="n">
+        <v>53678132808.2033</v>
+      </c>
+      <c r="I717" t="n">
+        <v>2.549317924703857</v>
+      </c>
+      <c r="J717" t="n">
+        <v>3.363860912515732</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>600</v>
+      </c>
+      <c r="C718" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D718" t="n">
+        <v>0</v>
+      </c>
+      <c r="E718" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F718" t="n">
+        <v>51.93524247071745</v>
+      </c>
+      <c r="G718" t="n">
+        <v>2017.738942474834</v>
+      </c>
+      <c r="H718" t="n">
+        <v>6900483598.743672</v>
+      </c>
+      <c r="I718" t="n">
+        <v>5.106751250001587</v>
+      </c>
+      <c r="J718" t="n">
+        <v>50.14151012197536</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>75</v>
+      </c>
+      <c r="C719" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D719" t="n">
+        <v>0</v>
+      </c>
+      <c r="E719" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F719" t="n">
+        <v>52.69689956467651</v>
+      </c>
+      <c r="G719" t="n">
+        <v>2338.011093656778</v>
+      </c>
+      <c r="H719" t="n">
+        <v>46174018703.68116</v>
+      </c>
+      <c r="I719" t="n">
+        <v>4.345094156042528</v>
+      </c>
+      <c r="J719" t="n">
+        <v>10.86797501703787</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>700</v>
+      </c>
+      <c r="C720" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D720" t="n">
+        <v>0</v>
+      </c>
+      <c r="E720" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F720" t="n">
+        <v>51.9081735712559</v>
+      </c>
+      <c r="G720" t="n">
+        <v>2008.584644606384</v>
+      </c>
+      <c r="H720" t="n">
+        <v>-394006745.3206395</v>
+      </c>
+      <c r="I720" t="n">
+        <v>5.133820149463133</v>
+      </c>
+      <c r="J720" t="n">
+        <v>57.43600046603967</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>800</v>
+      </c>
+      <c r="C721" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D721" t="n">
+        <v>0</v>
+      </c>
+      <c r="E721" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F721" t="n">
+        <v>51.88129120882746</v>
+      </c>
+      <c r="G721" t="n">
+        <v>1995.963360471527</v>
+      </c>
+      <c r="H721" t="n">
+        <v>-7517029531.237476</v>
+      </c>
+      <c r="I721" t="n">
+        <v>5.160702511891571</v>
+      </c>
+      <c r="J721" t="n">
+        <v>64.55902325195652</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>100</v>
+      </c>
+      <c r="C722" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D722" t="n">
+        <v>0</v>
+      </c>
+      <c r="E722" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F722" t="n">
+        <v>52.66885246873587</v>
+      </c>
+      <c r="G722" t="n">
+        <v>2311.989324675426</v>
+      </c>
+      <c r="H722" t="n">
+        <v>44068476443.90778</v>
+      </c>
+      <c r="I722" t="n">
+        <v>4.373141251983164</v>
+      </c>
+      <c r="J722" t="n">
+        <v>12.97351727681125</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>1</v>
+      </c>
+      <c r="C723" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D723" t="n">
+        <v>0</v>
+      </c>
+      <c r="E723" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F723" t="n">
+        <v>54.53428091305273</v>
+      </c>
+      <c r="G723" t="n">
+        <v>3702.871335279018</v>
+      </c>
+      <c r="H723" t="n">
+        <v>54396537691.16555</v>
+      </c>
+      <c r="I723" t="n">
+        <v>2.507712807666302</v>
+      </c>
+      <c r="J723" t="n">
+        <v>2.645456029553482</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>0</v>
+      </c>
+      <c r="C724" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D724" t="n">
+        <v>0</v>
+      </c>
+      <c r="E724" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F724" t="n">
+        <v>54.54074723822457</v>
+      </c>
+      <c r="G724" t="n">
+        <v>3710.225735109932</v>
+      </c>
+      <c r="H724" t="n">
+        <v>54540747238.22457</v>
+      </c>
+      <c r="I724" t="n">
+        <v>2.501246482494466</v>
+      </c>
+      <c r="J724" t="n">
+        <v>2.501246482494461</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>300</v>
+      </c>
+      <c r="C725" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D725" t="n">
+        <v>0</v>
+      </c>
+      <c r="E725" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F725" t="n">
+        <v>52.20819344335655</v>
+      </c>
+      <c r="G725" t="n">
+        <v>2106.172307579707</v>
+      </c>
+      <c r="H725" t="n">
+        <v>28703923386.90853</v>
+      </c>
+      <c r="I725" t="n">
+        <v>4.833800277362485</v>
+      </c>
+      <c r="J725" t="n">
+        <v>28.3380703338105</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>10</v>
+      </c>
+      <c r="C726" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D726" t="n">
+        <v>0</v>
+      </c>
+      <c r="E726" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F726" t="n">
+        <v>54.4666255586397</v>
+      </c>
+      <c r="G726" t="n">
+        <v>3147.773271058473</v>
+      </c>
+      <c r="H726" t="n">
+        <v>53295684435.20668</v>
+      </c>
+      <c r="I726" t="n">
+        <v>2.575368162079336</v>
+      </c>
+      <c r="J726" t="n">
+        <v>3.746309285512352</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>2</v>
+      </c>
+      <c r="C727" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D727" t="n">
+        <v>0</v>
+      </c>
+      <c r="E727" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F727" t="n">
+        <v>54.51945604859441</v>
+      </c>
+      <c r="G727" t="n">
+        <v>3683.870583743599</v>
+      </c>
+      <c r="H727" t="n">
+        <v>54245383223.87282</v>
+      </c>
+      <c r="I727" t="n">
+        <v>2.522537672124628</v>
+      </c>
+      <c r="J727" t="n">
+        <v>2.796610496846214</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>9</v>
+      </c>
+      <c r="C728" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D728" t="n">
+        <v>0</v>
+      </c>
+      <c r="E728" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F728" t="n">
+        <v>54.4643772802243</v>
+      </c>
+      <c r="G728" t="n">
+        <v>3458.591554761127</v>
+      </c>
+      <c r="H728" t="n">
+        <v>53306471021.19454</v>
+      </c>
+      <c r="I728" t="n">
+        <v>2.577616440494737</v>
+      </c>
+      <c r="J728" t="n">
+        <v>3.73552269952449</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>50</v>
+      </c>
+      <c r="C729" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D729" t="n">
+        <v>0</v>
+      </c>
+      <c r="E729" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F729" t="n">
+        <v>53.54223065408331</v>
+      </c>
+      <c r="G729" t="n">
+        <v>2619.070952267157</v>
+      </c>
+      <c r="H729" t="n">
+        <v>48670885707.80759</v>
+      </c>
+      <c r="I729" t="n">
+        <v>3.499763066635722</v>
+      </c>
+      <c r="J729" t="n">
+        <v>8.371108012911446</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>900</v>
+      </c>
+      <c r="C730" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D730" t="n">
+        <v>0</v>
+      </c>
+      <c r="E730" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F730" t="n">
+        <v>51.84588657394545</v>
+      </c>
+      <c r="G730" t="n">
+        <v>1983.42265301945</v>
+      </c>
+      <c r="H730" t="n">
+        <v>-14557372321.16965</v>
+      </c>
+      <c r="I730" t="n">
+        <v>5.196107146773585</v>
+      </c>
+      <c r="J730" t="n">
+        <v>71.59936604188869</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>5</v>
+      </c>
+      <c r="C731" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D731" t="n">
+        <v>0</v>
+      </c>
+      <c r="E731" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F731" t="n">
+        <v>54.49731851749695</v>
+      </c>
+      <c r="G731" t="n">
+        <v>3659.387571812661</v>
+      </c>
+      <c r="H731" t="n">
+        <v>53816690177.16952</v>
+      </c>
+      <c r="I731" t="n">
+        <v>2.544675203222084</v>
+      </c>
+      <c r="J731" t="n">
+        <v>3.225303543549515</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>150</v>
+      </c>
+      <c r="C732" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D732" t="n">
+        <v>0</v>
+      </c>
+      <c r="E732" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F732" t="n">
+        <v>52.38429926062624</v>
+      </c>
+      <c r="G732" t="n">
+        <v>2218.714996908566</v>
+      </c>
+      <c r="H732" t="n">
+        <v>40004192400.90849</v>
+      </c>
+      <c r="I732" t="n">
+        <v>4.657694460092792</v>
+      </c>
+      <c r="J732" t="n">
+        <v>17.03780131981054</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>175</v>
+      </c>
+      <c r="C733" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D733" t="n">
+        <v>0</v>
+      </c>
+      <c r="E733" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F733" t="n">
+        <v>52.36248152126667</v>
+      </c>
+      <c r="G733" t="n">
+        <v>2202.734387774035</v>
+      </c>
+      <c r="H733" t="n">
+        <v>38023054571.02001</v>
+      </c>
+      <c r="I733" t="n">
+        <v>4.679512199452361</v>
+      </c>
+      <c r="J733" t="n">
+        <v>19.01893914969902</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>3</v>
+      </c>
+      <c r="C734" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D734" t="n">
+        <v>0</v>
+      </c>
+      <c r="E734" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F734" t="n">
+        <v>54.51478507501312</v>
+      </c>
+      <c r="G734" t="n">
+        <v>3679.292464504578</v>
+      </c>
+      <c r="H734" t="n">
+        <v>54104186742.71548</v>
+      </c>
+      <c r="I734" t="n">
+        <v>2.527208645705912</v>
+      </c>
+      <c r="J734" t="n">
+        <v>2.937806978003555</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>200</v>
+      </c>
+      <c r="C735" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D735" t="n">
+        <v>0</v>
+      </c>
+      <c r="E735" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F735" t="n">
+        <v>52.34450908773352</v>
+      </c>
+      <c r="G735" t="n">
+        <v>2191.462475451832</v>
+      </c>
+      <c r="H735" t="n">
+        <v>36040453414.09213</v>
+      </c>
+      <c r="I735" t="n">
+        <v>4.697484632985514</v>
+      </c>
+      <c r="J735" t="n">
+        <v>21.0015403066269</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>125</v>
+      </c>
+      <c r="C736" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D736" t="n">
+        <v>0</v>
+      </c>
+      <c r="E736" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F736" t="n">
+        <v>52.40561555493483</v>
+      </c>
+      <c r="G736" t="n">
+        <v>2236.834899189876</v>
+      </c>
+      <c r="H736" t="n">
+        <v>42004604489.93343</v>
+      </c>
+      <c r="I736" t="n">
+        <v>4.636378165784201</v>
+      </c>
+      <c r="J736" t="n">
+        <v>15.0373892307856</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>7</v>
+      </c>
+      <c r="C737" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D737" t="n">
+        <v>0</v>
+      </c>
+      <c r="E737" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F737" t="n">
+        <v>54.49261506076927</v>
+      </c>
+      <c r="G737" t="n">
+        <v>3649.61243234213</v>
+      </c>
+      <c r="H737" t="n">
+        <v>53542280764.2558</v>
+      </c>
+      <c r="I737" t="n">
+        <v>2.549378659949767</v>
+      </c>
+      <c r="J737" t="n">
+        <v>3.499712956463234</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>8</v>
+      </c>
+      <c r="C738" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D738" t="n">
+        <v>0</v>
+      </c>
+      <c r="E738" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F738" t="n">
+        <v>54.48984630013535</v>
+      </c>
+      <c r="G738" t="n">
+        <v>3644.933791778639</v>
+      </c>
+      <c r="H738" t="n">
+        <v>53405142288.38825</v>
+      </c>
+      <c r="I738" t="n">
+        <v>2.552147420583687</v>
+      </c>
+      <c r="J738" t="n">
+        <v>3.63685143233078</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>500</v>
+      </c>
+      <c r="C739" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D739" t="n">
+        <v>0</v>
+      </c>
+      <c r="E739" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F739" t="n">
+        <v>51.97376176938014</v>
+      </c>
+      <c r="G739" t="n">
+        <v>2031.445228604623</v>
+      </c>
+      <c r="H739" t="n">
+        <v>14189865768.27002</v>
+      </c>
+      <c r="I739" t="n">
+        <v>5.068231951338895</v>
+      </c>
+      <c r="J739" t="n">
+        <v>42.85212795244901</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>250</v>
+      </c>
+      <c r="C740" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D740" t="n">
+        <v>0</v>
+      </c>
+      <c r="E740" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F740" t="n">
+        <v>52.29452997928436</v>
+      </c>
+      <c r="G740" t="n">
+        <v>2156.080660984004</v>
+      </c>
+      <c r="H740" t="n">
+        <v>32243502681.69341</v>
+      </c>
+      <c r="I740" t="n">
+        <v>4.747463741434672</v>
+      </c>
+      <c r="J740" t="n">
+        <v>24.79849103902562</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>4</v>
+      </c>
+      <c r="C741" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D741" t="n">
+        <v>0</v>
+      </c>
+      <c r="E741" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F741" t="n">
+        <v>54.50001652886882</v>
+      </c>
+      <c r="G741" t="n">
+        <v>3663.130019452994</v>
+      </c>
+      <c r="H741" t="n">
+        <v>53954956994.91869</v>
+      </c>
+      <c r="I741" t="n">
+        <v>2.541977191850215</v>
+      </c>
+      <c r="J741" t="n">
+        <v>3.087036725800339</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>400</v>
+      </c>
+      <c r="C742" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D742" t="n">
+        <v>0</v>
+      </c>
+      <c r="E742" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F742" t="n">
+        <v>52.0542663532513</v>
+      </c>
+      <c r="G742" t="n">
+        <v>2063.557456174832</v>
+      </c>
+      <c r="H742" t="n">
+        <v>21349332065.66279</v>
+      </c>
+      <c r="I742" t="n">
+        <v>4.987727367467734</v>
+      </c>
+      <c r="J742" t="n">
+        <v>35.69266165505624</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>6</v>
+      </c>
+      <c r="C743" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D743" t="n">
+        <v>0</v>
+      </c>
+      <c r="E743" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F743" t="n">
+        <v>54.4926742163704</v>
+      </c>
+      <c r="G743" t="n">
+        <v>3649.621206368119</v>
+      </c>
+      <c r="H743" t="n">
+        <v>53678100003.90446</v>
+      </c>
+      <c r="I743" t="n">
+        <v>2.549319504348631</v>
+      </c>
+      <c r="J743" t="n">
+        <v>3.363893716814575</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>600</v>
+      </c>
+      <c r="C744" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D744" t="n">
+        <v>0</v>
+      </c>
+      <c r="E744" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F744" t="n">
+        <v>51.92703879899781</v>
+      </c>
+      <c r="G744" t="n">
+        <v>2014.469989980094</v>
+      </c>
+      <c r="H744" t="n">
+        <v>6965241044.176284</v>
+      </c>
+      <c r="I744" t="n">
+        <v>5.114954921721221</v>
+      </c>
+      <c r="J744" t="n">
+        <v>50.07675267654275</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>75</v>
+      </c>
+      <c r="C745" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D745" t="n">
+        <v>0</v>
+      </c>
+      <c r="E745" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F745" t="n">
+        <v>52.69543084491954</v>
+      </c>
+      <c r="G745" t="n">
+        <v>2337.343624037869</v>
+      </c>
+      <c r="H745" t="n">
+        <v>46174412175.60253</v>
+      </c>
+      <c r="I745" t="n">
+        <v>4.346562875799492</v>
+      </c>
+      <c r="J745" t="n">
+        <v>10.8675815451165</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>700</v>
+      </c>
+      <c r="C746" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D746" t="n">
+        <v>0</v>
+      </c>
+      <c r="E746" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F746" t="n">
+        <v>51.9012130998244</v>
+      </c>
+      <c r="G746" t="n">
+        <v>2005.522871182003</v>
+      </c>
+      <c r="H746" t="n">
+        <v>-321240715.7254144</v>
+      </c>
+      <c r="I746" t="n">
+        <v>5.140780620894631</v>
+      </c>
+      <c r="J746" t="n">
+        <v>57.36323443644445</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>800</v>
+      </c>
+      <c r="C747" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D747" t="n">
+        <v>0</v>
+      </c>
+      <c r="E747" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F747" t="n">
+        <v>51.87337752180414</v>
+      </c>
+      <c r="G747" t="n">
+        <v>1992.607404527256</v>
+      </c>
+      <c r="H747" t="n">
+        <v>-7425072573.581092</v>
+      </c>
+      <c r="I747" t="n">
+        <v>5.168616198914897</v>
+      </c>
+      <c r="J747" t="n">
+        <v>64.46706629430012</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>100</v>
+      </c>
+      <c r="C748" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D748" t="n">
+        <v>0</v>
+      </c>
+      <c r="E748" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F748" t="n">
+        <v>52.6692470268318</v>
+      </c>
+      <c r="G748" t="n">
+        <v>2312.160056386355</v>
+      </c>
+      <c r="H748" t="n">
+        <v>44068235896.60002</v>
+      </c>
+      <c r="I748" t="n">
+        <v>4.372746693887237</v>
+      </c>
+      <c r="J748" t="n">
+        <v>12.97375782411901</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>1</v>
+      </c>
+      <c r="C749" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D749" t="n">
+        <v>0</v>
+      </c>
+      <c r="E749" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F749" t="n">
+        <v>54.53427928675102</v>
+      </c>
+      <c r="G749" t="n">
+        <v>3703.014724837753</v>
+      </c>
+      <c r="H749" t="n">
+        <v>54396530730.91134</v>
+      </c>
+      <c r="I749" t="n">
+        <v>2.507714433968012</v>
+      </c>
+      <c r="J749" t="n">
+        <v>2.645462989807693</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>0</v>
+      </c>
+      <c r="C750" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D750" t="n">
+        <v>0</v>
+      </c>
+      <c r="E750" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F750" t="n">
+        <v>54.54073604519105</v>
+      </c>
+      <c r="G750" t="n">
+        <v>3710.573398426688</v>
+      </c>
+      <c r="H750" t="n">
+        <v>54540736045.19106</v>
+      </c>
+      <c r="I750" t="n">
+        <v>2.501257675527981</v>
+      </c>
+      <c r="J750" t="n">
+        <v>2.501257675527969</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>300</v>
+      </c>
+      <c r="C751" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D751" t="n">
+        <v>0</v>
+      </c>
+      <c r="E751" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F751" t="n">
+        <v>52.20949216421626</v>
+      </c>
+      <c r="G751" t="n">
+        <v>2106.691866407357</v>
+      </c>
+      <c r="H751" t="n">
+        <v>28699423982.44328</v>
+      </c>
+      <c r="I751" t="n">
+        <v>4.832501556502777</v>
+      </c>
+      <c r="J751" t="n">
+        <v>28.34256973827575</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>10</v>
+      </c>
+      <c r="C752" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D752" t="n">
+        <v>0</v>
+      </c>
+      <c r="E752" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F752" t="n">
+        <v>54.46662428261657</v>
+      </c>
+      <c r="G752" t="n">
+        <v>3147.888583087769</v>
+      </c>
+      <c r="H752" t="n">
+        <v>53295640264.22717</v>
+      </c>
+      <c r="I752" t="n">
+        <v>2.575369438102463</v>
+      </c>
+      <c r="J752" t="n">
+        <v>3.746353456491859</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>2</v>
+      </c>
+      <c r="C753" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D753" t="n">
+        <v>0</v>
+      </c>
+      <c r="E753" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F753" t="n">
+        <v>54.51945444428137</v>
+      </c>
+      <c r="G753" t="n">
+        <v>3684.012602453474</v>
+      </c>
+      <c r="H753" t="n">
+        <v>54245371053.64327</v>
+      </c>
+      <c r="I753" t="n">
+        <v>2.522539276437662</v>
+      </c>
+      <c r="J753" t="n">
+        <v>2.79662266707576</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ORIGINAL_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>9</v>
+      </c>
+      <c r="C754" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D754" t="n">
+        <v>0</v>
+      </c>
+      <c r="E754" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F754" t="n">
+        <v>54.46437574757105</v>
+      </c>
+      <c r="G754" t="n">
+        <v>3458.723939160084</v>
+      </c>
+      <c r="H754" t="n">
+        <v>53306425167.40024</v>
+      </c>
+      <c r="I754" t="n">
+        <v>2.577617973147987</v>
+      </c>
+      <c r="J754" t="n">
+        <v>3.735568553318794</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=SIMPLE_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>4</v>
+      </c>
+      <c r="C755" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D755" t="n">
+        <v>0</v>
+      </c>
+      <c r="E755" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F755" t="n">
+        <v>54.72291217714366</v>
+      </c>
+      <c r="G755" t="n">
+        <v>6841.96619516696</v>
+      </c>
+      <c r="H755" t="n">
+        <v>53704854154.13165</v>
+      </c>
+      <c r="I755" t="n">
+        <v>2.319081543575372</v>
+      </c>
+      <c r="J755" t="n">
+        <v>3.337139566587379</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>50</v>
+      </c>
+      <c r="C756" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D756" t="n">
+        <v>0</v>
+      </c>
+      <c r="E756" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F756" t="n">
+        <v>53.53466733887225</v>
+      </c>
+      <c r="G756" t="n">
+        <v>2881.691106096606</v>
+      </c>
+      <c r="H756" t="n">
+        <v>48174861643.55121</v>
+      </c>
+      <c r="I756" t="n">
+        <v>3.507326381846788</v>
+      </c>
+      <c r="J756" t="n">
+        <v>8.867132077167824</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>900</v>
+      </c>
+      <c r="C757" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D757" t="n">
+        <v>0</v>
+      </c>
+      <c r="E757" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F757" t="n">
+        <v>53.37182749176805</v>
+      </c>
+      <c r="G757" t="n">
+        <v>2760.363538753271</v>
+      </c>
+      <c r="H757" t="n">
+        <v>-39042733988.32213</v>
+      </c>
+      <c r="I757" t="n">
+        <v>3.670166228950983</v>
+      </c>
+      <c r="J757" t="n">
+        <v>96.08472770904118</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>5</v>
+      </c>
+      <c r="C758" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D758" t="n">
+        <v>0</v>
+      </c>
+      <c r="E758" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F758" t="n">
+        <v>53.72639744928601</v>
+      </c>
+      <c r="G758" t="n">
+        <v>3149.97182133626</v>
+      </c>
+      <c r="H758" t="n">
+        <v>53140517967.8808</v>
+      </c>
+      <c r="I758" t="n">
+        <v>3.315596271433023</v>
+      </c>
+      <c r="J758" t="n">
+        <v>3.901475752838234</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>150</v>
+      </c>
+      <c r="C759" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D759" t="n">
+        <v>0</v>
+      </c>
+      <c r="E759" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F759" t="n">
+        <v>53.46365701325251</v>
+      </c>
+      <c r="G759" t="n">
+        <v>2821.656538788747</v>
+      </c>
+      <c r="H759" t="n">
+        <v>37719224077.83769</v>
+      </c>
+      <c r="I759" t="n">
+        <v>3.578336707466526</v>
+      </c>
+      <c r="J759" t="n">
+        <v>19.32276964288134</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B760" t="n">
+        <v>175</v>
+      </c>
+      <c r="C760" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D760" t="n">
+        <v>0</v>
+      </c>
+      <c r="E760" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F760" t="n">
+        <v>53.46360158755054</v>
+      </c>
+      <c r="G760" t="n">
+        <v>2821.647542083178</v>
+      </c>
+      <c r="H760" t="n">
+        <v>35095155063.25932</v>
+      </c>
+      <c r="I760" t="n">
+        <v>3.578392133168492</v>
+      </c>
+      <c r="J760" t="n">
+        <v>21.94683865745971</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B761" t="n">
+        <v>3</v>
+      </c>
+      <c r="C761" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D761" t="n">
+        <v>0</v>
+      </c>
+      <c r="E761" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F761" t="n">
+        <v>53.72944867706427</v>
+      </c>
+      <c r="G761" t="n">
+        <v>3154.880330734577</v>
+      </c>
+      <c r="H761" t="n">
+        <v>53377373212.85606</v>
+      </c>
+      <c r="I761" t="n">
+        <v>3.312545043654765</v>
+      </c>
+      <c r="J761" t="n">
+        <v>3.664620507862976</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B762" t="n">
+        <v>200</v>
+      </c>
+      <c r="C762" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D762" t="n">
+        <v>0</v>
+      </c>
+      <c r="E762" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F762" t="n">
+        <v>53.43924496405764</v>
+      </c>
+      <c r="G762" t="n">
+        <v>2797.404514634269</v>
+      </c>
+      <c r="H762" t="n">
+        <v>32627098071.65452</v>
+      </c>
+      <c r="I762" t="n">
+        <v>3.602748756661391</v>
+      </c>
+      <c r="J762" t="n">
+        <v>24.41489564906452</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B763" t="n">
+        <v>125</v>
+      </c>
+      <c r="C763" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D763" t="n">
+        <v>0</v>
+      </c>
+      <c r="E763" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F763" t="n">
+        <v>53.46371291859761</v>
+      </c>
+      <c r="G763" t="n">
+        <v>2821.658900991458</v>
+      </c>
+      <c r="H763" t="n">
+        <v>40343341155.12908</v>
+      </c>
+      <c r="I763" t="n">
+        <v>3.578280802121427</v>
+      </c>
+      <c r="J763" t="n">
+        <v>16.69865256558995</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B764" t="n">
+        <v>7</v>
+      </c>
+      <c r="C764" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D764" t="n">
+        <v>0</v>
+      </c>
+      <c r="E764" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F764" t="n">
+        <v>53.67348050246587</v>
+      </c>
+      <c r="G764" t="n">
+        <v>3029.371268885972</v>
+      </c>
+      <c r="H764" t="n">
+        <v>52884652793.47888</v>
+      </c>
+      <c r="I764" t="n">
+        <v>3.368513218253163</v>
+      </c>
+      <c r="J764" t="n">
+        <v>4.15734092724015</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B765" t="n">
+        <v>8</v>
+      </c>
+      <c r="C765" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D765" t="n">
+        <v>0</v>
+      </c>
+      <c r="E765" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F765" t="n">
+        <v>53.67348050246585</v>
+      </c>
+      <c r="G765" t="n">
+        <v>3029.371268885972</v>
+      </c>
+      <c r="H765" t="n">
+        <v>52771963120.76643</v>
+      </c>
+      <c r="I765" t="n">
+        <v>3.368513218253185</v>
+      </c>
+      <c r="J765" t="n">
+        <v>4.270030599952599</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B766" t="n">
+        <v>500</v>
+      </c>
+      <c r="C766" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D766" t="n">
+        <v>0</v>
+      </c>
+      <c r="E766" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F766" t="n">
+        <v>53.37344158666578</v>
+      </c>
+      <c r="G766" t="n">
+        <v>2760.566321366755</v>
+      </c>
+      <c r="H766" t="n">
+        <v>2028246883.910001</v>
+      </c>
+      <c r="I766" t="n">
+        <v>3.668552134053257</v>
+      </c>
+      <c r="J766" t="n">
+        <v>55.01374683680903</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B767" t="n">
+        <v>250</v>
+      </c>
+      <c r="C767" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D767" t="n">
+        <v>0</v>
+      </c>
+      <c r="E767" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F767" t="n">
+        <v>53.42141721688376</v>
+      </c>
+      <c r="G767" t="n">
+        <v>2784.268472737742</v>
+      </c>
+      <c r="H767" t="n">
+        <v>27528395605.52739</v>
+      </c>
+      <c r="I767" t="n">
+        <v>3.620576503835274</v>
+      </c>
+      <c r="J767" t="n">
+        <v>29.51359811519164</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B768" t="n">
+        <v>4</v>
+      </c>
+      <c r="C768" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D768" t="n">
+        <v>0</v>
+      </c>
+      <c r="E768" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F768" t="n">
+        <v>53.726397449286</v>
+      </c>
+      <c r="G768" t="n">
+        <v>3149.97182133626</v>
+      </c>
+      <c r="H768" t="n">
+        <v>53257693864.16183</v>
+      </c>
+      <c r="I768" t="n">
+        <v>3.315596271433037</v>
+      </c>
+      <c r="J768" t="n">
+        <v>3.784299856557205</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B769" t="n">
+        <v>400</v>
+      </c>
+      <c r="C769" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D769" t="n">
+        <v>0</v>
+      </c>
+      <c r="E769" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F769" t="n">
+        <v>53.38233155452917</v>
+      </c>
+      <c r="G769" t="n">
+        <v>2762.692839288929</v>
+      </c>
+      <c r="H769" t="n">
+        <v>12274534030.73155</v>
+      </c>
+      <c r="I769" t="n">
+        <v>3.659662166189861</v>
+      </c>
+      <c r="J769" t="n">
+        <v>44.76745968998748</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B770" t="n">
+        <v>6</v>
+      </c>
+      <c r="C770" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D770" t="n">
+        <v>0</v>
+      </c>
+      <c r="E770" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F770" t="n">
+        <v>53.72639744928601</v>
+      </c>
+      <c r="G770" t="n">
+        <v>3149.97182133626</v>
+      </c>
+      <c r="H770" t="n">
+        <v>53023342071.59975</v>
+      </c>
+      <c r="I770" t="n">
+        <v>3.315596271433023</v>
+      </c>
+      <c r="J770" t="n">
+        <v>4.018651649119286</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B771" t="n">
+        <v>600</v>
+      </c>
+      <c r="C771" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D771" t="n">
+        <v>0</v>
+      </c>
+      <c r="E771" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F771" t="n">
+        <v>53.37182734641621</v>
+      </c>
+      <c r="G771" t="n">
+        <v>2760.363514634455</v>
+      </c>
+      <c r="H771" t="n">
+        <v>-8237879768.65929</v>
+      </c>
+      <c r="I771" t="n">
+        <v>3.670166374302823</v>
+      </c>
+      <c r="J771" t="n">
+        <v>65.27987348937833</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B772" t="n">
+        <v>75</v>
+      </c>
+      <c r="C772" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D772" t="n">
+        <v>0</v>
+      </c>
+      <c r="E772" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F772" t="n">
+        <v>53.50995734589858</v>
+      </c>
+      <c r="G772" t="n">
+        <v>2851.085313556055</v>
+      </c>
+      <c r="H772" t="n">
+        <v>45555636737.53375</v>
+      </c>
+      <c r="I772" t="n">
+        <v>3.532036374820457</v>
+      </c>
+      <c r="J772" t="n">
+        <v>11.48635698318528</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B773" t="n">
+        <v>700</v>
+      </c>
+      <c r="C773" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D773" t="n">
+        <v>0</v>
+      </c>
+      <c r="E773" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F773" t="n">
+        <v>53.37182691002463</v>
+      </c>
+      <c r="G773" t="n">
+        <v>2760.363488261016</v>
+      </c>
+      <c r="H773" t="n">
+        <v>-18506164037.48369</v>
+      </c>
+      <c r="I773" t="n">
+        <v>3.670166810694404</v>
+      </c>
+      <c r="J773" t="n">
+        <v>75.54815775820273</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B774" t="n">
+        <v>800</v>
+      </c>
+      <c r="C774" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D774" t="n">
+        <v>0</v>
+      </c>
+      <c r="E774" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F774" t="n">
+        <v>53.3718269083701</v>
+      </c>
+      <c r="G774" t="n">
+        <v>2760.363507768349</v>
+      </c>
+      <c r="H774" t="n">
+        <v>-28774449040.73393</v>
+      </c>
+      <c r="I774" t="n">
+        <v>3.670166812348931</v>
+      </c>
+      <c r="J774" t="n">
+        <v>85.81644276145296</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B775" t="n">
+        <v>100</v>
+      </c>
+      <c r="C775" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D775" t="n">
+        <v>0</v>
+      </c>
+      <c r="E775" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F775" t="n">
+        <v>53.50984654604719</v>
+      </c>
+      <c r="G775" t="n">
+        <v>2851.065127984039</v>
+      </c>
+      <c r="H775" t="n">
+        <v>42904160823.26398</v>
+      </c>
+      <c r="I775" t="n">
+        <v>3.532147174671842</v>
+      </c>
+      <c r="J775" t="n">
+        <v>14.13783289745506</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B776" t="n">
+        <v>1</v>
+      </c>
+      <c r="C776" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D776" t="n">
+        <v>0</v>
+      </c>
+      <c r="E776" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F776" t="n">
+        <v>53.73436562017996</v>
+      </c>
+      <c r="G776" t="n">
+        <v>3162.730881247984</v>
+      </c>
+      <c r="H776" t="n">
+        <v>53616715099.24649</v>
+      </c>
+      <c r="I776" t="n">
+        <v>3.307628100539077</v>
+      </c>
+      <c r="J776" t="n">
+        <v>3.425278621472542</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B777" t="n">
+        <v>0</v>
+      </c>
+      <c r="C777" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D777" t="n">
+        <v>0</v>
+      </c>
+      <c r="E777" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F777" t="n">
+        <v>53.73436134089955</v>
+      </c>
+      <c r="G777" t="n">
+        <v>3162.811073290144</v>
+      </c>
+      <c r="H777" t="n">
+        <v>53734361340.89954</v>
+      </c>
+      <c r="I777" t="n">
+        <v>3.307632379819488</v>
+      </c>
+      <c r="J777" t="n">
+        <v>3.307632379819489</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B778" t="n">
+        <v>300</v>
+      </c>
+      <c r="C778" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D778" t="n">
+        <v>0</v>
+      </c>
+      <c r="E778" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F778" t="n">
+        <v>53.41317753394737</v>
+      </c>
+      <c r="G778" t="n">
+        <v>2774.487242571632</v>
+      </c>
+      <c r="H778" t="n">
+        <v>22450707282.63555</v>
+      </c>
+      <c r="I778" t="n">
+        <v>3.628816186771665</v>
+      </c>
+      <c r="J778" t="n">
+        <v>34.59128643808348</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B779" t="n">
+        <v>10</v>
+      </c>
+      <c r="C779" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D779" t="n">
+        <v>0</v>
+      </c>
+      <c r="E779" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F779" t="n">
+        <v>53.67348050246586</v>
+      </c>
+      <c r="G779" t="n">
+        <v>3029.371268885972</v>
+      </c>
+      <c r="H779" t="n">
+        <v>52546583775.34158</v>
+      </c>
+      <c r="I779" t="n">
+        <v>3.368513218253177</v>
+      </c>
+      <c r="J779" t="n">
+        <v>4.495409945377449</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B780" t="n">
+        <v>2</v>
+      </c>
+      <c r="C780" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D780" t="n">
+        <v>0</v>
+      </c>
+      <c r="E780" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F780" t="n">
+        <v>53.73436562017996</v>
+      </c>
+      <c r="G780" t="n">
+        <v>3162.730881247984</v>
+      </c>
+      <c r="H780" t="n">
+        <v>53499064578.31302</v>
+      </c>
+      <c r="I780" t="n">
+        <v>3.307628100539077</v>
+      </c>
+      <c r="J780" t="n">
+        <v>3.542929142406014</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_MINUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B781" t="n">
+        <v>9</v>
+      </c>
+      <c r="C781" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D781" t="n">
+        <v>0</v>
+      </c>
+      <c r="E781" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F781" t="n">
+        <v>53.67348050246586</v>
+      </c>
+      <c r="G781" t="n">
+        <v>3029.371268885972</v>
+      </c>
+      <c r="H781" t="n">
+        <v>52659273448.05402</v>
+      </c>
+      <c r="I781" t="n">
+        <v>3.368513218253177</v>
+      </c>
+      <c r="J781" t="n">
+        <v>4.382720272665009</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B782" t="n">
+        <v>50</v>
+      </c>
+      <c r="C782" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D782" t="n">
+        <v>0</v>
+      </c>
+      <c r="E782" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F782" t="n">
+        <v>53.91779155662243</v>
+      </c>
+      <c r="G782" t="n">
+        <v>3930.877805035103</v>
+      </c>
+      <c r="H782" t="n">
+        <v>46606549486.83068</v>
+      </c>
+      <c r="I782" t="n">
+        <v>3.124202164096602</v>
+      </c>
+      <c r="J782" t="n">
+        <v>10.43544423388835</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B783" t="n">
+        <v>900</v>
+      </c>
+      <c r="C783" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D783" t="n">
+        <v>0</v>
+      </c>
+      <c r="E783" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F783" t="n">
+        <v>52.6330585257647</v>
+      </c>
+      <c r="G783" t="n">
+        <v>3034.362838785173</v>
+      </c>
+      <c r="H783" t="n">
+        <v>-48954760318.00462</v>
+      </c>
+      <c r="I783" t="n">
+        <v>4.408935194954331</v>
+      </c>
+      <c r="J783" t="n">
+        <v>105.9967540387237</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B784" t="n">
+        <v>5</v>
+      </c>
+      <c r="C784" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D784" t="n">
+        <v>0</v>
+      </c>
+      <c r="E784" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F784" t="n">
+        <v>54.73936252173847</v>
+      </c>
+      <c r="G784" t="n">
+        <v>7094.593860506753</v>
+      </c>
+      <c r="H784" t="n">
+        <v>53419802472.46444</v>
+      </c>
+      <c r="I784" t="n">
+        <v>2.302631198980563</v>
+      </c>
+      <c r="J784" t="n">
+        <v>3.622191248254593</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B785" t="n">
+        <v>150</v>
+      </c>
+      <c r="C785" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D785" t="n">
+        <v>0</v>
+      </c>
+      <c r="E785" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F785" t="n">
+        <v>52.70327868244731</v>
+      </c>
+      <c r="G785" t="n">
+        <v>3102.663213709522</v>
+      </c>
+      <c r="H785" t="n">
+        <v>35390869387.44578</v>
+      </c>
+      <c r="I785" t="n">
+        <v>4.338715038271722</v>
+      </c>
+      <c r="J785" t="n">
+        <v>21.65112433327326</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B786" t="n">
+        <v>175</v>
+      </c>
+      <c r="C786" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D786" t="n">
+        <v>0</v>
+      </c>
+      <c r="E786" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F786" t="n">
+        <v>52.6456932023549</v>
+      </c>
+      <c r="G786" t="n">
+        <v>3046.10652915268</v>
+      </c>
+      <c r="H786" t="n">
+        <v>32816056774.15427</v>
+      </c>
+      <c r="I786" t="n">
+        <v>4.396300518364136</v>
+      </c>
+      <c r="J786" t="n">
+        <v>24.22593694656476</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B787" t="n">
+        <v>3</v>
+      </c>
+      <c r="C787" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D787" t="n">
+        <v>0</v>
+      </c>
+      <c r="E787" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F787" t="n">
+        <v>54.74377923672339</v>
+      </c>
+      <c r="G787" t="n">
+        <v>7134.53894535208</v>
+      </c>
+      <c r="H787" t="n">
+        <v>53947585451.93043</v>
+      </c>
+      <c r="I787" t="n">
+        <v>2.298214483995643</v>
+      </c>
+      <c r="J787" t="n">
+        <v>3.094408268788605</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B788" t="n">
+        <v>200</v>
+      </c>
+      <c r="C788" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D788" t="n">
+        <v>0</v>
+      </c>
+      <c r="E788" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F788" t="n">
+        <v>52.64569320235491</v>
+      </c>
+      <c r="G788" t="n">
+        <v>3046.10652915268</v>
+      </c>
+      <c r="H788" t="n">
+        <v>29983251570.12561</v>
+      </c>
+      <c r="I788" t="n">
+        <v>4.396300518364122</v>
+      </c>
+      <c r="J788" t="n">
+        <v>27.05874215059342</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B789" t="n">
+        <v>125</v>
+      </c>
+      <c r="C789" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D789" t="n">
+        <v>0</v>
+      </c>
+      <c r="E789" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F789" t="n">
+        <v>52.72911394634242</v>
+      </c>
+      <c r="G789" t="n">
+        <v>3165.769327000748</v>
+      </c>
+      <c r="H789" t="n">
+        <v>38008670425.31985</v>
+      </c>
+      <c r="I789" t="n">
+        <v>4.312879774376611</v>
+      </c>
+      <c r="J789" t="n">
+        <v>19.03332329539919</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B790" t="n">
+        <v>7</v>
+      </c>
+      <c r="C790" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D790" t="n">
+        <v>0</v>
+      </c>
+      <c r="E790" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F790" t="n">
+        <v>54.73936252173845</v>
+      </c>
+      <c r="G790" t="n">
+        <v>7094.593860506753</v>
+      </c>
+      <c r="H790" t="n">
+        <v>52891978452.75481</v>
+      </c>
+      <c r="I790" t="n">
+        <v>2.302631198980585</v>
+      </c>
+      <c r="J790" t="n">
+        <v>4.150015267964226</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B791" t="n">
+        <v>8</v>
+      </c>
+      <c r="C791" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D791" t="n">
+        <v>0</v>
+      </c>
+      <c r="E791" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F791" t="n">
+        <v>54.73936252173843</v>
+      </c>
+      <c r="G791" t="n">
+        <v>7094.593860506753</v>
+      </c>
+      <c r="H791" t="n">
+        <v>52628066442.89997</v>
+      </c>
+      <c r="I791" t="n">
+        <v>2.302631198980606</v>
+      </c>
+      <c r="J791" t="n">
+        <v>4.413927277819061</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B792" t="n">
+        <v>500</v>
+      </c>
+      <c r="C792" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D792" t="n">
+        <v>0</v>
+      </c>
+      <c r="E792" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F792" t="n">
+        <v>52.63578929778777</v>
+      </c>
+      <c r="G792" t="n">
+        <v>3035.465216039842</v>
+      </c>
+      <c r="H792" t="n">
+        <v>-3822391519.923512</v>
+      </c>
+      <c r="I792" t="n">
+        <v>4.406204422931268</v>
+      </c>
+      <c r="J792" t="n">
+        <v>60.86438524064255</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B793" t="n">
+        <v>250</v>
+      </c>
+      <c r="C793" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D793" t="n">
+        <v>0</v>
+      </c>
+      <c r="E793" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F793" t="n">
+        <v>52.64569320235491</v>
+      </c>
+      <c r="G793" t="n">
+        <v>3046.10652915268</v>
+      </c>
+      <c r="H793" t="n">
+        <v>24317641162.06829</v>
+      </c>
+      <c r="I793" t="n">
+        <v>4.396300518364122</v>
+      </c>
+      <c r="J793" t="n">
+        <v>32.72435255865074</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B794" t="n">
+        <v>4</v>
+      </c>
+      <c r="C794" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D794" t="n">
+        <v>0</v>
+      </c>
+      <c r="E794" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F794" t="n">
+        <v>54.73936252173846</v>
+      </c>
+      <c r="G794" t="n">
+        <v>7094.593860506753</v>
+      </c>
+      <c r="H794" t="n">
+        <v>53683714482.31924</v>
+      </c>
+      <c r="I794" t="n">
+        <v>2.302631198980578</v>
+      </c>
+      <c r="J794" t="n">
+        <v>3.358279238399795</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B795" t="n">
+        <v>400</v>
+      </c>
+      <c r="C795" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D795" t="n">
+        <v>0</v>
+      </c>
+      <c r="E795" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F795" t="n">
+        <v>52.64150562635838</v>
+      </c>
+      <c r="G795" t="n">
+        <v>3040.859933474869</v>
+      </c>
+      <c r="H795" t="n">
+        <v>7394689669.906528</v>
+      </c>
+      <c r="I795" t="n">
+        <v>4.400488094360654</v>
+      </c>
+      <c r="J795" t="n">
+        <v>49.6473040508125</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B796" t="n">
+        <v>6</v>
+      </c>
+      <c r="C796" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D796" t="n">
+        <v>0</v>
+      </c>
+      <c r="E796" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F796" t="n">
+        <v>54.73936252173846</v>
+      </c>
+      <c r="G796" t="n">
+        <v>7094.593860506753</v>
+      </c>
+      <c r="H796" t="n">
+        <v>53155890462.60962</v>
+      </c>
+      <c r="I796" t="n">
+        <v>2.302631198980578</v>
+      </c>
+      <c r="J796" t="n">
+        <v>3.886103258109413</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B797" t="n">
+        <v>600</v>
+      </c>
+      <c r="C797" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D797" t="n">
+        <v>0</v>
+      </c>
+      <c r="E797" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F797" t="n">
+        <v>52.63275246968931</v>
+      </c>
+      <c r="G797" t="n">
+        <v>3034.33632454106</v>
+      </c>
+      <c r="H797" t="n">
+        <v>-15091868310.32627</v>
+      </c>
+      <c r="I797" t="n">
+        <v>4.409241251029727</v>
+      </c>
+      <c r="J797" t="n">
+        <v>72.1338620310453</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B798" t="n">
+        <v>75</v>
+      </c>
+      <c r="C798" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D798" t="n">
+        <v>0</v>
+      </c>
+      <c r="E798" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F798" t="n">
+        <v>53.05741348373176</v>
+      </c>
+      <c r="G798" t="n">
+        <v>3424.360697310411</v>
+      </c>
+      <c r="H798" t="n">
+        <v>43503696260.47644</v>
+      </c>
+      <c r="I798" t="n">
+        <v>3.984580236987277</v>
+      </c>
+      <c r="J798" t="n">
+        <v>13.53829746024259</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B799" t="n">
+        <v>700</v>
+      </c>
+      <c r="C799" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D799" t="n">
+        <v>0</v>
+      </c>
+      <c r="E799" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F799" t="n">
+        <v>52.63306443262868</v>
+      </c>
+      <c r="G799" t="n">
+        <v>3034.363068210134</v>
+      </c>
+      <c r="H799" t="n">
+        <v>-26379689531.0399</v>
+      </c>
+      <c r="I799" t="n">
+        <v>4.408929288090356</v>
+      </c>
+      <c r="J799" t="n">
+        <v>83.42168325175894</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B800" t="n">
+        <v>800</v>
+      </c>
+      <c r="C800" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D800" t="n">
+        <v>0</v>
+      </c>
+      <c r="E800" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F800" t="n">
+        <v>52.63306021652147</v>
+      </c>
+      <c r="G800" t="n">
+        <v>3034.362738224718</v>
+      </c>
+      <c r="H800" t="n">
+        <v>-37667220207.56128</v>
+      </c>
+      <c r="I800" t="n">
+        <v>4.408933504197563</v>
+      </c>
+      <c r="J800" t="n">
+        <v>94.70921392828031</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B801" t="n">
+        <v>100</v>
+      </c>
+      <c r="C801" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D801" t="n">
+        <v>0</v>
+      </c>
+      <c r="E801" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F801" t="n">
+        <v>53.03558247887435</v>
+      </c>
+      <c r="G801" t="n">
+        <v>3310.72454766973</v>
+      </c>
+      <c r="H801" t="n">
+        <v>40720008301.82407</v>
+      </c>
+      <c r="I801" t="n">
+        <v>4.006411241844681</v>
+      </c>
+      <c r="J801" t="n">
+        <v>16.32198541889496</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B802" t="n">
+        <v>1</v>
+      </c>
+      <c r="C802" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D802" t="n">
+        <v>0</v>
+      </c>
+      <c r="E802" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F802" t="n">
+        <v>54.74377923672339</v>
+      </c>
+      <c r="G802" t="n">
+        <v>7134.53894535208</v>
+      </c>
+      <c r="H802" t="n">
+        <v>54478381308.45907</v>
+      </c>
+      <c r="I802" t="n">
+        <v>2.298214483995643</v>
+      </c>
+      <c r="J802" t="n">
+        <v>2.563612412259964</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B803" t="n">
+        <v>0</v>
+      </c>
+      <c r="C803" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D803" t="n">
+        <v>0</v>
+      </c>
+      <c r="E803" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F803" t="n">
+        <v>54.74373346523699</v>
+      </c>
+      <c r="G803" t="n">
+        <v>7134.90585058612</v>
+      </c>
+      <c r="H803" t="n">
+        <v>54743733465.23699</v>
+      </c>
+      <c r="I803" t="n">
+        <v>2.298260255482042</v>
+      </c>
+      <c r="J803" t="n">
+        <v>2.29826025548204</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B804" t="n">
+        <v>300</v>
+      </c>
+      <c r="C804" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D804" t="n">
+        <v>0</v>
+      </c>
+      <c r="E804" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F804" t="n">
+        <v>52.64569320235491</v>
+      </c>
+      <c r="G804" t="n">
+        <v>3046.10652915268</v>
+      </c>
+      <c r="H804" t="n">
+        <v>18652030754.01097</v>
+      </c>
+      <c r="I804" t="n">
+        <v>4.396300518364122</v>
+      </c>
+      <c r="J804" t="n">
+        <v>38.38996296670806</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B805" t="n">
+        <v>10</v>
+      </c>
+      <c r="C805" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D805" t="n">
+        <v>0</v>
+      </c>
+      <c r="E805" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F805" t="n">
+        <v>54.80031077989528</v>
+      </c>
+      <c r="G805" t="n">
+        <v>5746.308767878917</v>
+      </c>
+      <c r="H805" t="n">
+        <v>52662739657.43938</v>
+      </c>
+      <c r="I805" t="n">
+        <v>2.241682940823758</v>
+      </c>
+      <c r="J805" t="n">
+        <v>4.379254063279656</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B806" t="n">
+        <v>2</v>
+      </c>
+      <c r="C806" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D806" t="n">
+        <v>0</v>
+      </c>
+      <c r="E806" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F806" t="n">
+        <v>54.74377923672343</v>
+      </c>
+      <c r="G806" t="n">
+        <v>7134.53894535208</v>
+      </c>
+      <c r="H806" t="n">
+        <v>54212983380.19479</v>
+      </c>
+      <c r="I806" t="n">
+        <v>2.298214483995608</v>
+      </c>
+      <c r="J806" t="n">
+        <v>2.829010340524238</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ENGINEERED_1_PLUS_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B807" t="n">
+        <v>9</v>
+      </c>
+      <c r="C807" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D807" t="n">
+        <v>0</v>
+      </c>
+      <c r="E807" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F807" t="n">
+        <v>54.7528059225324</v>
+      </c>
+      <c r="G807" t="n">
+        <v>6522.951016040126</v>
+      </c>
+      <c r="H807" t="n">
+        <v>52568978867.72454</v>
+      </c>
+      <c r="I807" t="n">
+        <v>2.289187798186632</v>
+      </c>
+      <c r="J807" t="n">
+        <v>4.473014852994492</v>
       </c>
     </row>
   </sheetData>

--- a/benchmarks/results/plots/results-Fig1.xlsx
+++ b/benchmarks/results/plots/results-Fig1.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J807"/>
+  <dimension ref="A1:J1041"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27881,6 +27881,7962 @@
         <v>4.473014852994492</v>
       </c>
     </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B808" t="n">
+        <v>50</v>
+      </c>
+      <c r="C808" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D808" t="n">
+        <v>0</v>
+      </c>
+      <c r="E808" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F808" t="n">
+        <v>48.00336119205301</v>
+      </c>
+      <c r="G808" t="n">
+        <v>3528.550716767723</v>
+      </c>
+      <c r="H808" t="n">
+        <v>41440427993.57481</v>
+      </c>
+      <c r="I808" t="n">
+        <v>9.038632528666021</v>
+      </c>
+      <c r="J808" t="n">
+        <v>15.60156572714423</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B809" t="n">
+        <v>900</v>
+      </c>
+      <c r="C809" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D809" t="n">
+        <v>0</v>
+      </c>
+      <c r="E809" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F809" t="n">
+        <v>47.56317953993333</v>
+      </c>
+      <c r="G809" t="n">
+        <v>3116.007502974715</v>
+      </c>
+      <c r="H809" t="n">
+        <v>-56758031385.11004</v>
+      </c>
+      <c r="I809" t="n">
+        <v>9.478814180785704</v>
+      </c>
+      <c r="J809" t="n">
+        <v>113.8000251058291</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B810" t="n">
+        <v>5</v>
+      </c>
+      <c r="C810" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D810" t="n">
+        <v>0</v>
+      </c>
+      <c r="E810" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F810" t="n">
+        <v>49.2175131024426</v>
+      </c>
+      <c r="G810" t="n">
+        <v>4702.77177091825</v>
+      </c>
+      <c r="H810" t="n">
+        <v>48342820361.4949</v>
+      </c>
+      <c r="I810" t="n">
+        <v>7.824480618276432</v>
+      </c>
+      <c r="J810" t="n">
+        <v>8.69917335922413</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B811" t="n">
+        <v>150</v>
+      </c>
+      <c r="C811" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D811" t="n">
+        <v>0</v>
+      </c>
+      <c r="E811" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F811" t="n">
+        <v>47.56317953993332</v>
+      </c>
+      <c r="G811" t="n">
+        <v>3116.007502974715</v>
+      </c>
+      <c r="H811" t="n">
+        <v>30176311052.4261</v>
+      </c>
+      <c r="I811" t="n">
+        <v>9.478814180785712</v>
+      </c>
+      <c r="J811" t="n">
+        <v>26.86568266829293</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B812" t="n">
+        <v>175</v>
+      </c>
+      <c r="C812" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D812" t="n">
+        <v>0</v>
+      </c>
+      <c r="E812" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F812" t="n">
+        <v>47.5631795399333</v>
+      </c>
+      <c r="G812" t="n">
+        <v>3116.007502974715</v>
+      </c>
+      <c r="H812" t="n">
+        <v>27278499637.84154</v>
+      </c>
+      <c r="I812" t="n">
+        <v>9.478814180785733</v>
+      </c>
+      <c r="J812" t="n">
+        <v>29.76349408287749</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B813" t="n">
+        <v>3</v>
+      </c>
+      <c r="C813" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D813" t="n">
+        <v>0</v>
+      </c>
+      <c r="E813" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F813" t="n">
+        <v>49.2175131024426</v>
+      </c>
+      <c r="G813" t="n">
+        <v>4702.77177091825</v>
+      </c>
+      <c r="H813" t="n">
+        <v>48692697457.87397</v>
+      </c>
+      <c r="I813" t="n">
+        <v>7.824480618276432</v>
+      </c>
+      <c r="J813" t="n">
+        <v>8.349296262845062</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B814" t="n">
+        <v>200</v>
+      </c>
+      <c r="C814" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D814" t="n">
+        <v>0</v>
+      </c>
+      <c r="E814" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F814" t="n">
+        <v>47.56317953993332</v>
+      </c>
+      <c r="G814" t="n">
+        <v>3116.007502974715</v>
+      </c>
+      <c r="H814" t="n">
+        <v>24380688223.25701</v>
+      </c>
+      <c r="I814" t="n">
+        <v>9.478814180785712</v>
+      </c>
+      <c r="J814" t="n">
+        <v>32.66130549746202</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B815" t="n">
+        <v>125</v>
+      </c>
+      <c r="C815" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D815" t="n">
+        <v>0</v>
+      </c>
+      <c r="E815" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F815" t="n">
+        <v>48.003361192053</v>
+      </c>
+      <c r="G815" t="n">
+        <v>3528.550716767723</v>
+      </c>
+      <c r="H815" t="n">
+        <v>31596028195.85749</v>
+      </c>
+      <c r="I815" t="n">
+        <v>9.038632528666035</v>
+      </c>
+      <c r="J815" t="n">
+        <v>25.44596552486154</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B816" t="n">
+        <v>7</v>
+      </c>
+      <c r="C816" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D816" t="n">
+        <v>0</v>
+      </c>
+      <c r="E816" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F816" t="n">
+        <v>49.2175131024426</v>
+      </c>
+      <c r="G816" t="n">
+        <v>4702.77177091825</v>
+      </c>
+      <c r="H816" t="n">
+        <v>47992943265.11581</v>
+      </c>
+      <c r="I816" t="n">
+        <v>7.824480618276432</v>
+      </c>
+      <c r="J816" t="n">
+        <v>9.049050455603226</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B817" t="n">
+        <v>8</v>
+      </c>
+      <c r="C817" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D817" t="n">
+        <v>0</v>
+      </c>
+      <c r="E817" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F817" t="n">
+        <v>49.2175131024426</v>
+      </c>
+      <c r="G817" t="n">
+        <v>4702.77177091825</v>
+      </c>
+      <c r="H817" t="n">
+        <v>47818004716.92627</v>
+      </c>
+      <c r="I817" t="n">
+        <v>7.824480618276432</v>
+      </c>
+      <c r="J817" t="n">
+        <v>9.223989003792763</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B818" t="n">
+        <v>500</v>
+      </c>
+      <c r="C818" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D818" t="n">
+        <v>0</v>
+      </c>
+      <c r="E818" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F818" t="n">
+        <v>47.56317953993332</v>
+      </c>
+      <c r="G818" t="n">
+        <v>3116.007502974715</v>
+      </c>
+      <c r="H818" t="n">
+        <v>-10393048751.75744</v>
+      </c>
+      <c r="I818" t="n">
+        <v>9.478814180785712</v>
+      </c>
+      <c r="J818" t="n">
+        <v>67.43504247247647</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B819" t="n">
+        <v>250</v>
+      </c>
+      <c r="C819" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D819" t="n">
+        <v>0</v>
+      </c>
+      <c r="E819" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F819" t="n">
+        <v>47.56317953993332</v>
+      </c>
+      <c r="G819" t="n">
+        <v>3116.007502974715</v>
+      </c>
+      <c r="H819" t="n">
+        <v>18585065394.08794</v>
+      </c>
+      <c r="I819" t="n">
+        <v>9.478814180785712</v>
+      </c>
+      <c r="J819" t="n">
+        <v>38.45692832663109</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B820" t="n">
+        <v>4</v>
+      </c>
+      <c r="C820" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D820" t="n">
+        <v>0</v>
+      </c>
+      <c r="E820" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F820" t="n">
+        <v>49.2175131024426</v>
+      </c>
+      <c r="G820" t="n">
+        <v>4702.77177091825</v>
+      </c>
+      <c r="H820" t="n">
+        <v>48517758909.68444</v>
+      </c>
+      <c r="I820" t="n">
+        <v>7.824480618276432</v>
+      </c>
+      <c r="J820" t="n">
+        <v>8.524234811034592</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B821" t="n">
+        <v>400</v>
+      </c>
+      <c r="C821" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D821" t="n">
+        <v>0</v>
+      </c>
+      <c r="E821" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F821" t="n">
+        <v>47.56317953993332</v>
+      </c>
+      <c r="G821" t="n">
+        <v>3116.007502974715</v>
+      </c>
+      <c r="H821" t="n">
+        <v>1198196906.580714</v>
+      </c>
+      <c r="I821" t="n">
+        <v>9.478814180785712</v>
+      </c>
+      <c r="J821" t="n">
+        <v>55.84379681413832</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B822" t="n">
+        <v>6</v>
+      </c>
+      <c r="C822" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D822" t="n">
+        <v>0</v>
+      </c>
+      <c r="E822" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F822" t="n">
+        <v>49.21751310244258</v>
+      </c>
+      <c r="G822" t="n">
+        <v>4702.77177091825</v>
+      </c>
+      <c r="H822" t="n">
+        <v>48167881813.30534</v>
+      </c>
+      <c r="I822" t="n">
+        <v>7.824480618276453</v>
+      </c>
+      <c r="J822" t="n">
+        <v>8.874111907413688</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B823" t="n">
+        <v>600</v>
+      </c>
+      <c r="C823" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D823" t="n">
+        <v>0</v>
+      </c>
+      <c r="E823" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F823" t="n">
+        <v>47.5631795399333</v>
+      </c>
+      <c r="G823" t="n">
+        <v>3116.007502974715</v>
+      </c>
+      <c r="H823" t="n">
+        <v>-21984294410.09559</v>
+      </c>
+      <c r="I823" t="n">
+        <v>9.478814180785733</v>
+      </c>
+      <c r="J823" t="n">
+        <v>79.02628813081462</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B824" t="n">
+        <v>75</v>
+      </c>
+      <c r="C824" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D824" t="n">
+        <v>0</v>
+      </c>
+      <c r="E824" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F824" t="n">
+        <v>48.00336119205299</v>
+      </c>
+      <c r="G824" t="n">
+        <v>3528.550716767723</v>
+      </c>
+      <c r="H824" t="n">
+        <v>38158961394.33569</v>
+      </c>
+      <c r="I824" t="n">
+        <v>9.038632528666042</v>
+      </c>
+      <c r="J824" t="n">
+        <v>18.88303232638334</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B825" t="n">
+        <v>700</v>
+      </c>
+      <c r="C825" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D825" t="n">
+        <v>0</v>
+      </c>
+      <c r="E825" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F825" t="n">
+        <v>47.5631795399333</v>
+      </c>
+      <c r="G825" t="n">
+        <v>3116.007502974715</v>
+      </c>
+      <c r="H825" t="n">
+        <v>-33575540068.43375</v>
+      </c>
+      <c r="I825" t="n">
+        <v>9.478814180785733</v>
+      </c>
+      <c r="J825" t="n">
+        <v>90.61753378915279</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B826" t="n">
+        <v>800</v>
+      </c>
+      <c r="C826" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D826" t="n">
+        <v>0</v>
+      </c>
+      <c r="E826" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F826" t="n">
+        <v>47.5631795399333</v>
+      </c>
+      <c r="G826" t="n">
+        <v>3116.007502974715</v>
+      </c>
+      <c r="H826" t="n">
+        <v>-45166785726.77191</v>
+      </c>
+      <c r="I826" t="n">
+        <v>9.478814180785733</v>
+      </c>
+      <c r="J826" t="n">
+        <v>102.2087794474909</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B827" t="n">
+        <v>100</v>
+      </c>
+      <c r="C827" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D827" t="n">
+        <v>0</v>
+      </c>
+      <c r="E827" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F827" t="n">
+        <v>48.00336119205301</v>
+      </c>
+      <c r="G827" t="n">
+        <v>3528.550716767723</v>
+      </c>
+      <c r="H827" t="n">
+        <v>34877494795.09661</v>
+      </c>
+      <c r="I827" t="n">
+        <v>9.038632528666021</v>
+      </c>
+      <c r="J827" t="n">
+        <v>22.16449892562242</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B828" t="n">
+        <v>1</v>
+      </c>
+      <c r="C828" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D828" t="n">
+        <v>0</v>
+      </c>
+      <c r="E828" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F828" t="n">
+        <v>49.21751310244261</v>
+      </c>
+      <c r="G828" t="n">
+        <v>4702.77177091825</v>
+      </c>
+      <c r="H828" t="n">
+        <v>49042574554.25307</v>
+      </c>
+      <c r="I828" t="n">
+        <v>7.824480618276425</v>
+      </c>
+      <c r="J828" t="n">
+        <v>7.999419166465965</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B829" t="n">
+        <v>0</v>
+      </c>
+      <c r="C829" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D829" t="n">
+        <v>0</v>
+      </c>
+      <c r="E829" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F829" t="n">
+        <v>49.2175131024426</v>
+      </c>
+      <c r="G829" t="n">
+        <v>4702.77177091825</v>
+      </c>
+      <c r="H829" t="n">
+        <v>49217513102.4426</v>
+      </c>
+      <c r="I829" t="n">
+        <v>7.824480618276432</v>
+      </c>
+      <c r="J829" t="n">
+        <v>7.824480618276436</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B830" t="n">
+        <v>300</v>
+      </c>
+      <c r="C830" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D830" t="n">
+        <v>0</v>
+      </c>
+      <c r="E830" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F830" t="n">
+        <v>47.56317953993332</v>
+      </c>
+      <c r="G830" t="n">
+        <v>3116.007502974715</v>
+      </c>
+      <c r="H830" t="n">
+        <v>12789442564.91887</v>
+      </c>
+      <c r="I830" t="n">
+        <v>9.478814180785712</v>
+      </c>
+      <c r="J830" t="n">
+        <v>44.25255115580016</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B831" t="n">
+        <v>10</v>
+      </c>
+      <c r="C831" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D831" t="n">
+        <v>0</v>
+      </c>
+      <c r="E831" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F831" t="n">
+        <v>49.21751310244262</v>
+      </c>
+      <c r="G831" t="n">
+        <v>4702.77177091825</v>
+      </c>
+      <c r="H831" t="n">
+        <v>47468127620.54721</v>
+      </c>
+      <c r="I831" t="n">
+        <v>7.824480618276418</v>
+      </c>
+      <c r="J831" t="n">
+        <v>9.573866100171822</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B832" t="n">
+        <v>2</v>
+      </c>
+      <c r="C832" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D832" t="n">
+        <v>0</v>
+      </c>
+      <c r="E832" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F832" t="n">
+        <v>49.21751310244259</v>
+      </c>
+      <c r="G832" t="n">
+        <v>4702.77177091825</v>
+      </c>
+      <c r="H832" t="n">
+        <v>48867636006.06351</v>
+      </c>
+      <c r="I832" t="n">
+        <v>7.824480618276446</v>
+      </c>
+      <c r="J832" t="n">
+        <v>8.174357714655525</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B833" t="n">
+        <v>9</v>
+      </c>
+      <c r="C833" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D833" t="n">
+        <v>0</v>
+      </c>
+      <c r="E833" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F833" t="n">
+        <v>49.21751310244262</v>
+      </c>
+      <c r="G833" t="n">
+        <v>4702.77177091825</v>
+      </c>
+      <c r="H833" t="n">
+        <v>47643066168.73675</v>
+      </c>
+      <c r="I833" t="n">
+        <v>7.824480618276418</v>
+      </c>
+      <c r="J833" t="n">
+        <v>9.398927551982284</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B834" t="n">
+        <v>50</v>
+      </c>
+      <c r="C834" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D834" t="n">
+        <v>0</v>
+      </c>
+      <c r="E834" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F834" t="n">
+        <v>54.75776345607228</v>
+      </c>
+      <c r="G834" t="n">
+        <v>7421.05405119808</v>
+      </c>
+      <c r="H834" t="n">
+        <v>40954962841.96533</v>
+      </c>
+      <c r="I834" t="n">
+        <v>2.284230264646752</v>
+      </c>
+      <c r="J834" t="n">
+        <v>16.0870308787537</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B835" t="n">
+        <v>900</v>
+      </c>
+      <c r="C835" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D835" t="n">
+        <v>0</v>
+      </c>
+      <c r="E835" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F835" t="n">
+        <v>54.75776345607235</v>
+      </c>
+      <c r="G835" t="n">
+        <v>7421.05405119808</v>
+      </c>
+      <c r="H835" t="n">
+        <v>-193692647597.8527</v>
+      </c>
+      <c r="I835" t="n">
+        <v>2.284230264646688</v>
+      </c>
+      <c r="J835" t="n">
+        <v>250.7346413185717</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B836" t="n">
+        <v>5</v>
+      </c>
+      <c r="C836" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D836" t="n">
+        <v>0</v>
+      </c>
+      <c r="E836" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F836" t="n">
+        <v>54.61345545249434</v>
+      </c>
+      <c r="G836" t="n">
+        <v>8934.353649845107</v>
+      </c>
+      <c r="H836" t="n">
+        <v>52951709005.23835</v>
+      </c>
+      <c r="I836" t="n">
+        <v>2.428538268224692</v>
+      </c>
+      <c r="J836" t="n">
+        <v>4.090284715480682</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B837" t="n">
+        <v>150</v>
+      </c>
+      <c r="C837" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D837" t="n">
+        <v>0</v>
+      </c>
+      <c r="E837" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F837" t="n">
+        <v>54.75776345607228</v>
+      </c>
+      <c r="G837" t="n">
+        <v>7421.05405119808</v>
+      </c>
+      <c r="H837" t="n">
+        <v>13349361613.75143</v>
+      </c>
+      <c r="I837" t="n">
+        <v>2.284230264646752</v>
+      </c>
+      <c r="J837" t="n">
+        <v>43.69263210696761</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B838" t="n">
+        <v>175</v>
+      </c>
+      <c r="C838" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D838" t="n">
+        <v>0</v>
+      </c>
+      <c r="E838" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F838" t="n">
+        <v>54.75776345607227</v>
+      </c>
+      <c r="G838" t="n">
+        <v>7421.05405119808</v>
+      </c>
+      <c r="H838" t="n">
+        <v>6447961306.69796</v>
+      </c>
+      <c r="I838" t="n">
+        <v>2.284230264646766</v>
+      </c>
+      <c r="J838" t="n">
+        <v>50.59403241402107</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B839" t="n">
+        <v>3</v>
+      </c>
+      <c r="C839" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D839" t="n">
+        <v>0</v>
+      </c>
+      <c r="E839" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F839" t="n">
+        <v>54.61345545249431</v>
+      </c>
+      <c r="G839" t="n">
+        <v>8934.353649845107</v>
+      </c>
+      <c r="H839" t="n">
+        <v>53616407584.14072</v>
+      </c>
+      <c r="I839" t="n">
+        <v>2.428538268224727</v>
+      </c>
+      <c r="J839" t="n">
+        <v>3.425586136578316</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B840" t="n">
+        <v>200</v>
+      </c>
+      <c r="C840" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D840" t="n">
+        <v>0</v>
+      </c>
+      <c r="E840" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F840" t="n">
+        <v>54.75776345607228</v>
+      </c>
+      <c r="G840" t="n">
+        <v>7421.05405119808</v>
+      </c>
+      <c r="H840" t="n">
+        <v>-453439000.3555024</v>
+      </c>
+      <c r="I840" t="n">
+        <v>2.284230264646752</v>
+      </c>
+      <c r="J840" t="n">
+        <v>57.49543272107453</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B841" t="n">
+        <v>125</v>
+      </c>
+      <c r="C841" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D841" t="n">
+        <v>0</v>
+      </c>
+      <c r="E841" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F841" t="n">
+        <v>54.75776345607227</v>
+      </c>
+      <c r="G841" t="n">
+        <v>7421.05405119808</v>
+      </c>
+      <c r="H841" t="n">
+        <v>20250761920.8049</v>
+      </c>
+      <c r="I841" t="n">
+        <v>2.284230264646766</v>
+      </c>
+      <c r="J841" t="n">
+        <v>36.79123179991413</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B842" t="n">
+        <v>7</v>
+      </c>
+      <c r="C842" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D842" t="n">
+        <v>0</v>
+      </c>
+      <c r="E842" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F842" t="n">
+        <v>54.75776345607227</v>
+      </c>
+      <c r="G842" t="n">
+        <v>7421.05405119808</v>
+      </c>
+      <c r="H842" t="n">
+        <v>52825371370.09729</v>
+      </c>
+      <c r="I842" t="n">
+        <v>2.284230264646766</v>
+      </c>
+      <c r="J842" t="n">
+        <v>4.216622350621742</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B843" t="n">
+        <v>8</v>
+      </c>
+      <c r="C843" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D843" t="n">
+        <v>0</v>
+      </c>
+      <c r="E843" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F843" t="n">
+        <v>54.75776345607227</v>
+      </c>
+      <c r="G843" t="n">
+        <v>7421.05405119808</v>
+      </c>
+      <c r="H843" t="n">
+        <v>52549315357.81516</v>
+      </c>
+      <c r="I843" t="n">
+        <v>2.284230264646766</v>
+      </c>
+      <c r="J843" t="n">
+        <v>4.492678362903869</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B844" t="n">
+        <v>500</v>
+      </c>
+      <c r="C844" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D844" t="n">
+        <v>0</v>
+      </c>
+      <c r="E844" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F844" t="n">
+        <v>54.75776345607228</v>
+      </c>
+      <c r="G844" t="n">
+        <v>7421.05405119808</v>
+      </c>
+      <c r="H844" t="n">
+        <v>-83270242684.99718</v>
+      </c>
+      <c r="I844" t="n">
+        <v>2.284230264646752</v>
+      </c>
+      <c r="J844" t="n">
+        <v>140.3122364057162</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B845" t="n">
+        <v>250</v>
+      </c>
+      <c r="C845" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D845" t="n">
+        <v>0</v>
+      </c>
+      <c r="E845" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F845" t="n">
+        <v>54.75776345607228</v>
+      </c>
+      <c r="G845" t="n">
+        <v>7421.05405119808</v>
+      </c>
+      <c r="H845" t="n">
+        <v>-14256239614.46246</v>
+      </c>
+      <c r="I845" t="n">
+        <v>2.284230264646752</v>
+      </c>
+      <c r="J845" t="n">
+        <v>71.29823333518149</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B846" t="n">
+        <v>4</v>
+      </c>
+      <c r="C846" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D846" t="n">
+        <v>0</v>
+      </c>
+      <c r="E846" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F846" t="n">
+        <v>54.61345545249429</v>
+      </c>
+      <c r="G846" t="n">
+        <v>8934.353649845107</v>
+      </c>
+      <c r="H846" t="n">
+        <v>53284058294.6895</v>
+      </c>
+      <c r="I846" t="n">
+        <v>2.428538268224742</v>
+      </c>
+      <c r="J846" t="n">
+        <v>3.757935426029533</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B847" t="n">
+        <v>400</v>
+      </c>
+      <c r="C847" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D847" t="n">
+        <v>0</v>
+      </c>
+      <c r="E847" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F847" t="n">
+        <v>54.75776345607229</v>
+      </c>
+      <c r="G847" t="n">
+        <v>7421.05405119808</v>
+      </c>
+      <c r="H847" t="n">
+        <v>-55664641456.78327</v>
+      </c>
+      <c r="I847" t="n">
+        <v>2.284230264646745</v>
+      </c>
+      <c r="J847" t="n">
+        <v>112.7066351775023</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B848" t="n">
+        <v>6</v>
+      </c>
+      <c r="C848" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D848" t="n">
+        <v>0</v>
+      </c>
+      <c r="E848" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F848" t="n">
+        <v>54.75776345607225</v>
+      </c>
+      <c r="G848" t="n">
+        <v>7421.05405119808</v>
+      </c>
+      <c r="H848" t="n">
+        <v>53101427382.37942</v>
+      </c>
+      <c r="I848" t="n">
+        <v>2.284230264646787</v>
+      </c>
+      <c r="J848" t="n">
+        <v>3.940566338339615</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B849" t="n">
+        <v>600</v>
+      </c>
+      <c r="C849" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D849" t="n">
+        <v>0</v>
+      </c>
+      <c r="E849" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F849" t="n">
+        <v>54.75776345607231</v>
+      </c>
+      <c r="G849" t="n">
+        <v>7421.05405119808</v>
+      </c>
+      <c r="H849" t="n">
+        <v>-110875843913.211</v>
+      </c>
+      <c r="I849" t="n">
+        <v>2.284230264646723</v>
+      </c>
+      <c r="J849" t="n">
+        <v>167.91783763393</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B850" t="n">
+        <v>75</v>
+      </c>
+      <c r="C850" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D850" t="n">
+        <v>0</v>
+      </c>
+      <c r="E850" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F850" t="n">
+        <v>54.75776345607228</v>
+      </c>
+      <c r="G850" t="n">
+        <v>7421.05405119808</v>
+      </c>
+      <c r="H850" t="n">
+        <v>34053562534.91186</v>
+      </c>
+      <c r="I850" t="n">
+        <v>2.284230264646752</v>
+      </c>
+      <c r="J850" t="n">
+        <v>22.98843118580717</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B851" t="n">
+        <v>700</v>
+      </c>
+      <c r="C851" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D851" t="n">
+        <v>0</v>
+      </c>
+      <c r="E851" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F851" t="n">
+        <v>54.7577634560723</v>
+      </c>
+      <c r="G851" t="n">
+        <v>7421.05405119808</v>
+      </c>
+      <c r="H851" t="n">
+        <v>-138481445141.4249</v>
+      </c>
+      <c r="I851" t="n">
+        <v>2.284230264646737</v>
+      </c>
+      <c r="J851" t="n">
+        <v>195.5234388621439</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B852" t="n">
+        <v>800</v>
+      </c>
+      <c r="C852" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D852" t="n">
+        <v>0</v>
+      </c>
+      <c r="E852" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F852" t="n">
+        <v>54.75776345607235</v>
+      </c>
+      <c r="G852" t="n">
+        <v>7421.05405119808</v>
+      </c>
+      <c r="H852" t="n">
+        <v>-166087046369.6388</v>
+      </c>
+      <c r="I852" t="n">
+        <v>2.284230264646688</v>
+      </c>
+      <c r="J852" t="n">
+        <v>223.1290400903578</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B853" t="n">
+        <v>100</v>
+      </c>
+      <c r="C853" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D853" t="n">
+        <v>0</v>
+      </c>
+      <c r="E853" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F853" t="n">
+        <v>54.75776345607227</v>
+      </c>
+      <c r="G853" t="n">
+        <v>7421.05405119808</v>
+      </c>
+      <c r="H853" t="n">
+        <v>27152162227.85838</v>
+      </c>
+      <c r="I853" t="n">
+        <v>2.284230264646766</v>
+      </c>
+      <c r="J853" t="n">
+        <v>29.88983149286065</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B854" t="n">
+        <v>1</v>
+      </c>
+      <c r="C854" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D854" t="n">
+        <v>0</v>
+      </c>
+      <c r="E854" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F854" t="n">
+        <v>54.61345545249431</v>
+      </c>
+      <c r="G854" t="n">
+        <v>8934.353649845107</v>
+      </c>
+      <c r="H854" t="n">
+        <v>54281106163.04312</v>
+      </c>
+      <c r="I854" t="n">
+        <v>2.428538268224727</v>
+      </c>
+      <c r="J854" t="n">
+        <v>2.760887557675911</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B855" t="n">
+        <v>0</v>
+      </c>
+      <c r="C855" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D855" t="n">
+        <v>0</v>
+      </c>
+      <c r="E855" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F855" t="n">
+        <v>54.61345545249434</v>
+      </c>
+      <c r="G855" t="n">
+        <v>8934.353649845107</v>
+      </c>
+      <c r="H855" t="n">
+        <v>54613455452.49434</v>
+      </c>
+      <c r="I855" t="n">
+        <v>2.428538268224692</v>
+      </c>
+      <c r="J855" t="n">
+        <v>2.428538268224693</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B856" t="n">
+        <v>300</v>
+      </c>
+      <c r="C856" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D856" t="n">
+        <v>0</v>
+      </c>
+      <c r="E856" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F856" t="n">
+        <v>54.75776345607228</v>
+      </c>
+      <c r="G856" t="n">
+        <v>7421.05405119808</v>
+      </c>
+      <c r="H856" t="n">
+        <v>-28059040228.5694</v>
+      </c>
+      <c r="I856" t="n">
+        <v>2.284230264646752</v>
+      </c>
+      <c r="J856" t="n">
+        <v>85.10103394928844</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B857" t="n">
+        <v>10</v>
+      </c>
+      <c r="C857" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D857" t="n">
+        <v>0</v>
+      </c>
+      <c r="E857" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F857" t="n">
+        <v>54.75776345607226</v>
+      </c>
+      <c r="G857" t="n">
+        <v>7421.05405119808</v>
+      </c>
+      <c r="H857" t="n">
+        <v>51997203333.25087</v>
+      </c>
+      <c r="I857" t="n">
+        <v>2.284230264646773</v>
+      </c>
+      <c r="J857" t="n">
+        <v>5.044790387468162</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B858" t="n">
+        <v>2</v>
+      </c>
+      <c r="C858" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D858" t="n">
+        <v>0</v>
+      </c>
+      <c r="E858" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F858" t="n">
+        <v>54.61345545249431</v>
+      </c>
+      <c r="G858" t="n">
+        <v>8934.353649845107</v>
+      </c>
+      <c r="H858" t="n">
+        <v>53948756873.59191</v>
+      </c>
+      <c r="I858" t="n">
+        <v>2.428538268224727</v>
+      </c>
+      <c r="J858" t="n">
+        <v>3.093236847127121</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B859" t="n">
+        <v>9</v>
+      </c>
+      <c r="C859" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D859" t="n">
+        <v>0</v>
+      </c>
+      <c r="E859" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F859" t="n">
+        <v>54.75776345607226</v>
+      </c>
+      <c r="G859" t="n">
+        <v>7421.05405119808</v>
+      </c>
+      <c r="H859" t="n">
+        <v>52273259345.533</v>
+      </c>
+      <c r="I859" t="n">
+        <v>2.284230264646773</v>
+      </c>
+      <c r="J859" t="n">
+        <v>4.768734375186035</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B860" t="n">
+        <v>50</v>
+      </c>
+      <c r="C860" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D860" t="n">
+        <v>0</v>
+      </c>
+      <c r="E860" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F860" t="n">
+        <v>55.64557619924655</v>
+      </c>
+      <c r="G860" t="n">
+        <v>10607.69037362167</v>
+      </c>
+      <c r="H860" t="n">
+        <v>35915786577.29337</v>
+      </c>
+      <c r="I860" t="n">
+        <v>1.396417521472486</v>
+      </c>
+      <c r="J860" t="n">
+        <v>21.12620714342566</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B861" t="n">
+        <v>900</v>
+      </c>
+      <c r="C861" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D861" t="n">
+        <v>0</v>
+      </c>
+      <c r="E861" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F861" t="n">
+        <v>55.64557619924658</v>
+      </c>
+      <c r="G861" t="n">
+        <v>10607.69037362167</v>
+      </c>
+      <c r="H861" t="n">
+        <v>-299490636995.9107</v>
+      </c>
+      <c r="I861" t="n">
+        <v>1.396417521472458</v>
+      </c>
+      <c r="J861" t="n">
+        <v>356.5326307166297</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B862" t="n">
+        <v>5</v>
+      </c>
+      <c r="C862" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D862" t="n">
+        <v>0</v>
+      </c>
+      <c r="E862" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F862" t="n">
+        <v>55.45776372700355</v>
+      </c>
+      <c r="G862" t="n">
+        <v>12562.16178663779</v>
+      </c>
+      <c r="H862" t="n">
+        <v>53121262561.17359</v>
+      </c>
+      <c r="I862" t="n">
+        <v>1.584229993715482</v>
+      </c>
+      <c r="J862" t="n">
+        <v>3.920731159545441</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B863" t="n">
+        <v>150</v>
+      </c>
+      <c r="C863" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D863" t="n">
+        <v>0</v>
+      </c>
+      <c r="E863" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F863" t="n">
+        <v>55.64557619924654</v>
+      </c>
+      <c r="G863" t="n">
+        <v>10607.69037362167</v>
+      </c>
+      <c r="H863" t="n">
+        <v>-3543792666.612998</v>
+      </c>
+      <c r="I863" t="n">
+        <v>1.396417521472493</v>
+      </c>
+      <c r="J863" t="n">
+        <v>60.58578638733203</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B864" t="n">
+        <v>175</v>
+      </c>
+      <c r="C864" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D864" t="n">
+        <v>0</v>
+      </c>
+      <c r="E864" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F864" t="n">
+        <v>55.64557619924655</v>
+      </c>
+      <c r="G864" t="n">
+        <v>10607.69037362167</v>
+      </c>
+      <c r="H864" t="n">
+        <v>-13408687477.58958</v>
+      </c>
+      <c r="I864" t="n">
+        <v>1.396417521472486</v>
+      </c>
+      <c r="J864" t="n">
+        <v>70.45068119830862</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B865" t="n">
+        <v>3</v>
+      </c>
+      <c r="C865" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D865" t="n">
+        <v>0</v>
+      </c>
+      <c r="E865" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F865" t="n">
+        <v>55.45776372700355</v>
+      </c>
+      <c r="G865" t="n">
+        <v>12562.16178663779</v>
+      </c>
+      <c r="H865" t="n">
+        <v>54055863027.50557</v>
+      </c>
+      <c r="I865" t="n">
+        <v>1.584229993715482</v>
+      </c>
+      <c r="J865" t="n">
+        <v>2.986130693213463</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B866" t="n">
+        <v>200</v>
+      </c>
+      <c r="C866" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D866" t="n">
+        <v>0</v>
+      </c>
+      <c r="E866" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F866" t="n">
+        <v>55.64557619924656</v>
+      </c>
+      <c r="G866" t="n">
+        <v>10607.69037362167</v>
+      </c>
+      <c r="H866" t="n">
+        <v>-23273582288.56617</v>
+      </c>
+      <c r="I866" t="n">
+        <v>1.396417521472472</v>
+      </c>
+      <c r="J866" t="n">
+        <v>80.31557600928521</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B867" t="n">
+        <v>125</v>
+      </c>
+      <c r="C867" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D867" t="n">
+        <v>0</v>
+      </c>
+      <c r="E867" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F867" t="n">
+        <v>55.64557619924655</v>
+      </c>
+      <c r="G867" t="n">
+        <v>10607.69037362167</v>
+      </c>
+      <c r="H867" t="n">
+        <v>6321102144.363596</v>
+      </c>
+      <c r="I867" t="n">
+        <v>1.396417521472486</v>
+      </c>
+      <c r="J867" t="n">
+        <v>50.72089157635544</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B868" t="n">
+        <v>7</v>
+      </c>
+      <c r="C868" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D868" t="n">
+        <v>0</v>
+      </c>
+      <c r="E868" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F868" t="n">
+        <v>55.64557619924653</v>
+      </c>
+      <c r="G868" t="n">
+        <v>10607.69037362167</v>
+      </c>
+      <c r="H868" t="n">
+        <v>52883405652.17309</v>
+      </c>
+      <c r="I868" t="n">
+        <v>1.396417521472507</v>
+      </c>
+      <c r="J868" t="n">
+        <v>4.158588068545944</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B869" t="n">
+        <v>8</v>
+      </c>
+      <c r="C869" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D869" t="n">
+        <v>0</v>
+      </c>
+      <c r="E869" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F869" t="n">
+        <v>55.64557619924657</v>
+      </c>
+      <c r="G869" t="n">
+        <v>10607.69037362167</v>
+      </c>
+      <c r="H869" t="n">
+        <v>52488809859.73405</v>
+      </c>
+      <c r="I869" t="n">
+        <v>1.396417521472465</v>
+      </c>
+      <c r="J869" t="n">
+        <v>4.553183860984985</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B870" t="n">
+        <v>500</v>
+      </c>
+      <c r="C870" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D870" t="n">
+        <v>0</v>
+      </c>
+      <c r="E870" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F870" t="n">
+        <v>55.64557619924655</v>
+      </c>
+      <c r="G870" t="n">
+        <v>10607.69037362167</v>
+      </c>
+      <c r="H870" t="n">
+        <v>-141652320020.2853</v>
+      </c>
+      <c r="I870" t="n">
+        <v>1.396417521472486</v>
+      </c>
+      <c r="J870" t="n">
+        <v>198.6943137410043</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B871" t="n">
+        <v>250</v>
+      </c>
+      <c r="C871" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D871" t="n">
+        <v>0</v>
+      </c>
+      <c r="E871" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F871" t="n">
+        <v>55.64557619924657</v>
+      </c>
+      <c r="G871" t="n">
+        <v>10607.69037362167</v>
+      </c>
+      <c r="H871" t="n">
+        <v>-43003371910.51935</v>
+      </c>
+      <c r="I871" t="n">
+        <v>1.396417521472465</v>
+      </c>
+      <c r="J871" t="n">
+        <v>100.0453656312384</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B872" t="n">
+        <v>4</v>
+      </c>
+      <c r="C872" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D872" t="n">
+        <v>0</v>
+      </c>
+      <c r="E872" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F872" t="n">
+        <v>55.45776372700355</v>
+      </c>
+      <c r="G872" t="n">
+        <v>12562.16178663779</v>
+      </c>
+      <c r="H872" t="n">
+        <v>53588562794.33958</v>
+      </c>
+      <c r="I872" t="n">
+        <v>1.584229993715482</v>
+      </c>
+      <c r="J872" t="n">
+        <v>3.453430926379455</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B873" t="n">
+        <v>400</v>
+      </c>
+      <c r="C873" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D873" t="n">
+        <v>0</v>
+      </c>
+      <c r="E873" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F873" t="n">
+        <v>55.6455761992466</v>
+      </c>
+      <c r="G873" t="n">
+        <v>10607.69037362167</v>
+      </c>
+      <c r="H873" t="n">
+        <v>-102192740776.3789</v>
+      </c>
+      <c r="I873" t="n">
+        <v>1.396417521472436</v>
+      </c>
+      <c r="J873" t="n">
+        <v>159.2347344970979</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B874" t="n">
+        <v>6</v>
+      </c>
+      <c r="C874" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D874" t="n">
+        <v>0</v>
+      </c>
+      <c r="E874" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F874" t="n">
+        <v>55.64557619924651</v>
+      </c>
+      <c r="G874" t="n">
+        <v>10607.69037362167</v>
+      </c>
+      <c r="H874" t="n">
+        <v>53278001444.61213</v>
+      </c>
+      <c r="I874" t="n">
+        <v>1.396417521472522</v>
+      </c>
+      <c r="J874" t="n">
+        <v>3.763992276106903</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B875" t="n">
+        <v>600</v>
+      </c>
+      <c r="C875" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D875" t="n">
+        <v>0</v>
+      </c>
+      <c r="E875" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F875" t="n">
+        <v>55.64557619924664</v>
+      </c>
+      <c r="G875" t="n">
+        <v>10607.69037362167</v>
+      </c>
+      <c r="H875" t="n">
+        <v>-181111899264.1915</v>
+      </c>
+      <c r="I875" t="n">
+        <v>1.396417521472394</v>
+      </c>
+      <c r="J875" t="n">
+        <v>238.1538929849105</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B876" t="n">
+        <v>75</v>
+      </c>
+      <c r="C876" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D876" t="n">
+        <v>0</v>
+      </c>
+      <c r="E876" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F876" t="n">
+        <v>55.64557619924655</v>
+      </c>
+      <c r="G876" t="n">
+        <v>10607.69037362167</v>
+      </c>
+      <c r="H876" t="n">
+        <v>26050891766.31678</v>
+      </c>
+      <c r="I876" t="n">
+        <v>1.396417521472486</v>
+      </c>
+      <c r="J876" t="n">
+        <v>30.99110195440225</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B877" t="n">
+        <v>700</v>
+      </c>
+      <c r="C877" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D877" t="n">
+        <v>0</v>
+      </c>
+      <c r="E877" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F877" t="n">
+        <v>55.64557619924661</v>
+      </c>
+      <c r="G877" t="n">
+        <v>10607.69037362167</v>
+      </c>
+      <c r="H877" t="n">
+        <v>-220571478508.0979</v>
+      </c>
+      <c r="I877" t="n">
+        <v>1.396417521472422</v>
+      </c>
+      <c r="J877" t="n">
+        <v>277.6134722288169</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B878" t="n">
+        <v>800</v>
+      </c>
+      <c r="C878" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D878" t="n">
+        <v>0</v>
+      </c>
+      <c r="E878" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F878" t="n">
+        <v>55.64557619924655</v>
+      </c>
+      <c r="G878" t="n">
+        <v>10607.69037362167</v>
+      </c>
+      <c r="H878" t="n">
+        <v>-260031057752.0044</v>
+      </c>
+      <c r="I878" t="n">
+        <v>1.396417521472486</v>
+      </c>
+      <c r="J878" t="n">
+        <v>317.0730514727235</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B879" t="n">
+        <v>100</v>
+      </c>
+      <c r="C879" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D879" t="n">
+        <v>0</v>
+      </c>
+      <c r="E879" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F879" t="n">
+        <v>55.64557619924653</v>
+      </c>
+      <c r="G879" t="n">
+        <v>10607.69037362167</v>
+      </c>
+      <c r="H879" t="n">
+        <v>16185996955.34017</v>
+      </c>
+      <c r="I879" t="n">
+        <v>1.396417521472507</v>
+      </c>
+      <c r="J879" t="n">
+        <v>40.85599676537886</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B880" t="n">
+        <v>1</v>
+      </c>
+      <c r="C880" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D880" t="n">
+        <v>0</v>
+      </c>
+      <c r="E880" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F880" t="n">
+        <v>55.45776372700352</v>
+      </c>
+      <c r="G880" t="n">
+        <v>12562.16178663779</v>
+      </c>
+      <c r="H880" t="n">
+        <v>54990463493.83753</v>
+      </c>
+      <c r="I880" t="n">
+        <v>1.584229993715518</v>
+      </c>
+      <c r="J880" t="n">
+        <v>2.0515302268815</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B881" t="n">
+        <v>0</v>
+      </c>
+      <c r="C881" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D881" t="n">
+        <v>0</v>
+      </c>
+      <c r="E881" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F881" t="n">
+        <v>55.45776372700355</v>
+      </c>
+      <c r="G881" t="n">
+        <v>12562.16178663779</v>
+      </c>
+      <c r="H881" t="n">
+        <v>55457763727.00356</v>
+      </c>
+      <c r="I881" t="n">
+        <v>1.584229993715482</v>
+      </c>
+      <c r="J881" t="n">
+        <v>1.584229993715469</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B882" t="n">
+        <v>300</v>
+      </c>
+      <c r="C882" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D882" t="n">
+        <v>0</v>
+      </c>
+      <c r="E882" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F882" t="n">
+        <v>55.64557619924658</v>
+      </c>
+      <c r="G882" t="n">
+        <v>10607.69037362167</v>
+      </c>
+      <c r="H882" t="n">
+        <v>-62733161532.47251</v>
+      </c>
+      <c r="I882" t="n">
+        <v>1.396417521472458</v>
+      </c>
+      <c r="J882" t="n">
+        <v>119.7751552531915</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B883" t="n">
+        <v>10</v>
+      </c>
+      <c r="C883" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D883" t="n">
+        <v>0</v>
+      </c>
+      <c r="E883" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F883" t="n">
+        <v>55.64557619924655</v>
+      </c>
+      <c r="G883" t="n">
+        <v>10607.69037362167</v>
+      </c>
+      <c r="H883" t="n">
+        <v>51699618274.85591</v>
+      </c>
+      <c r="I883" t="n">
+        <v>1.396417521472486</v>
+      </c>
+      <c r="J883" t="n">
+        <v>5.342375445863121</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B884" t="n">
+        <v>2</v>
+      </c>
+      <c r="C884" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D884" t="n">
+        <v>0</v>
+      </c>
+      <c r="E884" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F884" t="n">
+        <v>55.45776372700353</v>
+      </c>
+      <c r="G884" t="n">
+        <v>12562.16178663779</v>
+      </c>
+      <c r="H884" t="n">
+        <v>54523163260.67155</v>
+      </c>
+      <c r="I884" t="n">
+        <v>1.584229993715503</v>
+      </c>
+      <c r="J884" t="n">
+        <v>2.518830460047485</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=4</t>
+        </is>
+      </c>
+      <c r="B885" t="n">
+        <v>9</v>
+      </c>
+      <c r="C885" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D885" t="n">
+        <v>0</v>
+      </c>
+      <c r="E885" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F885" t="n">
+        <v>55.64557619924654</v>
+      </c>
+      <c r="G885" t="n">
+        <v>10607.69037362167</v>
+      </c>
+      <c r="H885" t="n">
+        <v>52094214067.29497</v>
+      </c>
+      <c r="I885" t="n">
+        <v>1.396417521472493</v>
+      </c>
+      <c r="J885" t="n">
+        <v>4.947779653424065</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B886" t="n">
+        <v>50</v>
+      </c>
+      <c r="C886" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D886" t="n">
+        <v>0</v>
+      </c>
+      <c r="E886" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F886" t="n">
+        <v>48.06853174276731</v>
+      </c>
+      <c r="G886" t="n">
+        <v>3517.340754874969</v>
+      </c>
+      <c r="H886" t="n">
+        <v>41526448529.72647</v>
+      </c>
+      <c r="I886" t="n">
+        <v>8.973461977951722</v>
+      </c>
+      <c r="J886" t="n">
+        <v>15.51554519099256</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B887" t="n">
+        <v>900</v>
+      </c>
+      <c r="C887" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D887" t="n">
+        <v>0</v>
+      </c>
+      <c r="E887" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F887" t="n">
+        <v>47.16608724935976</v>
+      </c>
+      <c r="G887" t="n">
+        <v>2740.491891363496</v>
+      </c>
+      <c r="H887" t="n">
+        <v>-44583188824.06892</v>
+      </c>
+      <c r="I887" t="n">
+        <v>9.875906471359272</v>
+      </c>
+      <c r="J887" t="n">
+        <v>101.6251825447879</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B888" t="n">
+        <v>5</v>
+      </c>
+      <c r="C888" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D888" t="n">
+        <v>0</v>
+      </c>
+      <c r="E888" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F888" t="n">
+        <v>49.90360232236965</v>
+      </c>
+      <c r="G888" t="n">
+        <v>5427.150418466016</v>
+      </c>
+      <c r="H888" t="n">
+        <v>48894178666.2145</v>
+      </c>
+      <c r="I888" t="n">
+        <v>7.138391398349384</v>
+      </c>
+      <c r="J888" t="n">
+        <v>8.147815054504532</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B889" t="n">
+        <v>150</v>
+      </c>
+      <c r="C889" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D889" t="n">
+        <v>0</v>
+      </c>
+      <c r="E889" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F889" t="n">
+        <v>47.72672734081259</v>
+      </c>
+      <c r="G889" t="n">
+        <v>3222.90201816548</v>
+      </c>
+      <c r="H889" t="n">
+        <v>29743403011.69286</v>
+      </c>
+      <c r="I889" t="n">
+        <v>9.315266379906447</v>
+      </c>
+      <c r="J889" t="n">
+        <v>27.29859070902617</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B890" t="n">
+        <v>175</v>
+      </c>
+      <c r="C890" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D890" t="n">
+        <v>0</v>
+      </c>
+      <c r="E890" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F890" t="n">
+        <v>47.72672734081259</v>
+      </c>
+      <c r="G890" t="n">
+        <v>3222.90201816548</v>
+      </c>
+      <c r="H890" t="n">
+        <v>26746182290.1729</v>
+      </c>
+      <c r="I890" t="n">
+        <v>9.315266379906447</v>
+      </c>
+      <c r="J890" t="n">
+        <v>30.29581143054613</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B891" t="n">
+        <v>3</v>
+      </c>
+      <c r="C891" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D891" t="n">
+        <v>0</v>
+      </c>
+      <c r="E891" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F891" t="n">
+        <v>49.90360232236964</v>
+      </c>
+      <c r="G891" t="n">
+        <v>5427.150418466016</v>
+      </c>
+      <c r="H891" t="n">
+        <v>49297948128.67655</v>
+      </c>
+      <c r="I891" t="n">
+        <v>7.138391398349391</v>
+      </c>
+      <c r="J891" t="n">
+        <v>7.744045592042481</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B892" t="n">
+        <v>200</v>
+      </c>
+      <c r="C892" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D892" t="n">
+        <v>0</v>
+      </c>
+      <c r="E892" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F892" t="n">
+        <v>47.72672734081259</v>
+      </c>
+      <c r="G892" t="n">
+        <v>3222.90201816548</v>
+      </c>
+      <c r="H892" t="n">
+        <v>23748961568.65294</v>
+      </c>
+      <c r="I892" t="n">
+        <v>9.315266379906447</v>
+      </c>
+      <c r="J892" t="n">
+        <v>33.2930321520661</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B893" t="n">
+        <v>125</v>
+      </c>
+      <c r="C893" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D893" t="n">
+        <v>0</v>
+      </c>
+      <c r="E893" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F893" t="n">
+        <v>48.06853174276728</v>
+      </c>
+      <c r="G893" t="n">
+        <v>3517.340754874969</v>
+      </c>
+      <c r="H893" t="n">
+        <v>31713323710.16521</v>
+      </c>
+      <c r="I893" t="n">
+        <v>8.973461977951757</v>
+      </c>
+      <c r="J893" t="n">
+        <v>25.32867001055382</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B894" t="n">
+        <v>7</v>
+      </c>
+      <c r="C894" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D894" t="n">
+        <v>0</v>
+      </c>
+      <c r="E894" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F894" t="n">
+        <v>48.86182079569497</v>
+      </c>
+      <c r="G894" t="n">
+        <v>4299.388354937068</v>
+      </c>
+      <c r="H894" t="n">
+        <v>47742289260.91629</v>
+      </c>
+      <c r="I894" t="n">
+        <v>8.180172925024067</v>
+      </c>
+      <c r="J894" t="n">
+        <v>9.299704459802742</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B895" t="n">
+        <v>8</v>
+      </c>
+      <c r="C895" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D895" t="n">
+        <v>0</v>
+      </c>
+      <c r="E895" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F895" t="n">
+        <v>48.86182079569502</v>
+      </c>
+      <c r="G895" t="n">
+        <v>4299.388354937068</v>
+      </c>
+      <c r="H895" t="n">
+        <v>47582356184.51939</v>
+      </c>
+      <c r="I895" t="n">
+        <v>8.180172925024017</v>
+      </c>
+      <c r="J895" t="n">
+        <v>9.459637536199645</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B896" t="n">
+        <v>500</v>
+      </c>
+      <c r="C896" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D896" t="n">
+        <v>0</v>
+      </c>
+      <c r="E896" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F896" t="n">
+        <v>47.16608724935976</v>
+      </c>
+      <c r="G896" t="n">
+        <v>2740.491891363496</v>
+      </c>
+      <c r="H896" t="n">
+        <v>-3805732791.43395</v>
+      </c>
+      <c r="I896" t="n">
+        <v>9.875906471359272</v>
+      </c>
+      <c r="J896" t="n">
+        <v>60.84772651215298</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B897" t="n">
+        <v>250</v>
+      </c>
+      <c r="C897" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D897" t="n">
+        <v>0</v>
+      </c>
+      <c r="E897" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F897" t="n">
+        <v>47.72672734081259</v>
+      </c>
+      <c r="G897" t="n">
+        <v>3222.90201816548</v>
+      </c>
+      <c r="H897" t="n">
+        <v>17754520125.61303</v>
+      </c>
+      <c r="I897" t="n">
+        <v>9.315266379906447</v>
+      </c>
+      <c r="J897" t="n">
+        <v>39.287473595106</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B898" t="n">
+        <v>4</v>
+      </c>
+      <c r="C898" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D898" t="n">
+        <v>0</v>
+      </c>
+      <c r="E898" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F898" t="n">
+        <v>49.90360232236965</v>
+      </c>
+      <c r="G898" t="n">
+        <v>5427.150418466016</v>
+      </c>
+      <c r="H898" t="n">
+        <v>49096063397.44553</v>
+      </c>
+      <c r="I898" t="n">
+        <v>7.138391398349384</v>
+      </c>
+      <c r="J898" t="n">
+        <v>7.945930323273498</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B899" t="n">
+        <v>400</v>
+      </c>
+      <c r="C899" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D899" t="n">
+        <v>0</v>
+      </c>
+      <c r="E899" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F899" t="n">
+        <v>47.7267273408126</v>
+      </c>
+      <c r="G899" t="n">
+        <v>3222.90201816548</v>
+      </c>
+      <c r="H899" t="n">
+        <v>-228804203.5066998</v>
+      </c>
+      <c r="I899" t="n">
+        <v>9.315266379906433</v>
+      </c>
+      <c r="J899" t="n">
+        <v>57.27079792422573</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B900" t="n">
+        <v>6</v>
+      </c>
+      <c r="C900" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D900" t="n">
+        <v>0</v>
+      </c>
+      <c r="E900" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F900" t="n">
+        <v>48.86182079569499</v>
+      </c>
+      <c r="G900" t="n">
+        <v>4299.388354937068</v>
+      </c>
+      <c r="H900" t="n">
+        <v>47902222337.31326</v>
+      </c>
+      <c r="I900" t="n">
+        <v>8.180172925024046</v>
+      </c>
+      <c r="J900" t="n">
+        <v>9.139771383405769</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B901" t="n">
+        <v>600</v>
+      </c>
+      <c r="C901" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D901" t="n">
+        <v>0</v>
+      </c>
+      <c r="E901" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F901" t="n">
+        <v>47.16608724935977</v>
+      </c>
+      <c r="G901" t="n">
+        <v>2740.491891363496</v>
+      </c>
+      <c r="H901" t="n">
+        <v>-14000096799.59269</v>
+      </c>
+      <c r="I901" t="n">
+        <v>9.875906471359265</v>
+      </c>
+      <c r="J901" t="n">
+        <v>71.04209052031172</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B902" t="n">
+        <v>75</v>
+      </c>
+      <c r="C902" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D902" t="n">
+        <v>0</v>
+      </c>
+      <c r="E902" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F902" t="n">
+        <v>48.06853174276731</v>
+      </c>
+      <c r="G902" t="n">
+        <v>3517.340754874969</v>
+      </c>
+      <c r="H902" t="n">
+        <v>38255406923.20605</v>
+      </c>
+      <c r="I902" t="n">
+        <v>8.973461977951722</v>
+      </c>
+      <c r="J902" t="n">
+        <v>18.78658679751299</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B903" t="n">
+        <v>700</v>
+      </c>
+      <c r="C903" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D903" t="n">
+        <v>0</v>
+      </c>
+      <c r="E903" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F903" t="n">
+        <v>47.16608724935977</v>
+      </c>
+      <c r="G903" t="n">
+        <v>2740.491891363496</v>
+      </c>
+      <c r="H903" t="n">
+        <v>-24194460807.75143</v>
+      </c>
+      <c r="I903" t="n">
+        <v>9.875906471359265</v>
+      </c>
+      <c r="J903" t="n">
+        <v>81.23645452847046</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B904" t="n">
+        <v>800</v>
+      </c>
+      <c r="C904" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D904" t="n">
+        <v>0</v>
+      </c>
+      <c r="E904" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F904" t="n">
+        <v>47.16608724935976</v>
+      </c>
+      <c r="G904" t="n">
+        <v>2740.491891363496</v>
+      </c>
+      <c r="H904" t="n">
+        <v>-34388824815.91018</v>
+      </c>
+      <c r="I904" t="n">
+        <v>9.875906471359272</v>
+      </c>
+      <c r="J904" t="n">
+        <v>91.43081853662922</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B905" t="n">
+        <v>100</v>
+      </c>
+      <c r="C905" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D905" t="n">
+        <v>0</v>
+      </c>
+      <c r="E905" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F905" t="n">
+        <v>48.06853174276731</v>
+      </c>
+      <c r="G905" t="n">
+        <v>3517.340754874969</v>
+      </c>
+      <c r="H905" t="n">
+        <v>34984365316.68564</v>
+      </c>
+      <c r="I905" t="n">
+        <v>8.973461977951722</v>
+      </c>
+      <c r="J905" t="n">
+        <v>22.05762840403339</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B906" t="n">
+        <v>1</v>
+      </c>
+      <c r="C906" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D906" t="n">
+        <v>0</v>
+      </c>
+      <c r="E906" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F906" t="n">
+        <v>49.90360232236964</v>
+      </c>
+      <c r="G906" t="n">
+        <v>5427.150418466016</v>
+      </c>
+      <c r="H906" t="n">
+        <v>49701717591.13861</v>
+      </c>
+      <c r="I906" t="n">
+        <v>7.138391398349391</v>
+      </c>
+      <c r="J906" t="n">
+        <v>7.340276129580421</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B907" t="n">
+        <v>0</v>
+      </c>
+      <c r="C907" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D907" t="n">
+        <v>0</v>
+      </c>
+      <c r="E907" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F907" t="n">
+        <v>49.90360232236964</v>
+      </c>
+      <c r="G907" t="n">
+        <v>5427.150418466016</v>
+      </c>
+      <c r="H907" t="n">
+        <v>49903602322.36964</v>
+      </c>
+      <c r="I907" t="n">
+        <v>7.138391398349391</v>
+      </c>
+      <c r="J907" t="n">
+        <v>7.138391398349396</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B908" t="n">
+        <v>300</v>
+      </c>
+      <c r="C908" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D908" t="n">
+        <v>0</v>
+      </c>
+      <c r="E908" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F908" t="n">
+        <v>47.72672734081259</v>
+      </c>
+      <c r="G908" t="n">
+        <v>3222.90201816548</v>
+      </c>
+      <c r="H908" t="n">
+        <v>11760078682.57312</v>
+      </c>
+      <c r="I908" t="n">
+        <v>9.315266379906447</v>
+      </c>
+      <c r="J908" t="n">
+        <v>45.28191503814591</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B909" t="n">
+        <v>10</v>
+      </c>
+      <c r="C909" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D909" t="n">
+        <v>0</v>
+      </c>
+      <c r="E909" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F909" t="n">
+        <v>48.86182079569502</v>
+      </c>
+      <c r="G909" t="n">
+        <v>4299.388354937068</v>
+      </c>
+      <c r="H909" t="n">
+        <v>47262490031.72547</v>
+      </c>
+      <c r="I909" t="n">
+        <v>8.180172925024017</v>
+      </c>
+      <c r="J909" t="n">
+        <v>9.779503688993561</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B910" t="n">
+        <v>2</v>
+      </c>
+      <c r="C910" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D910" t="n">
+        <v>0</v>
+      </c>
+      <c r="E910" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F910" t="n">
+        <v>49.90360232236962</v>
+      </c>
+      <c r="G910" t="n">
+        <v>5427.150418466016</v>
+      </c>
+      <c r="H910" t="n">
+        <v>49499832859.90756</v>
+      </c>
+      <c r="I910" t="n">
+        <v>7.138391398349412</v>
+      </c>
+      <c r="J910" t="n">
+        <v>7.54216086081147</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B911" t="n">
+        <v>9</v>
+      </c>
+      <c r="C911" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D911" t="n">
+        <v>0</v>
+      </c>
+      <c r="E911" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F911" t="n">
+        <v>48.86182079569501</v>
+      </c>
+      <c r="G911" t="n">
+        <v>4299.388354937068</v>
+      </c>
+      <c r="H911" t="n">
+        <v>47422423108.12241</v>
+      </c>
+      <c r="I911" t="n">
+        <v>8.180172925024024</v>
+      </c>
+      <c r="J911" t="n">
+        <v>9.619570612596618</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B912" t="n">
+        <v>50</v>
+      </c>
+      <c r="C912" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D912" t="n">
+        <v>0</v>
+      </c>
+      <c r="E912" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F912" t="n">
+        <v>55.59248521686824</v>
+      </c>
+      <c r="G912" t="n">
+        <v>10256.99532531437</v>
+      </c>
+      <c r="H912" t="n">
+        <v>36514971376.05679</v>
+      </c>
+      <c r="I912" t="n">
+        <v>1.449508503850794</v>
+      </c>
+      <c r="J912" t="n">
+        <v>20.52702234466224</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B913" t="n">
+        <v>900</v>
+      </c>
+      <c r="C913" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D913" t="n">
+        <v>0</v>
+      </c>
+      <c r="E913" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F913" t="n">
+        <v>55.29952605212103</v>
+      </c>
+      <c r="G913" t="n">
+        <v>9173.933576488876</v>
+      </c>
+      <c r="H913" t="n">
+        <v>-251835761244.7143</v>
+      </c>
+      <c r="I913" t="n">
+        <v>1.742467668598003</v>
+      </c>
+      <c r="J913" t="n">
+        <v>308.8777549654333</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B914" t="n">
+        <v>5</v>
+      </c>
+      <c r="C914" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D914" t="n">
+        <v>0</v>
+      </c>
+      <c r="E914" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F914" t="n">
+        <v>55.55063778003397</v>
+      </c>
+      <c r="G914" t="n">
+        <v>10701.96236108375</v>
+      </c>
+      <c r="H914" t="n">
+        <v>53560124685.38984</v>
+      </c>
+      <c r="I914" t="n">
+        <v>1.491355940685061</v>
+      </c>
+      <c r="J914" t="n">
+        <v>3.481869035329193</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B915" t="n">
+        <v>150</v>
+      </c>
+      <c r="C915" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D915" t="n">
+        <v>0</v>
+      </c>
+      <c r="E915" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F915" t="n">
+        <v>55.29952605212103</v>
+      </c>
+      <c r="G915" t="n">
+        <v>9173.933576488876</v>
+      </c>
+      <c r="H915" t="n">
+        <v>4110311502.648481</v>
+      </c>
+      <c r="I915" t="n">
+        <v>1.742467668598003</v>
+      </c>
+      <c r="J915" t="n">
+        <v>52.93168221807055</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B916" t="n">
+        <v>175</v>
+      </c>
+      <c r="C916" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D916" t="n">
+        <v>0</v>
+      </c>
+      <c r="E916" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F916" t="n">
+        <v>55.29952605212103</v>
+      </c>
+      <c r="G916" t="n">
+        <v>9173.933576488876</v>
+      </c>
+      <c r="H916" t="n">
+        <v>-4421224255.596947</v>
+      </c>
+      <c r="I916" t="n">
+        <v>1.742467668598003</v>
+      </c>
+      <c r="J916" t="n">
+        <v>61.46321797631598</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B917" t="n">
+        <v>3</v>
+      </c>
+      <c r="C917" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D917" t="n">
+        <v>0</v>
+      </c>
+      <c r="E917" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F917" t="n">
+        <v>55.55063778003399</v>
+      </c>
+      <c r="G917" t="n">
+        <v>10701.96236108375</v>
+      </c>
+      <c r="H917" t="n">
+        <v>54356329923.24751</v>
+      </c>
+      <c r="I917" t="n">
+        <v>1.491355940685047</v>
+      </c>
+      <c r="J917" t="n">
+        <v>2.685663797471519</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B918" t="n">
+        <v>200</v>
+      </c>
+      <c r="C918" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D918" t="n">
+        <v>0</v>
+      </c>
+      <c r="E918" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F918" t="n">
+        <v>55.29952605212103</v>
+      </c>
+      <c r="G918" t="n">
+        <v>9173.933576488876</v>
+      </c>
+      <c r="H918" t="n">
+        <v>-12952760013.84237</v>
+      </c>
+      <c r="I918" t="n">
+        <v>1.742467668598003</v>
+      </c>
+      <c r="J918" t="n">
+        <v>69.9947537345614</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B919" t="n">
+        <v>125</v>
+      </c>
+      <c r="C919" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D919" t="n">
+        <v>0</v>
+      </c>
+      <c r="E919" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F919" t="n">
+        <v>54.99543208055869</v>
+      </c>
+      <c r="G919" t="n">
+        <v>8117.506313696399</v>
+      </c>
+      <c r="H919" t="n">
+        <v>17250011969.51097</v>
+      </c>
+      <c r="I919" t="n">
+        <v>2.046561640160341</v>
+      </c>
+      <c r="J919" t="n">
+        <v>39.79198175120806</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B920" t="n">
+        <v>7</v>
+      </c>
+      <c r="C920" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D920" t="n">
+        <v>0</v>
+      </c>
+      <c r="E920" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F920" t="n">
+        <v>55.59248521686824</v>
+      </c>
+      <c r="G920" t="n">
+        <v>10256.99532531437</v>
+      </c>
+      <c r="H920" t="n">
+        <v>52921633279.15464</v>
+      </c>
+      <c r="I920" t="n">
+        <v>1.449508503850794</v>
+      </c>
+      <c r="J920" t="n">
+        <v>4.120360441564392</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B921" t="n">
+        <v>8</v>
+      </c>
+      <c r="C921" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D921" t="n">
+        <v>0</v>
+      </c>
+      <c r="E921" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F921" t="n">
+        <v>55.59248521686825</v>
+      </c>
+      <c r="G921" t="n">
+        <v>10256.99532531437</v>
+      </c>
+      <c r="H921" t="n">
+        <v>52540083002.33842</v>
+      </c>
+      <c r="I921" t="n">
+        <v>1.449508503850787</v>
+      </c>
+      <c r="J921" t="n">
+        <v>4.501910718380615</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B922" t="n">
+        <v>500</v>
+      </c>
+      <c r="C922" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D922" t="n">
+        <v>0</v>
+      </c>
+      <c r="E922" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F922" t="n">
+        <v>55.29952605212103</v>
+      </c>
+      <c r="G922" t="n">
+        <v>9173.933576488876</v>
+      </c>
+      <c r="H922" t="n">
+        <v>-115331189112.7875</v>
+      </c>
+      <c r="I922" t="n">
+        <v>1.742467668598003</v>
+      </c>
+      <c r="J922" t="n">
+        <v>172.3731828335065</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B923" t="n">
+        <v>250</v>
+      </c>
+      <c r="C923" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D923" t="n">
+        <v>0</v>
+      </c>
+      <c r="E923" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F923" t="n">
+        <v>55.29952605212102</v>
+      </c>
+      <c r="G923" t="n">
+        <v>9173.933576488876</v>
+      </c>
+      <c r="H923" t="n">
+        <v>-30015831530.33323</v>
+      </c>
+      <c r="I923" t="n">
+        <v>1.742467668598017</v>
+      </c>
+      <c r="J923" t="n">
+        <v>87.05782525105226</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B924" t="n">
+        <v>4</v>
+      </c>
+      <c r="C924" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D924" t="n">
+        <v>0</v>
+      </c>
+      <c r="E924" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F924" t="n">
+        <v>55.55063778003396</v>
+      </c>
+      <c r="G924" t="n">
+        <v>10701.96236108375</v>
+      </c>
+      <c r="H924" t="n">
+        <v>53958227304.31866</v>
+      </c>
+      <c r="I924" t="n">
+        <v>1.491355940685075</v>
+      </c>
+      <c r="J924" t="n">
+        <v>3.083766416400375</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B925" t="n">
+        <v>400</v>
+      </c>
+      <c r="C925" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D925" t="n">
+        <v>0</v>
+      </c>
+      <c r="E925" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F925" t="n">
+        <v>55.29952605212103</v>
+      </c>
+      <c r="G925" t="n">
+        <v>9173.933576488876</v>
+      </c>
+      <c r="H925" t="n">
+        <v>-81205046079.80577</v>
+      </c>
+      <c r="I925" t="n">
+        <v>1.742467668598003</v>
+      </c>
+      <c r="J925" t="n">
+        <v>138.2470398005248</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B926" t="n">
+        <v>6</v>
+      </c>
+      <c r="C926" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D926" t="n">
+        <v>0</v>
+      </c>
+      <c r="E926" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F926" t="n">
+        <v>55.59248521686824</v>
+      </c>
+      <c r="G926" t="n">
+        <v>10256.99532531437</v>
+      </c>
+      <c r="H926" t="n">
+        <v>53303183555.97086</v>
+      </c>
+      <c r="I926" t="n">
+        <v>1.449508503850794</v>
+      </c>
+      <c r="J926" t="n">
+        <v>3.738810164748169</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B927" t="n">
+        <v>600</v>
+      </c>
+      <c r="C927" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D927" t="n">
+        <v>0</v>
+      </c>
+      <c r="E927" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F927" t="n">
+        <v>55.29952605212103</v>
+      </c>
+      <c r="G927" t="n">
+        <v>9173.933576488876</v>
+      </c>
+      <c r="H927" t="n">
+        <v>-149457332145.7692</v>
+      </c>
+      <c r="I927" t="n">
+        <v>1.742467668598003</v>
+      </c>
+      <c r="J927" t="n">
+        <v>206.4993258664882</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B928" t="n">
+        <v>75</v>
+      </c>
+      <c r="C928" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D928" t="n">
+        <v>0</v>
+      </c>
+      <c r="E928" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F928" t="n">
+        <v>55.59248521686825</v>
+      </c>
+      <c r="G928" t="n">
+        <v>10256.99532531437</v>
+      </c>
+      <c r="H928" t="n">
+        <v>26976214455.65106</v>
+      </c>
+      <c r="I928" t="n">
+        <v>1.449508503850787</v>
+      </c>
+      <c r="J928" t="n">
+        <v>30.06577926506797</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B929" t="n">
+        <v>700</v>
+      </c>
+      <c r="C929" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D929" t="n">
+        <v>0</v>
+      </c>
+      <c r="E929" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F929" t="n">
+        <v>55.29952605212103</v>
+      </c>
+      <c r="G929" t="n">
+        <v>9173.933576488876</v>
+      </c>
+      <c r="H929" t="n">
+        <v>-183583475178.7509</v>
+      </c>
+      <c r="I929" t="n">
+        <v>1.742467668598003</v>
+      </c>
+      <c r="J929" t="n">
+        <v>240.6254688994699</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B930" t="n">
+        <v>800</v>
+      </c>
+      <c r="C930" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D930" t="n">
+        <v>0</v>
+      </c>
+      <c r="E930" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F930" t="n">
+        <v>55.29952605212103</v>
+      </c>
+      <c r="G930" t="n">
+        <v>9173.933576488876</v>
+      </c>
+      <c r="H930" t="n">
+        <v>-217709618211.7326</v>
+      </c>
+      <c r="I930" t="n">
+        <v>1.742467668598003</v>
+      </c>
+      <c r="J930" t="n">
+        <v>274.7516119324516</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B931" t="n">
+        <v>100</v>
+      </c>
+      <c r="C931" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D931" t="n">
+        <v>0</v>
+      </c>
+      <c r="E931" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F931" t="n">
+        <v>54.9954320805587</v>
+      </c>
+      <c r="G931" t="n">
+        <v>8117.506313696399</v>
+      </c>
+      <c r="H931" t="n">
+        <v>24799095991.72052</v>
+      </c>
+      <c r="I931" t="n">
+        <v>2.046561640160334</v>
+      </c>
+      <c r="J931" t="n">
+        <v>32.24289772899851</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B932" t="n">
+        <v>1</v>
+      </c>
+      <c r="C932" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D932" t="n">
+        <v>0</v>
+      </c>
+      <c r="E932" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F932" t="n">
+        <v>55.55063778003398</v>
+      </c>
+      <c r="G932" t="n">
+        <v>10701.96236108375</v>
+      </c>
+      <c r="H932" t="n">
+        <v>55152535161.10516</v>
+      </c>
+      <c r="I932" t="n">
+        <v>1.491355940685054</v>
+      </c>
+      <c r="J932" t="n">
+        <v>1.889458559613869</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B933" t="n">
+        <v>0</v>
+      </c>
+      <c r="C933" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D933" t="n">
+        <v>0</v>
+      </c>
+      <c r="E933" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F933" t="n">
+        <v>55.55063778003397</v>
+      </c>
+      <c r="G933" t="n">
+        <v>10701.96236108375</v>
+      </c>
+      <c r="H933" t="n">
+        <v>55550637780.03397</v>
+      </c>
+      <c r="I933" t="n">
+        <v>1.491355940685061</v>
+      </c>
+      <c r="J933" t="n">
+        <v>1.491355940685059</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B934" t="n">
+        <v>300</v>
+      </c>
+      <c r="C934" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D934" t="n">
+        <v>0</v>
+      </c>
+      <c r="E934" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F934" t="n">
+        <v>55.29952605212102</v>
+      </c>
+      <c r="G934" t="n">
+        <v>9173.933576488876</v>
+      </c>
+      <c r="H934" t="n">
+        <v>-47078903046.82407</v>
+      </c>
+      <c r="I934" t="n">
+        <v>1.742467668598017</v>
+      </c>
+      <c r="J934" t="n">
+        <v>104.1208967675431</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B935" t="n">
+        <v>10</v>
+      </c>
+      <c r="C935" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D935" t="n">
+        <v>0</v>
+      </c>
+      <c r="E935" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F935" t="n">
+        <v>55.59248521686824</v>
+      </c>
+      <c r="G935" t="n">
+        <v>10256.99532531437</v>
+      </c>
+      <c r="H935" t="n">
+        <v>51776982448.70595</v>
+      </c>
+      <c r="I935" t="n">
+        <v>1.449508503850794</v>
+      </c>
+      <c r="J935" t="n">
+        <v>5.265011272013084</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B936" t="n">
+        <v>2</v>
+      </c>
+      <c r="C936" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D936" t="n">
+        <v>0</v>
+      </c>
+      <c r="E936" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F936" t="n">
+        <v>55.55063778003397</v>
+      </c>
+      <c r="G936" t="n">
+        <v>10701.96236108375</v>
+      </c>
+      <c r="H936" t="n">
+        <v>54754432542.17632</v>
+      </c>
+      <c r="I936" t="n">
+        <v>1.491355940685061</v>
+      </c>
+      <c r="J936" t="n">
+        <v>2.287561178542709</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B937" t="n">
+        <v>9</v>
+      </c>
+      <c r="C937" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D937" t="n">
+        <v>0</v>
+      </c>
+      <c r="E937" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F937" t="n">
+        <v>55.59248521686823</v>
+      </c>
+      <c r="G937" t="n">
+        <v>10256.99532531437</v>
+      </c>
+      <c r="H937" t="n">
+        <v>52158532725.52217</v>
+      </c>
+      <c r="I937" t="n">
+        <v>1.449508503850801</v>
+      </c>
+      <c r="J937" t="n">
+        <v>4.883460995196861</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B938" t="n">
+        <v>50</v>
+      </c>
+      <c r="C938" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D938" t="n">
+        <v>0</v>
+      </c>
+      <c r="E938" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F938" t="n">
+        <v>55.68116024772106</v>
+      </c>
+      <c r="G938" t="n">
+        <v>10664.45254955184</v>
+      </c>
+      <c r="H938" t="n">
+        <v>35845795731.50329</v>
+      </c>
+      <c r="I938" t="n">
+        <v>1.360833472997975</v>
+      </c>
+      <c r="J938" t="n">
+        <v>21.19619798921574</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B939" t="n">
+        <v>900</v>
+      </c>
+      <c r="C939" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D939" t="n">
+        <v>0</v>
+      </c>
+      <c r="E939" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F939" t="n">
+        <v>55.68116024772107</v>
+      </c>
+      <c r="G939" t="n">
+        <v>10664.45254955184</v>
+      </c>
+      <c r="H939" t="n">
+        <v>-301355401044.1989</v>
+      </c>
+      <c r="I939" t="n">
+        <v>1.360833472997967</v>
+      </c>
+      <c r="J939" t="n">
+        <v>358.397394764918</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B940" t="n">
+        <v>5</v>
+      </c>
+      <c r="C940" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D940" t="n">
+        <v>0</v>
+      </c>
+      <c r="E940" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F940" t="n">
+        <v>55.70312561536401</v>
+      </c>
+      <c r="G940" t="n">
+        <v>10428.69763523227</v>
+      </c>
+      <c r="H940" t="n">
+        <v>53763438434.39433</v>
+      </c>
+      <c r="I940" t="n">
+        <v>1.338868105355026</v>
+      </c>
+      <c r="J940" t="n">
+        <v>3.278555286324699</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B941" t="n">
+        <v>150</v>
+      </c>
+      <c r="C941" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D941" t="n">
+        <v>0</v>
+      </c>
+      <c r="E941" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F941" t="n">
+        <v>55.68116024772107</v>
+      </c>
+      <c r="G941" t="n">
+        <v>10664.45254955184</v>
+      </c>
+      <c r="H941" t="n">
+        <v>-3824933300.932246</v>
+      </c>
+      <c r="I941" t="n">
+        <v>1.360833472997967</v>
+      </c>
+      <c r="J941" t="n">
+        <v>60.86692702165128</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B942" t="n">
+        <v>175</v>
+      </c>
+      <c r="C942" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D942" t="n">
+        <v>0</v>
+      </c>
+      <c r="E942" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F942" t="n">
+        <v>55.68116024772106</v>
+      </c>
+      <c r="G942" t="n">
+        <v>10664.45254955184</v>
+      </c>
+      <c r="H942" t="n">
+        <v>-13742615559.04115</v>
+      </c>
+      <c r="I942" t="n">
+        <v>1.360833472997975</v>
+      </c>
+      <c r="J942" t="n">
+        <v>70.78460927976018</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B943" t="n">
+        <v>3</v>
+      </c>
+      <c r="C943" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D943" t="n">
+        <v>0</v>
+      </c>
+      <c r="E943" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F943" t="n">
+        <v>55.70312561536399</v>
+      </c>
+      <c r="G943" t="n">
+        <v>10428.69763523227</v>
+      </c>
+      <c r="H943" t="n">
+        <v>54539313306.78219</v>
+      </c>
+      <c r="I943" t="n">
+        <v>1.338868105355047</v>
+      </c>
+      <c r="J943" t="n">
+        <v>2.502680413936844</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B944" t="n">
+        <v>200</v>
+      </c>
+      <c r="C944" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D944" t="n">
+        <v>0</v>
+      </c>
+      <c r="E944" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F944" t="n">
+        <v>55.68116024772107</v>
+      </c>
+      <c r="G944" t="n">
+        <v>10664.45254955184</v>
+      </c>
+      <c r="H944" t="n">
+        <v>-23660297817.15002</v>
+      </c>
+      <c r="I944" t="n">
+        <v>1.360833472997967</v>
+      </c>
+      <c r="J944" t="n">
+        <v>80.70229153786904</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B945" t="n">
+        <v>125</v>
+      </c>
+      <c r="C945" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D945" t="n">
+        <v>0</v>
+      </c>
+      <c r="E945" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F945" t="n">
+        <v>55.68116024772106</v>
+      </c>
+      <c r="G945" t="n">
+        <v>10664.45254955184</v>
+      </c>
+      <c r="H945" t="n">
+        <v>6092748957.176626</v>
+      </c>
+      <c r="I945" t="n">
+        <v>1.360833472997975</v>
+      </c>
+      <c r="J945" t="n">
+        <v>50.9492447635424</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B946" t="n">
+        <v>7</v>
+      </c>
+      <c r="C946" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D946" t="n">
+        <v>0</v>
+      </c>
+      <c r="E946" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F946" t="n">
+        <v>55.68116024772105</v>
+      </c>
+      <c r="G946" t="n">
+        <v>10664.45254955184</v>
+      </c>
+      <c r="H946" t="n">
+        <v>52904209215.45057</v>
+      </c>
+      <c r="I946" t="n">
+        <v>1.360833472997982</v>
+      </c>
+      <c r="J946" t="n">
+        <v>4.137784505268463</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B947" t="n">
+        <v>8</v>
+      </c>
+      <c r="C947" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D947" t="n">
+        <v>0</v>
+      </c>
+      <c r="E947" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F947" t="n">
+        <v>55.68116024772105</v>
+      </c>
+      <c r="G947" t="n">
+        <v>10664.45254955184</v>
+      </c>
+      <c r="H947" t="n">
+        <v>52507501925.12621</v>
+      </c>
+      <c r="I947" t="n">
+        <v>1.360833472997982</v>
+      </c>
+      <c r="J947" t="n">
+        <v>4.534491795592819</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B948" t="n">
+        <v>500</v>
+      </c>
+      <c r="C948" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D948" t="n">
+        <v>0</v>
+      </c>
+      <c r="E948" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F948" t="n">
+        <v>55.68116024772113</v>
+      </c>
+      <c r="G948" t="n">
+        <v>10664.45254955184</v>
+      </c>
+      <c r="H948" t="n">
+        <v>-142672484914.4566</v>
+      </c>
+      <c r="I948" t="n">
+        <v>1.360833472997903</v>
+      </c>
+      <c r="J948" t="n">
+        <v>199.7144786351756</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B949" t="n">
+        <v>250</v>
+      </c>
+      <c r="C949" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D949" t="n">
+        <v>0</v>
+      </c>
+      <c r="E949" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F949" t="n">
+        <v>55.68116024772107</v>
+      </c>
+      <c r="G949" t="n">
+        <v>10664.45254955184</v>
+      </c>
+      <c r="H949" t="n">
+        <v>-43495662333.3678</v>
+      </c>
+      <c r="I949" t="n">
+        <v>1.360833472997967</v>
+      </c>
+      <c r="J949" t="n">
+        <v>100.5376560540868</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B950" t="n">
+        <v>4</v>
+      </c>
+      <c r="C950" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D950" t="n">
+        <v>0</v>
+      </c>
+      <c r="E950" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F950" t="n">
+        <v>55.70312561536397</v>
+      </c>
+      <c r="G950" t="n">
+        <v>10428.69763523227</v>
+      </c>
+      <c r="H950" t="n">
+        <v>54151375870.58824</v>
+      </c>
+      <c r="I950" t="n">
+        <v>1.338868105355061</v>
+      </c>
+      <c r="J950" t="n">
+        <v>2.890617850130791</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B951" t="n">
+        <v>400</v>
+      </c>
+      <c r="C951" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D951" t="n">
+        <v>0</v>
+      </c>
+      <c r="E951" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F951" t="n">
+        <v>55.68116024772108</v>
+      </c>
+      <c r="G951" t="n">
+        <v>10664.45254955184</v>
+      </c>
+      <c r="H951" t="n">
+        <v>-103001755882.0211</v>
+      </c>
+      <c r="I951" t="n">
+        <v>1.360833472997953</v>
+      </c>
+      <c r="J951" t="n">
+        <v>160.0437496027401</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B952" t="n">
+        <v>6</v>
+      </c>
+      <c r="C952" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D952" t="n">
+        <v>0</v>
+      </c>
+      <c r="E952" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F952" t="n">
+        <v>55.68116024772104</v>
+      </c>
+      <c r="G952" t="n">
+        <v>10664.45254955184</v>
+      </c>
+      <c r="H952" t="n">
+        <v>53300916505.7749</v>
+      </c>
+      <c r="I952" t="n">
+        <v>1.360833472997996</v>
+      </c>
+      <c r="J952" t="n">
+        <v>3.74107721494413</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B953" t="n">
+        <v>600</v>
+      </c>
+      <c r="C953" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D953" t="n">
+        <v>0</v>
+      </c>
+      <c r="E953" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F953" t="n">
+        <v>55.68116024772113</v>
+      </c>
+      <c r="G953" t="n">
+        <v>10664.45254955184</v>
+      </c>
+      <c r="H953" t="n">
+        <v>-182343213946.8922</v>
+      </c>
+      <c r="I953" t="n">
+        <v>1.360833472997903</v>
+      </c>
+      <c r="J953" t="n">
+        <v>239.3852076676112</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B954" t="n">
+        <v>75</v>
+      </c>
+      <c r="C954" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D954" t="n">
+        <v>0</v>
+      </c>
+      <c r="E954" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F954" t="n">
+        <v>55.68116024772105</v>
+      </c>
+      <c r="G954" t="n">
+        <v>10664.45254955184</v>
+      </c>
+      <c r="H954" t="n">
+        <v>25928113473.39439</v>
+      </c>
+      <c r="I954" t="n">
+        <v>1.360833472997982</v>
+      </c>
+      <c r="J954" t="n">
+        <v>31.11388024732464</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B955" t="n">
+        <v>700</v>
+      </c>
+      <c r="C955" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D955" t="n">
+        <v>0</v>
+      </c>
+      <c r="E955" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F955" t="n">
+        <v>55.68116024772104</v>
+      </c>
+      <c r="G955" t="n">
+        <v>10664.45254955184</v>
+      </c>
+      <c r="H955" t="n">
+        <v>-222013942979.3278</v>
+      </c>
+      <c r="I955" t="n">
+        <v>1.360833472997996</v>
+      </c>
+      <c r="J955" t="n">
+        <v>279.0559367000468</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B956" t="n">
+        <v>800</v>
+      </c>
+      <c r="C956" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D956" t="n">
+        <v>0</v>
+      </c>
+      <c r="E956" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F956" t="n">
+        <v>55.68116024772113</v>
+      </c>
+      <c r="G956" t="n">
+        <v>10664.45254955184</v>
+      </c>
+      <c r="H956" t="n">
+        <v>-261684672011.7632</v>
+      </c>
+      <c r="I956" t="n">
+        <v>1.360833472997903</v>
+      </c>
+      <c r="J956" t="n">
+        <v>318.7266657324822</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B957" t="n">
+        <v>100</v>
+      </c>
+      <c r="C957" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D957" t="n">
+        <v>0</v>
+      </c>
+      <c r="E957" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F957" t="n">
+        <v>55.68116024772107</v>
+      </c>
+      <c r="G957" t="n">
+        <v>10664.45254955184</v>
+      </c>
+      <c r="H957" t="n">
+        <v>16010431215.28553</v>
+      </c>
+      <c r="I957" t="n">
+        <v>1.360833472997967</v>
+      </c>
+      <c r="J957" t="n">
+        <v>41.0315625054335</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B958" t="n">
+        <v>1</v>
+      </c>
+      <c r="C958" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D958" t="n">
+        <v>0</v>
+      </c>
+      <c r="E958" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F958" t="n">
+        <v>55.70312561536399</v>
+      </c>
+      <c r="G958" t="n">
+        <v>10428.69763523227</v>
+      </c>
+      <c r="H958" t="n">
+        <v>55315188179.17006</v>
+      </c>
+      <c r="I958" t="n">
+        <v>1.338868105355047</v>
+      </c>
+      <c r="J958" t="n">
+        <v>1.726805541548973</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B959" t="n">
+        <v>0</v>
+      </c>
+      <c r="C959" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D959" t="n">
+        <v>0</v>
+      </c>
+      <c r="E959" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F959" t="n">
+        <v>55.70312561536403</v>
+      </c>
+      <c r="G959" t="n">
+        <v>10428.69763523227</v>
+      </c>
+      <c r="H959" t="n">
+        <v>55703125615.36403</v>
+      </c>
+      <c r="I959" t="n">
+        <v>1.338868105355004</v>
+      </c>
+      <c r="J959" t="n">
+        <v>1.338868105355003</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B960" t="n">
+        <v>300</v>
+      </c>
+      <c r="C960" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D960" t="n">
+        <v>0</v>
+      </c>
+      <c r="E960" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F960" t="n">
+        <v>55.68116024772107</v>
+      </c>
+      <c r="G960" t="n">
+        <v>10664.45254955184</v>
+      </c>
+      <c r="H960" t="n">
+        <v>-63331026849.58557</v>
+      </c>
+      <c r="I960" t="n">
+        <v>1.360833472997967</v>
+      </c>
+      <c r="J960" t="n">
+        <v>120.3730205703046</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B961" t="n">
+        <v>10</v>
+      </c>
+      <c r="C961" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D961" t="n">
+        <v>0</v>
+      </c>
+      <c r="E961" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F961" t="n">
+        <v>55.68116024772107</v>
+      </c>
+      <c r="G961" t="n">
+        <v>10664.45254955184</v>
+      </c>
+      <c r="H961" t="n">
+        <v>51714087344.47752</v>
+      </c>
+      <c r="I961" t="n">
+        <v>1.360833472997967</v>
+      </c>
+      <c r="J961" t="n">
+        <v>5.327906376241509</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B962" t="n">
+        <v>2</v>
+      </c>
+      <c r="C962" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D962" t="n">
+        <v>0</v>
+      </c>
+      <c r="E962" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F962" t="n">
+        <v>55.70312561536399</v>
+      </c>
+      <c r="G962" t="n">
+        <v>10428.69763523227</v>
+      </c>
+      <c r="H962" t="n">
+        <v>54927250742.97612</v>
+      </c>
+      <c r="I962" t="n">
+        <v>1.338868105355047</v>
+      </c>
+      <c r="J962" t="n">
+        <v>2.114742977742912</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=6</t>
+        </is>
+      </c>
+      <c r="B963" t="n">
+        <v>9</v>
+      </c>
+      <c r="C963" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D963" t="n">
+        <v>0</v>
+      </c>
+      <c r="E963" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F963" t="n">
+        <v>55.68116024772106</v>
+      </c>
+      <c r="G963" t="n">
+        <v>10664.45254955184</v>
+      </c>
+      <c r="H963" t="n">
+        <v>52110794634.80186</v>
+      </c>
+      <c r="I963" t="n">
+        <v>1.360833472997975</v>
+      </c>
+      <c r="J963" t="n">
+        <v>4.931199085917175</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B964" t="n">
+        <v>50</v>
+      </c>
+      <c r="C964" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D964" t="n">
+        <v>0</v>
+      </c>
+      <c r="E964" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F964" t="n">
+        <v>48.57382674468669</v>
+      </c>
+      <c r="G964" t="n">
+        <v>3961.477811054248</v>
+      </c>
+      <c r="H964" t="n">
+        <v>41205670147.79963</v>
+      </c>
+      <c r="I964" t="n">
+        <v>8.468166976032343</v>
+      </c>
+      <c r="J964" t="n">
+        <v>15.8363235729194</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B965" t="n">
+        <v>900</v>
+      </c>
+      <c r="C965" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D965" t="n">
+        <v>0</v>
+      </c>
+      <c r="E965" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F965" t="n">
+        <v>47.75515174145483</v>
+      </c>
+      <c r="G965" t="n">
+        <v>3166.107879544595</v>
+      </c>
+      <c r="H965" t="n">
+        <v>-58243376053.51935</v>
+      </c>
+      <c r="I965" t="n">
+        <v>9.286841979264203</v>
+      </c>
+      <c r="J965" t="n">
+        <v>115.2853697742384</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B966" t="n">
+        <v>5</v>
+      </c>
+      <c r="C966" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D966" t="n">
+        <v>0</v>
+      </c>
+      <c r="E966" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F966" t="n">
+        <v>49.81358268013163</v>
+      </c>
+      <c r="G966" t="n">
+        <v>5287.317985664302</v>
+      </c>
+      <c r="H966" t="n">
+        <v>48830167178.2903</v>
+      </c>
+      <c r="I966" t="n">
+        <v>7.228411040587403</v>
+      </c>
+      <c r="J966" t="n">
+        <v>8.211826542428733</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B967" t="n">
+        <v>150</v>
+      </c>
+      <c r="C967" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D967" t="n">
+        <v>0</v>
+      </c>
+      <c r="E967" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F967" t="n">
+        <v>48.27970944564612</v>
+      </c>
+      <c r="G967" t="n">
+        <v>3670.605609140714</v>
+      </c>
+      <c r="H967" t="n">
+        <v>27798264219.75707</v>
+      </c>
+      <c r="I967" t="n">
+        <v>8.762284275072915</v>
+      </c>
+      <c r="J967" t="n">
+        <v>29.24372950096197</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B968" t="n">
+        <v>175</v>
+      </c>
+      <c r="C968" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D968" t="n">
+        <v>0</v>
+      </c>
+      <c r="E968" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F968" t="n">
+        <v>48.27970944564613</v>
+      </c>
+      <c r="G968" t="n">
+        <v>3670.605609140714</v>
+      </c>
+      <c r="H968" t="n">
+        <v>24384690015.44224</v>
+      </c>
+      <c r="I968" t="n">
+        <v>8.762284275072908</v>
+      </c>
+      <c r="J968" t="n">
+        <v>32.65730370527679</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B969" t="n">
+        <v>3</v>
+      </c>
+      <c r="C969" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D969" t="n">
+        <v>0</v>
+      </c>
+      <c r="E969" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F969" t="n">
+        <v>49.81358268013163</v>
+      </c>
+      <c r="G969" t="n">
+        <v>5287.317985664302</v>
+      </c>
+      <c r="H969" t="n">
+        <v>49223533379.02683</v>
+      </c>
+      <c r="I969" t="n">
+        <v>7.228411040587403</v>
+      </c>
+      <c r="J969" t="n">
+        <v>7.8184603416922</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B970" t="n">
+        <v>200</v>
+      </c>
+      <c r="C970" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D970" t="n">
+        <v>0</v>
+      </c>
+      <c r="E970" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F970" t="n">
+        <v>48.27970944564613</v>
+      </c>
+      <c r="G970" t="n">
+        <v>3670.605609140714</v>
+      </c>
+      <c r="H970" t="n">
+        <v>20971115811.12739</v>
+      </c>
+      <c r="I970" t="n">
+        <v>8.762284275072908</v>
+      </c>
+      <c r="J970" t="n">
+        <v>36.07087790959164</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B971" t="n">
+        <v>125</v>
+      </c>
+      <c r="C971" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D971" t="n">
+        <v>0</v>
+      </c>
+      <c r="E971" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F971" t="n">
+        <v>48.38098611659103</v>
+      </c>
+      <c r="G971" t="n">
+        <v>3732.052542646137</v>
+      </c>
+      <c r="H971" t="n">
+        <v>31027394304.6573</v>
+      </c>
+      <c r="I971" t="n">
+        <v>8.661007604128002</v>
+      </c>
+      <c r="J971" t="n">
+        <v>26.01459941606173</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B972" t="n">
+        <v>7</v>
+      </c>
+      <c r="C972" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D972" t="n">
+        <v>0</v>
+      </c>
+      <c r="E972" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F972" t="n">
+        <v>48.84317516829916</v>
+      </c>
+      <c r="G972" t="n">
+        <v>4258.597772801614</v>
+      </c>
+      <c r="H972" t="n">
+        <v>47734265224.1405</v>
+      </c>
+      <c r="I972" t="n">
+        <v>8.198818552419873</v>
+      </c>
+      <c r="J972" t="n">
+        <v>9.307728496578529</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B973" t="n">
+        <v>8</v>
+      </c>
+      <c r="C973" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D973" t="n">
+        <v>0</v>
+      </c>
+      <c r="E973" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F973" t="n">
+        <v>48.84317516829915</v>
+      </c>
+      <c r="G973" t="n">
+        <v>4258.597772801614</v>
+      </c>
+      <c r="H973" t="n">
+        <v>47575849517.83212</v>
+      </c>
+      <c r="I973" t="n">
+        <v>8.198818552419887</v>
+      </c>
+      <c r="J973" t="n">
+        <v>9.466144202886909</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B974" t="n">
+        <v>500</v>
+      </c>
+      <c r="C974" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D974" t="n">
+        <v>0</v>
+      </c>
+      <c r="E974" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F974" t="n">
+        <v>47.75515174145485</v>
+      </c>
+      <c r="G974" t="n">
+        <v>3166.107879544595</v>
+      </c>
+      <c r="H974" t="n">
+        <v>-11132919255.75303</v>
+      </c>
+      <c r="I974" t="n">
+        <v>9.286841979264182</v>
+      </c>
+      <c r="J974" t="n">
+        <v>68.17491297647206</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B975" t="n">
+        <v>250</v>
+      </c>
+      <c r="C975" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D975" t="n">
+        <v>0</v>
+      </c>
+      <c r="E975" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F975" t="n">
+        <v>48.27970944564613</v>
+      </c>
+      <c r="G975" t="n">
+        <v>3670.605609140714</v>
+      </c>
+      <c r="H975" t="n">
+        <v>14143967402.49771</v>
+      </c>
+      <c r="I975" t="n">
+        <v>8.762284275072908</v>
+      </c>
+      <c r="J975" t="n">
+        <v>42.89802631822132</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B976" t="n">
+        <v>4</v>
+      </c>
+      <c r="C976" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D976" t="n">
+        <v>0</v>
+      </c>
+      <c r="E976" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F976" t="n">
+        <v>49.81358268013165</v>
+      </c>
+      <c r="G976" t="n">
+        <v>5287.317985664302</v>
+      </c>
+      <c r="H976" t="n">
+        <v>49026850278.65858</v>
+      </c>
+      <c r="I976" t="n">
+        <v>7.228411040587382</v>
+      </c>
+      <c r="J976" t="n">
+        <v>8.015143442060456</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B977" t="n">
+        <v>400</v>
+      </c>
+      <c r="C977" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D977" t="n">
+        <v>0</v>
+      </c>
+      <c r="E977" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F977" t="n">
+        <v>48.27970944564611</v>
+      </c>
+      <c r="G977" t="n">
+        <v>3670.605609140714</v>
+      </c>
+      <c r="H977" t="n">
+        <v>-6337477823.391355</v>
+      </c>
+      <c r="I977" t="n">
+        <v>8.762284275072922</v>
+      </c>
+      <c r="J977" t="n">
+        <v>63.37947154411039</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B978" t="n">
+        <v>6</v>
+      </c>
+      <c r="C978" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D978" t="n">
+        <v>0</v>
+      </c>
+      <c r="E978" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F978" t="n">
+        <v>48.84317516829915</v>
+      </c>
+      <c r="G978" t="n">
+        <v>4258.597772801614</v>
+      </c>
+      <c r="H978" t="n">
+        <v>47892680930.44887</v>
+      </c>
+      <c r="I978" t="n">
+        <v>8.198818552419887</v>
+      </c>
+      <c r="J978" t="n">
+        <v>9.149312790270164</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B979" t="n">
+        <v>600</v>
+      </c>
+      <c r="C979" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D979" t="n">
+        <v>0</v>
+      </c>
+      <c r="E979" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F979" t="n">
+        <v>47.75515174145487</v>
+      </c>
+      <c r="G979" t="n">
+        <v>3166.107879544595</v>
+      </c>
+      <c r="H979" t="n">
+        <v>-22910533455.1946</v>
+      </c>
+      <c r="I979" t="n">
+        <v>9.286841979264167</v>
+      </c>
+      <c r="J979" t="n">
+        <v>79.95252717591363</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B980" t="n">
+        <v>75</v>
+      </c>
+      <c r="C980" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D980" t="n">
+        <v>0</v>
+      </c>
+      <c r="E980" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F980" t="n">
+        <v>48.5738267446867</v>
+      </c>
+      <c r="G980" t="n">
+        <v>3961.477811054248</v>
+      </c>
+      <c r="H980" t="n">
+        <v>37521591849.3561</v>
+      </c>
+      <c r="I980" t="n">
+        <v>8.468166976032336</v>
+      </c>
+      <c r="J980" t="n">
+        <v>19.52040187136293</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B981" t="n">
+        <v>700</v>
+      </c>
+      <c r="C981" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D981" t="n">
+        <v>0</v>
+      </c>
+      <c r="E981" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F981" t="n">
+        <v>47.75515174145484</v>
+      </c>
+      <c r="G981" t="n">
+        <v>3166.107879544595</v>
+      </c>
+      <c r="H981" t="n">
+        <v>-34688147654.63619</v>
+      </c>
+      <c r="I981" t="n">
+        <v>9.286841979264196</v>
+      </c>
+      <c r="J981" t="n">
+        <v>91.73014137535523</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B982" t="n">
+        <v>800</v>
+      </c>
+      <c r="C982" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D982" t="n">
+        <v>0</v>
+      </c>
+      <c r="E982" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F982" t="n">
+        <v>47.75515174145484</v>
+      </c>
+      <c r="G982" t="n">
+        <v>3166.107879544595</v>
+      </c>
+      <c r="H982" t="n">
+        <v>-46465761854.07777</v>
+      </c>
+      <c r="I982" t="n">
+        <v>9.286841979264196</v>
+      </c>
+      <c r="J982" t="n">
+        <v>103.5077555747968</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B983" t="n">
+        <v>100</v>
+      </c>
+      <c r="C983" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D983" t="n">
+        <v>0</v>
+      </c>
+      <c r="E983" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F983" t="n">
+        <v>48.38098611659102</v>
+      </c>
+      <c r="G983" t="n">
+        <v>3732.052542646137</v>
+      </c>
+      <c r="H983" t="n">
+        <v>34498112667.04404</v>
+      </c>
+      <c r="I983" t="n">
+        <v>8.661007604128017</v>
+      </c>
+      <c r="J983" t="n">
+        <v>22.54388105367499</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B984" t="n">
+        <v>1</v>
+      </c>
+      <c r="C984" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D984" t="n">
+        <v>0</v>
+      </c>
+      <c r="E984" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F984" t="n">
+        <v>49.81358268013164</v>
+      </c>
+      <c r="G984" t="n">
+        <v>5287.317985664302</v>
+      </c>
+      <c r="H984" t="n">
+        <v>49616899579.76337</v>
+      </c>
+      <c r="I984" t="n">
+        <v>7.228411040587396</v>
+      </c>
+      <c r="J984" t="n">
+        <v>7.425094140955665</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B985" t="n">
+        <v>0</v>
+      </c>
+      <c r="C985" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D985" t="n">
+        <v>0</v>
+      </c>
+      <c r="E985" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F985" t="n">
+        <v>49.81358268013162</v>
+      </c>
+      <c r="G985" t="n">
+        <v>5287.317985664302</v>
+      </c>
+      <c r="H985" t="n">
+        <v>49813582680.13162</v>
+      </c>
+      <c r="I985" t="n">
+        <v>7.228411040587417</v>
+      </c>
+      <c r="J985" t="n">
+        <v>7.22841104058741</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B986" t="n">
+        <v>300</v>
+      </c>
+      <c r="C986" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D986" t="n">
+        <v>0</v>
+      </c>
+      <c r="E986" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F986" t="n">
+        <v>48.27970944564613</v>
+      </c>
+      <c r="G986" t="n">
+        <v>3670.605609140714</v>
+      </c>
+      <c r="H986" t="n">
+        <v>7316818993.868017</v>
+      </c>
+      <c r="I986" t="n">
+        <v>8.762284275072908</v>
+      </c>
+      <c r="J986" t="n">
+        <v>49.72517472685102</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B987" t="n">
+        <v>10</v>
+      </c>
+      <c r="C987" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D987" t="n">
+        <v>0</v>
+      </c>
+      <c r="E987" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F987" t="n">
+        <v>48.84317516829914</v>
+      </c>
+      <c r="G987" t="n">
+        <v>4258.597772801614</v>
+      </c>
+      <c r="H987" t="n">
+        <v>47259018105.21534</v>
+      </c>
+      <c r="I987" t="n">
+        <v>8.198818552419894</v>
+      </c>
+      <c r="J987" t="n">
+        <v>9.782975615503693</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B988" t="n">
+        <v>2</v>
+      </c>
+      <c r="C988" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D988" t="n">
+        <v>0</v>
+      </c>
+      <c r="E988" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F988" t="n">
+        <v>49.81358268013165</v>
+      </c>
+      <c r="G988" t="n">
+        <v>5287.317985664302</v>
+      </c>
+      <c r="H988" t="n">
+        <v>49420216479.39512</v>
+      </c>
+      <c r="I988" t="n">
+        <v>7.228411040587382</v>
+      </c>
+      <c r="J988" t="n">
+        <v>7.621777241323914</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=NON_TARGETED_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B989" t="n">
+        <v>9</v>
+      </c>
+      <c r="C989" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D989" t="n">
+        <v>0</v>
+      </c>
+      <c r="E989" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F989" t="n">
+        <v>48.84317516829915</v>
+      </c>
+      <c r="G989" t="n">
+        <v>4258.597772801614</v>
+      </c>
+      <c r="H989" t="n">
+        <v>47417433811.52374</v>
+      </c>
+      <c r="I989" t="n">
+        <v>8.198818552419887</v>
+      </c>
+      <c r="J989" t="n">
+        <v>9.624559909195289</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B990" t="n">
+        <v>50</v>
+      </c>
+      <c r="C990" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D990" t="n">
+        <v>0</v>
+      </c>
+      <c r="E990" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F990" t="n">
+        <v>55.6525743976241</v>
+      </c>
+      <c r="G990" t="n">
+        <v>10507.84294733625</v>
+      </c>
+      <c r="H990" t="n">
+        <v>36108496145.96162</v>
+      </c>
+      <c r="I990" t="n">
+        <v>1.389419323094934</v>
+      </c>
+      <c r="J990" t="n">
+        <v>20.93349757475741</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B991" t="n">
+        <v>900</v>
+      </c>
+      <c r="C991" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D991" t="n">
+        <v>0</v>
+      </c>
+      <c r="E991" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F991" t="n">
+        <v>55.62289388545597</v>
+      </c>
+      <c r="G991" t="n">
+        <v>9676.319752114669</v>
+      </c>
+      <c r="H991" t="n">
+        <v>-268331843988.1996</v>
+      </c>
+      <c r="I991" t="n">
+        <v>1.419099835263061</v>
+      </c>
+      <c r="J991" t="n">
+        <v>325.3738377089186</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B992" t="n">
+        <v>5</v>
+      </c>
+      <c r="C992" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D992" t="n">
+        <v>0</v>
+      </c>
+      <c r="E992" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F992" t="n">
+        <v>55.63295281526188</v>
+      </c>
+      <c r="G992" t="n">
+        <v>10717.67743689406</v>
+      </c>
+      <c r="H992" t="n">
+        <v>53639516792.73515</v>
+      </c>
+      <c r="I992" t="n">
+        <v>1.409040905457154</v>
+      </c>
+      <c r="J992" t="n">
+        <v>3.402476927983879</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B993" t="n">
+        <v>150</v>
+      </c>
+      <c r="C993" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D993" t="n">
+        <v>0</v>
+      </c>
+      <c r="E993" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F993" t="n">
+        <v>55.6228938854561</v>
+      </c>
+      <c r="G993" t="n">
+        <v>9676.319752114669</v>
+      </c>
+      <c r="H993" t="n">
+        <v>1630437573.180185</v>
+      </c>
+      <c r="I993" t="n">
+        <v>1.419099835262934</v>
+      </c>
+      <c r="J993" t="n">
+        <v>55.41155614753885</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B994" t="n">
+        <v>175</v>
+      </c>
+      <c r="C994" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D994" t="n">
+        <v>0</v>
+      </c>
+      <c r="E994" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F994" t="n">
+        <v>55.6228938854561</v>
+      </c>
+      <c r="G994" t="n">
+        <v>9676.319752114669</v>
+      </c>
+      <c r="H994" t="n">
+        <v>-7368305145.532472</v>
+      </c>
+      <c r="I994" t="n">
+        <v>1.419099835262934</v>
+      </c>
+      <c r="J994" t="n">
+        <v>64.41029886625151</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B995" t="n">
+        <v>3</v>
+      </c>
+      <c r="C995" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D995" t="n">
+        <v>0</v>
+      </c>
+      <c r="E995" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F995" t="n">
+        <v>55.63295281526191</v>
+      </c>
+      <c r="G995" t="n">
+        <v>10717.67743689406</v>
+      </c>
+      <c r="H995" t="n">
+        <v>54436891201.74587</v>
+      </c>
+      <c r="I995" t="n">
+        <v>1.409040905457125</v>
+      </c>
+      <c r="J995" t="n">
+        <v>2.60510251897316</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B996" t="n">
+        <v>200</v>
+      </c>
+      <c r="C996" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D996" t="n">
+        <v>0</v>
+      </c>
+      <c r="E996" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F996" t="n">
+        <v>55.6228938854561</v>
+      </c>
+      <c r="G996" t="n">
+        <v>9676.319752114669</v>
+      </c>
+      <c r="H996" t="n">
+        <v>-16367047864.24512</v>
+      </c>
+      <c r="I996" t="n">
+        <v>1.419099835262934</v>
+      </c>
+      <c r="J996" t="n">
+        <v>73.40904158496416</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B997" t="n">
+        <v>125</v>
+      </c>
+      <c r="C997" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D997" t="n">
+        <v>0</v>
+      </c>
+      <c r="E997" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F997" t="n">
+        <v>55.65533748010812</v>
+      </c>
+      <c r="G997" t="n">
+        <v>10518.52407633485</v>
+      </c>
+      <c r="H997" t="n">
+        <v>6745475896.195346</v>
+      </c>
+      <c r="I997" t="n">
+        <v>1.386656240610911</v>
+      </c>
+      <c r="J997" t="n">
+        <v>50.29651782452369</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B998" t="n">
+        <v>7</v>
+      </c>
+      <c r="C998" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D998" t="n">
+        <v>0</v>
+      </c>
+      <c r="E998" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F998" t="n">
+        <v>55.65257439762412</v>
+      </c>
+      <c r="G998" t="n">
+        <v>10507.84294733625</v>
+      </c>
+      <c r="H998" t="n">
+        <v>52916403442.39137</v>
+      </c>
+      <c r="I998" t="n">
+        <v>1.389419323094913</v>
+      </c>
+      <c r="J998" t="n">
+        <v>4.125590278327659</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B999" t="n">
+        <v>8</v>
+      </c>
+      <c r="C999" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D999" t="n">
+        <v>0</v>
+      </c>
+      <c r="E999" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F999" t="n">
+        <v>55.65257439762409</v>
+      </c>
+      <c r="G999" t="n">
+        <v>10507.84294733625</v>
+      </c>
+      <c r="H999" t="n">
+        <v>52525521877.35809</v>
+      </c>
+      <c r="I999" t="n">
+        <v>1.389419323094941</v>
+      </c>
+      <c r="J999" t="n">
+        <v>4.516471843360939</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1000" t="n">
+        <v>500</v>
+      </c>
+      <c r="C1000" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1000" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1000" t="n">
+        <v>55.62289388545607</v>
+      </c>
+      <c r="G1000" t="n">
+        <v>9676.319752114669</v>
+      </c>
+      <c r="H1000" t="n">
+        <v>-124351960488.797</v>
+      </c>
+      <c r="I1000" t="n">
+        <v>1.419099835262962</v>
+      </c>
+      <c r="J1000" t="n">
+        <v>181.393954209516</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1001" t="n">
+        <v>250</v>
+      </c>
+      <c r="C1001" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1001" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1001" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1001" t="n">
+        <v>55.6228938854561</v>
+      </c>
+      <c r="G1001" t="n">
+        <v>9676.319752114669</v>
+      </c>
+      <c r="H1001" t="n">
+        <v>-34364533301.67043</v>
+      </c>
+      <c r="I1001" t="n">
+        <v>1.419099835262934</v>
+      </c>
+      <c r="J1001" t="n">
+        <v>91.40652702238947</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1002" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1002" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1002" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1002" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1002" t="n">
+        <v>55.63295281526192</v>
+      </c>
+      <c r="G1002" t="n">
+        <v>10717.67743689406</v>
+      </c>
+      <c r="H1002" t="n">
+        <v>54038203997.24055</v>
+      </c>
+      <c r="I1002" t="n">
+        <v>1.409040905457111</v>
+      </c>
+      <c r="J1002" t="n">
+        <v>3.003789723478485</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1003" t="n">
+        <v>400</v>
+      </c>
+      <c r="C1003" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1003" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1003" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1003" t="n">
+        <v>55.62289388545609</v>
+      </c>
+      <c r="G1003" t="n">
+        <v>9676.319752114669</v>
+      </c>
+      <c r="H1003" t="n">
+        <v>-88356989613.94635</v>
+      </c>
+      <c r="I1003" t="n">
+        <v>1.419099835262948</v>
+      </c>
+      <c r="J1003" t="n">
+        <v>145.3989833346654</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1004" t="n">
+        <v>6</v>
+      </c>
+      <c r="C1004" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1004" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1004" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1004" t="n">
+        <v>55.6525743976241</v>
+      </c>
+      <c r="G1004" t="n">
+        <v>10507.84294733625</v>
+      </c>
+      <c r="H1004" t="n">
+        <v>53307285007.42461</v>
+      </c>
+      <c r="I1004" t="n">
+        <v>1.389419323094934</v>
+      </c>
+      <c r="J1004" t="n">
+        <v>3.734708713294426</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1005" t="n">
+        <v>600</v>
+      </c>
+      <c r="C1005" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1005" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1005" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1005" t="n">
+        <v>55.62289388545609</v>
+      </c>
+      <c r="G1005" t="n">
+        <v>9676.319752114669</v>
+      </c>
+      <c r="H1005" t="n">
+        <v>-160346931363.6476</v>
+      </c>
+      <c r="I1005" t="n">
+        <v>1.419099835262948</v>
+      </c>
+      <c r="J1005" t="n">
+        <v>217.3889250843666</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1006" t="n">
+        <v>75</v>
+      </c>
+      <c r="C1006" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1006" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1006" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1006" t="n">
+        <v>55.6525743976241</v>
+      </c>
+      <c r="G1006" t="n">
+        <v>10507.84294733625</v>
+      </c>
+      <c r="H1006" t="n">
+        <v>26336457020.13039</v>
+      </c>
+      <c r="I1006" t="n">
+        <v>1.389419323094934</v>
+      </c>
+      <c r="J1006" t="n">
+        <v>30.70553670058864</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1007" t="n">
+        <v>700</v>
+      </c>
+      <c r="C1007" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1007" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1007" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>55.62289388545602</v>
+      </c>
+      <c r="G1007" t="n">
+        <v>9676.319752114669</v>
+      </c>
+      <c r="H1007" t="n">
+        <v>-196341902238.4983</v>
+      </c>
+      <c r="I1007" t="n">
+        <v>1.419099835263012</v>
+      </c>
+      <c r="J1007" t="n">
+        <v>253.3838959592173</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1008" t="n">
+        <v>800</v>
+      </c>
+      <c r="C1008" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1008" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1008" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1008" t="n">
+        <v>55.62289388545602</v>
+      </c>
+      <c r="G1008" t="n">
+        <v>9676.319752114669</v>
+      </c>
+      <c r="H1008" t="n">
+        <v>-232336873113.3488</v>
+      </c>
+      <c r="I1008" t="n">
+        <v>1.419099835263012</v>
+      </c>
+      <c r="J1008" t="n">
+        <v>289.3788668340678</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1009" t="n">
+        <v>100</v>
+      </c>
+      <c r="C1009" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1009" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1009" t="n">
+        <v>55.65533748010815</v>
+      </c>
+      <c r="G1009" t="n">
+        <v>10518.52407633485</v>
+      </c>
+      <c r="H1009" t="n">
+        <v>16527448212.97793</v>
+      </c>
+      <c r="I1009" t="n">
+        <v>1.386656240610883</v>
+      </c>
+      <c r="J1009" t="n">
+        <v>40.5145455077411</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1010" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1010" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1010" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1010" t="n">
+        <v>55.63295281526191</v>
+      </c>
+      <c r="G1010" t="n">
+        <v>10717.67743689406</v>
+      </c>
+      <c r="H1010" t="n">
+        <v>55234265610.75656</v>
+      </c>
+      <c r="I1010" t="n">
+        <v>1.409040905457125</v>
+      </c>
+      <c r="J1010" t="n">
+        <v>1.807728109962471</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1011" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1011" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1011" t="n">
+        <v>55.6329528152619</v>
+      </c>
+      <c r="G1011" t="n">
+        <v>10717.67743689406</v>
+      </c>
+      <c r="H1011" t="n">
+        <v>55632952815.2619</v>
+      </c>
+      <c r="I1011" t="n">
+        <v>1.409040905457132</v>
+      </c>
+      <c r="J1011" t="n">
+        <v>1.40904090545713</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1012" t="n">
+        <v>300</v>
+      </c>
+      <c r="C1012" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1012" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1012" t="n">
+        <v>55.62289388545609</v>
+      </c>
+      <c r="G1012" t="n">
+        <v>9676.319752114669</v>
+      </c>
+      <c r="H1012" t="n">
+        <v>-52362018739.09575</v>
+      </c>
+      <c r="I1012" t="n">
+        <v>1.419099835262948</v>
+      </c>
+      <c r="J1012" t="n">
+        <v>109.4040124598148</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1013" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1013" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1013" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1013" t="n">
+        <v>55.65257439762411</v>
+      </c>
+      <c r="G1013" t="n">
+        <v>10507.84294733625</v>
+      </c>
+      <c r="H1013" t="n">
+        <v>51743758747.29161</v>
+      </c>
+      <c r="I1013" t="n">
+        <v>1.389419323094927</v>
+      </c>
+      <c r="J1013" t="n">
+        <v>5.298234973427421</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1014" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1014" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1014" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1014" t="n">
+        <v>55.63295281526191</v>
+      </c>
+      <c r="G1014" t="n">
+        <v>10717.67743689406</v>
+      </c>
+      <c r="H1014" t="n">
+        <v>54835578406.25122</v>
+      </c>
+      <c r="I1014" t="n">
+        <v>1.409040905457125</v>
+      </c>
+      <c r="J1014" t="n">
+        <v>2.206415314467812</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=ALL_2_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1015" t="n">
+        <v>9</v>
+      </c>
+      <c r="C1015" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1015" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1015" t="n">
+        <v>55.65257439762411</v>
+      </c>
+      <c r="G1015" t="n">
+        <v>10507.84294733625</v>
+      </c>
+      <c r="H1015" t="n">
+        <v>52134640312.32487</v>
+      </c>
+      <c r="I1015" t="n">
+        <v>1.389419323094927</v>
+      </c>
+      <c r="J1015" t="n">
+        <v>4.907353408394165</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1016" t="n">
+        <v>50</v>
+      </c>
+      <c r="C1016" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1016" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1016" t="n">
+        <v>55.68236340001565</v>
+      </c>
+      <c r="G1016" t="n">
+        <v>10651.59712672821</v>
+      </c>
+      <c r="H1016" t="n">
+        <v>35870909346.76184</v>
+      </c>
+      <c r="I1016" t="n">
+        <v>1.359630320703381</v>
+      </c>
+      <c r="J1016" t="n">
+        <v>21.17108437395719</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1017" t="n">
+        <v>900</v>
+      </c>
+      <c r="C1017" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1017" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1017" t="n">
+        <v>55.68236340001556</v>
+      </c>
+      <c r="G1017" t="n">
+        <v>10651.59712672821</v>
+      </c>
+      <c r="H1017" t="n">
+        <v>-300923809558.5532</v>
+      </c>
+      <c r="I1017" t="n">
+        <v>1.359630320703474</v>
+      </c>
+      <c r="J1017" t="n">
+        <v>357.9658032792723</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1018" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1018" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1018" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1018" t="n">
+        <v>55.70312986240994</v>
+      </c>
+      <c r="G1018" t="n">
+        <v>10428.62225227714</v>
+      </c>
+      <c r="H1018" t="n">
+        <v>53763456702.30431</v>
+      </c>
+      <c r="I1018" t="n">
+        <v>1.338863858309097</v>
+      </c>
+      <c r="J1018" t="n">
+        <v>3.278537018414719</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1019" t="n">
+        <v>150</v>
+      </c>
+      <c r="C1019" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1019" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1019" t="n">
+        <v>55.68236340001566</v>
+      </c>
+      <c r="G1019" t="n">
+        <v>10651.59712672821</v>
+      </c>
+      <c r="H1019" t="n">
+        <v>-3751998759.745798</v>
+      </c>
+      <c r="I1019" t="n">
+        <v>1.359630320703374</v>
+      </c>
+      <c r="J1019" t="n">
+        <v>60.79399248046483</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1020" t="n">
+        <v>175</v>
+      </c>
+      <c r="C1020" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1020" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1020" t="n">
+        <v>55.68236340001565</v>
+      </c>
+      <c r="G1020" t="n">
+        <v>10651.59712672821</v>
+      </c>
+      <c r="H1020" t="n">
+        <v>-13657725786.37272</v>
+      </c>
+      <c r="I1020" t="n">
+        <v>1.359630320703381</v>
+      </c>
+      <c r="J1020" t="n">
+        <v>70.69971950709176</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1021" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1021" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1021" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1021" t="n">
+        <v>55.70312986240993</v>
+      </c>
+      <c r="G1021" t="n">
+        <v>10428.62225227714</v>
+      </c>
+      <c r="H1021" t="n">
+        <v>54539325966.34655</v>
+      </c>
+      <c r="I1021" t="n">
+        <v>1.338863858309104</v>
+      </c>
+      <c r="J1021" t="n">
+        <v>2.502667754372482</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1022" t="n">
+        <v>200</v>
+      </c>
+      <c r="C1022" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1022" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1022" t="n">
+        <v>55.68236340001566</v>
+      </c>
+      <c r="G1022" t="n">
+        <v>10651.59712672821</v>
+      </c>
+      <c r="H1022" t="n">
+        <v>-23563452812.99961</v>
+      </c>
+      <c r="I1022" t="n">
+        <v>1.359630320703374</v>
+      </c>
+      <c r="J1022" t="n">
+        <v>80.60544653371865</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1023" t="n">
+        <v>125</v>
+      </c>
+      <c r="C1023" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1023" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1023" t="n">
+        <v>55.68236340001567</v>
+      </c>
+      <c r="G1023" t="n">
+        <v>10651.59712672821</v>
+      </c>
+      <c r="H1023" t="n">
+        <v>6153728266.881117</v>
+      </c>
+      <c r="I1023" t="n">
+        <v>1.359630320703367</v>
+      </c>
+      <c r="J1023" t="n">
+        <v>50.88826545383791</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1024" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1024" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1024" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1024" t="n">
+        <v>55.68236340001566</v>
+      </c>
+      <c r="G1024" t="n">
+        <v>10651.59712672821</v>
+      </c>
+      <c r="H1024" t="n">
+        <v>52908759832.56013</v>
+      </c>
+      <c r="I1024" t="n">
+        <v>1.359630320703374</v>
+      </c>
+      <c r="J1024" t="n">
+        <v>4.133233888158905</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1025" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1025" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1025" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1025" t="n">
+        <v>55.68236340001567</v>
+      </c>
+      <c r="G1025" t="n">
+        <v>10651.59712672821</v>
+      </c>
+      <c r="H1025" t="n">
+        <v>52512530751.49506</v>
+      </c>
+      <c r="I1025" t="n">
+        <v>1.359630320703367</v>
+      </c>
+      <c r="J1025" t="n">
+        <v>4.529462969223968</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1026" t="n">
+        <v>500</v>
+      </c>
+      <c r="C1026" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1026" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1026" t="n">
+        <v>55.68236340001569</v>
+      </c>
+      <c r="G1026" t="n">
+        <v>10651.59712672821</v>
+      </c>
+      <c r="H1026" t="n">
+        <v>-142432177132.5225</v>
+      </c>
+      <c r="I1026" t="n">
+        <v>1.359630320703346</v>
+      </c>
+      <c r="J1026" t="n">
+        <v>199.4741708532415</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1027" t="n">
+        <v>250</v>
+      </c>
+      <c r="C1027" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1027" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1027" t="n">
+        <v>55.68236340001566</v>
+      </c>
+      <c r="G1027" t="n">
+        <v>10651.59712672821</v>
+      </c>
+      <c r="H1027" t="n">
+        <v>-43374906866.25344</v>
+      </c>
+      <c r="I1027" t="n">
+        <v>1.359630320703374</v>
+      </c>
+      <c r="J1027" t="n">
+        <v>100.4169005869725</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1028" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1028" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1028" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1028" t="n">
+        <v>55.70312986240992</v>
+      </c>
+      <c r="G1028" t="n">
+        <v>10428.62225227714</v>
+      </c>
+      <c r="H1028" t="n">
+        <v>54151391334.32542</v>
+      </c>
+      <c r="I1028" t="n">
+        <v>1.338863858309118</v>
+      </c>
+      <c r="J1028" t="n">
+        <v>2.890602386393616</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1029" t="n">
+        <v>400</v>
+      </c>
+      <c r="C1029" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1029" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1029" t="n">
+        <v>55.68236340001561</v>
+      </c>
+      <c r="G1029" t="n">
+        <v>10651.59712672821</v>
+      </c>
+      <c r="H1029" t="n">
+        <v>-102809269026.0149</v>
+      </c>
+      <c r="I1029" t="n">
+        <v>1.359630320703424</v>
+      </c>
+      <c r="J1029" t="n">
+        <v>159.8512627467339</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1030" t="n">
+        <v>6</v>
+      </c>
+      <c r="C1030" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1030" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1030" t="n">
+        <v>55.68236340001562</v>
+      </c>
+      <c r="G1030" t="n">
+        <v>10651.59712672821</v>
+      </c>
+      <c r="H1030" t="n">
+        <v>53304988913.62517</v>
+      </c>
+      <c r="I1030" t="n">
+        <v>1.359630320703417</v>
+      </c>
+      <c r="J1030" t="n">
+        <v>3.737004807093864</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1031" t="n">
+        <v>600</v>
+      </c>
+      <c r="C1031" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1031" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1031" t="n">
+        <v>55.68236340001572</v>
+      </c>
+      <c r="G1031" t="n">
+        <v>10651.59712672821</v>
+      </c>
+      <c r="H1031" t="n">
+        <v>-182055085239.0301</v>
+      </c>
+      <c r="I1031" t="n">
+        <v>1.359630320703317</v>
+      </c>
+      <c r="J1031" t="n">
+        <v>239.0970789597491</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1032" t="n">
+        <v>75</v>
+      </c>
+      <c r="C1032" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1032" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1032" t="n">
+        <v>55.68236340001565</v>
+      </c>
+      <c r="G1032" t="n">
+        <v>10651.59712672821</v>
+      </c>
+      <c r="H1032" t="n">
+        <v>25965182320.13493</v>
+      </c>
+      <c r="I1032" t="n">
+        <v>1.359630320703381</v>
+      </c>
+      <c r="J1032" t="n">
+        <v>31.0768114005841</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1033" t="n">
+        <v>700</v>
+      </c>
+      <c r="C1033" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1033" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1033" t="n">
+        <v>55.68236340001562</v>
+      </c>
+      <c r="G1033" t="n">
+        <v>10651.59712672821</v>
+      </c>
+      <c r="H1033" t="n">
+        <v>-221677993345.5378</v>
+      </c>
+      <c r="I1033" t="n">
+        <v>1.359630320703417</v>
+      </c>
+      <c r="J1033" t="n">
+        <v>278.7199870662569</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1034" t="n">
+        <v>800</v>
+      </c>
+      <c r="C1034" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1034" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1034" t="n">
+        <v>55.68236340001562</v>
+      </c>
+      <c r="G1034" t="n">
+        <v>10651.59712672821</v>
+      </c>
+      <c r="H1034" t="n">
+        <v>-261300901452.0455</v>
+      </c>
+      <c r="I1034" t="n">
+        <v>1.359630320703417</v>
+      </c>
+      <c r="J1034" t="n">
+        <v>318.3428951727645</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1035" t="n">
+        <v>100</v>
+      </c>
+      <c r="C1035" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1035" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1035" t="n">
+        <v>55.68236340001565</v>
+      </c>
+      <c r="G1035" t="n">
+        <v>10651.59712672821</v>
+      </c>
+      <c r="H1035" t="n">
+        <v>16059455293.50801</v>
+      </c>
+      <c r="I1035" t="n">
+        <v>1.359630320703381</v>
+      </c>
+      <c r="J1035" t="n">
+        <v>40.98253842721102</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1036" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1036" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1036" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1036" t="n">
+        <v>55.70312986240993</v>
+      </c>
+      <c r="G1036" t="n">
+        <v>10428.62225227714</v>
+      </c>
+      <c r="H1036" t="n">
+        <v>55315195230.3888</v>
+      </c>
+      <c r="I1036" t="n">
+        <v>1.338863858309104</v>
+      </c>
+      <c r="J1036" t="n">
+        <v>1.726798490330231</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1037" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1037" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1037" t="n">
+        <v>55.7031298624099</v>
+      </c>
+      <c r="G1037" t="n">
+        <v>10428.62225227714</v>
+      </c>
+      <c r="H1037" t="n">
+        <v>55703129862.4099</v>
+      </c>
+      <c r="I1037" t="n">
+        <v>1.338863858309132</v>
+      </c>
+      <c r="J1037" t="n">
+        <v>1.338863858309135</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1038" t="n">
+        <v>300</v>
+      </c>
+      <c r="C1038" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1038" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1038" t="n">
+        <v>55.68236340001567</v>
+      </c>
+      <c r="G1038" t="n">
+        <v>10651.59712672821</v>
+      </c>
+      <c r="H1038" t="n">
+        <v>-63186360919.50725</v>
+      </c>
+      <c r="I1038" t="n">
+        <v>1.359630320703367</v>
+      </c>
+      <c r="J1038" t="n">
+        <v>120.2283546402263</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1039" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1039" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1039" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1039" t="n">
+        <v>55.68236340001565</v>
+      </c>
+      <c r="G1039" t="n">
+        <v>10651.59712672821</v>
+      </c>
+      <c r="H1039" t="n">
+        <v>51720072589.36489</v>
+      </c>
+      <c r="I1039" t="n">
+        <v>1.359630320703381</v>
+      </c>
+      <c r="J1039" t="n">
+        <v>5.321921131354141</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1040" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1040" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1040" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1040" t="n">
+        <v>55.70312986240994</v>
+      </c>
+      <c r="G1040" t="n">
+        <v>10428.62225227714</v>
+      </c>
+      <c r="H1040" t="n">
+        <v>54927260598.36769</v>
+      </c>
+      <c r="I1040" t="n">
+        <v>1.338863858309097</v>
+      </c>
+      <c r="J1040" t="n">
+        <v>2.114733122351341</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>tree_heuristic_featureSet=TARGETED_ECON_CONT_RATIO_treeDepth=7</t>
+        </is>
+      </c>
+      <c r="B1041" t="n">
+        <v>9</v>
+      </c>
+      <c r="C1041" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1041" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1041" t="n">
+        <v>55.68236340001565</v>
+      </c>
+      <c r="G1041" t="n">
+        <v>10651.59712672821</v>
+      </c>
+      <c r="H1041" t="n">
+        <v>52116301670.42997</v>
+      </c>
+      <c r="I1041" t="n">
+        <v>1.359630320703381</v>
+      </c>
+      <c r="J1041" t="n">
+        <v>4.925692050289062</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
